--- a/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.158</v>
+        <v>-0.0183</v>
       </c>
       <c r="G2">
-        <v>-0.2980825565912117</v>
+        <v>-0.05051857197732484</v>
       </c>
       <c r="H2">
-        <v>-0.2980825565912117</v>
+        <v>-0.05051857197732484</v>
       </c>
       <c r="I2">
-        <v>-0.4588548601864181</v>
+        <v>-0.02511960330116752</v>
       </c>
       <c r="J2">
-        <v>-0.4588548601864181</v>
+        <v>-0.02511960330116752</v>
       </c>
       <c r="K2">
-        <v>-2854.9</v>
+        <v>-3954.4</v>
       </c>
       <c r="L2">
-        <v>-0.7602929427430093</v>
+        <v>-0.4603010161915516</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>930.2</v>
+        <v>897.2</v>
       </c>
       <c r="V2">
-        <v>4.014674147604661</v>
+        <v>0.2285918112563377</v>
       </c>
       <c r="W2">
-        <v>1.939206629534031</v>
+        <v>0.917174997100777</v>
       </c>
       <c r="X2">
-        <v>1.486322847144444</v>
+        <v>0.2199285520742187</v>
       </c>
       <c r="Y2">
-        <v>0.452883782389587</v>
+        <v>0.6972464450265583</v>
       </c>
       <c r="Z2">
-        <v>0.489697443922796</v>
+        <v>1.715401050298516</v>
       </c>
       <c r="AA2">
-        <v>-0.2247000521648409</v>
+        <v>-0.04309019388590484</v>
       </c>
       <c r="AB2">
-        <v>0.06327631999496346</v>
+        <v>0.1221535653296326</v>
       </c>
       <c r="AC2">
-        <v>-0.2879763721598044</v>
+        <v>-0.1652437592155375</v>
       </c>
       <c r="AD2">
-        <v>10249.8</v>
+        <v>11818.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10249.8</v>
+        <v>11818.8</v>
       </c>
       <c r="AG2">
-        <v>9319.599999999999</v>
+        <v>10921.6</v>
       </c>
       <c r="AH2">
-        <v>0.9778943853456089</v>
+        <v>0.7507002801120448</v>
       </c>
       <c r="AI2">
-        <v>1.730099250557019</v>
+        <v>3.324182933003319</v>
       </c>
       <c r="AJ2">
-        <v>0.9757415220964685</v>
+        <v>0.7356346613679992</v>
       </c>
       <c r="AK2">
-        <v>1.866084658203516</v>
+        <v>4.108644947708977</v>
       </c>
       <c r="AL2">
-        <v>721.5</v>
+        <v>884.4</v>
       </c>
       <c r="AM2">
-        <v>698.4</v>
+        <v>843.6</v>
       </c>
       <c r="AN2">
-        <v>-9.037827352085355</v>
+        <v>23.50129250347982</v>
       </c>
       <c r="AO2">
-        <v>-2.388080388080388</v>
+        <v>-0.24400723654455</v>
       </c>
       <c r="AP2">
-        <v>-8.217617494048143</v>
+        <v>21.71724000795387</v>
       </c>
       <c r="AQ2">
-        <v>-2.467067583046965</v>
+        <v>-0.2558084400189664</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.158</v>
+        <v>-0.0183</v>
       </c>
       <c r="G3">
-        <v>-0.2980825565912117</v>
+        <v>-0.05051857197732484</v>
       </c>
       <c r="H3">
-        <v>-0.2980825565912117</v>
+        <v>-0.05051857197732484</v>
       </c>
       <c r="I3">
-        <v>-0.4588548601864181</v>
+        <v>-0.02511960330116752</v>
       </c>
       <c r="J3">
-        <v>-0.4588548601864181</v>
+        <v>-0.02511960330116752</v>
       </c>
       <c r="K3">
-        <v>-2854.9</v>
+        <v>-3954.4</v>
       </c>
       <c r="L3">
-        <v>-0.7602929427430093</v>
+        <v>-0.4603010161915516</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>930.2</v>
+        <v>897.2</v>
       </c>
       <c r="V3">
-        <v>4.014674147604661</v>
+        <v>0.2285918112563377</v>
       </c>
       <c r="W3">
-        <v>1.939206629534031</v>
+        <v>0.917174997100777</v>
       </c>
       <c r="X3">
-        <v>1.486322847144444</v>
+        <v>0.2199285520742187</v>
       </c>
       <c r="Y3">
-        <v>0.452883782389587</v>
+        <v>0.6972464450265583</v>
       </c>
       <c r="Z3">
-        <v>0.489697443922796</v>
+        <v>1.715401050298516</v>
       </c>
       <c r="AA3">
-        <v>-0.2247000521648409</v>
+        <v>-0.04309019388590484</v>
       </c>
       <c r="AB3">
-        <v>0.06327631999496346</v>
+        <v>0.1221535653296326</v>
       </c>
       <c r="AC3">
-        <v>-0.2879763721598044</v>
+        <v>-0.1652437592155375</v>
       </c>
       <c r="AD3">
-        <v>10249.8</v>
+        <v>11818.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10249.8</v>
+        <v>11818.8</v>
       </c>
       <c r="AG3">
-        <v>9319.599999999999</v>
+        <v>10921.6</v>
       </c>
       <c r="AH3">
-        <v>0.9778943853456089</v>
+        <v>0.7507002801120448</v>
       </c>
       <c r="AI3">
-        <v>1.730099250557019</v>
+        <v>3.324182933003319</v>
       </c>
       <c r="AJ3">
-        <v>0.9757415220964685</v>
+        <v>0.7356346613679992</v>
       </c>
       <c r="AK3">
-        <v>1.866084658203516</v>
+        <v>4.108644947708977</v>
       </c>
       <c r="AL3">
-        <v>721.5</v>
+        <v>884.4</v>
       </c>
       <c r="AM3">
-        <v>698.4</v>
+        <v>843.6</v>
       </c>
       <c r="AN3">
-        <v>-9.037827352085355</v>
+        <v>23.50129250347982</v>
       </c>
       <c r="AO3">
-        <v>-2.388080388080388</v>
+        <v>-0.24400723654455</v>
       </c>
       <c r="AP3">
-        <v>-8.217617494048143</v>
+        <v>21.71724000795387</v>
       </c>
       <c r="AQ3">
-        <v>-2.467067583046965</v>
+        <v>-0.2558084400189664</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="snse_ltm" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0183</v>
+        <v>0.0246</v>
       </c>
       <c r="G2">
-        <v>-0.05051857197732484</v>
+        <v>0.05171175699693015</v>
       </c>
       <c r="H2">
-        <v>-0.05051857197732484</v>
+        <v>0.05171175699693015</v>
       </c>
       <c r="I2">
-        <v>-0.02511960330116752</v>
+        <v>0.08552501660592786</v>
       </c>
       <c r="J2">
-        <v>-0.02511960330116752</v>
+        <v>0.08307417658677312</v>
       </c>
       <c r="K2">
-        <v>-3954.4</v>
+        <v>3037.3</v>
       </c>
       <c r="L2">
-        <v>-0.4603010161915516</v>
+        <v>0.2726334308744592</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>897.2</v>
+        <v>1629.5</v>
       </c>
       <c r="V2">
-        <v>0.2285918112563377</v>
+        <v>0.2474074973809271</v>
       </c>
       <c r="W2">
-        <v>0.917174997100777</v>
+        <v>-0.3681575757575758</v>
       </c>
       <c r="X2">
-        <v>0.2199285520742187</v>
+        <v>0.1204808429757944</v>
       </c>
       <c r="Y2">
-        <v>0.6972464450265583</v>
+        <v>-0.4886384187333702</v>
       </c>
       <c r="Z2">
-        <v>1.715401050298516</v>
+        <v>4.170010480610871</v>
       </c>
       <c r="AA2">
-        <v>-0.04309019388590484</v>
+        <v>0.3464201870349621</v>
       </c>
       <c r="AB2">
-        <v>0.1221535653296326</v>
+        <v>0.09072998511530184</v>
       </c>
       <c r="AC2">
-        <v>-0.1652437592155375</v>
+        <v>0.2556902019196603</v>
       </c>
       <c r="AD2">
-        <v>11818.8</v>
+        <v>6675.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11818.8</v>
+        <v>6675.1</v>
       </c>
       <c r="AG2">
-        <v>10921.6</v>
+        <v>5045.6</v>
       </c>
       <c r="AH2">
-        <v>0.7507002801120448</v>
+        <v>0.5033480627987995</v>
       </c>
       <c r="AI2">
-        <v>3.324182933003319</v>
+        <v>0.9395065377415586</v>
       </c>
       <c r="AJ2">
-        <v>0.7356346613679992</v>
+        <v>0.4337726424745742</v>
       </c>
       <c r="AK2">
-        <v>4.108644947708977</v>
+        <v>0.921503451802608</v>
       </c>
       <c r="AL2">
-        <v>884.4</v>
+        <v>730.2</v>
       </c>
       <c r="AM2">
-        <v>843.6</v>
+        <v>619</v>
       </c>
       <c r="AN2">
-        <v>23.50129250347982</v>
+        <v>3.854874104874105</v>
       </c>
       <c r="AO2">
-        <v>-0.24400723654455</v>
+        <v>1.304847986852917</v>
       </c>
       <c r="AP2">
-        <v>21.71724000795387</v>
+        <v>2.913836913836914</v>
       </c>
       <c r="AQ2">
-        <v>-0.2558084400189664</v>
+        <v>1.539256865912762</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0183</v>
+        <v>0.0246</v>
       </c>
       <c r="G3">
-        <v>-0.05051857197732484</v>
+        <v>0.05171175699693015</v>
       </c>
       <c r="H3">
-        <v>-0.05051857197732484</v>
+        <v>0.05171175699693015</v>
       </c>
       <c r="I3">
-        <v>-0.02511960330116752</v>
+        <v>0.08552501660592786</v>
       </c>
       <c r="J3">
-        <v>-0.02511960330116752</v>
+        <v>0.08307417658677312</v>
       </c>
       <c r="K3">
-        <v>-3954.4</v>
+        <v>3037.3</v>
       </c>
       <c r="L3">
-        <v>-0.4603010161915516</v>
+        <v>0.2726334308744592</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>897.2</v>
+        <v>1629.5</v>
       </c>
       <c r="V3">
-        <v>0.2285918112563377</v>
+        <v>0.2474074973809271</v>
       </c>
       <c r="W3">
-        <v>0.917174997100777</v>
+        <v>-0.3681575757575758</v>
       </c>
       <c r="X3">
-        <v>0.2199285520742187</v>
+        <v>0.1204808429757944</v>
       </c>
       <c r="Y3">
-        <v>0.6972464450265583</v>
+        <v>-0.4886384187333702</v>
       </c>
       <c r="Z3">
-        <v>1.715401050298516</v>
+        <v>4.170010480610871</v>
       </c>
       <c r="AA3">
-        <v>-0.04309019388590484</v>
+        <v>0.3464201870349621</v>
       </c>
       <c r="AB3">
-        <v>0.1221535653296326</v>
+        <v>0.09072998511530184</v>
       </c>
       <c r="AC3">
-        <v>-0.1652437592155375</v>
+        <v>0.2556902019196603</v>
       </c>
       <c r="AD3">
-        <v>11818.8</v>
+        <v>6675.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11818.8</v>
+        <v>6675.1</v>
       </c>
       <c r="AG3">
-        <v>10921.6</v>
+        <v>5045.6</v>
       </c>
       <c r="AH3">
-        <v>0.7507002801120448</v>
+        <v>0.5033480627987995</v>
       </c>
       <c r="AI3">
-        <v>3.324182933003319</v>
+        <v>0.9395065377415586</v>
       </c>
       <c r="AJ3">
-        <v>0.7356346613679992</v>
+        <v>0.4337726424745742</v>
       </c>
       <c r="AK3">
-        <v>4.108644947708977</v>
+        <v>0.921503451802608</v>
       </c>
       <c r="AL3">
-        <v>884.4</v>
+        <v>730.2</v>
       </c>
       <c r="AM3">
-        <v>843.6</v>
+        <v>619</v>
       </c>
       <c r="AN3">
-        <v>23.50129250347982</v>
+        <v>3.854874104874105</v>
       </c>
       <c r="AO3">
-        <v>-0.24400723654455</v>
+        <v>1.304847986852917</v>
       </c>
       <c r="AP3">
-        <v>21.71724000795387</v>
+        <v>2.913836913836914</v>
       </c>
       <c r="AQ3">
-        <v>-0.2558084400189664</v>
+        <v>1.539256865912762</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LATAM Airlines Group S.A. (SNSE:LTM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SNSE:LTM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.30484798685292</v>
+      </c>
+      <c r="F2">
+        <v>3.04612832366712</v>
+      </c>
+      <c r="G2">
+        <v>3.85487410487411</v>
+      </c>
+      <c r="H2">
+        <v>4.82483367983368</v>
+      </c>
+      <c r="I2">
+        <v>0.5033480627988</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2">
+        <v>6586.3</v>
+      </c>
+      <c r="L2">
+        <v>7600.08341970529</v>
+      </c>
+      <c r="M2">
+        <v>11631.9</v>
+      </c>
+      <c r="N2">
+        <v>14325.2654197053</v>
+      </c>
+      <c r="O2">
+        <v>6675.1</v>
+      </c>
+      <c r="P2">
+        <v>8354.682000000001</v>
+      </c>
+      <c r="Q2">
+        <v>0.09072998511530179</v>
+      </c>
+      <c r="R2">
+        <v>0.08096636663721279</v>
+      </c>
+      <c r="S2">
+        <v>0.0613749080188445</v>
+      </c>
+      <c r="T2">
+        <v>0.0438870280188445</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.120480842975794</v>
+      </c>
+      <c r="X2">
+        <v>0.144101456717137</v>
+      </c>
+      <c r="Y2">
+        <v>1.39921381333028</v>
+      </c>
+      <c r="Z2">
+        <v>1.80384099177432</v>
+      </c>
+      <c r="AA2">
+        <v>6675.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.0840752164641706</v>
+      </c>
+      <c r="AC2">
+        <v>1.304847986852917</v>
+      </c>
+      <c r="AD2">
+        <v>6675.1</v>
+      </c>
+      <c r="AE2">
+        <v>730.2</v>
+      </c>
+      <c r="AF2">
+        <v>778.8</v>
+      </c>
+      <c r="AG2">
+        <v>1731.6</v>
+      </c>
+      <c r="AH2">
+        <v>0.0092192164641706</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>6586.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.0583762411417202</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.27</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1526.5</v>
+      </c>
+      <c r="AR2">
+        <v>730.2</v>
+      </c>
+      <c r="AS2">
+        <v>6675.1</v>
+      </c>
+      <c r="AT2">
+        <v>1629.5</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08574726953288439</v>
+      </c>
+      <c r="C2">
+        <v>14495.94356259259</v>
+      </c>
+      <c r="D2">
+        <v>12866.44356259259</v>
+      </c>
+      <c r="E2">
+        <v>-6675.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1629.5</v>
+      </c>
+      <c r="H2">
+        <v>6586.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2308.8</v>
+      </c>
+      <c r="K2">
+        <v>778.8</v>
+      </c>
+      <c r="L2">
+        <v>1530</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1530</v>
+      </c>
+      <c r="O2">
+        <v>413.1</v>
+      </c>
+      <c r="P2">
+        <v>1116.9</v>
+      </c>
+      <c r="Q2">
+        <v>1895.7</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08574726953288439</v>
+      </c>
+      <c r="T2">
+        <v>0.8042187817285175</v>
+      </c>
+      <c r="U2">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V2">
+        <v>0.27</v>
+      </c>
+      <c r="W2">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08562612218533404</v>
+      </c>
+      <c r="C3">
+        <v>14396.61729681592</v>
+      </c>
+      <c r="D3">
+        <v>12899.73129681591</v>
+      </c>
+      <c r="E3">
+        <v>-6542.486000000001</v>
+      </c>
+      <c r="F3">
+        <v>132.614</v>
+      </c>
+      <c r="G3">
+        <v>1629.5</v>
+      </c>
+      <c r="H3">
+        <v>6586.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2308.8</v>
+      </c>
+      <c r="K3">
+        <v>778.8</v>
+      </c>
+      <c r="L3">
+        <v>1530</v>
+      </c>
+      <c r="M3">
+        <v>7.15044297217952</v>
+      </c>
+      <c r="N3">
+        <v>1522.84955702782</v>
+      </c>
+      <c r="O3">
+        <v>411.1693803975115</v>
+      </c>
+      <c r="P3">
+        <v>1111.680176630309</v>
+      </c>
+      <c r="Q3">
+        <v>1890.480176630309</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08609344636883394</v>
+      </c>
+      <c r="T3">
+        <v>0.8101488798160107</v>
+      </c>
+      <c r="U3">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V3">
+        <v>0.27</v>
+      </c>
+      <c r="W3">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>213.9727574854907</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08550497483778369</v>
+      </c>
+      <c r="C4">
+        <v>14297.46372016802</v>
+      </c>
+      <c r="D4">
+        <v>12933.19172016802</v>
+      </c>
+      <c r="E4">
+        <v>-6409.872</v>
+      </c>
+      <c r="F4">
+        <v>265.228</v>
+      </c>
+      <c r="G4">
+        <v>1629.5</v>
+      </c>
+      <c r="H4">
+        <v>6586.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2308.8</v>
+      </c>
+      <c r="K4">
+        <v>778.8</v>
+      </c>
+      <c r="L4">
+        <v>1530</v>
+      </c>
+      <c r="M4">
+        <v>14.30088594435904</v>
+      </c>
+      <c r="N4">
+        <v>1515.699114055641</v>
+      </c>
+      <c r="O4">
+        <v>409.238760795023</v>
+      </c>
+      <c r="P4">
+        <v>1106.460353260618</v>
+      </c>
+      <c r="Q4">
+        <v>1885.260353260618</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08644668803817021</v>
+      </c>
+      <c r="T4">
+        <v>0.8162000003134525</v>
+      </c>
+      <c r="U4">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V4">
+        <v>0.27</v>
+      </c>
+      <c r="W4">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>106.9863787427453</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08538382749023335</v>
+      </c>
+      <c r="C5">
+        <v>14198.48417995101</v>
+      </c>
+      <c r="D5">
+        <v>12966.82617995101</v>
+      </c>
+      <c r="E5">
+        <v>-6277.258000000001</v>
+      </c>
+      <c r="F5">
+        <v>397.842</v>
+      </c>
+      <c r="G5">
+        <v>1629.5</v>
+      </c>
+      <c r="H5">
+        <v>6586.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2308.8</v>
+      </c>
+      <c r="K5">
+        <v>778.8</v>
+      </c>
+      <c r="L5">
+        <v>1530</v>
+      </c>
+      <c r="M5">
+        <v>21.45132891653856</v>
+      </c>
+      <c r="N5">
+        <v>1508.548671083461</v>
+      </c>
+      <c r="O5">
+        <v>407.3081411925345</v>
+      </c>
+      <c r="P5">
+        <v>1101.240529890927</v>
+      </c>
+      <c r="Q5">
+        <v>1880.040529890927</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08680721304089487</v>
+      </c>
+      <c r="T5">
+        <v>0.8223758861819758</v>
+      </c>
+      <c r="U5">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V5">
+        <v>0.27</v>
+      </c>
+      <c r="W5">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>71.32425249516356</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08526268014268301</v>
+      </c>
+      <c r="C6">
+        <v>14099.68003751892</v>
+      </c>
+      <c r="D6">
+        <v>13000.63603751892</v>
+      </c>
+      <c r="E6">
+        <v>-6144.644</v>
+      </c>
+      <c r="F6">
+        <v>530.456</v>
+      </c>
+      <c r="G6">
+        <v>1629.5</v>
+      </c>
+      <c r="H6">
+        <v>6586.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2308.8</v>
+      </c>
+      <c r="K6">
+        <v>778.8</v>
+      </c>
+      <c r="L6">
+        <v>1530</v>
+      </c>
+      <c r="M6">
+        <v>28.60177188871808</v>
+      </c>
+      <c r="N6">
+        <v>1501.398228111282</v>
+      </c>
+      <c r="O6">
+        <v>405.3775215900461</v>
+      </c>
+      <c r="P6">
+        <v>1096.020706521236</v>
+      </c>
+      <c r="Q6">
+        <v>1874.820706521236</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08717524898117629</v>
+      </c>
+      <c r="T6">
+        <v>0.8286804363394266</v>
+      </c>
+      <c r="U6">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V6">
+        <v>0.27</v>
+      </c>
+      <c r="W6">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>53.49318937137268</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08514153279513266</v>
+      </c>
+      <c r="C7">
+        <v>14001.05266846131</v>
+      </c>
+      <c r="D7">
+        <v>13034.62266846131</v>
+      </c>
+      <c r="E7">
+        <v>-6012.030000000001</v>
+      </c>
+      <c r="F7">
+        <v>663.0700000000002</v>
+      </c>
+      <c r="G7">
+        <v>1629.5</v>
+      </c>
+      <c r="H7">
+        <v>6586.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2308.8</v>
+      </c>
+      <c r="K7">
+        <v>778.8</v>
+      </c>
+      <c r="L7">
+        <v>1530</v>
+      </c>
+      <c r="M7">
+        <v>35.75221486089761</v>
+      </c>
+      <c r="N7">
+        <v>1494.247785139102</v>
+      </c>
+      <c r="O7">
+        <v>403.4469019875576</v>
+      </c>
+      <c r="P7">
+        <v>1090.800883151545</v>
+      </c>
+      <c r="Q7">
+        <v>1869.600883151545</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08755103304651625</v>
+      </c>
+      <c r="T7">
+        <v>0.8351177138686131</v>
+      </c>
+      <c r="U7">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V7">
+        <v>0.27</v>
+      </c>
+      <c r="W7">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>42.79455149709813</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08502038544758232</v>
+      </c>
+      <c r="C8">
+        <v>13902.60346278988</v>
+      </c>
+      <c r="D8">
+        <v>13068.78746278988</v>
+      </c>
+      <c r="E8">
+        <v>-5879.416</v>
+      </c>
+      <c r="F8">
+        <v>795.6840000000001</v>
+      </c>
+      <c r="G8">
+        <v>1629.5</v>
+      </c>
+      <c r="H8">
+        <v>6586.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2308.8</v>
+      </c>
+      <c r="K8">
+        <v>778.8</v>
+      </c>
+      <c r="L8">
+        <v>1530</v>
+      </c>
+      <c r="M8">
+        <v>42.90265783307712</v>
+      </c>
+      <c r="N8">
+        <v>1487.097342166923</v>
+      </c>
+      <c r="O8">
+        <v>401.5162823850691</v>
+      </c>
+      <c r="P8">
+        <v>1085.581059781853</v>
+      </c>
+      <c r="Q8">
+        <v>1864.381059781853</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08793481251750176</v>
+      </c>
+      <c r="T8">
+        <v>0.8416919547494847</v>
+      </c>
+      <c r="U8">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V8">
+        <v>0.27</v>
+      </c>
+      <c r="W8">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>35.66212624758178</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08489923810003197</v>
+      </c>
+      <c r="C9">
+        <v>13804.33382512794</v>
+      </c>
+      <c r="D9">
+        <v>13103.13182512794</v>
+      </c>
+      <c r="E9">
+        <v>-5746.802</v>
+      </c>
+      <c r="F9">
+        <v>928.2980000000002</v>
+      </c>
+      <c r="G9">
+        <v>1629.5</v>
+      </c>
+      <c r="H9">
+        <v>6586.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2308.8</v>
+      </c>
+      <c r="K9">
+        <v>778.8</v>
+      </c>
+      <c r="L9">
+        <v>1530</v>
+      </c>
+      <c r="M9">
+        <v>50.05310080525665</v>
+      </c>
+      <c r="N9">
+        <v>1479.946899194743</v>
+      </c>
+      <c r="O9">
+        <v>399.5856627825806</v>
+      </c>
+      <c r="P9">
+        <v>1080.361236412162</v>
+      </c>
+      <c r="Q9">
+        <v>1859.161236412162</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08832684531044394</v>
+      </c>
+      <c r="T9">
+        <v>0.8484075771546757</v>
+      </c>
+      <c r="U9">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V9">
+        <v>0.27</v>
+      </c>
+      <c r="W9">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>30.56753678364152</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08477809075248165</v>
+      </c>
+      <c r="C10">
+        <v>13706.24517490295</v>
+      </c>
+      <c r="D10">
+        <v>13137.65717490295</v>
+      </c>
+      <c r="E10">
+        <v>-5614.188</v>
+      </c>
+      <c r="F10">
+        <v>1060.912</v>
+      </c>
+      <c r="G10">
+        <v>1629.5</v>
+      </c>
+      <c r="H10">
+        <v>6586.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2308.8</v>
+      </c>
+      <c r="K10">
+        <v>778.8</v>
+      </c>
+      <c r="L10">
+        <v>1530</v>
+      </c>
+      <c r="M10">
+        <v>57.20354377743616</v>
+      </c>
+      <c r="N10">
+        <v>1472.796456222564</v>
+      </c>
+      <c r="O10">
+        <v>397.6550431800922</v>
+      </c>
+      <c r="P10">
+        <v>1075.141413042471</v>
+      </c>
+      <c r="Q10">
+        <v>1853.941413042471</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08872740055540661</v>
+      </c>
+      <c r="T10">
+        <v>0.8552691913512842</v>
+      </c>
+      <c r="U10">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V10">
+        <v>0.27</v>
+      </c>
+      <c r="W10">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>26.74659468568634</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08465694340493131</v>
+      </c>
+      <c r="C11">
+        <v>13608.33894654204</v>
+      </c>
+      <c r="D11">
+        <v>13172.36494654204</v>
+      </c>
+      <c r="E11">
+        <v>-5481.574000000001</v>
+      </c>
+      <c r="F11">
+        <v>1193.526</v>
+      </c>
+      <c r="G11">
+        <v>1629.5</v>
+      </c>
+      <c r="H11">
+        <v>6586.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2308.8</v>
+      </c>
+      <c r="K11">
+        <v>778.8</v>
+      </c>
+      <c r="L11">
+        <v>1530</v>
+      </c>
+      <c r="M11">
+        <v>64.35398674961569</v>
+      </c>
+      <c r="N11">
+        <v>1465.646013250384</v>
+      </c>
+      <c r="O11">
+        <v>395.7244235776038</v>
+      </c>
+      <c r="P11">
+        <v>1069.92158967278</v>
+      </c>
+      <c r="Q11">
+        <v>1848.72158967278</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08913675921234647</v>
+      </c>
+      <c r="T11">
+        <v>0.8622816102555104</v>
+      </c>
+      <c r="U11">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V11">
+        <v>0.27</v>
+      </c>
+      <c r="W11">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>23.77475083172119</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08453579605738096</v>
+      </c>
+      <c r="C12">
+        <v>13510.61658967069</v>
+      </c>
+      <c r="D12">
+        <v>13207.25658967069</v>
+      </c>
+      <c r="E12">
+        <v>-5348.96</v>
+      </c>
+      <c r="F12">
+        <v>1326.14</v>
+      </c>
+      <c r="G12">
+        <v>1629.5</v>
+      </c>
+      <c r="H12">
+        <v>6586.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2308.8</v>
+      </c>
+      <c r="K12">
+        <v>778.8</v>
+      </c>
+      <c r="L12">
+        <v>1530</v>
+      </c>
+      <c r="M12">
+        <v>71.50442972179522</v>
+      </c>
+      <c r="N12">
+        <v>1458.495570278204</v>
+      </c>
+      <c r="O12">
+        <v>393.7938039751152</v>
+      </c>
+      <c r="P12">
+        <v>1064.701766303089</v>
+      </c>
+      <c r="Q12">
+        <v>1843.501766303089</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08955521472832945</v>
+      </c>
+      <c r="T12">
+        <v>0.8694498606909417</v>
+      </c>
+      <c r="U12">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V12">
+        <v>0.27</v>
+      </c>
+      <c r="W12">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>21.39727574854906</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08441464870983062</v>
+      </c>
+      <c r="C13">
+        <v>13413.07956931452</v>
+      </c>
+      <c r="D13">
+        <v>13242.33356931452</v>
+      </c>
+      <c r="E13">
+        <v>-5216.346</v>
+      </c>
+      <c r="F13">
+        <v>1458.754</v>
+      </c>
+      <c r="G13">
+        <v>1629.5</v>
+      </c>
+      <c r="H13">
+        <v>6586.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2308.8</v>
+      </c>
+      <c r="K13">
+        <v>778.8</v>
+      </c>
+      <c r="L13">
+        <v>1530</v>
+      </c>
+      <c r="M13">
+        <v>78.65487269397472</v>
+      </c>
+      <c r="N13">
+        <v>1451.345127306025</v>
+      </c>
+      <c r="O13">
+        <v>391.8631843726268</v>
+      </c>
+      <c r="P13">
+        <v>1059.481942933398</v>
+      </c>
+      <c r="Q13">
+        <v>1838.281942933398</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08998307373905362</v>
+      </c>
+      <c r="T13">
+        <v>0.8767791954058208</v>
+      </c>
+      <c r="U13">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V13">
+        <v>0.27</v>
+      </c>
+      <c r="W13">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>19.45206886231734</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08429350136228028</v>
+      </c>
+      <c r="C14">
+        <v>13315.7293661044</v>
+      </c>
+      <c r="D14">
+        <v>13277.5973661044</v>
+      </c>
+      <c r="E14">
+        <v>-5083.732</v>
+      </c>
+      <c r="F14">
+        <v>1591.368</v>
+      </c>
+      <c r="G14">
+        <v>1629.5</v>
+      </c>
+      <c r="H14">
+        <v>6586.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2308.8</v>
+      </c>
+      <c r="K14">
+        <v>778.8</v>
+      </c>
+      <c r="L14">
+        <v>1530</v>
+      </c>
+      <c r="M14">
+        <v>85.80531566615424</v>
+      </c>
+      <c r="N14">
+        <v>1444.194684333846</v>
+      </c>
+      <c r="O14">
+        <v>389.9325647701383</v>
+      </c>
+      <c r="P14">
+        <v>1054.262119563707</v>
+      </c>
+      <c r="Q14">
+        <v>1833.062119563707</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09042065681820333</v>
+      </c>
+      <c r="T14">
+        <v>0.8842751059096745</v>
+      </c>
+      <c r="U14">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V14">
+        <v>0.27</v>
+      </c>
+      <c r="W14">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>17.83106312379089</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08417235401472993</v>
+      </c>
+      <c r="C15">
+        <v>13218.56747648472</v>
+      </c>
+      <c r="D15">
+        <v>13313.04947648472</v>
+      </c>
+      <c r="E15">
+        <v>-4951.118</v>
+      </c>
+      <c r="F15">
+        <v>1723.982</v>
+      </c>
+      <c r="G15">
+        <v>1629.5</v>
+      </c>
+      <c r="H15">
+        <v>6586.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2308.8</v>
+      </c>
+      <c r="K15">
+        <v>778.8</v>
+      </c>
+      <c r="L15">
+        <v>1530</v>
+      </c>
+      <c r="M15">
+        <v>92.95575863833376</v>
+      </c>
+      <c r="N15">
+        <v>1437.044241361666</v>
+      </c>
+      <c r="O15">
+        <v>388.0019451676499</v>
+      </c>
+      <c r="P15">
+        <v>1049.042296194016</v>
+      </c>
+      <c r="Q15">
+        <v>1827.842296194016</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09086829927848292</v>
+      </c>
+      <c r="T15">
+        <v>0.8919433361952258</v>
+      </c>
+      <c r="U15">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V15">
+        <v>0.27</v>
+      </c>
+      <c r="W15">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>16.45944288349929</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08405120666717958</v>
+      </c>
+      <c r="C16">
+        <v>13121.59541292511</v>
+      </c>
+      <c r="D16">
+        <v>13348.69141292511</v>
+      </c>
+      <c r="E16">
+        <v>-4818.504</v>
+      </c>
+      <c r="F16">
+        <v>1856.596</v>
+      </c>
+      <c r="G16">
+        <v>1629.5</v>
+      </c>
+      <c r="H16">
+        <v>6586.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2308.8</v>
+      </c>
+      <c r="K16">
+        <v>778.8</v>
+      </c>
+      <c r="L16">
+        <v>1530</v>
+      </c>
+      <c r="M16">
+        <v>100.1062016105133</v>
+      </c>
+      <c r="N16">
+        <v>1429.893798389486</v>
+      </c>
+      <c r="O16">
+        <v>386.0713255651614</v>
+      </c>
+      <c r="P16">
+        <v>1043.822472824325</v>
+      </c>
+      <c r="Q16">
+        <v>1822.622472824325</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09132635202853645</v>
+      </c>
+      <c r="T16">
+        <v>0.8997898974176506</v>
+      </c>
+      <c r="U16">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V16">
+        <v>0.27</v>
+      </c>
+      <c r="W16">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>15.28376839182076</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08393005931962924</v>
+      </c>
+      <c r="C17">
+        <v>13024.81470413553</v>
+      </c>
+      <c r="D17">
+        <v>13384.52470413553</v>
+      </c>
+      <c r="E17">
+        <v>-4685.89</v>
+      </c>
+      <c r="F17">
+        <v>1989.21</v>
+      </c>
+      <c r="G17">
+        <v>1629.5</v>
+      </c>
+      <c r="H17">
+        <v>6586.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2308.8</v>
+      </c>
+      <c r="K17">
+        <v>778.8</v>
+      </c>
+      <c r="L17">
+        <v>1530</v>
+      </c>
+      <c r="M17">
+        <v>107.2566445826928</v>
+      </c>
+      <c r="N17">
+        <v>1422.743355417307</v>
+      </c>
+      <c r="O17">
+        <v>384.1407059626729</v>
+      </c>
+      <c r="P17">
+        <v>1038.602649454634</v>
+      </c>
+      <c r="Q17">
+        <v>1817.402649454634</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09179518249035595</v>
+      </c>
+      <c r="T17">
+        <v>0.9078210836100148</v>
+      </c>
+      <c r="U17">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V17">
+        <v>0.27</v>
+      </c>
+      <c r="W17">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>14.26485049903271</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.0838089119720789</v>
+      </c>
+      <c r="C18">
+        <v>12928.22689528483</v>
+      </c>
+      <c r="D18">
+        <v>13420.55089528483</v>
+      </c>
+      <c r="E18">
+        <v>-4553.276</v>
+      </c>
+      <c r="F18">
+        <v>2121.824</v>
+      </c>
+      <c r="G18">
+        <v>1629.5</v>
+      </c>
+      <c r="H18">
+        <v>6586.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2308.8</v>
+      </c>
+      <c r="K18">
+        <v>778.8</v>
+      </c>
+      <c r="L18">
+        <v>1530</v>
+      </c>
+      <c r="M18">
+        <v>114.4070875548723</v>
+      </c>
+      <c r="N18">
+        <v>1415.592912445127</v>
+      </c>
+      <c r="O18">
+        <v>382.2100863601844</v>
+      </c>
+      <c r="P18">
+        <v>1033.382826084943</v>
+      </c>
+      <c r="Q18">
+        <v>1812.182826084943</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09227517558221879</v>
+      </c>
+      <c r="T18">
+        <v>0.9160434885212447</v>
+      </c>
+      <c r="U18">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V18">
+        <v>0.27</v>
+      </c>
+      <c r="W18">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>13.37329734284317</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08368776462452857</v>
+      </c>
+      <c r="C19">
+        <v>12831.83354822284</v>
+      </c>
+      <c r="D19">
+        <v>13456.77154822284</v>
+      </c>
+      <c r="E19">
+        <v>-4420.662</v>
+      </c>
+      <c r="F19">
+        <v>2254.438000000001</v>
+      </c>
+      <c r="G19">
+        <v>1629.5</v>
+      </c>
+      <c r="H19">
+        <v>6586.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2308.8</v>
+      </c>
+      <c r="K19">
+        <v>778.8</v>
+      </c>
+      <c r="L19">
+        <v>1530</v>
+      </c>
+      <c r="M19">
+        <v>121.5575305270519</v>
+      </c>
+      <c r="N19">
+        <v>1408.442469472948</v>
+      </c>
+      <c r="O19">
+        <v>380.279466757696</v>
+      </c>
+      <c r="P19">
+        <v>1028.163002715252</v>
+      </c>
+      <c r="Q19">
+        <v>1806.963002715252</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09276673477268071</v>
+      </c>
+      <c r="T19">
+        <v>0.9244640236712994</v>
+      </c>
+      <c r="U19">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V19">
+        <v>0.27</v>
+      </c>
+      <c r="W19">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>12.58663279326416</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08356661727697821</v>
+      </c>
+      <c r="C20">
+        <v>12735.6362417061</v>
+      </c>
+      <c r="D20">
+        <v>13493.1882417061</v>
+      </c>
+      <c r="E20">
+        <v>-4288.048000000001</v>
+      </c>
+      <c r="F20">
+        <v>2387.052</v>
+      </c>
+      <c r="G20">
+        <v>1629.5</v>
+      </c>
+      <c r="H20">
+        <v>6586.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2308.8</v>
+      </c>
+      <c r="K20">
+        <v>778.8</v>
+      </c>
+      <c r="L20">
+        <v>1530</v>
+      </c>
+      <c r="M20">
+        <v>128.7079734992314</v>
+      </c>
+      <c r="N20">
+        <v>1401.292026500768</v>
+      </c>
+      <c r="O20">
+        <v>378.3488471552075</v>
+      </c>
+      <c r="P20">
+        <v>1022.943179345561</v>
+      </c>
+      <c r="Q20">
+        <v>1801.743179345561</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09327028321169048</v>
+      </c>
+      <c r="T20">
+        <v>0.933089937727453</v>
+      </c>
+      <c r="U20">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V20">
+        <v>0.27</v>
+      </c>
+      <c r="W20">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>11.88737541586059</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08344546992942788</v>
+      </c>
+      <c r="C21">
+        <v>12639.63657162723</v>
+      </c>
+      <c r="D21">
+        <v>13529.80257162723</v>
+      </c>
+      <c r="E21">
+        <v>-4155.434</v>
+      </c>
+      <c r="F21">
+        <v>2519.666</v>
+      </c>
+      <c r="G21">
+        <v>1629.5</v>
+      </c>
+      <c r="H21">
+        <v>6586.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2308.8</v>
+      </c>
+      <c r="K21">
+        <v>778.8</v>
+      </c>
+      <c r="L21">
+        <v>1530</v>
+      </c>
+      <c r="M21">
+        <v>135.8584164714109</v>
+      </c>
+      <c r="N21">
+        <v>1394.141583528589</v>
+      </c>
+      <c r="O21">
+        <v>376.418227552719</v>
+      </c>
+      <c r="P21">
+        <v>1017.72335597587</v>
+      </c>
+      <c r="Q21">
+        <v>1796.52335597587</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09378626494549064</v>
+      </c>
+      <c r="T21">
+        <v>0.9419288373158574</v>
+      </c>
+      <c r="U21">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V21">
+        <v>0.27</v>
+      </c>
+      <c r="W21">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.26172407818372</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08332432258187754</v>
+      </c>
+      <c r="C22">
+        <v>12543.83615124808</v>
+      </c>
+      <c r="D22">
+        <v>13566.61615124808</v>
+      </c>
+      <c r="E22">
+        <v>-4022.82</v>
+      </c>
+      <c r="F22">
+        <v>2652.280000000001</v>
+      </c>
+      <c r="G22">
+        <v>1629.5</v>
+      </c>
+      <c r="H22">
+        <v>6586.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2308.8</v>
+      </c>
+      <c r="K22">
+        <v>778.8</v>
+      </c>
+      <c r="L22">
+        <v>1530</v>
+      </c>
+      <c r="M22">
+        <v>143.0088594435904</v>
+      </c>
+      <c r="N22">
+        <v>1386.991140556409</v>
+      </c>
+      <c r="O22">
+        <v>374.4876079502305</v>
+      </c>
+      <c r="P22">
+        <v>1012.503532606179</v>
+      </c>
+      <c r="Q22">
+        <v>1791.303532606179</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09431514622263579</v>
+      </c>
+      <c r="T22">
+        <v>0.950988709393972</v>
+      </c>
+      <c r="U22">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V22">
+        <v>0.27</v>
+      </c>
+      <c r="W22">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>10.69863787427453</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08320317523432719</v>
+      </c>
+      <c r="C23">
+        <v>12448.23661143666</v>
+      </c>
+      <c r="D23">
+        <v>13603.63061143666</v>
+      </c>
+      <c r="E23">
+        <v>-3890.206</v>
+      </c>
+      <c r="F23">
+        <v>2784.894</v>
+      </c>
+      <c r="G23">
+        <v>1629.5</v>
+      </c>
+      <c r="H23">
+        <v>6586.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2308.8</v>
+      </c>
+      <c r="K23">
+        <v>778.8</v>
+      </c>
+      <c r="L23">
+        <v>1530</v>
+      </c>
+      <c r="M23">
+        <v>150.1593024157699</v>
+      </c>
+      <c r="N23">
+        <v>1379.84069758423</v>
+      </c>
+      <c r="O23">
+        <v>372.5569883477421</v>
+      </c>
+      <c r="P23">
+        <v>1007.283709236488</v>
+      </c>
+      <c r="Q23">
+        <v>1786.083709236488</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09485741689920232</v>
+      </c>
+      <c r="T23">
+        <v>0.9602779453221653</v>
+      </c>
+      <c r="U23">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V23">
+        <v>0.27</v>
+      </c>
+      <c r="W23">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.18917892788051</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08308202788677685</v>
+      </c>
+      <c r="C24">
+        <v>12352.83960090796</v>
+      </c>
+      <c r="D24">
+        <v>13640.84760090796</v>
+      </c>
+      <c r="E24">
+        <v>-3757.592</v>
+      </c>
+      <c r="F24">
+        <v>2917.508</v>
+      </c>
+      <c r="G24">
+        <v>1629.5</v>
+      </c>
+      <c r="H24">
+        <v>6586.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2308.8</v>
+      </c>
+      <c r="K24">
+        <v>778.8</v>
+      </c>
+      <c r="L24">
+        <v>1530</v>
+      </c>
+      <c r="M24">
+        <v>157.3097453879494</v>
+      </c>
+      <c r="N24">
+        <v>1372.69025461205</v>
+      </c>
+      <c r="O24">
+        <v>370.6263687452536</v>
+      </c>
+      <c r="P24">
+        <v>1002.063885866797</v>
+      </c>
+      <c r="Q24">
+        <v>1780.863885866797</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09541359195209109</v>
+      </c>
+      <c r="T24">
+        <v>0.9698053667869789</v>
+      </c>
+      <c r="U24">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V24">
+        <v>0.27</v>
+      </c>
+      <c r="W24">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>9.726034431158666</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08296088053922651</v>
+      </c>
+      <c r="C25">
+        <v>12257.6467864688</v>
+      </c>
+      <c r="D25">
+        <v>13678.2687864688</v>
+      </c>
+      <c r="E25">
+        <v>-3624.978</v>
+      </c>
+      <c r="F25">
+        <v>3050.122</v>
+      </c>
+      <c r="G25">
+        <v>1629.5</v>
+      </c>
+      <c r="H25">
+        <v>6586.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2308.8</v>
+      </c>
+      <c r="K25">
+        <v>778.8</v>
+      </c>
+      <c r="L25">
+        <v>1530</v>
+      </c>
+      <c r="M25">
+        <v>164.460188360129</v>
+      </c>
+      <c r="N25">
+        <v>1365.539811639871</v>
+      </c>
+      <c r="O25">
+        <v>368.6957491427651</v>
+      </c>
+      <c r="P25">
+        <v>996.8440624971056</v>
+      </c>
+      <c r="Q25">
+        <v>1775.644062497106</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09598421311024968</v>
+      </c>
+      <c r="T25">
+        <v>0.9795802537443851</v>
+      </c>
+      <c r="U25">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V25">
+        <v>0.27</v>
+      </c>
+      <c r="W25">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.303163368934378</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08283973319167617</v>
+      </c>
+      <c r="C26">
+        <v>12162.65985326662</v>
+      </c>
+      <c r="D26">
+        <v>13715.89585326662</v>
+      </c>
+      <c r="E26">
+        <v>-3492.364</v>
+      </c>
+      <c r="F26">
+        <v>3182.736</v>
+      </c>
+      <c r="G26">
+        <v>1629.5</v>
+      </c>
+      <c r="H26">
+        <v>6586.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2308.8</v>
+      </c>
+      <c r="K26">
+        <v>778.8</v>
+      </c>
+      <c r="L26">
+        <v>1530</v>
+      </c>
+      <c r="M26">
+        <v>171.6106313323085</v>
+      </c>
+      <c r="N26">
+        <v>1358.389368667691</v>
+      </c>
+      <c r="O26">
+        <v>366.7651295402767</v>
+      </c>
+      <c r="P26">
+        <v>991.6242391274146</v>
+      </c>
+      <c r="Q26">
+        <v>1770.424239127415</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09656985061467563</v>
+      </c>
+      <c r="T26">
+        <v>0.9896123745690915</v>
+      </c>
+      <c r="U26">
+        <v>0.0539192164641706</v>
+      </c>
+      <c r="V26">
+        <v>0.27</v>
+      </c>
+      <c r="W26">
+        <v>0.03936102801884454</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.915531561895445</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08291933584412584</v>
+      </c>
+      <c r="C27">
+        <v>12005.29884223951</v>
+      </c>
+      <c r="D27">
+        <v>13691.14884223951</v>
+      </c>
+      <c r="E27">
+        <v>-3359.75</v>
+      </c>
+      <c r="F27">
+        <v>3315.35</v>
+      </c>
+      <c r="G27">
+        <v>1629.5</v>
+      </c>
+      <c r="H27">
+        <v>6586.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2308.8</v>
+      </c>
+      <c r="K27">
+        <v>778.8</v>
+      </c>
+      <c r="L27">
+        <v>1530</v>
+      </c>
+      <c r="M27">
+        <v>182.407959304488</v>
+      </c>
+      <c r="N27">
+        <v>1347.592040695512</v>
+      </c>
+      <c r="O27">
+        <v>363.8498509877882</v>
+      </c>
+      <c r="P27">
+        <v>983.7421897077236</v>
+      </c>
+      <c r="Q27">
+        <v>1762.542189707724</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09717110511921959</v>
+      </c>
+      <c r="T27">
+        <v>0.9999120186157902</v>
+      </c>
+      <c r="U27">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V27">
+        <v>0.27</v>
+      </c>
+      <c r="W27">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.387791880539694</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08280621849657546</v>
+      </c>
+      <c r="C28">
+        <v>11907.87774212642</v>
+      </c>
+      <c r="D28">
+        <v>13726.34174212642</v>
+      </c>
+      <c r="E28">
+        <v>-3227.136</v>
+      </c>
+      <c r="F28">
+        <v>3447.964</v>
+      </c>
+      <c r="G28">
+        <v>1629.5</v>
+      </c>
+      <c r="H28">
+        <v>6586.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2308.8</v>
+      </c>
+      <c r="K28">
+        <v>778.8</v>
+      </c>
+      <c r="L28">
+        <v>1530</v>
+      </c>
+      <c r="M28">
+        <v>189.7042776766675</v>
+      </c>
+      <c r="N28">
+        <v>1340.295722323332</v>
+      </c>
+      <c r="O28">
+        <v>361.8798450272997</v>
+      </c>
+      <c r="P28">
+        <v>978.4158772960325</v>
+      </c>
+      <c r="Q28">
+        <v>1757.215877296032</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09778860974550796</v>
+      </c>
+      <c r="T28">
+        <v>1.010490031420507</v>
+      </c>
+      <c r="U28">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V28">
+        <v>0.27</v>
+      </c>
+      <c r="W28">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.065184500518939</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08269310114902513</v>
+      </c>
+      <c r="C29">
+        <v>11810.638033958</v>
+      </c>
+      <c r="D29">
+        <v>13761.716033958</v>
+      </c>
+      <c r="E29">
+        <v>-3094.522</v>
+      </c>
+      <c r="F29">
+        <v>3580.578</v>
+      </c>
+      <c r="G29">
+        <v>1629.5</v>
+      </c>
+      <c r="H29">
+        <v>6586.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2308.8</v>
+      </c>
+      <c r="K29">
+        <v>778.8</v>
+      </c>
+      <c r="L29">
+        <v>1530</v>
+      </c>
+      <c r="M29">
+        <v>197.0005960488471</v>
+      </c>
+      <c r="N29">
+        <v>1332.999403951153</v>
+      </c>
+      <c r="O29">
+        <v>359.9098390668113</v>
+      </c>
+      <c r="P29">
+        <v>973.0895648843415</v>
+      </c>
+      <c r="Q29">
+        <v>1751.889564884341</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09842303230676316</v>
+      </c>
+      <c r="T29">
+        <v>1.021357852795217</v>
+      </c>
+      <c r="U29">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V29">
+        <v>0.27</v>
+      </c>
+      <c r="W29">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.766473963462682</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.0825799838014748</v>
+      </c>
+      <c r="C30">
+        <v>11713.5811237587</v>
+      </c>
+      <c r="D30">
+        <v>13797.2731237587</v>
+      </c>
+      <c r="E30">
+        <v>-2961.907999999999</v>
+      </c>
+      <c r="F30">
+        <v>3713.192000000001</v>
+      </c>
+      <c r="G30">
+        <v>1629.5</v>
+      </c>
+      <c r="H30">
+        <v>6586.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2308.8</v>
+      </c>
+      <c r="K30">
+        <v>778.8</v>
+      </c>
+      <c r="L30">
+        <v>1530</v>
+      </c>
+      <c r="M30">
+        <v>204.2969144210266</v>
+      </c>
+      <c r="N30">
+        <v>1325.703085578973</v>
+      </c>
+      <c r="O30">
+        <v>357.9398331063227</v>
+      </c>
+      <c r="P30">
+        <v>967.7632524726503</v>
+      </c>
+      <c r="Q30">
+        <v>1746.56325247265</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09907507771694211</v>
+      </c>
+      <c r="T30">
+        <v>1.032527558097002</v>
+      </c>
+      <c r="U30">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V30">
+        <v>0.27</v>
+      </c>
+      <c r="W30">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.489099893339012</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08246686645392444</v>
+      </c>
+      <c r="C31">
+        <v>11616.70843212197</v>
+      </c>
+      <c r="D31">
+        <v>13833.01443212197</v>
+      </c>
+      <c r="E31">
+        <v>-2829.294</v>
+      </c>
+      <c r="F31">
+        <v>3845.806</v>
+      </c>
+      <c r="G31">
+        <v>1629.5</v>
+      </c>
+      <c r="H31">
+        <v>6586.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2308.8</v>
+      </c>
+      <c r="K31">
+        <v>778.8</v>
+      </c>
+      <c r="L31">
+        <v>1530</v>
+      </c>
+      <c r="M31">
+        <v>211.5932327932061</v>
+      </c>
+      <c r="N31">
+        <v>1318.406767206794</v>
+      </c>
+      <c r="O31">
+        <v>355.9698271458343</v>
+      </c>
+      <c r="P31">
+        <v>962.4369400609593</v>
+      </c>
+      <c r="Q31">
+        <v>1741.236940060959</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09974549060346413</v>
+      </c>
+      <c r="T31">
+        <v>1.044011902984753</v>
+      </c>
+      <c r="U31">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V31">
+        <v>0.27</v>
+      </c>
+      <c r="W31">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.230855069430772</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08235374910637411</v>
+      </c>
+      <c r="C32">
+        <v>11520.02139439944</v>
+      </c>
+      <c r="D32">
+        <v>13868.94139439944</v>
+      </c>
+      <c r="E32">
+        <v>-2696.68</v>
+      </c>
+      <c r="F32">
+        <v>3978.42</v>
+      </c>
+      <c r="G32">
+        <v>1629.5</v>
+      </c>
+      <c r="H32">
+        <v>6586.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2308.8</v>
+      </c>
+      <c r="K32">
+        <v>778.8</v>
+      </c>
+      <c r="L32">
+        <v>1530</v>
+      </c>
+      <c r="M32">
+        <v>218.8895511653856</v>
+      </c>
+      <c r="N32">
+        <v>1311.110448834614</v>
+      </c>
+      <c r="O32">
+        <v>353.9998211853458</v>
+      </c>
+      <c r="P32">
+        <v>957.1106276492683</v>
+      </c>
+      <c r="Q32">
+        <v>1735.910627649268</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1004350581438868</v>
+      </c>
+      <c r="T32">
+        <v>1.055824372012154</v>
+      </c>
+      <c r="U32">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V32">
+        <v>0.27</v>
+      </c>
+      <c r="W32">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.989826567116413</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08224063175882376</v>
+      </c>
+      <c r="C33">
+        <v>11423.52146089312</v>
+      </c>
+      <c r="D33">
+        <v>13905.05546089312</v>
+      </c>
+      <c r="E33">
+        <v>-2564.066</v>
+      </c>
+      <c r="F33">
+        <v>4111.034000000001</v>
+      </c>
+      <c r="G33">
+        <v>1629.5</v>
+      </c>
+      <c r="H33">
+        <v>6586.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2308.8</v>
+      </c>
+      <c r="K33">
+        <v>778.8</v>
+      </c>
+      <c r="L33">
+        <v>1530</v>
+      </c>
+      <c r="M33">
+        <v>226.1858695375651</v>
+      </c>
+      <c r="N33">
+        <v>1303.814130462435</v>
+      </c>
+      <c r="O33">
+        <v>352.0298152248574</v>
+      </c>
+      <c r="P33">
+        <v>951.7843152375772</v>
+      </c>
+      <c r="Q33">
+        <v>1730.584315237577</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1011446131492492</v>
+      </c>
+      <c r="T33">
+        <v>1.067979231446146</v>
+      </c>
+      <c r="U33">
+        <v>0.0550192164641706</v>
+      </c>
+      <c r="V33">
+        <v>0.27</v>
+      </c>
+      <c r="W33">
+        <v>0.04016402801884453</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.764348290757819</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08264143441127342</v>
+      </c>
+      <c r="C34">
+        <v>11163.78609303586</v>
+      </c>
+      <c r="D34">
+        <v>13777.93409303586</v>
+      </c>
+      <c r="E34">
+        <v>-2431.452</v>
+      </c>
+      <c r="F34">
+        <v>4243.648</v>
+      </c>
+      <c r="G34">
+        <v>1629.5</v>
+      </c>
+      <c r="H34">
+        <v>6586.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2308.8</v>
+      </c>
+      <c r="K34">
+        <v>778.8</v>
+      </c>
+      <c r="L34">
+        <v>1530</v>
+      </c>
+      <c r="M34">
+        <v>242.8182135097447</v>
+      </c>
+      <c r="N34">
+        <v>1287.181786490255</v>
+      </c>
+      <c r="O34">
+        <v>347.5390823523689</v>
+      </c>
+      <c r="P34">
+        <v>939.6427041378861</v>
+      </c>
+      <c r="Q34">
+        <v>1718.442704137886</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1018750374194752</v>
+      </c>
+      <c r="T34">
+        <v>1.080491586745843</v>
+      </c>
+      <c r="U34">
+        <v>0.0572192164641706</v>
+      </c>
+      <c r="V34">
+        <v>0.27</v>
+      </c>
+      <c r="W34">
+        <v>0.04177002801884454</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.301010034976633</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08254437706372307</v>
+      </c>
+      <c r="C35">
+        <v>11061.74173026822</v>
+      </c>
+      <c r="D35">
+        <v>13808.50373026822</v>
+      </c>
+      <c r="E35">
+        <v>-2298.838</v>
+      </c>
+      <c r="F35">
+        <v>4376.262000000001</v>
+      </c>
+      <c r="G35">
+        <v>1629.5</v>
+      </c>
+      <c r="H35">
+        <v>6586.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2308.8</v>
+      </c>
+      <c r="K35">
+        <v>778.8</v>
+      </c>
+      <c r="L35">
+        <v>1530</v>
+      </c>
+      <c r="M35">
+        <v>250.4062826819242</v>
+      </c>
+      <c r="N35">
+        <v>1279.593717318076</v>
+      </c>
+      <c r="O35">
+        <v>345.4903036758804</v>
+      </c>
+      <c r="P35">
+        <v>934.1034136421952</v>
+      </c>
+      <c r="Q35">
+        <v>1712.903413642195</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1026272653992603</v>
+      </c>
+      <c r="T35">
+        <v>1.093377445188816</v>
+      </c>
+      <c r="U35">
+        <v>0.0572192164641706</v>
+      </c>
+      <c r="V35">
+        <v>0.27</v>
+      </c>
+      <c r="W35">
+        <v>0.04177002801884454</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.110070336947037</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08244731971617274</v>
+      </c>
+      <c r="C36">
+        <v>10959.83332122807</v>
+      </c>
+      <c r="D36">
+        <v>13839.20932122807</v>
+      </c>
+      <c r="E36">
+        <v>-2166.223999999999</v>
+      </c>
+      <c r="F36">
+        <v>4508.876000000001</v>
+      </c>
+      <c r="G36">
+        <v>1629.5</v>
+      </c>
+      <c r="H36">
+        <v>6586.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2308.8</v>
+      </c>
+      <c r="K36">
+        <v>778.8</v>
+      </c>
+      <c r="L36">
+        <v>1530</v>
+      </c>
+      <c r="M36">
+        <v>257.9943518541037</v>
+      </c>
+      <c r="N36">
+        <v>1272.005648145896</v>
+      </c>
+      <c r="O36">
+        <v>343.441524999392</v>
+      </c>
+      <c r="P36">
+        <v>928.564123146504</v>
+      </c>
+      <c r="Q36">
+        <v>1707.364123146504</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1034022881663115</v>
+      </c>
+      <c r="T36">
+        <v>1.106653784190666</v>
+      </c>
+      <c r="U36">
+        <v>0.0572192164641706</v>
+      </c>
+      <c r="V36">
+        <v>0.27</v>
+      </c>
+      <c r="W36">
+        <v>0.04177002801884454</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.930362385860359</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08235026236862239</v>
+      </c>
+      <c r="C37">
+        <v>10858.0617748864</v>
+      </c>
+      <c r="D37">
+        <v>13870.0517748864</v>
+      </c>
+      <c r="E37">
+        <v>-2033.61</v>
+      </c>
+      <c r="F37">
+        <v>4641.490000000001</v>
+      </c>
+      <c r="G37">
+        <v>1629.5</v>
+      </c>
+      <c r="H37">
+        <v>6586.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2308.8</v>
+      </c>
+      <c r="K37">
+        <v>778.8</v>
+      </c>
+      <c r="L37">
+        <v>1530</v>
+      </c>
+      <c r="M37">
+        <v>265.5824210262833</v>
+      </c>
+      <c r="N37">
+        <v>1264.417578973716</v>
+      </c>
+      <c r="O37">
+        <v>341.3927463229035</v>
+      </c>
+      <c r="P37">
+        <v>923.024832650813</v>
+      </c>
+      <c r="Q37">
+        <v>1701.824832650813</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1042011577877336</v>
+      </c>
+      <c r="T37">
+        <v>1.120338625931035</v>
+      </c>
+      <c r="U37">
+        <v>0.0572192164641706</v>
+      </c>
+      <c r="V37">
+        <v>0.27</v>
+      </c>
+      <c r="W37">
+        <v>0.04177002801884454</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.760923460550063</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08264740502107205</v>
+      </c>
+      <c r="C38">
+        <v>10631.45398045265</v>
+      </c>
+      <c r="D38">
+        <v>13776.05798045266</v>
+      </c>
+      <c r="E38">
+        <v>-1900.996</v>
+      </c>
+      <c r="F38">
+        <v>4774.104</v>
+      </c>
+      <c r="G38">
+        <v>1629.5</v>
+      </c>
+      <c r="H38">
+        <v>6586.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2308.8</v>
+      </c>
+      <c r="K38">
+        <v>778.8</v>
+      </c>
+      <c r="L38">
+        <v>1530</v>
+      </c>
+      <c r="M38">
+        <v>280.3316461984627</v>
+      </c>
+      <c r="N38">
+        <v>1249.668353801537</v>
+      </c>
+      <c r="O38">
+        <v>337.410455526415</v>
+      </c>
+      <c r="P38">
+        <v>912.257898275122</v>
+      </c>
+      <c r="Q38">
+        <v>1691.057898275122</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.105024992084825</v>
+      </c>
+      <c r="T38">
+        <v>1.13445111897579</v>
+      </c>
+      <c r="U38">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V38">
+        <v>0.27</v>
+      </c>
+      <c r="W38">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.457821194103878</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.0825612976735217</v>
+      </c>
+      <c r="C39">
+        <v>10525.94657635953</v>
+      </c>
+      <c r="D39">
+        <v>13803.16457635953</v>
+      </c>
+      <c r="E39">
+        <v>-1768.382</v>
+      </c>
+      <c r="F39">
+        <v>4906.718000000001</v>
+      </c>
+      <c r="G39">
+        <v>1629.5</v>
+      </c>
+      <c r="H39">
+        <v>6586.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2308.8</v>
+      </c>
+      <c r="K39">
+        <v>778.8</v>
+      </c>
+      <c r="L39">
+        <v>1530</v>
+      </c>
+      <c r="M39">
+        <v>288.1186363706423</v>
+      </c>
+      <c r="N39">
+        <v>1241.881363629358</v>
+      </c>
+      <c r="O39">
+        <v>335.3079681799265</v>
+      </c>
+      <c r="P39">
+        <v>906.573395449431</v>
+      </c>
+      <c r="Q39">
+        <v>1685.373395449431</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1058749798516654</v>
+      </c>
+      <c r="T39">
+        <v>1.14901162767276</v>
+      </c>
+      <c r="U39">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V39">
+        <v>0.27</v>
+      </c>
+      <c r="W39">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.310312513182151</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08247519032597136</v>
+      </c>
+      <c r="C40">
+        <v>10420.54605569643</v>
+      </c>
+      <c r="D40">
+        <v>13830.37805569643</v>
+      </c>
+      <c r="E40">
+        <v>-1635.768</v>
+      </c>
+      <c r="F40">
+        <v>5039.332</v>
+      </c>
+      <c r="G40">
+        <v>1629.5</v>
+      </c>
+      <c r="H40">
+        <v>6586.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2308.8</v>
+      </c>
+      <c r="K40">
+        <v>778.8</v>
+      </c>
+      <c r="L40">
+        <v>1530</v>
+      </c>
+      <c r="M40">
+        <v>295.9056265428218</v>
+      </c>
+      <c r="N40">
+        <v>1234.094373457178</v>
+      </c>
+      <c r="O40">
+        <v>333.2054808334381</v>
+      </c>
+      <c r="P40">
+        <v>900.8888926237398</v>
+      </c>
+      <c r="Q40">
+        <v>1679.68889262374</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1067523865787265</v>
+      </c>
+      <c r="T40">
+        <v>1.164041830198664</v>
+      </c>
+      <c r="U40">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V40">
+        <v>0.27</v>
+      </c>
+      <c r="W40">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.170567447045779</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08238908297842101</v>
+      </c>
+      <c r="C41">
+        <v>10315.25305188679</v>
+      </c>
+      <c r="D41">
+        <v>13857.69905188679</v>
+      </c>
+      <c r="E41">
+        <v>-1503.154</v>
+      </c>
+      <c r="F41">
+        <v>5171.946000000001</v>
+      </c>
+      <c r="G41">
+        <v>1629.5</v>
+      </c>
+      <c r="H41">
+        <v>6586.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2308.8</v>
+      </c>
+      <c r="K41">
+        <v>778.8</v>
+      </c>
+      <c r="L41">
+        <v>1530</v>
+      </c>
+      <c r="M41">
+        <v>303.6926167150013</v>
+      </c>
+      <c r="N41">
+        <v>1226.307383284998</v>
+      </c>
+      <c r="O41">
+        <v>331.1029934869496</v>
+      </c>
+      <c r="P41">
+        <v>895.2043897980489</v>
+      </c>
+      <c r="Q41">
+        <v>1674.004389798049</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1076585607394617</v>
+      </c>
+      <c r="T41">
+        <v>1.179564826250008</v>
+      </c>
+      <c r="U41">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V41">
+        <v>0.27</v>
+      </c>
+      <c r="W41">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.037988794557425</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08230297563087069</v>
+      </c>
+      <c r="C42">
+        <v>10210.06820336906</v>
+      </c>
+      <c r="D42">
+        <v>13885.12820336906</v>
+      </c>
+      <c r="E42">
+        <v>-1370.539999999999</v>
+      </c>
+      <c r="F42">
+        <v>5304.560000000001</v>
+      </c>
+      <c r="G42">
+        <v>1629.5</v>
+      </c>
+      <c r="H42">
+        <v>6586.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2308.8</v>
+      </c>
+      <c r="K42">
+        <v>778.8</v>
+      </c>
+      <c r="L42">
+        <v>1530</v>
+      </c>
+      <c r="M42">
+        <v>311.4796068871809</v>
+      </c>
+      <c r="N42">
+        <v>1218.520393112819</v>
+      </c>
+      <c r="O42">
+        <v>329.0005061404611</v>
+      </c>
+      <c r="P42">
+        <v>889.5198869723579</v>
+      </c>
+      <c r="Q42">
+        <v>1668.319886972358</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1085949407055548</v>
+      </c>
+      <c r="T42">
+        <v>1.195605255503063</v>
+      </c>
+      <c r="U42">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V42">
+        <v>0.27</v>
+      </c>
+      <c r="W42">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.91203907469349</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08221686828332034</v>
+      </c>
+      <c r="C43">
+        <v>10104.99215364651</v>
+      </c>
+      <c r="D43">
+        <v>13912.66615364651</v>
+      </c>
+      <c r="E43">
+        <v>-1237.925999999999</v>
+      </c>
+      <c r="F43">
+        <v>5437.174000000001</v>
+      </c>
+      <c r="G43">
+        <v>1629.5</v>
+      </c>
+      <c r="H43">
+        <v>6586.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2308.8</v>
+      </c>
+      <c r="K43">
+        <v>778.8</v>
+      </c>
+      <c r="L43">
+        <v>1530</v>
+      </c>
+      <c r="M43">
+        <v>319.2665970593604</v>
+      </c>
+      <c r="N43">
+        <v>1210.733402940639</v>
+      </c>
+      <c r="O43">
+        <v>326.8980187939727</v>
+      </c>
+      <c r="P43">
+        <v>883.8353841466667</v>
+      </c>
+      <c r="Q43">
+        <v>1662.635384146667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1095630623654137</v>
+      </c>
+      <c r="T43">
+        <v>1.212189428120628</v>
+      </c>
+      <c r="U43">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V43">
+        <v>0.27</v>
+      </c>
+      <c r="W43">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.792233243603404</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08213076093576999</v>
+      </c>
+      <c r="C44">
+        <v>10000.02555133749</v>
+      </c>
+      <c r="D44">
+        <v>13940.31355133749</v>
+      </c>
+      <c r="E44">
+        <v>-1105.312</v>
+      </c>
+      <c r="F44">
+        <v>5569.788</v>
+      </c>
+      <c r="G44">
+        <v>1629.5</v>
+      </c>
+      <c r="H44">
+        <v>6586.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2308.8</v>
+      </c>
+      <c r="K44">
+        <v>778.8</v>
+      </c>
+      <c r="L44">
+        <v>1530</v>
+      </c>
+      <c r="M44">
+        <v>327.0535872315399</v>
+      </c>
+      <c r="N44">
+        <v>1202.94641276846</v>
+      </c>
+      <c r="O44">
+        <v>324.7955314474842</v>
+      </c>
+      <c r="P44">
+        <v>878.1508813209757</v>
+      </c>
+      <c r="Q44">
+        <v>1656.950881320976</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.110564567530785</v>
+      </c>
+      <c r="T44">
+        <v>1.229345468759489</v>
+      </c>
+      <c r="U44">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V44">
+        <v>0.27</v>
+      </c>
+      <c r="W44">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.678132452089038</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08204465358821966</v>
+      </c>
+      <c r="C45">
+        <v>9895.169050226381</v>
+      </c>
+      <c r="D45">
+        <v>13968.07105022638</v>
+      </c>
+      <c r="E45">
+        <v>-972.6979999999994</v>
+      </c>
+      <c r="F45">
+        <v>5702.402000000001</v>
+      </c>
+      <c r="G45">
+        <v>1629.5</v>
+      </c>
+      <c r="H45">
+        <v>6586.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2308.8</v>
+      </c>
+      <c r="K45">
+        <v>778.8</v>
+      </c>
+      <c r="L45">
+        <v>1530</v>
+      </c>
+      <c r="M45">
+        <v>334.8405774037194</v>
+      </c>
+      <c r="N45">
+        <v>1195.15942259628</v>
+      </c>
+      <c r="O45">
+        <v>322.6930441009957</v>
+      </c>
+      <c r="P45">
+        <v>872.4663784952846</v>
+      </c>
+      <c r="Q45">
+        <v>1651.266378495285</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1116012132282746</v>
+      </c>
+      <c r="T45">
+        <v>1.247103475736555</v>
+      </c>
+      <c r="U45">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V45">
+        <v>0.27</v>
+      </c>
+      <c r="W45">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.569338674133479</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08195854624066931</v>
+      </c>
+      <c r="C46">
+        <v>9790.423309315156</v>
+      </c>
+      <c r="D46">
+        <v>13995.93930931516</v>
+      </c>
+      <c r="E46">
+        <v>-840.0839999999998</v>
+      </c>
+      <c r="F46">
+        <v>5835.016000000001</v>
+      </c>
+      <c r="G46">
+        <v>1629.5</v>
+      </c>
+      <c r="H46">
+        <v>6586.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2308.8</v>
+      </c>
+      <c r="K46">
+        <v>778.8</v>
+      </c>
+      <c r="L46">
+        <v>1530</v>
+      </c>
+      <c r="M46">
+        <v>342.6275675758989</v>
+      </c>
+      <c r="N46">
+        <v>1187.372432424101</v>
+      </c>
+      <c r="O46">
+        <v>320.5905567545072</v>
+      </c>
+      <c r="P46">
+        <v>866.7818756695937</v>
+      </c>
+      <c r="Q46">
+        <v>1645.581875669594</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1126748819863888</v>
+      </c>
+      <c r="T46">
+        <v>1.265495697248517</v>
+      </c>
+      <c r="U46">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V46">
+        <v>0.27</v>
+      </c>
+      <c r="W46">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.465490067903173</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08187243889311897</v>
+      </c>
+      <c r="C47">
+        <v>9685.788992875474</v>
+      </c>
+      <c r="D47">
+        <v>14023.91899287547</v>
+      </c>
+      <c r="E47">
+        <v>-707.4699999999993</v>
+      </c>
+      <c r="F47">
+        <v>5967.630000000001</v>
+      </c>
+      <c r="G47">
+        <v>1629.5</v>
+      </c>
+      <c r="H47">
+        <v>6586.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2308.8</v>
+      </c>
+      <c r="K47">
+        <v>778.8</v>
+      </c>
+      <c r="L47">
+        <v>1530</v>
+      </c>
+      <c r="M47">
+        <v>350.4145577480785</v>
+      </c>
+      <c r="N47">
+        <v>1179.585442251921</v>
+      </c>
+      <c r="O47">
+        <v>318.4880694080188</v>
+      </c>
+      <c r="P47">
+        <v>861.0973728439025</v>
+      </c>
+      <c r="Q47">
+        <v>1639.897372843902</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.113787593244798</v>
+      </c>
+      <c r="T47">
+        <v>1.284556726815459</v>
+      </c>
+      <c r="U47">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V47">
+        <v>0.27</v>
+      </c>
+      <c r="W47">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.366256955283101</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08178633154556864</v>
+      </c>
+      <c r="C48">
+        <v>9581.266770501514</v>
+      </c>
+      <c r="D48">
+        <v>14052.01077050151</v>
+      </c>
+      <c r="E48">
+        <v>-574.8559999999998</v>
+      </c>
+      <c r="F48">
+        <v>6100.244000000001</v>
+      </c>
+      <c r="G48">
+        <v>1629.5</v>
+      </c>
+      <c r="H48">
+        <v>6586.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2308.8</v>
+      </c>
+      <c r="K48">
+        <v>778.8</v>
+      </c>
+      <c r="L48">
+        <v>1530</v>
+      </c>
+      <c r="M48">
+        <v>358.201547920258</v>
+      </c>
+      <c r="N48">
+        <v>1171.798452079742</v>
+      </c>
+      <c r="O48">
+        <v>316.3855820615303</v>
+      </c>
+      <c r="P48">
+        <v>855.4128700182115</v>
+      </c>
+      <c r="Q48">
+        <v>1634.212870018212</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1149415160312966</v>
+      </c>
+      <c r="T48">
+        <v>1.304323720440436</v>
+      </c>
+      <c r="U48">
+        <v>0.0587192164641706</v>
+      </c>
+      <c r="V48">
+        <v>0.27</v>
+      </c>
+      <c r="W48">
+        <v>0.04286502801884454</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.271338325820427</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08218056419801829</v>
+      </c>
+      <c r="C49">
+        <v>9320.95130832092</v>
+      </c>
+      <c r="D49">
+        <v>13924.30930832092</v>
+      </c>
+      <c r="E49">
+        <v>-442.2419999999993</v>
+      </c>
+      <c r="F49">
+        <v>6232.858000000001</v>
+      </c>
+      <c r="G49">
+        <v>1629.5</v>
+      </c>
+      <c r="H49">
+        <v>6586.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2308.8</v>
+      </c>
+      <c r="K49">
+        <v>778.8</v>
+      </c>
+      <c r="L49">
+        <v>1530</v>
+      </c>
+      <c r="M49">
+        <v>374.7145392924375</v>
+      </c>
+      <c r="N49">
+        <v>1155.285460707562</v>
+      </c>
+      <c r="O49">
+        <v>311.9270743910419</v>
+      </c>
+      <c r="P49">
+        <v>843.3583863165205</v>
+      </c>
+      <c r="Q49">
+        <v>1622.158386316521</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1161389830738893</v>
+      </c>
+      <c r="T49">
+        <v>1.324836638353148</v>
+      </c>
+      <c r="U49">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V49">
+        <v>0.27</v>
+      </c>
+      <c r="W49">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.083108178532528</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08210467685046793</v>
+      </c>
+      <c r="C50">
+        <v>9212.738342498546</v>
+      </c>
+      <c r="D50">
+        <v>13948.71034249855</v>
+      </c>
+      <c r="E50">
+        <v>-309.6279999999997</v>
+      </c>
+      <c r="F50">
+        <v>6365.472000000001</v>
+      </c>
+      <c r="G50">
+        <v>1629.5</v>
+      </c>
+      <c r="H50">
+        <v>6586.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2308.8</v>
+      </c>
+      <c r="K50">
+        <v>778.8</v>
+      </c>
+      <c r="L50">
+        <v>1530</v>
+      </c>
+      <c r="M50">
+        <v>382.687189064617</v>
+      </c>
+      <c r="N50">
+        <v>1147.312810935383</v>
+      </c>
+      <c r="O50">
+        <v>309.7744589525533</v>
+      </c>
+      <c r="P50">
+        <v>837.5383519828293</v>
+      </c>
+      <c r="Q50">
+        <v>1616.338351982829</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1173825065411972</v>
+      </c>
+      <c r="T50">
+        <v>1.346138514647118</v>
+      </c>
+      <c r="U50">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V50">
+        <v>0.27</v>
+      </c>
+      <c r="W50">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.9980434248131</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08202878950291759</v>
+      </c>
+      <c r="C51">
+        <v>9104.611047812581</v>
+      </c>
+      <c r="D51">
+        <v>13973.19704781258</v>
+      </c>
+      <c r="E51">
+        <v>-177.0140000000001</v>
+      </c>
+      <c r="F51">
+        <v>6498.086</v>
+      </c>
+      <c r="G51">
+        <v>1629.5</v>
+      </c>
+      <c r="H51">
+        <v>6586.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2308.8</v>
+      </c>
+      <c r="K51">
+        <v>778.8</v>
+      </c>
+      <c r="L51">
+        <v>1530</v>
+      </c>
+      <c r="M51">
+        <v>390.6598388367965</v>
+      </c>
+      <c r="N51">
+        <v>1139.340161163203</v>
+      </c>
+      <c r="O51">
+        <v>307.6218435140649</v>
+      </c>
+      <c r="P51">
+        <v>831.7183176491383</v>
+      </c>
+      <c r="Q51">
+        <v>1610.518317649138</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1186747956346741</v>
+      </c>
+      <c r="T51">
+        <v>1.368275758638891</v>
+      </c>
+      <c r="U51">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V51">
+        <v>0.27</v>
+      </c>
+      <c r="W51">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.916450701857731</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08195290215536725</v>
+      </c>
+      <c r="C52">
+        <v>8996.569876238786</v>
+      </c>
+      <c r="D52">
+        <v>13997.76987623879</v>
+      </c>
+      <c r="E52">
+        <v>-44.39999999999964</v>
+      </c>
+      <c r="F52">
+        <v>6630.700000000001</v>
+      </c>
+      <c r="G52">
+        <v>1629.5</v>
+      </c>
+      <c r="H52">
+        <v>6586.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2308.8</v>
+      </c>
+      <c r="K52">
+        <v>778.8</v>
+      </c>
+      <c r="L52">
+        <v>1530</v>
+      </c>
+      <c r="M52">
+        <v>398.6324886089761</v>
+      </c>
+      <c r="N52">
+        <v>1131.367511391024</v>
+      </c>
+      <c r="O52">
+        <v>305.4692280755764</v>
+      </c>
+      <c r="P52">
+        <v>825.8982833154473</v>
+      </c>
+      <c r="Q52">
+        <v>1604.698283315447</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.12001877629189</v>
+      </c>
+      <c r="T52">
+        <v>1.391298492390335</v>
+      </c>
+      <c r="U52">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V52">
+        <v>0.27</v>
+      </c>
+      <c r="W52">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.838121687820576</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08187701480781692</v>
+      </c>
+      <c r="C53">
+        <v>8888.615282937852</v>
+      </c>
+      <c r="D53">
+        <v>14022.42928293785</v>
+      </c>
+      <c r="E53">
+        <v>88.21400000000085</v>
+      </c>
+      <c r="F53">
+        <v>6763.314000000001</v>
+      </c>
+      <c r="G53">
+        <v>1629.5</v>
+      </c>
+      <c r="H53">
+        <v>6586.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2308.8</v>
+      </c>
+      <c r="K53">
+        <v>778.8</v>
+      </c>
+      <c r="L53">
+        <v>1530</v>
+      </c>
+      <c r="M53">
+        <v>406.6051383811556</v>
+      </c>
+      <c r="N53">
+        <v>1123.394861618844</v>
+      </c>
+      <c r="O53">
+        <v>303.3166126370879</v>
+      </c>
+      <c r="P53">
+        <v>820.0782489817561</v>
+      </c>
+      <c r="Q53">
+        <v>1598.878248981756</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1214176133024616</v>
+      </c>
+      <c r="T53">
+        <v>1.415260929560205</v>
+      </c>
+      <c r="U53">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V53">
+        <v>0.27</v>
+      </c>
+      <c r="W53">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.762864399824094</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08180112746026658</v>
+      </c>
+      <c r="C54">
+        <v>8780.747726283498</v>
+      </c>
+      <c r="D54">
+        <v>14047.1757262835</v>
+      </c>
+      <c r="E54">
+        <v>220.8280000000004</v>
+      </c>
+      <c r="F54">
+        <v>6895.928000000001</v>
+      </c>
+      <c r="G54">
+        <v>1629.5</v>
+      </c>
+      <c r="H54">
+        <v>6586.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2308.8</v>
+      </c>
+      <c r="K54">
+        <v>778.8</v>
+      </c>
+      <c r="L54">
+        <v>1530</v>
+      </c>
+      <c r="M54">
+        <v>414.5777881533351</v>
+      </c>
+      <c r="N54">
+        <v>1115.422211846665</v>
+      </c>
+      <c r="O54">
+        <v>301.1639971985995</v>
+      </c>
+      <c r="P54">
+        <v>814.2582146480652</v>
+      </c>
+      <c r="Q54">
+        <v>1593.058214648065</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1228747351884738</v>
+      </c>
+      <c r="T54">
+        <v>1.440221801612154</v>
+      </c>
+      <c r="U54">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V54">
+        <v>0.27</v>
+      </c>
+      <c r="W54">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.6905016229044</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08172524011271623</v>
+      </c>
+      <c r="C55">
+        <v>8672.967667890864</v>
+      </c>
+      <c r="D55">
+        <v>14072.00966789086</v>
+      </c>
+      <c r="E55">
+        <v>353.4420000000009</v>
+      </c>
+      <c r="F55">
+        <v>7028.542000000001</v>
+      </c>
+      <c r="G55">
+        <v>1629.5</v>
+      </c>
+      <c r="H55">
+        <v>6586.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2308.8</v>
+      </c>
+      <c r="K55">
+        <v>778.8</v>
+      </c>
+      <c r="L55">
+        <v>1530</v>
+      </c>
+      <c r="M55">
+        <v>422.5504379255146</v>
+      </c>
+      <c r="N55">
+        <v>1107.449562074485</v>
+      </c>
+      <c r="O55">
+        <v>299.011381760111</v>
+      </c>
+      <c r="P55">
+        <v>808.4381803143741</v>
+      </c>
+      <c r="Q55">
+        <v>1587.238180314374</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1243938622611247</v>
+      </c>
+      <c r="T55">
+        <v>1.466244838432269</v>
+      </c>
+      <c r="U55">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V55">
+        <v>0.27</v>
+      </c>
+      <c r="W55">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.620869516811864</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08164935276516588</v>
+      </c>
+      <c r="C56">
+        <v>8565.275572645216</v>
+      </c>
+      <c r="D56">
+        <v>14096.93157264522</v>
+      </c>
+      <c r="E56">
+        <v>486.0560000000005</v>
+      </c>
+      <c r="F56">
+        <v>7161.156000000001</v>
+      </c>
+      <c r="G56">
+        <v>1629.5</v>
+      </c>
+      <c r="H56">
+        <v>6586.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2308.8</v>
+      </c>
+      <c r="K56">
+        <v>778.8</v>
+      </c>
+      <c r="L56">
+        <v>1530</v>
+      </c>
+      <c r="M56">
+        <v>430.5230876976941</v>
+      </c>
+      <c r="N56">
+        <v>1099.476912302306</v>
+      </c>
+      <c r="O56">
+        <v>296.8587663216226</v>
+      </c>
+      <c r="P56">
+        <v>802.618145980683</v>
+      </c>
+      <c r="Q56">
+        <v>1581.418145980683</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1259790383369344</v>
+      </c>
+      <c r="T56">
+        <v>1.493399311635869</v>
+      </c>
+      <c r="U56">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V56">
+        <v>0.27</v>
+      </c>
+      <c r="W56">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.553816377611645</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08157346541761555</v>
+      </c>
+      <c r="C57">
+        <v>8457.671908730961</v>
+      </c>
+      <c r="D57">
+        <v>14121.94190873096</v>
+      </c>
+      <c r="E57">
+        <v>618.670000000001</v>
+      </c>
+      <c r="F57">
+        <v>7293.770000000001</v>
+      </c>
+      <c r="G57">
+        <v>1629.5</v>
+      </c>
+      <c r="H57">
+        <v>6586.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2308.8</v>
+      </c>
+      <c r="K57">
+        <v>778.8</v>
+      </c>
+      <c r="L57">
+        <v>1530</v>
+      </c>
+      <c r="M57">
+        <v>438.4957374698737</v>
+      </c>
+      <c r="N57">
+        <v>1091.504262530126</v>
+      </c>
+      <c r="O57">
+        <v>294.7061508831341</v>
+      </c>
+      <c r="P57">
+        <v>796.7981116469921</v>
+      </c>
+      <c r="Q57">
+        <v>1575.598111646992</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1276346666827801</v>
+      </c>
+      <c r="T57">
+        <v>1.521760650315184</v>
+      </c>
+      <c r="U57">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V57">
+        <v>0.27</v>
+      </c>
+      <c r="W57">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.489201534382342</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.0814975780700652</v>
+      </c>
+      <c r="C58">
+        <v>8350.157147660977</v>
+      </c>
+      <c r="D58">
+        <v>14147.04114766098</v>
+      </c>
+      <c r="E58">
+        <v>751.2840000000015</v>
+      </c>
+      <c r="F58">
+        <v>7426.384000000002</v>
+      </c>
+      <c r="G58">
+        <v>1629.5</v>
+      </c>
+      <c r="H58">
+        <v>6586.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2308.8</v>
+      </c>
+      <c r="K58">
+        <v>778.8</v>
+      </c>
+      <c r="L58">
+        <v>1530</v>
+      </c>
+      <c r="M58">
+        <v>446.4683872420532</v>
+      </c>
+      <c r="N58">
+        <v>1083.531612757947</v>
+      </c>
+      <c r="O58">
+        <v>292.5535354446455</v>
+      </c>
+      <c r="P58">
+        <v>790.9780773133009</v>
+      </c>
+      <c r="Q58">
+        <v>1569.778077313301</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1293655508625279</v>
+      </c>
+      <c r="T58">
+        <v>1.551411140752649</v>
+      </c>
+      <c r="U58">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V58">
+        <v>0.27</v>
+      </c>
+      <c r="W58">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>3.426894364125514</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08142169072251486</v>
+      </c>
+      <c r="C59">
+        <v>8242.731764306222</v>
+      </c>
+      <c r="D59">
+        <v>14172.22976430622</v>
+      </c>
+      <c r="E59">
+        <v>883.898000000001</v>
+      </c>
+      <c r="F59">
+        <v>7558.998000000001</v>
+      </c>
+      <c r="G59">
+        <v>1629.5</v>
+      </c>
+      <c r="H59">
+        <v>6586.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2308.8</v>
+      </c>
+      <c r="K59">
+        <v>778.8</v>
+      </c>
+      <c r="L59">
+        <v>1530</v>
+      </c>
+      <c r="M59">
+        <v>454.4410370142327</v>
+      </c>
+      <c r="N59">
+        <v>1075.558962985767</v>
+      </c>
+      <c r="O59">
+        <v>290.4009200061571</v>
+      </c>
+      <c r="P59">
+        <v>785.1580429796099</v>
+      </c>
+      <c r="Q59">
+        <v>1563.95804297961</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1311769412831941</v>
+      </c>
+      <c r="T59">
+        <v>1.582440723768602</v>
+      </c>
+      <c r="U59">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V59">
+        <v>0.27</v>
+      </c>
+      <c r="W59">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.366773410368926</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.0813458033749645</v>
+      </c>
+      <c r="C60">
+        <v>8135.396236925694</v>
+      </c>
+      <c r="D60">
+        <v>14197.50823692569</v>
+      </c>
+      <c r="E60">
+        <v>1016.512</v>
+      </c>
+      <c r="F60">
+        <v>7691.612</v>
+      </c>
+      <c r="G60">
+        <v>1629.5</v>
+      </c>
+      <c r="H60">
+        <v>6586.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2308.8</v>
+      </c>
+      <c r="K60">
+        <v>778.8</v>
+      </c>
+      <c r="L60">
+        <v>1530</v>
+      </c>
+      <c r="M60">
+        <v>462.4136867864121</v>
+      </c>
+      <c r="N60">
+        <v>1067.586313213588</v>
+      </c>
+      <c r="O60">
+        <v>288.2483045676686</v>
+      </c>
+      <c r="P60">
+        <v>779.338008645919</v>
+      </c>
+      <c r="Q60">
+        <v>1558.138008645919</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1330745883905587</v>
+      </c>
+      <c r="T60">
+        <v>1.614947905975789</v>
+      </c>
+      <c r="U60">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V60">
+        <v>0.27</v>
+      </c>
+      <c r="W60">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.308725592948773</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.08126991602741418</v>
+      </c>
+      <c r="C61">
+        <v>8028.151047196678</v>
+      </c>
+      <c r="D61">
+        <v>14222.87704719668</v>
+      </c>
+      <c r="E61">
+        <v>1149.126</v>
+      </c>
+      <c r="F61">
+        <v>7824.226000000001</v>
+      </c>
+      <c r="G61">
+        <v>1629.5</v>
+      </c>
+      <c r="H61">
+        <v>6586.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2308.8</v>
+      </c>
+      <c r="K61">
+        <v>778.8</v>
+      </c>
+      <c r="L61">
+        <v>1530</v>
+      </c>
+      <c r="M61">
+        <v>470.3863365585917</v>
+      </c>
+      <c r="N61">
+        <v>1059.613663441408</v>
+      </c>
+      <c r="O61">
+        <v>286.0956891291802</v>
+      </c>
+      <c r="P61">
+        <v>773.5179743122279</v>
+      </c>
+      <c r="Q61">
+        <v>1552.317974312228</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1350648036495022</v>
+      </c>
+      <c r="T61">
+        <v>1.649040804388206</v>
+      </c>
+      <c r="U61">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V61">
+        <v>0.27</v>
+      </c>
+      <c r="W61">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.252645498153031</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08119402867986382</v>
+      </c>
+      <c r="C62">
+        <v>7920.996680245409</v>
+      </c>
+      <c r="D62">
+        <v>14248.33668024541</v>
+      </c>
+      <c r="E62">
+        <v>1281.74</v>
+      </c>
+      <c r="F62">
+        <v>7956.84</v>
+      </c>
+      <c r="G62">
+        <v>1629.5</v>
+      </c>
+      <c r="H62">
+        <v>6586.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2308.8</v>
+      </c>
+      <c r="K62">
+        <v>778.8</v>
+      </c>
+      <c r="L62">
+        <v>1530</v>
+      </c>
+      <c r="M62">
+        <v>478.3589863307712</v>
+      </c>
+      <c r="N62">
+        <v>1051.641013669229</v>
+      </c>
+      <c r="O62">
+        <v>283.9430736906917</v>
+      </c>
+      <c r="P62">
+        <v>767.6979399785369</v>
+      </c>
+      <c r="Q62">
+        <v>1546.497939978537</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1371545296713927</v>
+      </c>
+      <c r="T62">
+        <v>1.684838347721244</v>
+      </c>
+      <c r="U62">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V62">
+        <v>0.27</v>
+      </c>
+      <c r="W62">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.198434739850481</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.0811181413323135</v>
+      </c>
+      <c r="C63">
+        <v>7813.933624677888</v>
+      </c>
+      <c r="D63">
+        <v>14273.88762467789</v>
+      </c>
+      <c r="E63">
+        <v>1414.354</v>
+      </c>
+      <c r="F63">
+        <v>8089.454000000001</v>
+      </c>
+      <c r="G63">
+        <v>1629.5</v>
+      </c>
+      <c r="H63">
+        <v>6586.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2308.8</v>
+      </c>
+      <c r="K63">
+        <v>778.8</v>
+      </c>
+      <c r="L63">
+        <v>1530</v>
+      </c>
+      <c r="M63">
+        <v>486.3316361029508</v>
+      </c>
+      <c r="N63">
+        <v>1043.668363897049</v>
+      </c>
+      <c r="O63">
+        <v>281.7904582522032</v>
+      </c>
+      <c r="P63">
+        <v>761.8779056448457</v>
+      </c>
+      <c r="Q63">
+        <v>1540.677905644846</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1393514211303034</v>
+      </c>
+      <c r="T63">
+        <v>1.722471662507258</v>
+      </c>
+      <c r="U63">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V63">
+        <v>0.27</v>
+      </c>
+      <c r="W63">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.146001383459489</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.08104225398476314</v>
+      </c>
+      <c r="C64">
+        <v>7706.962372611257</v>
+      </c>
+      <c r="D64">
+        <v>14299.53037261126</v>
+      </c>
+      <c r="E64">
+        <v>1546.968000000001</v>
+      </c>
+      <c r="F64">
+        <v>8222.068000000001</v>
+      </c>
+      <c r="G64">
+        <v>1629.5</v>
+      </c>
+      <c r="H64">
+        <v>6586.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2308.8</v>
+      </c>
+      <c r="K64">
+        <v>778.8</v>
+      </c>
+      <c r="L64">
+        <v>1530</v>
+      </c>
+      <c r="M64">
+        <v>494.3042858751303</v>
+      </c>
+      <c r="N64">
+        <v>1035.695714124869</v>
+      </c>
+      <c r="O64">
+        <v>279.6378428137148</v>
+      </c>
+      <c r="P64">
+        <v>756.0578713111547</v>
+      </c>
+      <c r="Q64">
+        <v>1534.857871311155</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1416639384554725</v>
+      </c>
+      <c r="T64">
+        <v>1.762085678071483</v>
+      </c>
+      <c r="U64">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V64">
+        <v>0.27</v>
+      </c>
+      <c r="W64">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.095259425661755</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.08096636663721281</v>
+      </c>
+      <c r="C65">
+        <v>7600.08341970529</v>
+      </c>
+      <c r="D65">
+        <v>14325.26541970529</v>
+      </c>
+      <c r="E65">
+        <v>1679.582</v>
+      </c>
+      <c r="F65">
+        <v>8354.682000000001</v>
+      </c>
+      <c r="G65">
+        <v>1629.5</v>
+      </c>
+      <c r="H65">
+        <v>6586.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2308.8</v>
+      </c>
+      <c r="K65">
+        <v>778.8</v>
+      </c>
+      <c r="L65">
+        <v>1530</v>
+      </c>
+      <c r="M65">
+        <v>502.2769356473098</v>
+      </c>
+      <c r="N65">
+        <v>1027.72306435269</v>
+      </c>
+      <c r="O65">
+        <v>277.4852273752263</v>
+      </c>
+      <c r="P65">
+        <v>750.2378369774638</v>
+      </c>
+      <c r="Q65">
+        <v>1529.037836977464</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1441014567171371</v>
+      </c>
+      <c r="T65">
+        <v>1.803840991774315</v>
+      </c>
+      <c r="U65">
+        <v>0.0601192164641706</v>
+      </c>
+      <c r="V65">
+        <v>0.27</v>
+      </c>
+      <c r="W65">
+        <v>0.04388702801884454</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.046128323667124</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.08210519928966246</v>
+      </c>
+      <c r="C66">
+        <v>7090.746063559398</v>
+      </c>
+      <c r="D66">
+        <v>13948.5420635594</v>
+      </c>
+      <c r="E66">
+        <v>1812.196</v>
+      </c>
+      <c r="F66">
+        <v>8487.296</v>
+      </c>
+      <c r="G66">
+        <v>1629.5</v>
+      </c>
+      <c r="H66">
+        <v>6586.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2308.8</v>
+      </c>
+      <c r="K66">
+        <v>778.8</v>
+      </c>
+      <c r="L66">
+        <v>1530</v>
+      </c>
+      <c r="M66">
+        <v>532.3165550194893</v>
+      </c>
+      <c r="N66">
+        <v>997.6834449805104</v>
+      </c>
+      <c r="O66">
+        <v>269.3745301447378</v>
+      </c>
+      <c r="P66">
+        <v>728.3089148357726</v>
+      </c>
+      <c r="Q66">
+        <v>1507.108914835773</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1466743926600055</v>
+      </c>
+      <c r="T66">
+        <v>1.847916045127305</v>
+      </c>
+      <c r="U66">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V66">
+        <v>0.27</v>
+      </c>
+      <c r="W66">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.874229601865347</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.08204829194211212</v>
+      </c>
+      <c r="C67">
+        <v>6976.485956751158</v>
+      </c>
+      <c r="D67">
+        <v>13966.89595675116</v>
+      </c>
+      <c r="E67">
+        <v>1944.810000000001</v>
+      </c>
+      <c r="F67">
+        <v>8619.910000000002</v>
+      </c>
+      <c r="G67">
+        <v>1629.5</v>
+      </c>
+      <c r="H67">
+        <v>6586.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2308.8</v>
+      </c>
+      <c r="K67">
+        <v>778.8</v>
+      </c>
+      <c r="L67">
+        <v>1530</v>
+      </c>
+      <c r="M67">
+        <v>540.6340011916689</v>
+      </c>
+      <c r="N67">
+        <v>989.3659988083309</v>
+      </c>
+      <c r="O67">
+        <v>267.1288196782494</v>
+      </c>
+      <c r="P67">
+        <v>722.2371791300816</v>
+      </c>
+      <c r="Q67">
+        <v>1501.037179130082</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1493943535138948</v>
+      </c>
+      <c r="T67">
+        <v>1.894509672957608</v>
+      </c>
+      <c r="U67">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V67">
+        <v>0.27</v>
+      </c>
+      <c r="W67">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.830010684913572</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.08199138459456176</v>
+      </c>
+      <c r="C68">
+        <v>6862.274214744772</v>
+      </c>
+      <c r="D68">
+        <v>13985.29821474477</v>
+      </c>
+      <c r="E68">
+        <v>2077.424000000001</v>
+      </c>
+      <c r="F68">
+        <v>8752.524000000001</v>
+      </c>
+      <c r="G68">
+        <v>1629.5</v>
+      </c>
+      <c r="H68">
+        <v>6586.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2308.8</v>
+      </c>
+      <c r="K68">
+        <v>778.8</v>
+      </c>
+      <c r="L68">
+        <v>1530</v>
+      </c>
+      <c r="M68">
+        <v>548.9514473638484</v>
+      </c>
+      <c r="N68">
+        <v>981.0485526361514</v>
+      </c>
+      <c r="O68">
+        <v>264.8831092117609</v>
+      </c>
+      <c r="P68">
+        <v>716.1654434243906</v>
+      </c>
+      <c r="Q68">
+        <v>1494.965443424391</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1522743120650717</v>
+      </c>
+      <c r="T68">
+        <v>1.943844102424987</v>
+      </c>
+      <c r="U68">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V68">
+        <v>0.27</v>
+      </c>
+      <c r="W68">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.787131735142154</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.08193447724701143</v>
+      </c>
+      <c r="C69">
+        <v>6748.111028963383</v>
+      </c>
+      <c r="D69">
+        <v>14003.74902896338</v>
+      </c>
+      <c r="E69">
+        <v>2210.038</v>
+      </c>
+      <c r="F69">
+        <v>8885.138000000001</v>
+      </c>
+      <c r="G69">
+        <v>1629.5</v>
+      </c>
+      <c r="H69">
+        <v>6586.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2308.8</v>
+      </c>
+      <c r="K69">
+        <v>778.8</v>
+      </c>
+      <c r="L69">
+        <v>1530</v>
+      </c>
+      <c r="M69">
+        <v>557.2688935360279</v>
+      </c>
+      <c r="N69">
+        <v>972.7311064639719</v>
+      </c>
+      <c r="O69">
+        <v>262.6373987452724</v>
+      </c>
+      <c r="P69">
+        <v>710.0937077186994</v>
+      </c>
+      <c r="Q69">
+        <v>1488.893707718699</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1553288135587442</v>
+      </c>
+      <c r="T69">
+        <v>1.996168497314633</v>
+      </c>
+      <c r="U69">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V69">
+        <v>0.27</v>
+      </c>
+      <c r="W69">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.74553275402063</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.08187756989946109</v>
+      </c>
+      <c r="C70">
+        <v>6633.996591841671</v>
+      </c>
+      <c r="D70">
+        <v>14022.24859184167</v>
+      </c>
+      <c r="E70">
+        <v>2342.652000000002</v>
+      </c>
+      <c r="F70">
+        <v>9017.752000000002</v>
+      </c>
+      <c r="G70">
+        <v>1629.5</v>
+      </c>
+      <c r="H70">
+        <v>6586.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2308.8</v>
+      </c>
+      <c r="K70">
+        <v>778.8</v>
+      </c>
+      <c r="L70">
+        <v>1530</v>
+      </c>
+      <c r="M70">
+        <v>565.5863397082074</v>
+      </c>
+      <c r="N70">
+        <v>964.4136602917923</v>
+      </c>
+      <c r="O70">
+        <v>260.3916882787839</v>
+      </c>
+      <c r="P70">
+        <v>704.0219720130084</v>
+      </c>
+      <c r="Q70">
+        <v>1482.821972013008</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1585742213957713</v>
+      </c>
+      <c r="T70">
+        <v>2.05176316688488</v>
+      </c>
+      <c r="U70">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V70">
+        <v>0.27</v>
+      </c>
+      <c r="W70">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.705157272343856</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.08182066255191074</v>
+      </c>
+      <c r="C71">
+        <v>6519.93109683251</v>
+      </c>
+      <c r="D71">
+        <v>14040.79709683251</v>
+      </c>
+      <c r="E71">
+        <v>2475.266000000001</v>
+      </c>
+      <c r="F71">
+        <v>9150.366000000002</v>
+      </c>
+      <c r="G71">
+        <v>1629.5</v>
+      </c>
+      <c r="H71">
+        <v>6586.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2308.8</v>
+      </c>
+      <c r="K71">
+        <v>778.8</v>
+      </c>
+      <c r="L71">
+        <v>1530</v>
+      </c>
+      <c r="M71">
+        <v>573.903785880387</v>
+      </c>
+      <c r="N71">
+        <v>956.0962141196128</v>
+      </c>
+      <c r="O71">
+        <v>258.1459778122955</v>
+      </c>
+      <c r="P71">
+        <v>697.9502363073173</v>
+      </c>
+      <c r="Q71">
+        <v>1476.750236307317</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1620290103835743</v>
+      </c>
+      <c r="T71">
+        <v>2.110944589330628</v>
+      </c>
+      <c r="U71">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V71">
+        <v>0.27</v>
+      </c>
+      <c r="W71">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.6659520944838</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.08176375520436041</v>
+      </c>
+      <c r="C72">
+        <v>6405.914738413712</v>
+      </c>
+      <c r="D72">
+        <v>14059.39473841371</v>
+      </c>
+      <c r="E72">
+        <v>2607.880000000001</v>
+      </c>
+      <c r="F72">
+        <v>9282.980000000001</v>
+      </c>
+      <c r="G72">
+        <v>1629.5</v>
+      </c>
+      <c r="H72">
+        <v>6586.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2308.8</v>
+      </c>
+      <c r="K72">
+        <v>778.8</v>
+      </c>
+      <c r="L72">
+        <v>1530</v>
+      </c>
+      <c r="M72">
+        <v>582.2212320525665</v>
+      </c>
+      <c r="N72">
+        <v>947.7787679474333</v>
+      </c>
+      <c r="O72">
+        <v>255.900267345807</v>
+      </c>
+      <c r="P72">
+        <v>691.8785006016262</v>
+      </c>
+      <c r="Q72">
+        <v>1470.678500601626</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1657141186372308</v>
+      </c>
+      <c r="T72">
+        <v>2.174071439939426</v>
+      </c>
+      <c r="U72">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V72">
+        <v>0.27</v>
+      </c>
+      <c r="W72">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.627867064562603</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.08170684785681007</v>
+      </c>
+      <c r="C73">
+        <v>6291.947712094845</v>
+      </c>
+      <c r="D73">
+        <v>14078.04171209485</v>
+      </c>
+      <c r="E73">
+        <v>2740.494000000001</v>
+      </c>
+      <c r="F73">
+        <v>9415.594000000001</v>
+      </c>
+      <c r="G73">
+        <v>1629.5</v>
+      </c>
+      <c r="H73">
+        <v>6586.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2308.8</v>
+      </c>
+      <c r="K73">
+        <v>778.8</v>
+      </c>
+      <c r="L73">
+        <v>1530</v>
+      </c>
+      <c r="M73">
+        <v>590.5386782247459</v>
+      </c>
+      <c r="N73">
+        <v>939.4613217752539</v>
+      </c>
+      <c r="O73">
+        <v>253.6545568793186</v>
+      </c>
+      <c r="P73">
+        <v>685.8067648959353</v>
+      </c>
+      <c r="Q73">
+        <v>1464.606764895935</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1696533722876912</v>
+      </c>
+      <c r="T73">
+        <v>2.241551866452278</v>
+      </c>
+      <c r="U73">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V73">
+        <v>0.27</v>
+      </c>
+      <c r="W73">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.590854852385665</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.08164994050925972</v>
+      </c>
+      <c r="C74">
+        <v>6178.03021442407</v>
+      </c>
+      <c r="D74">
+        <v>14096.73821442407</v>
+      </c>
+      <c r="E74">
+        <v>2873.108</v>
+      </c>
+      <c r="F74">
+        <v>9548.208000000001</v>
+      </c>
+      <c r="G74">
+        <v>1629.5</v>
+      </c>
+      <c r="H74">
+        <v>6586.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2308.8</v>
+      </c>
+      <c r="K74">
+        <v>778.8</v>
+      </c>
+      <c r="L74">
+        <v>1530</v>
+      </c>
+      <c r="M74">
+        <v>598.8561243969255</v>
+      </c>
+      <c r="N74">
+        <v>931.1438756030743</v>
+      </c>
+      <c r="O74">
+        <v>251.4088464128301</v>
+      </c>
+      <c r="P74">
+        <v>679.7350291902442</v>
+      </c>
+      <c r="Q74">
+        <v>1458.535029190244</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1738740011988988</v>
+      </c>
+      <c r="T74">
+        <v>2.313852323430335</v>
+      </c>
+      <c r="U74">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V74">
+        <v>0.27</v>
+      </c>
+      <c r="W74">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.554870757213642</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.08159303316170938</v>
+      </c>
+      <c r="C75">
+        <v>6064.162442995039</v>
+      </c>
+      <c r="D75">
+        <v>14115.48444299504</v>
+      </c>
+      <c r="E75">
+        <v>3005.722</v>
+      </c>
+      <c r="F75">
+        <v>9680.822</v>
+      </c>
+      <c r="G75">
+        <v>1629.5</v>
+      </c>
+      <c r="H75">
+        <v>6586.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2308.8</v>
+      </c>
+      <c r="K75">
+        <v>778.8</v>
+      </c>
+      <c r="L75">
+        <v>1530</v>
+      </c>
+      <c r="M75">
+        <v>607.173570569105</v>
+      </c>
+      <c r="N75">
+        <v>922.8264294308948</v>
+      </c>
+      <c r="O75">
+        <v>249.1631359463416</v>
+      </c>
+      <c r="P75">
+        <v>673.6632934845532</v>
+      </c>
+      <c r="Q75">
+        <v>1452.463293484553</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1784072692887143</v>
+      </c>
+      <c r="T75">
+        <v>2.391508369814173</v>
+      </c>
+      <c r="U75">
+        <v>0.0627192164641706</v>
+      </c>
+      <c r="V75">
+        <v>0.27</v>
+      </c>
+      <c r="W75">
+        <v>0.04578502801884454</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.51987252766277</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.08299466581415903</v>
+      </c>
+      <c r="C76">
+        <v>5483.87622880424</v>
+      </c>
+      <c r="D76">
+        <v>13667.81222880424</v>
+      </c>
+      <c r="E76">
+        <v>3138.336000000001</v>
+      </c>
+      <c r="F76">
+        <v>9813.436000000002</v>
+      </c>
+      <c r="G76">
+        <v>1629.5</v>
+      </c>
+      <c r="H76">
+        <v>6586.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2308.8</v>
+      </c>
+      <c r="K76">
+        <v>778.8</v>
+      </c>
+      <c r="L76">
+        <v>1530</v>
+      </c>
+      <c r="M76">
+        <v>641.9872939412845</v>
+      </c>
+      <c r="N76">
+        <v>888.0127060587153</v>
+      </c>
+      <c r="O76">
+        <v>239.7634306358531</v>
+      </c>
+      <c r="P76">
+        <v>648.2492754228622</v>
+      </c>
+      <c r="Q76">
+        <v>1427.049275422862</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1832892503085157</v>
+      </c>
+      <c r="T76">
+        <v>2.475137958227537</v>
+      </c>
+      <c r="U76">
+        <v>0.06541921646417059</v>
+      </c>
+      <c r="V76">
+        <v>0.27</v>
+      </c>
+      <c r="W76">
+        <v>0.04775602801884453</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.383224737372967</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.08295746846660867</v>
+      </c>
+      <c r="C77">
+        <v>5362.775714051073</v>
+      </c>
+      <c r="D77">
+        <v>13679.32571405107</v>
+      </c>
+      <c r="E77">
+        <v>3270.950000000001</v>
+      </c>
+      <c r="F77">
+        <v>9946.050000000001</v>
+      </c>
+      <c r="G77">
+        <v>1629.5</v>
+      </c>
+      <c r="H77">
+        <v>6586.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2308.8</v>
+      </c>
+      <c r="K77">
+        <v>778.8</v>
+      </c>
+      <c r="L77">
+        <v>1530</v>
+      </c>
+      <c r="M77">
+        <v>650.662797913464</v>
+      </c>
+      <c r="N77">
+        <v>879.3372020865357</v>
+      </c>
+      <c r="O77">
+        <v>237.4210445633647</v>
+      </c>
+      <c r="P77">
+        <v>641.916157523171</v>
+      </c>
+      <c r="Q77">
+        <v>1420.716157523171</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1885617898099012</v>
+      </c>
+      <c r="T77">
+        <v>2.565457913713971</v>
+      </c>
+      <c r="U77">
+        <v>0.06541921646417059</v>
+      </c>
+      <c r="V77">
+        <v>0.27</v>
+      </c>
+      <c r="W77">
+        <v>0.04775602801884453</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.351448407541328</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.08292027111905836</v>
+      </c>
+      <c r="C78">
+        <v>5241.694613100273</v>
+      </c>
+      <c r="D78">
+        <v>13690.85861310027</v>
+      </c>
+      <c r="E78">
+        <v>3403.564</v>
+      </c>
+      <c r="F78">
+        <v>10078.664</v>
+      </c>
+      <c r="G78">
+        <v>1629.5</v>
+      </c>
+      <c r="H78">
+        <v>6586.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2308.8</v>
+      </c>
+      <c r="K78">
+        <v>778.8</v>
+      </c>
+      <c r="L78">
+        <v>1530</v>
+      </c>
+      <c r="M78">
+        <v>659.3383018856435</v>
+      </c>
+      <c r="N78">
+        <v>870.6616981143562</v>
+      </c>
+      <c r="O78">
+        <v>235.0786584908762</v>
+      </c>
+      <c r="P78">
+        <v>635.5830396234801</v>
+      </c>
+      <c r="Q78">
+        <v>1414.38303962348</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1942737076030688</v>
+      </c>
+      <c r="T78">
+        <v>2.663304532157607</v>
+      </c>
+      <c r="U78">
+        <v>0.06541921646417059</v>
+      </c>
+      <c r="V78">
+        <v>0.27</v>
+      </c>
+      <c r="W78">
+        <v>0.04775602801884453</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.320508296915784</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.082883073771508</v>
+      </c>
+      <c r="C79">
+        <v>5120.632975096038</v>
+      </c>
+      <c r="D79">
+        <v>13702.41097509604</v>
+      </c>
+      <c r="E79">
+        <v>3536.178000000002</v>
+      </c>
+      <c r="F79">
+        <v>10211.278</v>
+      </c>
+      <c r="G79">
+        <v>1629.5</v>
+      </c>
+      <c r="H79">
+        <v>6586.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2308.8</v>
+      </c>
+      <c r="K79">
+        <v>778.8</v>
+      </c>
+      <c r="L79">
+        <v>1530</v>
+      </c>
+      <c r="M79">
+        <v>668.0138058578231</v>
+      </c>
+      <c r="N79">
+        <v>861.9861941421767</v>
+      </c>
+      <c r="O79">
+        <v>232.7362724183877</v>
+      </c>
+      <c r="P79">
+        <v>629.2499217237889</v>
+      </c>
+      <c r="Q79">
+        <v>1408.049921723789</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2004823138999901</v>
+      </c>
+      <c r="T79">
+        <v>2.769659552205038</v>
+      </c>
+      <c r="U79">
+        <v>0.06541921646417059</v>
+      </c>
+      <c r="V79">
+        <v>0.27</v>
+      </c>
+      <c r="W79">
+        <v>0.04775602801884453</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.290371825527267</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.08284587642395766</v>
+      </c>
+      <c r="C80">
+        <v>4999.590849348513</v>
+      </c>
+      <c r="D80">
+        <v>13713.98284934851</v>
+      </c>
+      <c r="E80">
+        <v>3668.792000000001</v>
+      </c>
+      <c r="F80">
+        <v>10343.892</v>
+      </c>
+      <c r="G80">
+        <v>1629.5</v>
+      </c>
+      <c r="H80">
+        <v>6586.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2308.8</v>
+      </c>
+      <c r="K80">
+        <v>778.8</v>
+      </c>
+      <c r="L80">
+        <v>1530</v>
+      </c>
+      <c r="M80">
+        <v>676.6893098300026</v>
+      </c>
+      <c r="N80">
+        <v>853.3106901699972</v>
+      </c>
+      <c r="O80">
+        <v>230.3938863458993</v>
+      </c>
+      <c r="P80">
+        <v>622.916803824098</v>
+      </c>
+      <c r="Q80">
+        <v>1401.716803824098</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.207255338951177</v>
+      </c>
+      <c r="T80">
+        <v>2.885683210438599</v>
+      </c>
+      <c r="U80">
+        <v>0.06541921646417059</v>
+      </c>
+      <c r="V80">
+        <v>0.27</v>
+      </c>
+      <c r="W80">
+        <v>0.04775602801884453</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.261008084174354</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.08551916907640733</v>
+      </c>
+      <c r="C81">
+        <v>4082.25635213621</v>
+      </c>
+      <c r="D81">
+        <v>12929.26235213621</v>
+      </c>
+      <c r="E81">
+        <v>3801.406000000001</v>
+      </c>
+      <c r="F81">
+        <v>10476.506</v>
+      </c>
+      <c r="G81">
+        <v>1629.5</v>
+      </c>
+      <c r="H81">
+        <v>6586.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2308.8</v>
+      </c>
+      <c r="K81">
+        <v>778.8</v>
+      </c>
+      <c r="L81">
+        <v>1530</v>
+      </c>
+      <c r="M81">
+        <v>734.6043920021822</v>
+      </c>
+      <c r="N81">
+        <v>795.3956079978176</v>
+      </c>
+      <c r="O81">
+        <v>214.7568141594108</v>
+      </c>
+      <c r="P81">
+        <v>580.6387938384069</v>
+      </c>
+      <c r="Q81">
+        <v>1359.438793838407</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2146734140072388</v>
+      </c>
+      <c r="T81">
+        <v>3.01275674088488</v>
+      </c>
+      <c r="U81">
+        <v>0.0701192164641706</v>
+      </c>
+      <c r="V81">
+        <v>0.27</v>
+      </c>
+      <c r="W81">
+        <v>0.05118702801884454</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.082753678929073</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.08551628172885697</v>
+      </c>
+      <c r="C82">
+        <v>3950.441458413481</v>
+      </c>
+      <c r="D82">
+        <v>12930.06145841348</v>
+      </c>
+      <c r="E82">
+        <v>3934.020000000002</v>
+      </c>
+      <c r="F82">
+        <v>10609.12</v>
+      </c>
+      <c r="G82">
+        <v>1629.5</v>
+      </c>
+      <c r="H82">
+        <v>6586.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2308.8</v>
+      </c>
+      <c r="K82">
+        <v>778.8</v>
+      </c>
+      <c r="L82">
+        <v>1530</v>
+      </c>
+      <c r="M82">
+        <v>743.9031817743618</v>
+      </c>
+      <c r="N82">
+        <v>786.096818225638</v>
+      </c>
+      <c r="O82">
+        <v>212.2461409209223</v>
+      </c>
+      <c r="P82">
+        <v>573.8506773047158</v>
+      </c>
+      <c r="Q82">
+        <v>1352.650677304716</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2228332965689068</v>
+      </c>
+      <c r="T82">
+        <v>3.152537624375789</v>
+      </c>
+      <c r="U82">
+        <v>0.0701192164641706</v>
+      </c>
+      <c r="V82">
+        <v>0.27</v>
+      </c>
+      <c r="W82">
+        <v>0.05118702801884454</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.05671925794246</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.08551339438130663</v>
+      </c>
+      <c r="C83">
+        <v>3818.626663476014</v>
+      </c>
+      <c r="D83">
+        <v>12930.86066347602</v>
+      </c>
+      <c r="E83">
+        <v>4066.634000000002</v>
+      </c>
+      <c r="F83">
+        <v>10741.734</v>
+      </c>
+      <c r="G83">
+        <v>1629.5</v>
+      </c>
+      <c r="H83">
+        <v>6586.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2308.8</v>
+      </c>
+      <c r="K83">
+        <v>778.8</v>
+      </c>
+      <c r="L83">
+        <v>1530</v>
+      </c>
+      <c r="M83">
+        <v>753.2019715465412</v>
+      </c>
+      <c r="N83">
+        <v>776.7980284534585</v>
+      </c>
+      <c r="O83">
+        <v>209.7354676824338</v>
+      </c>
+      <c r="P83">
+        <v>567.0625607710247</v>
+      </c>
+      <c r="Q83">
+        <v>1345.862560771025</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2318521141370661</v>
+      </c>
+      <c r="T83">
+        <v>3.307032285076267</v>
+      </c>
+      <c r="U83">
+        <v>0.0701192164641706</v>
+      </c>
+      <c r="V83">
+        <v>0.27</v>
+      </c>
+      <c r="W83">
+        <v>0.05118702801884454</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>2.031327662165392</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.08551050703375629</v>
+      </c>
+      <c r="C84">
+        <v>3686.811967342133</v>
+      </c>
+      <c r="D84">
+        <v>12931.65996734214</v>
+      </c>
+      <c r="E84">
+        <v>4199.248000000001</v>
+      </c>
+      <c r="F84">
+        <v>10874.348</v>
+      </c>
+      <c r="G84">
+        <v>1629.5</v>
+      </c>
+      <c r="H84">
+        <v>6586.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2308.8</v>
+      </c>
+      <c r="K84">
+        <v>778.8</v>
+      </c>
+      <c r="L84">
+        <v>1530</v>
+      </c>
+      <c r="M84">
+        <v>762.5007613187208</v>
+      </c>
+      <c r="N84">
+        <v>767.4992386812789</v>
+      </c>
+      <c r="O84">
+        <v>207.2247944439453</v>
+      </c>
+      <c r="P84">
+        <v>560.2744442373337</v>
+      </c>
+      <c r="Q84">
+        <v>1339.074444237334</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2418730225461321</v>
+      </c>
+      <c r="T84">
+        <v>3.47869301918791</v>
+      </c>
+      <c r="U84">
+        <v>0.0701192164641706</v>
+      </c>
+      <c r="V84">
+        <v>0.27</v>
+      </c>
+      <c r="W84">
+        <v>0.05118702801884454</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>2.006555373602399</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.09114248968620596</v>
+      </c>
+      <c r="C85">
+        <v>2162.768460643638</v>
+      </c>
+      <c r="D85">
+        <v>11540.23046064364</v>
+      </c>
+      <c r="E85">
+        <v>4331.862000000001</v>
+      </c>
+      <c r="F85">
+        <v>11006.962</v>
+      </c>
+      <c r="G85">
+        <v>1629.5</v>
+      </c>
+      <c r="H85">
+        <v>6586.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2308.8</v>
+      </c>
+      <c r="K85">
+        <v>778.8</v>
+      </c>
+      <c r="L85">
+        <v>1530</v>
+      </c>
+      <c r="M85">
+        <v>874.1642976909003</v>
+      </c>
+      <c r="N85">
+        <v>655.8357023090995</v>
+      </c>
+      <c r="O85">
+        <v>177.0756396234569</v>
+      </c>
+      <c r="P85">
+        <v>478.7600626856426</v>
+      </c>
+      <c r="Q85">
+        <v>1257.560062685643</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2530728613562647</v>
+      </c>
+      <c r="T85">
+        <v>3.670549133783276</v>
+      </c>
+      <c r="U85">
+        <v>0.07941921646417061</v>
+      </c>
+      <c r="V85">
+        <v>0.27</v>
+      </c>
+      <c r="W85">
+        <v>0.05797602801884454</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.750243065338501</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.09408953233865562</v>
+      </c>
+      <c r="C86">
+        <v>1415.037096685797</v>
+      </c>
+      <c r="D86">
+        <v>10925.1130966858</v>
+      </c>
+      <c r="E86">
+        <v>4464.476000000001</v>
+      </c>
+      <c r="F86">
+        <v>11139.576</v>
+      </c>
+      <c r="G86">
+        <v>1629.5</v>
+      </c>
+      <c r="H86">
+        <v>6586.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2308.8</v>
+      </c>
+      <c r="K86">
+        <v>778.8</v>
+      </c>
+      <c r="L86">
+        <v>1530</v>
+      </c>
+      <c r="M86">
+        <v>937.0524048630798</v>
+      </c>
+      <c r="N86">
+        <v>592.94759513692</v>
+      </c>
+      <c r="O86">
+        <v>160.0958506869684</v>
+      </c>
+      <c r="P86">
+        <v>432.8517444499516</v>
+      </c>
+      <c r="Q86">
+        <v>1211.651744449952</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2656726800176638</v>
+      </c>
+      <c r="T86">
+        <v>3.88638726270306</v>
+      </c>
+      <c r="U86">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V86">
+        <v>0.27</v>
+      </c>
+      <c r="W86">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.632779545796652</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.09418884499110527</v>
+      </c>
+      <c r="C87">
+        <v>1262.834279476872</v>
+      </c>
+      <c r="D87">
+        <v>10905.52427947687</v>
+      </c>
+      <c r="E87">
+        <v>4597.09</v>
+      </c>
+      <c r="F87">
+        <v>11272.19</v>
+      </c>
+      <c r="G87">
+        <v>1629.5</v>
+      </c>
+      <c r="H87">
+        <v>6586.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2308.8</v>
+      </c>
+      <c r="K87">
+        <v>778.8</v>
+      </c>
+      <c r="L87">
+        <v>1530</v>
+      </c>
+      <c r="M87">
+        <v>948.2077906352592</v>
+      </c>
+      <c r="N87">
+        <v>581.7922093647405</v>
+      </c>
+      <c r="O87">
+        <v>157.08389652848</v>
+      </c>
+      <c r="P87">
+        <v>424.7083128362606</v>
+      </c>
+      <c r="Q87">
+        <v>1203.508312836261</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2799524745005827</v>
+      </c>
+      <c r="T87">
+        <v>4.13100380881215</v>
+      </c>
+      <c r="U87">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V87">
+        <v>0.27</v>
+      </c>
+      <c r="W87">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>1.613570374669633</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.09428815764355493</v>
+      </c>
+      <c r="C88">
+        <v>1110.701582361238</v>
+      </c>
+      <c r="D88">
+        <v>10886.00558236124</v>
+      </c>
+      <c r="E88">
+        <v>4729.704000000002</v>
+      </c>
+      <c r="F88">
+        <v>11404.804</v>
+      </c>
+      <c r="G88">
+        <v>1629.5</v>
+      </c>
+      <c r="H88">
+        <v>6586.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2308.8</v>
+      </c>
+      <c r="K88">
+        <v>778.8</v>
+      </c>
+      <c r="L88">
+        <v>1530</v>
+      </c>
+      <c r="M88">
+        <v>959.3631764074389</v>
+      </c>
+      <c r="N88">
+        <v>570.6368235925609</v>
+      </c>
+      <c r="O88">
+        <v>154.0719423699914</v>
+      </c>
+      <c r="P88">
+        <v>416.5648812225694</v>
+      </c>
+      <c r="Q88">
+        <v>1195.364881222569</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2962722396239187</v>
+      </c>
+      <c r="T88">
+        <v>4.410565575793969</v>
+      </c>
+      <c r="U88">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V88">
+        <v>0.27</v>
+      </c>
+      <c r="W88">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>1.594807928452544</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.09438747029600458</v>
+      </c>
+      <c r="C89">
+        <v>958.6386295089324</v>
+      </c>
+      <c r="D89">
+        <v>10866.55662950893</v>
+      </c>
+      <c r="E89">
+        <v>4862.318000000001</v>
+      </c>
+      <c r="F89">
+        <v>11537.418</v>
+      </c>
+      <c r="G89">
+        <v>1629.5</v>
+      </c>
+      <c r="H89">
+        <v>6586.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2308.8</v>
+      </c>
+      <c r="K89">
+        <v>778.8</v>
+      </c>
+      <c r="L89">
+        <v>1530</v>
+      </c>
+      <c r="M89">
+        <v>970.5185621796184</v>
+      </c>
+      <c r="N89">
+        <v>559.4814378203814</v>
+      </c>
+      <c r="O89">
+        <v>151.059988211503</v>
+      </c>
+      <c r="P89">
+        <v>408.4214496088784</v>
+      </c>
+      <c r="Q89">
+        <v>1187.221449608878</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3151027378431526</v>
+      </c>
+      <c r="T89">
+        <v>4.733136845388374</v>
+      </c>
+      <c r="U89">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V89">
+        <v>0.27</v>
+      </c>
+      <c r="W89">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.576476802838147</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.09448678294845425</v>
+      </c>
+      <c r="C90">
+        <v>806.6450477710187</v>
+      </c>
+      <c r="D90">
+        <v>10847.17704777102</v>
+      </c>
+      <c r="E90">
+        <v>4994.932000000001</v>
+      </c>
+      <c r="F90">
+        <v>11670.032</v>
+      </c>
+      <c r="G90">
+        <v>1629.5</v>
+      </c>
+      <c r="H90">
+        <v>6586.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2308.8</v>
+      </c>
+      <c r="K90">
+        <v>778.8</v>
+      </c>
+      <c r="L90">
+        <v>1530</v>
+      </c>
+      <c r="M90">
+        <v>981.6739479517979</v>
+      </c>
+      <c r="N90">
+        <v>548.3260520482019</v>
+      </c>
+      <c r="O90">
+        <v>148.0480340530145</v>
+      </c>
+      <c r="P90">
+        <v>400.2780179951874</v>
+      </c>
+      <c r="Q90">
+        <v>1179.078017995187</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3370716524322588</v>
+      </c>
+      <c r="T90">
+        <v>5.109469993248514</v>
+      </c>
+      <c r="U90">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V90">
+        <v>0.27</v>
+      </c>
+      <c r="W90">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.558562293714986</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.09458609560090391</v>
+      </c>
+      <c r="C91">
+        <v>654.7204666557536</v>
+      </c>
+      <c r="D91">
+        <v>10827.86646665575</v>
+      </c>
+      <c r="E91">
+        <v>5127.546</v>
+      </c>
+      <c r="F91">
+        <v>11802.646</v>
+      </c>
+      <c r="G91">
+        <v>1629.5</v>
+      </c>
+      <c r="H91">
+        <v>6586.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2308.8</v>
+      </c>
+      <c r="K91">
+        <v>778.8</v>
+      </c>
+      <c r="L91">
+        <v>1530</v>
+      </c>
+      <c r="M91">
+        <v>992.8293337239774</v>
+      </c>
+      <c r="N91">
+        <v>537.1706662760224</v>
+      </c>
+      <c r="O91">
+        <v>145.0360798945261</v>
+      </c>
+      <c r="P91">
+        <v>392.1345863814963</v>
+      </c>
+      <c r="Q91">
+        <v>1170.934586381496</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3630349151284751</v>
+      </c>
+      <c r="T91">
+        <v>5.554227349810498</v>
+      </c>
+      <c r="U91">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V91">
+        <v>0.27</v>
+      </c>
+      <c r="W91">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>1.541050357830548</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.09468540825335356</v>
+      </c>
+      <c r="C92">
+        <v>502.8645183049557</v>
+      </c>
+      <c r="D92">
+        <v>10808.62451830496</v>
+      </c>
+      <c r="E92">
+        <v>5260.160000000002</v>
+      </c>
+      <c r="F92">
+        <v>11935.26</v>
+      </c>
+      <c r="G92">
+        <v>1629.5</v>
+      </c>
+      <c r="H92">
+        <v>6586.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2308.8</v>
+      </c>
+      <c r="K92">
+        <v>778.8</v>
+      </c>
+      <c r="L92">
+        <v>1530</v>
+      </c>
+      <c r="M92">
+        <v>1003.984719496157</v>
+      </c>
+      <c r="N92">
+        <v>526.0152805038427</v>
+      </c>
+      <c r="O92">
+        <v>142.0241257360375</v>
+      </c>
+      <c r="P92">
+        <v>383.9911547678052</v>
+      </c>
+      <c r="Q92">
+        <v>1162.791154767805</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3941908303639348</v>
+      </c>
+      <c r="T92">
+        <v>6.087936177684878</v>
+      </c>
+      <c r="U92">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V92">
+        <v>0.27</v>
+      </c>
+      <c r="W92">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>1.523927576076875</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.09478472090580321</v>
+      </c>
+      <c r="C93">
+        <v>351.0768374706568</v>
+      </c>
+      <c r="D93">
+        <v>10789.45083747066</v>
+      </c>
+      <c r="E93">
+        <v>5392.774000000001</v>
+      </c>
+      <c r="F93">
+        <v>12067.874</v>
+      </c>
+      <c r="G93">
+        <v>1629.5</v>
+      </c>
+      <c r="H93">
+        <v>6586.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2308.8</v>
+      </c>
+      <c r="K93">
+        <v>778.8</v>
+      </c>
+      <c r="L93">
+        <v>1530</v>
+      </c>
+      <c r="M93">
+        <v>1015.140105268336</v>
+      </c>
+      <c r="N93">
+        <v>514.8598947316633</v>
+      </c>
+      <c r="O93">
+        <v>139.0121715775491</v>
+      </c>
+      <c r="P93">
+        <v>375.8477231541142</v>
+      </c>
+      <c r="Q93">
+        <v>1154.647723154114</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4322702823183855</v>
+      </c>
+      <c r="T93">
+        <v>6.740246967309122</v>
+      </c>
+      <c r="U93">
+        <v>0.0841192164641706</v>
+      </c>
+      <c r="V93">
+        <v>0.27</v>
+      </c>
+      <c r="W93">
+        <v>0.06140702801884454</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>1.507181119196909</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1303844973771192</v>
+      </c>
+      <c r="C94">
+        <v>-3975.500650482816</v>
+      </c>
+      <c r="D94">
+        <v>6595.487349517184</v>
+      </c>
+      <c r="E94">
+        <v>5525.388000000001</v>
+      </c>
+      <c r="F94">
+        <v>12200.488</v>
+      </c>
+      <c r="G94">
+        <v>1629.5</v>
+      </c>
+      <c r="H94">
+        <v>6586.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2308.8</v>
+      </c>
+      <c r="K94">
+        <v>778.8</v>
+      </c>
+      <c r="L94">
+        <v>1530</v>
+      </c>
+      <c r="M94">
+        <v>1624.119403040516</v>
+      </c>
+      <c r="N94">
+        <v>-94.11940304051632</v>
+      </c>
+      <c r="O94">
+        <v>-25.41223882093941</v>
+      </c>
+      <c r="P94">
+        <v>-68.70716421957691</v>
+      </c>
+      <c r="Q94">
+        <v>710.092835780423</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4883171935810068</v>
+      </c>
+      <c r="T94">
+        <v>7.700344948379126</v>
+      </c>
+      <c r="U94">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V94">
+        <v>0.2543532201060063</v>
+      </c>
+      <c r="W94">
+        <v>0.09925991509852031</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.9420489633555789</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1313276895417609</v>
+      </c>
+      <c r="C95">
+        <v>-4175.346546371136</v>
+      </c>
+      <c r="D95">
+        <v>6528.255453628866</v>
+      </c>
+      <c r="E95">
+        <v>5658.002000000002</v>
+      </c>
+      <c r="F95">
+        <v>12333.102</v>
+      </c>
+      <c r="G95">
+        <v>1629.5</v>
+      </c>
+      <c r="H95">
+        <v>6586.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2308.8</v>
+      </c>
+      <c r="K95">
+        <v>778.8</v>
+      </c>
+      <c r="L95">
+        <v>1530</v>
+      </c>
+      <c r="M95">
+        <v>1641.772874812696</v>
+      </c>
+      <c r="N95">
+        <v>-111.772874812696</v>
+      </c>
+      <c r="O95">
+        <v>-30.17867619942793</v>
+      </c>
+      <c r="P95">
+        <v>-81.59419861326811</v>
+      </c>
+      <c r="Q95">
+        <v>697.2058013867319</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5525339355211509</v>
+      </c>
+      <c r="T95">
+        <v>8.800394226719005</v>
+      </c>
+      <c r="U95">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V95">
+        <v>0.2516182392446514</v>
+      </c>
+      <c r="W95">
+        <v>0.09962399360782839</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.9319194046098198</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1322708817064027</v>
+      </c>
+      <c r="C96">
+        <v>-4373.835600508136</v>
+      </c>
+      <c r="D96">
+        <v>6462.380399491866</v>
+      </c>
+      <c r="E96">
+        <v>5790.616000000002</v>
+      </c>
+      <c r="F96">
+        <v>12465.716</v>
+      </c>
+      <c r="G96">
+        <v>1629.5</v>
+      </c>
+      <c r="H96">
+        <v>6586.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2308.8</v>
+      </c>
+      <c r="K96">
+        <v>778.8</v>
+      </c>
+      <c r="L96">
+        <v>1530</v>
+      </c>
+      <c r="M96">
+        <v>1659.426346584875</v>
+      </c>
+      <c r="N96">
+        <v>-129.4263465848753</v>
+      </c>
+      <c r="O96">
+        <v>-34.94511357791634</v>
+      </c>
+      <c r="P96">
+        <v>-94.48123300695897</v>
+      </c>
+      <c r="Q96">
+        <v>684.318766993041</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6381562581080096</v>
+      </c>
+      <c r="T96">
+        <v>10.26712659783884</v>
+      </c>
+      <c r="U96">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V96">
+        <v>0.248941449465453</v>
+      </c>
+      <c r="W96">
+        <v>0.09998032576587458</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.9220053683905666</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1332140738710443</v>
+      </c>
+      <c r="C97">
+        <v>-4571.008477249963</v>
+      </c>
+      <c r="D97">
+        <v>6397.821522750039</v>
+      </c>
+      <c r="E97">
+        <v>5923.230000000001</v>
+      </c>
+      <c r="F97">
+        <v>12598.33</v>
+      </c>
+      <c r="G97">
+        <v>1629.5</v>
+      </c>
+      <c r="H97">
+        <v>6586.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2308.8</v>
+      </c>
+      <c r="K97">
+        <v>778.8</v>
+      </c>
+      <c r="L97">
+        <v>1530</v>
+      </c>
+      <c r="M97">
+        <v>1677.079818357055</v>
+      </c>
+      <c r="N97">
+        <v>-147.0798183570548</v>
+      </c>
+      <c r="O97">
+        <v>-39.71155095640481</v>
+      </c>
+      <c r="P97">
+        <v>-107.36826740065</v>
+      </c>
+      <c r="Q97">
+        <v>671.43173259935</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7580275097296116</v>
+      </c>
+      <c r="T97">
+        <v>12.32055191740661</v>
+      </c>
+      <c r="U97">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V97">
+        <v>0.2463210131552903</v>
+      </c>
+      <c r="W97">
+        <v>0.1003291561942777</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.9123000487232975</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.134157266035686</v>
+      </c>
+      <c r="C98">
+        <v>-4766.904232085253</v>
+      </c>
+      <c r="D98">
+        <v>6334.539767914748</v>
+      </c>
+      <c r="E98">
+        <v>6055.844000000001</v>
+      </c>
+      <c r="F98">
+        <v>12730.944</v>
+      </c>
+      <c r="G98">
+        <v>1629.5</v>
+      </c>
+      <c r="H98">
+        <v>6586.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2308.8</v>
+      </c>
+      <c r="K98">
+        <v>778.8</v>
+      </c>
+      <c r="L98">
+        <v>1530</v>
+      </c>
+      <c r="M98">
+        <v>1694.733290129234</v>
+      </c>
+      <c r="N98">
+        <v>-164.7332901292343</v>
+      </c>
+      <c r="O98">
+        <v>-44.47798833489327</v>
+      </c>
+      <c r="P98">
+        <v>-120.2553017943411</v>
+      </c>
+      <c r="Q98">
+        <v>658.544698205659</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9378343871620125</v>
+      </c>
+      <c r="T98">
+        <v>15.40068989675823</v>
+      </c>
+      <c r="U98">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V98">
+        <v>0.2437551692682561</v>
+      </c>
+      <c r="W98">
+        <v>0.1006707193220891</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.9027969232157631</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1351004582003277</v>
+      </c>
+      <c r="C99">
+        <v>-4961.560390423479</v>
+      </c>
+      <c r="D99">
+        <v>6272.497609576522</v>
+      </c>
+      <c r="E99">
+        <v>6188.458000000001</v>
+      </c>
+      <c r="F99">
+        <v>12863.558</v>
+      </c>
+      <c r="G99">
+        <v>1629.5</v>
+      </c>
+      <c r="H99">
+        <v>6586.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2308.8</v>
+      </c>
+      <c r="K99">
+        <v>778.8</v>
+      </c>
+      <c r="L99">
+        <v>1530</v>
+      </c>
+      <c r="M99">
+        <v>1712.386761901414</v>
+      </c>
+      <c r="N99">
+        <v>-182.3867619014138</v>
+      </c>
+      <c r="O99">
+        <v>-49.24442571338174</v>
+      </c>
+      <c r="P99">
+        <v>-133.1423361880321</v>
+      </c>
+      <c r="Q99">
+        <v>645.6576638119678</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.237512516216017</v>
+      </c>
+      <c r="T99">
+        <v>20.53425319567764</v>
+      </c>
+      <c r="U99">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V99">
+        <v>0.2412422293788926</v>
+      </c>
+      <c r="W99">
+        <v>0.1010052399111827</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.8934897384403429</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1360436503649695</v>
+      </c>
+      <c r="C100">
+        <v>-5155.013021798199</v>
+      </c>
+      <c r="D100">
+        <v>6211.658978201802</v>
+      </c>
+      <c r="E100">
+        <v>6321.072</v>
+      </c>
+      <c r="F100">
+        <v>12996.172</v>
+      </c>
+      <c r="G100">
+        <v>1629.5</v>
+      </c>
+      <c r="H100">
+        <v>6586.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2308.8</v>
+      </c>
+      <c r="K100">
+        <v>778.8</v>
+      </c>
+      <c r="L100">
+        <v>1530</v>
+      </c>
+      <c r="M100">
+        <v>1730.040233673593</v>
+      </c>
+      <c r="N100">
+        <v>-200.0402336735933</v>
+      </c>
+      <c r="O100">
+        <v>-54.0108630918702</v>
+      </c>
+      <c r="P100">
+        <v>-146.0293705817231</v>
+      </c>
+      <c r="Q100">
+        <v>632.7706294182768</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.836868774324025</v>
+      </c>
+      <c r="T100">
+        <v>30.80137979351646</v>
+      </c>
+      <c r="U100">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V100">
+        <v>0.2387805739770672</v>
+      </c>
+      <c r="W100">
+        <v>0.1013329335494785</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.8843724962113598</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1369868425296112</v>
+      </c>
+      <c r="C101">
+        <v>-5347.296809793464</v>
+      </c>
+      <c r="D101">
+        <v>6151.989190206538</v>
+      </c>
+      <c r="E101">
+        <v>6453.686000000002</v>
+      </c>
+      <c r="F101">
+        <v>13128.786</v>
+      </c>
+      <c r="G101">
+        <v>1629.5</v>
+      </c>
+      <c r="H101">
+        <v>6586.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2308.8</v>
+      </c>
+      <c r="K101">
+        <v>778.8</v>
+      </c>
+      <c r="L101">
+        <v>1530</v>
+      </c>
+      <c r="M101">
+        <v>1747.693705445773</v>
+      </c>
+      <c r="N101">
+        <v>-217.693705445773</v>
+      </c>
+      <c r="O101">
+        <v>-58.77730047035872</v>
+      </c>
+      <c r="P101">
+        <v>-158.9164049754143</v>
+      </c>
+      <c r="Q101">
+        <v>619.8835950245857</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.63493754864805</v>
+      </c>
+      <c r="T101">
+        <v>61.60275958703293</v>
+      </c>
+      <c r="U101">
+        <v>0.1331192164641706</v>
+      </c>
+      <c r="V101">
+        <v>0.2363686489873998</v>
+      </c>
+      <c r="W101">
+        <v>0.1016540071142734</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.8754394406940733</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
@@ -647,10 +647,10 @@
         <v>1.801554641060814</v>
       </c>
       <c r="X2">
-        <v>0.1170548846109062</v>
+        <v>0.1170257017768461</v>
       </c>
       <c r="Y2">
-        <v>1.684499756449908</v>
+        <v>1.684528939283968</v>
       </c>
       <c r="Z2">
         <v>2.317563377712931</v>
@@ -659,10 +659,10 @@
         <v>0.2511098306364181</v>
       </c>
       <c r="AB2">
-        <v>0.08885232436309159</v>
+        <v>0.08883656853146868</v>
       </c>
       <c r="AC2">
-        <v>0.1622575062733265</v>
+        <v>0.1622732621049494</v>
       </c>
       <c r="AD2">
         <v>7114.7</v>
@@ -781,10 +781,10 @@
         <v>1.801554641060814</v>
       </c>
       <c r="X3">
-        <v>0.1170548846109062</v>
+        <v>0.1170257017768461</v>
       </c>
       <c r="Y3">
-        <v>1.684499756449908</v>
+        <v>1.684528939283968</v>
       </c>
       <c r="Z3">
         <v>2.317563377712931</v>
@@ -793,10 +793,10 @@
         <v>0.2511098306364181</v>
       </c>
       <c r="AB3">
-        <v>0.08885232436309159</v>
+        <v>0.08883656853146868</v>
       </c>
       <c r="AC3">
-        <v>0.1622575062733265</v>
+        <v>0.1622732621049494</v>
       </c>
       <c r="AD3">
         <v>7114.7</v>
@@ -1133,49 +1133,49 @@
         <v>1.89064382278142</v>
       </c>
       <c r="F2">
-        <v>3.00546072446602</v>
+        <v>3.03337598777861</v>
       </c>
       <c r="G2">
         <v>3.18217192951069</v>
       </c>
       <c r="H2">
-        <v>4.42641381161106</v>
+        <v>4.5647392432239</v>
       </c>
       <c r="I2">
         <v>0.460099331324288</v>
       </c>
       <c r="J2">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="K2">
         <v>8348.700000000001</v>
       </c>
       <c r="L2">
-        <v>7358.95973331646</v>
+        <v>7650.1292402395</v>
       </c>
       <c r="M2">
         <v>13453.2</v>
       </c>
       <c r="N2">
-        <v>15245.3357333165</v>
+        <v>15845.7732402395</v>
       </c>
       <c r="O2">
         <v>7114.7</v>
       </c>
       <c r="P2">
-        <v>9896.575999999999</v>
+        <v>10205.844</v>
       </c>
       <c r="Q2">
-        <v>0.08885232436309159</v>
+        <v>0.08883656853146869</v>
       </c>
       <c r="R2">
-        <v>0.0837913922692962</v>
+        <v>0.0823384228960987</v>
       </c>
       <c r="S2">
         <v>0.0557582072898587</v>
       </c>
       <c r="T2">
-        <v>0.0483852072898587</v>
+        <v>0.0464872072898587</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.117054884610906</v>
+        <v>0.117025701776846</v>
       </c>
       <c r="X2">
-        <v>0.146735721121629</v>
+        <v>0.151931959072917</v>
       </c>
       <c r="Y2">
         <v>1.30452374147622</v>
       </c>
       <c r="Z2">
-        <v>1.8479160451273</v>
+        <v>1.94384410242499</v>
       </c>
       <c r="AA2">
         <v>7114.7</v>
@@ -1230,7 +1230,7 @@
         <v>8348.700000000001</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788713</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08972753820573817</v>
+        <v>0.08970954743829636</v>
       </c>
       <c r="C2">
-        <v>15195.35796193389</v>
+        <v>15195.93288830094</v>
       </c>
       <c r="D2">
-        <v>13185.15796193389</v>
+        <v>13185.73288830094</v>
       </c>
       <c r="E2">
         <v>-7114.7</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08972753820573817</v>
+        <v>0.08970954743829636</v>
       </c>
       <c r="T2">
         <v>0.8042187817285175</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0.27</v>
       </c>
       <c r="W2">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08958952592548128</v>
+        <v>0.08956136373311155</v>
       </c>
       <c r="C3">
-        <v>15082.27987461882</v>
+        <v>15085.94810825857</v>
       </c>
       <c r="D3">
-        <v>13226.71387461882</v>
+        <v>13230.38210825857</v>
       </c>
       <c r="E3">
         <v>-6960.066</v>
@@ -1533,37 +1533,37 @@
         <v>1971.45</v>
       </c>
       <c r="M3">
-        <v>9.290581726109599</v>
+        <v>9.074094126109598</v>
       </c>
       <c r="N3">
-        <v>1962.15941827389</v>
+        <v>1962.37590587389</v>
       </c>
       <c r="O3">
-        <v>529.7830429339504</v>
+        <v>529.8414945859504</v>
       </c>
       <c r="P3">
-        <v>1432.37637533994</v>
+        <v>1432.53441128794</v>
       </c>
       <c r="Q3">
-        <v>2255.67637533994</v>
+        <v>2255.83441128794</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09005144833594211</v>
+        <v>0.09003332490930602</v>
       </c>
       <c r="T3">
         <v>0.8101488798160107</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0.27</v>
       </c>
       <c r="W3">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>212.1987683999997</v>
+        <v>217.2613566270371</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08945151364522434</v>
+        <v>0.08941318002792673</v>
       </c>
       <c r="C4">
-        <v>14969.46456060938</v>
+        <v>14976.26673589447</v>
       </c>
       <c r="D4">
-        <v>13268.53256060938</v>
+        <v>13275.33473589447</v>
       </c>
       <c r="E4">
         <v>-6805.432</v>
@@ -1615,37 +1615,37 @@
         <v>1971.45</v>
       </c>
       <c r="M4">
-        <v>18.5811634522192</v>
+        <v>18.1481882522192</v>
       </c>
       <c r="N4">
-        <v>1952.868836547781</v>
+        <v>1953.301811747781</v>
       </c>
       <c r="O4">
-        <v>527.2745858679008</v>
+        <v>527.3914891719008</v>
       </c>
       <c r="P4">
-        <v>1425.59425067988</v>
+        <v>1425.91032257588</v>
       </c>
       <c r="Q4">
-        <v>2248.89425067988</v>
+        <v>2249.21032257588</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09038196887696651</v>
+        <v>0.09036371008380567</v>
       </c>
       <c r="T4">
         <v>0.8162000003134525</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0.27</v>
       </c>
       <c r="W4">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.0993841999998</v>
+        <v>108.6306783135185</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08931350136496743</v>
+        <v>0.08926499632274192</v>
       </c>
       <c r="C5">
-        <v>14856.91452022903</v>
+        <v>14866.89187440046</v>
       </c>
       <c r="D5">
-        <v>13310.61652022903</v>
+        <v>13320.59387440046</v>
       </c>
       <c r="E5">
         <v>-6650.798</v>
@@ -1697,37 +1697,37 @@
         <v>1971.45</v>
       </c>
       <c r="M5">
-        <v>27.87174517832879</v>
+        <v>27.2222823783288</v>
       </c>
       <c r="N5">
-        <v>1943.578254821671</v>
+        <v>1944.227717621671</v>
       </c>
       <c r="O5">
-        <v>524.7661288018512</v>
+        <v>524.9414837578512</v>
       </c>
       <c r="P5">
-        <v>1418.81212601982</v>
+        <v>1419.28623386382</v>
       </c>
       <c r="Q5">
-        <v>2242.11212601982</v>
+        <v>2242.58623386382</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09071930427450689</v>
+        <v>0.09070090732375893</v>
       </c>
       <c r="T5">
         <v>0.8223758861819758</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0.27</v>
       </c>
       <c r="W5">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.73292279999988</v>
+        <v>72.42045220901235</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08917548908471055</v>
+        <v>0.08911681261755711</v>
       </c>
       <c r="C6">
-        <v>14744.6322856234</v>
+        <v>14757.82666943158</v>
       </c>
       <c r="D6">
-        <v>13352.9682856234</v>
+        <v>13366.16266943158</v>
       </c>
       <c r="E6">
         <v>-6496.164</v>
@@ -1779,37 +1779,37 @@
         <v>1971.45</v>
       </c>
       <c r="M6">
-        <v>37.16232690443839</v>
+        <v>36.29637650443839</v>
       </c>
       <c r="N6">
-        <v>1934.287673095561</v>
+        <v>1935.153623495562</v>
       </c>
       <c r="O6">
-        <v>522.2576717358016</v>
+        <v>522.4914783438016</v>
       </c>
       <c r="P6">
-        <v>1412.03000135976</v>
+        <v>1412.66214515176</v>
       </c>
       <c r="Q6">
-        <v>2235.33000135976</v>
+        <v>2235.96214515176</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09106366749282938</v>
+        <v>0.09104512950621121</v>
       </c>
       <c r="T6">
         <v>0.8286804363394266</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0.27</v>
       </c>
       <c r="W6">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.04969209999992</v>
+        <v>54.31533915675927</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08903747680445363</v>
+        <v>0.08896862891237228</v>
       </c>
       <c r="C7">
-        <v>14632.62042126817</v>
+        <v>14649.07430983484</v>
       </c>
       <c r="D7">
-        <v>13395.59042126817</v>
+        <v>13412.04430983484</v>
       </c>
       <c r="E7">
         <v>-6341.53</v>
@@ -1861,37 +1861,37 @@
         <v>1971.45</v>
       </c>
       <c r="M7">
-        <v>46.45290863054799</v>
+        <v>45.37047063054799</v>
       </c>
       <c r="N7">
-        <v>1924.997091369452</v>
+        <v>1926.079529369452</v>
       </c>
       <c r="O7">
-        <v>519.7492146697521</v>
+        <v>520.041472929752</v>
       </c>
       <c r="P7">
-        <v>1405.2478766997</v>
+        <v>1406.0380564397</v>
       </c>
       <c r="Q7">
-        <v>2228.5478766997</v>
+        <v>2229.3380564397</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09141528046311653</v>
+        <v>0.09139659847145196</v>
       </c>
       <c r="T7">
         <v>0.8351177138686131</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.43975367999994</v>
+        <v>43.45227132540742</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08889946452419674</v>
+        <v>0.08882044520718747</v>
       </c>
       <c r="C8">
-        <v>14520.88152448665</v>
+        <v>14540.63802839314</v>
       </c>
       <c r="D8">
-        <v>13438.48552448665</v>
+        <v>13458.24202839314</v>
       </c>
       <c r="E8">
         <v>-6186.896</v>
@@ -1943,37 +1943,37 @@
         <v>1971.45</v>
       </c>
       <c r="M8">
-        <v>55.74349035665759</v>
+        <v>54.44456475665759</v>
       </c>
       <c r="N8">
-        <v>1915.706509643342</v>
+        <v>1917.005435243342</v>
       </c>
       <c r="O8">
-        <v>517.2407576037025</v>
+        <v>517.5914675157024</v>
       </c>
       <c r="P8">
-        <v>1398.46575203964</v>
+        <v>1399.41396772764</v>
       </c>
       <c r="Q8">
-        <v>2221.76575203964</v>
+        <v>2222.71396772764</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09177437456043108</v>
+        <v>0.09175554549978293</v>
       </c>
       <c r="T8">
         <v>0.8416919547494847</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.36646139999995</v>
+        <v>36.21022610450618</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08876145224393982</v>
+        <v>0.08867226150200265</v>
       </c>
       <c r="C9">
-        <v>14409.41822597744</v>
+        <v>14432.52110258453</v>
       </c>
       <c r="D9">
-        <v>13481.65622597744</v>
+        <v>13504.75910258453</v>
       </c>
       <c r="E9">
         <v>-6032.262</v>
@@ -2025,37 +2025,37 @@
         <v>1971.45</v>
       </c>
       <c r="M9">
-        <v>65.03407208276718</v>
+        <v>63.51865888276718</v>
       </c>
       <c r="N9">
-        <v>1906.415927917233</v>
+        <v>1907.931341117233</v>
       </c>
       <c r="O9">
-        <v>514.7323005376528</v>
+        <v>515.1414621016529</v>
       </c>
       <c r="P9">
-        <v>1391.68362737958</v>
+        <v>1392.78987901558</v>
       </c>
       <c r="Q9">
-        <v>2214.98362737958</v>
+        <v>2216.08987901558</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0921411911114513</v>
+        <v>0.09212221181904576</v>
       </c>
       <c r="T9">
         <v>0.8484075771546757</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0.27</v>
       </c>
       <c r="W9">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.31410977142853</v>
+        <v>31.0373366610053</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08862343996368292</v>
+        <v>0.08852407779681785</v>
       </c>
       <c r="C10">
-        <v>14298.2331903522</v>
+        <v>14324.72685535733</v>
       </c>
       <c r="D10">
-        <v>13525.1051903522</v>
+        <v>13551.59885535733</v>
       </c>
       <c r="E10">
         <v>-5877.628</v>
@@ -2107,37 +2107,37 @@
         <v>1971.45</v>
       </c>
       <c r="M10">
-        <v>74.32465380887679</v>
+        <v>72.59275300887678</v>
       </c>
       <c r="N10">
-        <v>1897.125346191123</v>
+        <v>1898.857246991123</v>
       </c>
       <c r="O10">
-        <v>512.2238434716032</v>
+        <v>512.6914566876032</v>
       </c>
       <c r="P10">
-        <v>1384.90150271952</v>
+        <v>1386.16579030352</v>
       </c>
       <c r="Q10">
-        <v>2208.20150271952</v>
+        <v>2209.46579030352</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09251598193531982</v>
+        <v>0.09249684914524908</v>
       </c>
       <c r="T10">
         <v>0.8552691913512842</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.52484604999996</v>
+        <v>27.15766957837964</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08848542768342602</v>
+        <v>0.08837589409163303</v>
       </c>
       <c r="C11">
-        <v>14187.32911668394</v>
+        <v>14217.25865592146</v>
       </c>
       <c r="D11">
-        <v>13568.83511668394</v>
+        <v>13598.76465592146</v>
       </c>
       <c r="E11">
         <v>-5722.994</v>
@@ -2189,37 +2189,37 @@
         <v>1971.45</v>
       </c>
       <c r="M11">
-        <v>83.61523553498638</v>
+        <v>81.66684713498638</v>
       </c>
       <c r="N11">
-        <v>1887.834764465013</v>
+        <v>1889.783152865013</v>
       </c>
       <c r="O11">
-        <v>509.7153864055537</v>
+        <v>510.2414512735537</v>
       </c>
       <c r="P11">
-        <v>1378.11937805946</v>
+        <v>1379.54170159146</v>
       </c>
       <c r="Q11">
-        <v>2201.41937805946</v>
+        <v>2202.84170159146</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09289900992015246</v>
+        <v>0.09287972025884149</v>
       </c>
       <c r="T11">
         <v>0.8622816102555104</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.5776409333333</v>
+        <v>24.14015073633745</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08834741540316911</v>
+        <v>0.08822771038644821</v>
       </c>
       <c r="C12">
-        <v>14076.70873906591</v>
+        <v>14110.11992055621</v>
       </c>
       <c r="D12">
-        <v>13612.84873906591</v>
+        <v>13646.25992055621</v>
       </c>
       <c r="E12">
         <v>-5568.36</v>
@@ -2271,37 +2271,37 @@
         <v>1971.45</v>
       </c>
       <c r="M12">
-        <v>92.90581726109598</v>
+        <v>90.74094126109598</v>
       </c>
       <c r="N12">
-        <v>1878.544182738904</v>
+        <v>1880.709058738904</v>
       </c>
       <c r="O12">
-        <v>507.2069293395041</v>
+        <v>507.7914458595041</v>
       </c>
       <c r="P12">
-        <v>1371.3372533994</v>
+        <v>1372.9176128794</v>
       </c>
       <c r="Q12">
-        <v>2194.6372533994</v>
+        <v>2196.2176128794</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09329054963798138</v>
+        <v>0.09327109961940261</v>
       </c>
       <c r="T12">
         <v>0.8694498606909417</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.21987683999997</v>
+        <v>21.72613566270371</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0882094031229122</v>
+        <v>0.08807952668126341</v>
       </c>
       <c r="C13">
-        <v>13966.37482718141</v>
+        <v>14003.31411343517</v>
       </c>
       <c r="D13">
-        <v>13657.14882718141</v>
+        <v>13694.08811343517</v>
       </c>
       <c r="E13">
         <v>-5413.726</v>
@@ -2353,37 +2353,37 @@
         <v>1971.45</v>
       </c>
       <c r="M13">
-        <v>102.1963989872056</v>
+        <v>99.81503538720558</v>
       </c>
       <c r="N13">
-        <v>1869.253601012794</v>
+        <v>1871.634964612794</v>
       </c>
       <c r="O13">
-        <v>504.6984722734545</v>
+        <v>505.3414404454545</v>
       </c>
       <c r="P13">
-        <v>1364.55512873934</v>
+        <v>1366.29352416734</v>
       </c>
       <c r="Q13">
-        <v>2187.85512873934</v>
+        <v>2189.59352416734</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09369088800115477</v>
+        <v>0.09367127402177411</v>
       </c>
       <c r="T13">
         <v>0.8767791954058208</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.2907971272727</v>
+        <v>19.75103242063973</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08807139084265531</v>
+        <v>0.0879313429760786</v>
       </c>
       <c r="C14">
-        <v>13856.33018688483</v>
+        <v>13896.84474746851</v>
       </c>
       <c r="D14">
-        <v>13701.73818688483</v>
+        <v>13742.25274746851</v>
       </c>
       <c r="E14">
         <v>-5259.092</v>
@@ -2435,37 +2435,37 @@
         <v>1971.45</v>
       </c>
       <c r="M14">
-        <v>111.4869807133152</v>
+        <v>108.8891295133152</v>
       </c>
       <c r="N14">
-        <v>1859.963019286685</v>
+        <v>1862.560870486685</v>
       </c>
       <c r="O14">
-        <v>502.1900152074049</v>
+        <v>502.8914350314049</v>
       </c>
       <c r="P14">
-        <v>1357.77300407928</v>
+        <v>1359.66943545528</v>
       </c>
       <c r="Q14">
-        <v>2181.07300407928</v>
+        <v>2182.96943545528</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0941003249634912</v>
+        <v>0.09408054329692678</v>
       </c>
       <c r="T14">
         <v>0.8842751059096745</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.68323069999997</v>
+        <v>18.10511305225309</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08793337856239838</v>
+        <v>0.08778315927089378</v>
       </c>
       <c r="C15">
-        <v>13746.57766079404</v>
+        <v>13790.71538516304</v>
       </c>
       <c r="D15">
-        <v>13746.61966079404</v>
+        <v>13790.75738516304</v>
       </c>
       <c r="E15">
         <v>-5104.458</v>
@@ -2517,37 +2517,37 @@
         <v>1971.45</v>
       </c>
       <c r="M15">
-        <v>120.7775624394248</v>
+        <v>117.9632236394248</v>
       </c>
       <c r="N15">
-        <v>1850.672437560575</v>
+        <v>1853.486776360575</v>
       </c>
       <c r="O15">
-        <v>499.6815581413553</v>
+        <v>500.4414296173553</v>
       </c>
       <c r="P15">
-        <v>1350.99087941922</v>
+        <v>1353.04534674322</v>
       </c>
       <c r="Q15">
-        <v>2174.29087941922</v>
+        <v>2176.34534674322</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09451917426978937</v>
+        <v>0.0944992210611634</v>
       </c>
       <c r="T15">
         <v>0.8919433361952258</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.32298218461536</v>
+        <v>16.71241204823362</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08779536628214148</v>
+        <v>0.08763497556570896</v>
       </c>
       <c r="C16">
-        <v>13637.12012889446</v>
+        <v>13684.92963950058</v>
       </c>
       <c r="D16">
-        <v>13791.79612889446</v>
+        <v>13839.60563950058</v>
       </c>
       <c r="E16">
         <v>-4949.824</v>
@@ -2599,37 +2599,37 @@
         <v>1971.45</v>
       </c>
       <c r="M16">
-        <v>130.0681441655344</v>
+        <v>127.0373177655344</v>
       </c>
       <c r="N16">
-        <v>1841.381855834466</v>
+        <v>1844.412682234465</v>
       </c>
       <c r="O16">
-        <v>497.1731010753057</v>
+        <v>497.9914242033057</v>
       </c>
       <c r="P16">
-        <v>1344.20875475916</v>
+        <v>1346.42125803116</v>
       </c>
       <c r="Q16">
-        <v>2167.50875475916</v>
+        <v>2169.72125803116</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09494776425762938</v>
+        <v>0.09492763551759158</v>
       </c>
       <c r="T16">
         <v>0.8997898974176506</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.15705488571427</v>
+        <v>15.51866833050265</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08765735400188458</v>
+        <v>0.08748679186052416</v>
       </c>
       <c r="C17">
-        <v>13527.96050915513</v>
+        <v>13579.49117483511</v>
       </c>
       <c r="D17">
-        <v>13837.27050915513</v>
+        <v>13888.80117483511</v>
       </c>
       <c r="E17">
         <v>-4795.19</v>
@@ -2681,37 +2681,37 @@
         <v>1971.45</v>
       </c>
       <c r="M17">
-        <v>139.358725891644</v>
+        <v>136.111411891644</v>
       </c>
       <c r="N17">
-        <v>1832.091274108356</v>
+        <v>1835.338588108356</v>
       </c>
       <c r="O17">
-        <v>494.6646440092562</v>
+        <v>495.5414187892561</v>
       </c>
       <c r="P17">
-        <v>1337.4266300991</v>
+        <v>1339.7971693191</v>
       </c>
       <c r="Q17">
-        <v>2160.7266300991</v>
+        <v>2163.0971693191</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.0953864387157715</v>
+        <v>0.09536613031417102</v>
       </c>
       <c r="T17">
         <v>0.9078210836100148</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.14658455999998</v>
+        <v>14.48409044180247</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08751934172162767</v>
+        <v>0.08733860815533935</v>
       </c>
       <c r="C18">
-        <v>13419.10175815696</v>
+        <v>13474.4037078091</v>
       </c>
       <c r="D18">
-        <v>13883.04575815696</v>
+        <v>13938.34770780909</v>
       </c>
       <c r="E18">
         <v>-4640.556</v>
@@ -2763,37 +2763,37 @@
         <v>1971.45</v>
       </c>
       <c r="M18">
-        <v>148.6493076177536</v>
+        <v>145.1855060177536</v>
       </c>
       <c r="N18">
-        <v>1822.800692382246</v>
+        <v>1826.264493982246</v>
       </c>
       <c r="O18">
-        <v>492.1561869432065</v>
+        <v>493.0914133752065</v>
       </c>
       <c r="P18">
-        <v>1330.64450543904</v>
+        <v>1333.17308060704</v>
       </c>
       <c r="Q18">
-        <v>2153.94450543904</v>
+        <v>2156.47308060704</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09583555780386939</v>
+        <v>0.09581506546304995</v>
       </c>
       <c r="T18">
         <v>0.9160434885212447</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.26242302499998</v>
+        <v>13.57883478918982</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08738132944137075</v>
+        <v>0.08719042445015453</v>
       </c>
       <c r="C19">
-        <v>13310.54687173355</v>
+        <v>13369.67100828948</v>
       </c>
       <c r="D19">
-        <v>13929.12487173355</v>
+        <v>13988.24900828947</v>
       </c>
       <c r="E19">
         <v>-4485.922</v>
@@ -2845,37 +2845,37 @@
         <v>1971.45</v>
       </c>
       <c r="M19">
-        <v>157.9398893438632</v>
+        <v>154.2596001438632</v>
       </c>
       <c r="N19">
-        <v>1813.510110656137</v>
+        <v>1817.190399856137</v>
       </c>
       <c r="O19">
-        <v>489.647729877157</v>
+        <v>490.6414079611569</v>
       </c>
       <c r="P19">
-        <v>1323.86238077898</v>
+        <v>1326.54899189498</v>
       </c>
       <c r="Q19">
-        <v>2147.16238077898</v>
+        <v>2149.84899189498</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09629549903866842</v>
+        <v>0.0962748183263597</v>
       </c>
       <c r="T19">
         <v>0.9244640236712994</v>
       </c>
       <c r="U19">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.48228049411763</v>
+        <v>12.78007980159042</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08724331716111386</v>
+        <v>0.08704224074496972</v>
       </c>
       <c r="C20">
-        <v>13202.29888562471</v>
+        <v>13265.29690032381</v>
       </c>
       <c r="D20">
-        <v>13975.51088562471</v>
+        <v>14038.50890032381</v>
       </c>
       <c r="E20">
         <v>-4331.288</v>
@@ -2927,37 +2927,37 @@
         <v>1971.45</v>
       </c>
       <c r="M20">
-        <v>167.2304710699728</v>
+        <v>163.3336942699728</v>
       </c>
       <c r="N20">
-        <v>1804.219528930027</v>
+        <v>1808.116305730027</v>
       </c>
       <c r="O20">
-        <v>487.1392728111073</v>
+        <v>488.1914025471073</v>
       </c>
       <c r="P20">
-        <v>1317.08025611892</v>
+        <v>1319.92490318292</v>
       </c>
       <c r="Q20">
-        <v>2140.38025611892</v>
+        <v>2143.22490318292</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09676665835236499</v>
+        <v>0.09674578467414043</v>
       </c>
       <c r="T20">
         <v>0.933089937727453</v>
       </c>
       <c r="U20">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.78882046666665</v>
+        <v>12.07007536816873</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08710530488085694</v>
+        <v>0.08689405703978491</v>
       </c>
       <c r="C21">
-        <v>13094.36087614321</v>
+        <v>13161.28526311719</v>
       </c>
       <c r="D21">
-        <v>14022.20687614321</v>
+        <v>14089.13126311719</v>
       </c>
       <c r="E21">
         <v>-4176.654</v>
@@ -3009,37 +3009,37 @@
         <v>1971.45</v>
       </c>
       <c r="M21">
-        <v>176.5210527960824</v>
+        <v>172.4077883960824</v>
       </c>
       <c r="N21">
-        <v>1794.928947203917</v>
+        <v>1799.042211603917</v>
       </c>
       <c r="O21">
-        <v>484.6308157450578</v>
+        <v>485.7413971330577</v>
       </c>
       <c r="P21">
-        <v>1310.29813145886</v>
+        <v>1313.30081447086</v>
       </c>
       <c r="Q21">
-        <v>2133.59813145886</v>
+        <v>2136.60081447086</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09724945122936271</v>
+        <v>0.09722837982063179</v>
       </c>
       <c r="T21">
         <v>0.9419288373158574</v>
       </c>
       <c r="U21">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.16835623157893</v>
+        <v>11.43480824352827</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08696729260060006</v>
+        <v>0.08674587333460011</v>
       </c>
       <c r="C22">
-        <v>12986.73596085484</v>
+        <v>13057.6400320303</v>
       </c>
       <c r="D22">
-        <v>14069.21596085484</v>
+        <v>14140.1200320303</v>
       </c>
       <c r="E22">
         <v>-4022.02</v>
@@ -3091,37 +3091,37 @@
         <v>1971.45</v>
       </c>
       <c r="M22">
-        <v>185.811634522192</v>
+        <v>181.481882522192</v>
       </c>
       <c r="N22">
-        <v>1785.638365477808</v>
+        <v>1789.968117477808</v>
       </c>
       <c r="O22">
-        <v>482.1223586790081</v>
+        <v>483.2913917190082</v>
       </c>
       <c r="P22">
-        <v>1303.5160067988</v>
+        <v>1306.6767257588</v>
       </c>
       <c r="Q22">
-        <v>2126.8160067988</v>
+        <v>2129.9767257588</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09774431392828539</v>
+        <v>0.09772303984578545</v>
       </c>
       <c r="T22">
         <v>0.950988709393972</v>
       </c>
       <c r="U22">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.60993841999998</v>
+        <v>10.86306783135185</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08682928032034315</v>
+        <v>0.08659768962941529</v>
       </c>
       <c r="C23">
-        <v>12879.42729927229</v>
+        <v>12954.36519959929</v>
       </c>
       <c r="D23">
-        <v>14116.54129927229</v>
+        <v>14191.47919959929</v>
       </c>
       <c r="E23">
         <v>-3867.386</v>
@@ -3173,37 +3173,37 @@
         <v>1971.45</v>
       </c>
       <c r="M23">
-        <v>195.1022162483015</v>
+        <v>190.5559766483016</v>
       </c>
       <c r="N23">
-        <v>1776.347783751698</v>
+        <v>1780.894023351698</v>
       </c>
       <c r="O23">
-        <v>479.6139016129586</v>
+        <v>480.8413863049586</v>
       </c>
       <c r="P23">
-        <v>1296.73388213874</v>
+        <v>1300.05263704674</v>
       </c>
       <c r="Q23">
-        <v>2120.03388213874</v>
+        <v>2123.35263704674</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09825170479680104</v>
+        <v>0.09823022290955058</v>
       </c>
       <c r="T23">
         <v>0.9602779453221653</v>
       </c>
       <c r="U23">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.10470325714284</v>
+        <v>10.34577888700177</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08669126804008623</v>
+        <v>0.08644950592423047</v>
       </c>
       <c r="C24">
-        <v>12772.43809356294</v>
+        <v>12851.4648165778</v>
       </c>
       <c r="D24">
-        <v>14164.18609356294</v>
+        <v>14243.2128165778</v>
       </c>
       <c r="E24">
         <v>-3712.751999999999</v>
@@ -3255,37 +3255,37 @@
         <v>1971.45</v>
       </c>
       <c r="M24">
-        <v>204.3927979744112</v>
+        <v>199.6300707744112</v>
       </c>
       <c r="N24">
-        <v>1767.057202025589</v>
+        <v>1771.819929225589</v>
       </c>
       <c r="O24">
-        <v>477.1054445469089</v>
+        <v>478.3913808909089</v>
       </c>
       <c r="P24">
-        <v>1289.95175747868</v>
+        <v>1293.42854833468</v>
       </c>
       <c r="Q24">
-        <v>2113.25175747868</v>
+        <v>2116.72854833468</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09877210568758632</v>
+        <v>0.0987504106672584</v>
       </c>
       <c r="T24">
         <v>0.9698053667869789</v>
       </c>
       <c r="U24">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.645398563636348</v>
+        <v>9.875516210319867</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08655325575982932</v>
+        <v>0.08630132221904566</v>
       </c>
       <c r="C25">
-        <v>12665.77158927116</v>
+        <v>12748.9429930021</v>
       </c>
       <c r="D25">
-        <v>14212.15358927116</v>
+        <v>14295.3249930021</v>
       </c>
       <c r="E25">
         <v>-3558.117999999999</v>
@@ -3337,37 +3337,37 @@
         <v>1971.45</v>
       </c>
       <c r="M25">
-        <v>213.6833797005208</v>
+        <v>208.7041649005208</v>
       </c>
       <c r="N25">
-        <v>1757.766620299479</v>
+        <v>1762.745835099479</v>
       </c>
       <c r="O25">
-        <v>474.5969874808594</v>
+        <v>475.9413754768594</v>
       </c>
       <c r="P25">
-        <v>1283.16963281862</v>
+        <v>1286.80445962262</v>
       </c>
       <c r="Q25">
-        <v>2106.46963281862</v>
+        <v>2110.10445962262</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09930602348462575</v>
+        <v>0.09928410979529631</v>
       </c>
       <c r="T25">
         <v>0.9795802537443851</v>
       </c>
       <c r="U25">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.226033408695637</v>
+        <v>9.446145940305961</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08641524347957243</v>
+        <v>0.08615313851386083</v>
       </c>
       <c r="C26">
-        <v>12559.43107605533</v>
+        <v>12646.8038992795</v>
       </c>
       <c r="D26">
-        <v>14260.44707605533</v>
+        <v>14347.8198992795</v>
       </c>
       <c r="E26">
         <v>-3403.483999999999</v>
@@ -3419,37 +3419,37 @@
         <v>1971.45</v>
       </c>
       <c r="M26">
-        <v>222.9739614266304</v>
+        <v>217.7782590266304</v>
       </c>
       <c r="N26">
-        <v>1748.476038573369</v>
+        <v>1753.671740973369</v>
       </c>
       <c r="O26">
-        <v>472.0885304148098</v>
+        <v>473.4913700628098</v>
       </c>
       <c r="P26">
-        <v>1276.38750815856</v>
+        <v>1280.18037091056</v>
       </c>
       <c r="Q26">
-        <v>2099.687508158559</v>
+        <v>2103.48037091056</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09985399175000834</v>
+        <v>0.09983185363722993</v>
       </c>
       <c r="T26">
         <v>0.9896123745690915</v>
       </c>
       <c r="U26">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.841615349999987</v>
+        <v>9.052556526126544</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.0864779811993155</v>
+        <v>0.08627870480867603</v>
       </c>
       <c r="C27">
-        <v>12382.80316422168</v>
+        <v>12447.662482554</v>
       </c>
       <c r="D27">
-        <v>14238.45316422168</v>
+        <v>14303.312482554</v>
       </c>
       <c r="E27">
         <v>-3248.849999999999</v>
@@ -3501,37 +3501,37 @@
         <v>1971.45</v>
       </c>
       <c r="M27">
-        <v>236.5169781527399</v>
+        <v>232.6511281527399</v>
       </c>
       <c r="N27">
-        <v>1734.93302184726</v>
+        <v>1738.79887184726</v>
       </c>
       <c r="O27">
-        <v>468.4319158987602</v>
+        <v>469.4756953987602</v>
       </c>
       <c r="P27">
-        <v>1266.5011059485</v>
+        <v>1269.323176448499</v>
       </c>
       <c r="Q27">
-        <v>2089.8011059485</v>
+        <v>2092.6231764485</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1004165725024678</v>
+        <v>0.1003942039816151</v>
       </c>
       <c r="T27">
         <v>0.9999120186157902</v>
       </c>
       <c r="U27">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.335342415574328</v>
+        <v>8.473846723432628</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08634799891905862</v>
+        <v>0.08614147110349121</v>
       </c>
       <c r="C28">
-        <v>12273.81251676568</v>
+        <v>12341.6855224364</v>
       </c>
       <c r="D28">
-        <v>14284.09651676568</v>
+        <v>14351.96952243639</v>
       </c>
       <c r="E28">
         <v>-3094.215999999999</v>
@@ -3583,37 +3583,37 @@
         <v>1971.45</v>
       </c>
       <c r="M28">
-        <v>245.9776572788495</v>
+        <v>241.9571732788495</v>
       </c>
       <c r="N28">
-        <v>1725.47234272115</v>
+        <v>1729.49282672115</v>
       </c>
       <c r="O28">
-        <v>465.8775325347106</v>
+        <v>466.9630632147106</v>
       </c>
       <c r="P28">
-        <v>1259.59481018644</v>
+        <v>1262.52976350644</v>
       </c>
       <c r="Q28">
-        <v>2082.89481018644</v>
+        <v>2085.82976350644</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1009943581401289</v>
+        <v>0.1009717529839567</v>
       </c>
       <c r="T28">
         <v>1.010490031420507</v>
       </c>
       <c r="U28">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.014752322667622</v>
+        <v>8.147929541762142</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.0862180166388017</v>
+        <v>0.08600423739830639</v>
       </c>
       <c r="C29">
-        <v>12165.11544269778</v>
+        <v>12236.04073555717</v>
       </c>
       <c r="D29">
-        <v>14330.03344269778</v>
+        <v>14400.95873555717</v>
       </c>
       <c r="E29">
         <v>-2939.581999999999</v>
@@ -3665,37 +3665,37 @@
         <v>1971.45</v>
       </c>
       <c r="M29">
-        <v>255.4383364049591</v>
+        <v>251.2632184049591</v>
       </c>
       <c r="N29">
-        <v>1716.011663595041</v>
+        <v>1720.186781595041</v>
       </c>
       <c r="O29">
-        <v>463.3231491706611</v>
+        <v>464.450431030661</v>
       </c>
       <c r="P29">
-        <v>1252.68851442438</v>
+        <v>1255.73635056438</v>
       </c>
       <c r="Q29">
-        <v>2075.98851442438</v>
+        <v>2079.03635056438</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1015879735212875</v>
+        <v>0.1015651252466364</v>
       </c>
       <c r="T29">
         <v>1.021357852795217</v>
       </c>
       <c r="U29">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.717909644050303</v>
+        <v>7.84615437354873</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08608803435854478</v>
+        <v>0.08586700369312159</v>
       </c>
       <c r="C30">
-        <v>12056.71478350719</v>
+        <v>12130.73153510121</v>
       </c>
       <c r="D30">
-        <v>14376.26678350719</v>
+        <v>14450.28353510122</v>
       </c>
       <c r="E30">
         <v>-2784.947999999999</v>
@@ -3747,37 +3747,37 @@
         <v>1971.45</v>
       </c>
       <c r="M30">
-        <v>264.8990155310688</v>
+        <v>260.5692635310687</v>
       </c>
       <c r="N30">
-        <v>1706.550984468931</v>
+        <v>1710.880736468931</v>
       </c>
       <c r="O30">
-        <v>460.7687658066114</v>
+        <v>461.9377988466114</v>
       </c>
       <c r="P30">
-        <v>1245.78221866232</v>
+        <v>1248.94293762232</v>
       </c>
       <c r="Q30">
-        <v>2069.08221866232</v>
+        <v>2072.24293762232</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1021980782185894</v>
+        <v>0.1021749800721683</v>
       </c>
       <c r="T30">
         <v>1.032527558097002</v>
       </c>
       <c r="U30">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.44227001390565</v>
+        <v>7.565934574493419</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08595805207828787</v>
+        <v>0.08572976998793677</v>
       </c>
       <c r="C31">
-        <v>11948.61341747208</v>
+        <v>12025.76138117627</v>
       </c>
       <c r="D31">
-        <v>14422.79941747208</v>
+        <v>14499.94738117627</v>
       </c>
       <c r="E31">
         <v>-2630.313999999999</v>
@@ -3829,37 +3829,37 @@
         <v>1971.45</v>
       </c>
       <c r="M31">
-        <v>274.3596946571784</v>
+        <v>269.8753086571783</v>
       </c>
       <c r="N31">
-        <v>1697.090305342821</v>
+        <v>1701.574691342822</v>
       </c>
       <c r="O31">
-        <v>458.2143824425618</v>
+        <v>459.4251666625618</v>
       </c>
       <c r="P31">
-        <v>1238.87592290026</v>
+        <v>1242.14952468026</v>
       </c>
       <c r="Q31">
-        <v>2062.17592290026</v>
+        <v>2065.44952468026</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1028253689637026</v>
+        <v>0.1028020139068701</v>
       </c>
       <c r="T31">
         <v>1.044011902984753</v>
       </c>
       <c r="U31">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.185640013426144</v>
+        <v>7.305040278821232</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08582806979803097</v>
+        <v>0.08559253628275193</v>
       </c>
       <c r="C32">
-        <v>11840.81426025691</v>
+        <v>11921.13378162193</v>
       </c>
       <c r="D32">
-        <v>14469.63426025691</v>
+        <v>14549.95378162193</v>
       </c>
       <c r="E32">
         <v>-2475.679999999999</v>
@@ -3911,37 +3911,37 @@
         <v>1971.45</v>
       </c>
       <c r="M32">
-        <v>283.8203737832879</v>
+        <v>279.1813537832879</v>
       </c>
       <c r="N32">
-        <v>1687.629626216712</v>
+        <v>1692.268646216712</v>
       </c>
       <c r="O32">
-        <v>455.6599990785122</v>
+        <v>456.9125344785122</v>
       </c>
       <c r="P32">
-        <v>1231.969627138199</v>
+        <v>1235.3561117382</v>
       </c>
       <c r="Q32">
-        <v>2055.2696271382</v>
+        <v>2058.6561117382</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1034705823015334</v>
+        <v>0.1034469629939919</v>
       </c>
       <c r="T32">
         <v>1.055824372012154</v>
       </c>
       <c r="U32">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.946118679645273</v>
+        <v>7.061538936193856</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08619594751777407</v>
+        <v>0.08545530257756714</v>
       </c>
       <c r="C33">
-        <v>11554.40822904418</v>
+        <v>11816.85229283563</v>
       </c>
       <c r="D33">
-        <v>14337.86222904418</v>
+        <v>14600.30629283563</v>
       </c>
       <c r="E33">
         <v>-2321.045999999999</v>
@@ -3993,45 +3993,45 @@
         <v>1971.45</v>
       </c>
       <c r="M33">
-        <v>303.8270917093975</v>
+        <v>288.4873989093975</v>
       </c>
       <c r="N33">
-        <v>1667.622908290602</v>
+        <v>1682.962601090602</v>
       </c>
       <c r="O33">
-        <v>450.2581852384627</v>
+        <v>454.3999022944626</v>
       </c>
       <c r="P33">
-        <v>1217.36472305214</v>
+        <v>1228.56269879614</v>
       </c>
       <c r="Q33">
-        <v>2040.66472305214</v>
+        <v>2051.86269879614</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1041344974752433</v>
+        <v>0.1041106062575521</v>
       </c>
       <c r="T33">
         <v>1.067979231446146</v>
       </c>
       <c r="U33">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.04626820728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.488723533204995</v>
+        <v>6.833747357606958</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08608202523751717</v>
+        <v>0.08571518887238232</v>
       </c>
       <c r="C34">
-        <v>11440.32338091802</v>
+        <v>11567.15624721326</v>
       </c>
       <c r="D34">
-        <v>14378.41138091803</v>
+        <v>14505.24424721326</v>
       </c>
       <c r="E34">
         <v>-2166.411999999999</v>
@@ -4075,37 +4075,37 @@
         <v>1971.45</v>
       </c>
       <c r="M34">
-        <v>313.6279656355071</v>
+        <v>306.2055336355071</v>
       </c>
       <c r="N34">
-        <v>1657.822034364493</v>
+        <v>1665.244466364493</v>
       </c>
       <c r="O34">
-        <v>447.6119492784131</v>
+        <v>449.6160059184131</v>
       </c>
       <c r="P34">
-        <v>1210.21008508608</v>
+        <v>1215.62846044608</v>
       </c>
       <c r="Q34">
-        <v>2033.51008508608</v>
+        <v>2038.92846044608</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1048179395658271</v>
+        <v>0.1047937684406287</v>
       </c>
       <c r="T34">
         <v>1.080491586745843</v>
       </c>
       <c r="U34">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.285950922792339</v>
+        <v>6.438322575668155</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08596810295726026</v>
+        <v>0.08559036516719751</v>
       </c>
       <c r="C35">
-        <v>11326.46853876695</v>
+        <v>11458.02568313147</v>
       </c>
       <c r="D35">
-        <v>14419.19053876695</v>
+        <v>14550.74768313148</v>
       </c>
       <c r="E35">
         <v>-2011.777999999999</v>
@@ -4157,37 +4157,37 @@
         <v>1971.45</v>
       </c>
       <c r="M35">
-        <v>323.4288395616167</v>
+        <v>315.7744565616167</v>
       </c>
       <c r="N35">
-        <v>1648.021160438383</v>
+        <v>1655.675543438383</v>
       </c>
       <c r="O35">
-        <v>444.9657133183634</v>
+        <v>447.0323967283635</v>
       </c>
       <c r="P35">
-        <v>1203.05544712002</v>
+        <v>1208.64314671002</v>
       </c>
       <c r="Q35">
-        <v>2026.35544712002</v>
+        <v>2031.94314671002</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1055217829128461</v>
+        <v>0.1054973235246928</v>
       </c>
       <c r="T35">
         <v>1.093377445188816</v>
       </c>
       <c r="U35">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.095467561495601</v>
+        <v>6.243221891556998</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08585418067700336</v>
+        <v>0.08546554146201268</v>
       </c>
       <c r="C36">
-        <v>11212.84566514303</v>
+        <v>11349.18150906282</v>
       </c>
       <c r="D36">
-        <v>14460.20166514303</v>
+        <v>14596.53750906282</v>
       </c>
       <c r="E36">
         <v>-1857.143999999999</v>
@@ -4239,37 +4239,37 @@
         <v>1971.45</v>
       </c>
       <c r="M36">
-        <v>333.2297134877263</v>
+        <v>325.3433794877263</v>
       </c>
       <c r="N36">
-        <v>1638.220286512274</v>
+        <v>1646.106620512274</v>
       </c>
       <c r="O36">
-        <v>442.3194773583139</v>
+        <v>444.4487875383139</v>
       </c>
       <c r="P36">
-        <v>1195.90080915396</v>
+        <v>1201.65783297396</v>
       </c>
       <c r="Q36">
-        <v>2019.20080915396</v>
+        <v>2024.95783297396</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1062469548461385</v>
+        <v>0.106222198459789</v>
       </c>
       <c r="T36">
         <v>1.106653784190666</v>
       </c>
       <c r="U36">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.916189103804554</v>
+        <v>6.059597718275911</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08574025839674644</v>
+        <v>0.08534071775682787</v>
       </c>
       <c r="C37">
-        <v>11099.45674498964</v>
+        <v>11240.62643726931</v>
       </c>
       <c r="D37">
-        <v>14501.44674498964</v>
+        <v>14642.61643726931</v>
       </c>
       <c r="E37">
         <v>-1702.509999999998</v>
@@ -4321,37 +4321,37 @@
         <v>1971.45</v>
       </c>
       <c r="M37">
-        <v>343.030587413836</v>
+        <v>334.912302413836</v>
       </c>
       <c r="N37">
-        <v>1628.419412586164</v>
+        <v>1636.537697586164</v>
       </c>
       <c r="O37">
-        <v>439.6732413982643</v>
+        <v>441.8651783482643</v>
       </c>
       <c r="P37">
-        <v>1188.7461711879</v>
+        <v>1194.672519237899</v>
       </c>
       <c r="Q37">
-        <v>2012.0461711879</v>
+        <v>2017.9725192379</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1069944397619937</v>
+        <v>0.1069693772390421</v>
       </c>
       <c r="T37">
         <v>1.120338625931035</v>
       </c>
       <c r="U37">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.747155129410137</v>
+        <v>5.886466354896597</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08602053611648955</v>
+        <v>0.08521589405164308</v>
       </c>
       <c r="C38">
-        <v>10843.76908387259</v>
+        <v>11132.36321437017</v>
       </c>
       <c r="D38">
-        <v>14400.39308387259</v>
+        <v>14688.98721437017</v>
       </c>
       <c r="E38">
         <v>-1547.875999999999</v>
@@ -4403,45 +4403,45 @@
         <v>1971.45</v>
       </c>
       <c r="M38">
-        <v>361.1816973399455</v>
+        <v>344.4812253399455</v>
       </c>
       <c r="N38">
-        <v>1610.268302660054</v>
+        <v>1626.968774660054</v>
       </c>
       <c r="O38">
-        <v>434.7724417182147</v>
+        <v>439.2815691582147</v>
       </c>
       <c r="P38">
-        <v>1175.49586094184</v>
+        <v>1187.68720550184</v>
       </c>
       <c r="Q38">
-        <v>1998.79586094184</v>
+        <v>2010.98720550184</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1077652835814694</v>
+        <v>0.1077399053551468</v>
       </c>
       <c r="T38">
         <v>1.13445111897579</v>
       </c>
       <c r="U38">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.04736320728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>5.458333062055645</v>
+        <v>5.722953400593915</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08591756383623264</v>
+        <v>0.08530715034645825</v>
       </c>
       <c r="C39">
-        <v>10726.09748065459</v>
+        <v>10943.79959565519</v>
       </c>
       <c r="D39">
-        <v>14437.35548065459</v>
+        <v>14655.05759565519</v>
       </c>
       <c r="E39">
         <v>-1393.241999999999</v>
@@ -4485,37 +4485,37 @@
         <v>1971.45</v>
       </c>
       <c r="M39">
-        <v>371.2145222660551</v>
+        <v>358.6273146660552</v>
       </c>
       <c r="N39">
-        <v>1600.235477733945</v>
+        <v>1612.822685333945</v>
       </c>
       <c r="O39">
-        <v>432.0635789881651</v>
+        <v>435.4621250401651</v>
       </c>
       <c r="P39">
-        <v>1168.17189874578</v>
+        <v>1177.36056029378</v>
       </c>
       <c r="Q39">
-        <v>1991.47189874578</v>
+        <v>2000.66056029378</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1085605986333094</v>
+        <v>0.1085348946812866</v>
       </c>
       <c r="T39">
         <v>1.14901162767276</v>
       </c>
       <c r="U39">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.310810546864952</v>
+        <v>5.497210946789608</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08581459155597572</v>
+        <v>0.08518816664127343</v>
       </c>
       <c r="C40">
-        <v>10608.61611315475</v>
+        <v>10833.4355681144</v>
       </c>
       <c r="D40">
-        <v>14474.50811315474</v>
+        <v>14699.3275681144</v>
       </c>
       <c r="E40">
         <v>-1238.607999999999</v>
@@ -4567,37 +4567,37 @@
         <v>1971.45</v>
       </c>
       <c r="M40">
-        <v>381.2473471921647</v>
+        <v>368.3199447921647</v>
       </c>
       <c r="N40">
-        <v>1590.202652807835</v>
+        <v>1603.130055207835</v>
       </c>
       <c r="O40">
-        <v>429.3547162581154</v>
+        <v>432.8451149061155</v>
       </c>
       <c r="P40">
-        <v>1160.84793654972</v>
+        <v>1170.28494030172</v>
       </c>
       <c r="Q40">
-        <v>1984.14793654972</v>
+        <v>1993.58494030172</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1093815690094023</v>
+        <v>0.1093555288243986</v>
       </c>
       <c r="T40">
         <v>1.164041830198664</v>
       </c>
       <c r="U40">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.171052374579031</v>
+        <v>5.352547500821461</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08571161927571883</v>
+        <v>0.08506918293608863</v>
       </c>
       <c r="C41">
-        <v>10491.32645380181</v>
+        <v>10723.3398122797</v>
       </c>
       <c r="D41">
-        <v>14511.85245380181</v>
+        <v>14743.8658122797</v>
       </c>
       <c r="E41">
         <v>-1083.973999999999</v>
@@ -4649,37 +4649,37 @@
         <v>1971.45</v>
       </c>
       <c r="M41">
-        <v>391.2801721182743</v>
+        <v>378.0125749182744</v>
       </c>
       <c r="N41">
-        <v>1580.169827881725</v>
+        <v>1593.437425081725</v>
       </c>
       <c r="O41">
-        <v>426.6458535280659</v>
+        <v>430.2281047720659</v>
       </c>
       <c r="P41">
-        <v>1153.523974353659</v>
+        <v>1163.20932030966</v>
       </c>
       <c r="Q41">
-        <v>1976.82397435366</v>
+        <v>1986.50932030966</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1102294564470065</v>
+        <v>0.1102030690049897</v>
       </c>
       <c r="T41">
         <v>1.179564826250008</v>
       </c>
       <c r="U41">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.038461288051364</v>
+        <v>5.215302693108089</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08560864699546192</v>
+        <v>0.08495019923090383</v>
       </c>
       <c r="C42">
-        <v>10374.22999025941</v>
+        <v>10613.51477411271</v>
       </c>
       <c r="D42">
-        <v>14549.38999025941</v>
+        <v>14788.67477411271</v>
       </c>
       <c r="E42">
         <v>-929.3399999999992</v>
@@ -4731,37 +4731,37 @@
         <v>1971.45</v>
       </c>
       <c r="M42">
-        <v>401.3129970443839</v>
+        <v>387.7052050443839</v>
       </c>
       <c r="N42">
-        <v>1570.137002955616</v>
+        <v>1583.744794955616</v>
       </c>
       <c r="O42">
-        <v>423.9369907980164</v>
+        <v>427.6110946380163</v>
       </c>
       <c r="P42">
-        <v>1146.2000121576</v>
+        <v>1156.1337003176</v>
       </c>
       <c r="Q42">
-        <v>1969.5000121576</v>
+        <v>1979.4337003176</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1111056067991974</v>
+        <v>0.1110788605249339</v>
       </c>
       <c r="T42">
         <v>1.195605255503063</v>
       </c>
       <c r="U42">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.91249975585008</v>
+        <v>5.084920125780387</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08550567471520502</v>
+        <v>0.08483121552571901</v>
       </c>
       <c r="C43">
-        <v>10257.32822562349</v>
+        <v>10503.96292940039</v>
       </c>
       <c r="D43">
-        <v>14587.12222562349</v>
+        <v>14833.75692940039</v>
       </c>
       <c r="E43">
         <v>-774.7059999999983</v>
@@ -4813,37 +4813,37 @@
         <v>1971.45</v>
       </c>
       <c r="M43">
-        <v>411.3458219704935</v>
+        <v>397.3978351704936</v>
       </c>
       <c r="N43">
-        <v>1560.104178029506</v>
+        <v>1574.052164829506</v>
       </c>
       <c r="O43">
-        <v>421.2281280679667</v>
+        <v>424.9940845039667</v>
       </c>
       <c r="P43">
-        <v>1138.87604996154</v>
+        <v>1149.05808032554</v>
       </c>
       <c r="Q43">
-        <v>1962.17604996154</v>
+        <v>1972.35808032554</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1120114571633271</v>
+        <v>0.1119843398930118</v>
       </c>
       <c r="T43">
         <v>1.212189428120628</v>
       </c>
       <c r="U43">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.792682688634224</v>
+        <v>4.960897683688183</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0854027024349481</v>
+        <v>0.0847122318205342</v>
       </c>
       <c r="C44">
-        <v>10140.62267862304</v>
+        <v>10394.68678421096</v>
       </c>
       <c r="D44">
-        <v>14625.05067862304</v>
+        <v>14879.11478421096</v>
       </c>
       <c r="E44">
         <v>-620.0719999999992</v>
@@ -4895,37 +4895,37 @@
         <v>1971.45</v>
       </c>
       <c r="M44">
-        <v>421.3786468966031</v>
+        <v>407.0904652966032</v>
       </c>
       <c r="N44">
-        <v>1550.071353103397</v>
+        <v>1564.359534703397</v>
       </c>
       <c r="O44">
-        <v>418.5192653379171</v>
+        <v>422.3770743699171</v>
       </c>
       <c r="P44">
-        <v>1131.552087765479</v>
+        <v>1141.98246033348</v>
       </c>
       <c r="Q44">
-        <v>1954.85208776548</v>
+        <v>1965.28246033348</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1129485437469094</v>
+        <v>0.1129210426875751</v>
       </c>
       <c r="T44">
         <v>1.229345468759489</v>
       </c>
       <c r="U44">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.678571196047695</v>
+        <v>4.842781072171798</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08529973015469121</v>
+        <v>0.08459324811534938</v>
       </c>
       <c r="C45">
-        <v>10024.11488382374</v>
+        <v>10285.68887535835</v>
       </c>
       <c r="D45">
-        <v>14663.17688382375</v>
+        <v>14924.75087535836</v>
       </c>
       <c r="E45">
         <v>-465.4379999999992</v>
@@ -4977,37 +4977,37 @@
         <v>1971.45</v>
       </c>
       <c r="M45">
-        <v>431.4114718227127</v>
+        <v>416.7830954227127</v>
       </c>
       <c r="N45">
-        <v>1540.038528177287</v>
+        <v>1554.666904577287</v>
       </c>
       <c r="O45">
-        <v>415.8104026078676</v>
+        <v>419.7600642358676</v>
       </c>
       <c r="P45">
-        <v>1124.22812556942</v>
+        <v>1134.90684034142</v>
       </c>
       <c r="Q45">
-        <v>1947.52812556942</v>
+        <v>1958.20684034142</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1139185105614947</v>
+        <v>0.1138906122468599</v>
       </c>
       <c r="T45">
         <v>1.247103475736555</v>
       </c>
       <c r="U45">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.56976721474426</v>
+        <v>4.730158256539896</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08519675787443429</v>
+        <v>0.08447426441016456</v>
       </c>
       <c r="C46">
-        <v>9907.806391835096</v>
+        <v>10176.97177087515</v>
       </c>
       <c r="D46">
-        <v>14701.5023918351</v>
+        <v>14970.66777087515</v>
       </c>
       <c r="E46">
         <v>-310.8039999999992</v>
@@ -5059,37 +5059,37 @@
         <v>1971.45</v>
       </c>
       <c r="M46">
-        <v>441.4442967488223</v>
+        <v>426.4757255488224</v>
       </c>
       <c r="N46">
-        <v>1530.005703251177</v>
+        <v>1544.974274451178</v>
       </c>
       <c r="O46">
-        <v>413.101539877818</v>
+        <v>417.1430541018179</v>
       </c>
       <c r="P46">
-        <v>1116.90416337336</v>
+        <v>1127.83122034936</v>
       </c>
       <c r="Q46">
-        <v>1940.20416337336</v>
+        <v>1951.13122034936</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1149231190480294</v>
+        <v>0.1148948092904049</v>
       </c>
       <c r="T46">
         <v>1.265495697248517</v>
       </c>
       <c r="U46">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.465908868954618</v>
+        <v>4.622654659800352</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08509378559417738</v>
+        <v>0.08435528070497975</v>
       </c>
       <c r="C47">
-        <v>9791.698769520475</v>
+        <v>10068.53807049427</v>
       </c>
       <c r="D47">
-        <v>14740.02876952048</v>
+        <v>15016.86807049428</v>
       </c>
       <c r="E47">
         <v>-156.1699999999992</v>
@@ -5141,37 +5141,37 @@
         <v>1971.45</v>
       </c>
       <c r="M47">
-        <v>451.4771216749319</v>
+        <v>436.1683556749319</v>
       </c>
       <c r="N47">
-        <v>1519.972878325068</v>
+        <v>1535.281644325068</v>
       </c>
       <c r="O47">
-        <v>410.3926771477684</v>
+        <v>414.5260439677684</v>
       </c>
       <c r="P47">
-        <v>1109.5802011773</v>
+        <v>1120.755600357299</v>
       </c>
       <c r="Q47">
-        <v>1932.8802011773</v>
+        <v>1944.0556003573</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1159642587522563</v>
+        <v>0.1159355225900788</v>
       </c>
       <c r="T47">
         <v>1.284556726815459</v>
       </c>
       <c r="U47">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.366666449644516</v>
+        <v>4.519929000693677</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08499081331392049</v>
+        <v>0.08423629699979496</v>
       </c>
       <c r="C48">
-        <v>9675.793600210771</v>
+        <v>9960.390406139675</v>
       </c>
       <c r="D48">
-        <v>14778.75760021077</v>
+        <v>15063.35440613968</v>
       </c>
       <c r="E48">
         <v>-1.535999999999149</v>
@@ -5223,37 +5223,37 @@
         <v>1971.45</v>
       </c>
       <c r="M48">
-        <v>461.5099466010415</v>
+        <v>445.8609858010415</v>
       </c>
       <c r="N48">
-        <v>1509.940053398958</v>
+        <v>1525.589014198958</v>
       </c>
       <c r="O48">
-        <v>407.6838144177188</v>
+        <v>411.9090338337188</v>
       </c>
       <c r="P48">
-        <v>1102.256238981239</v>
+        <v>1113.67998036524</v>
       </c>
       <c r="Q48">
-        <v>1925.55623898124</v>
+        <v>1936.97998036524</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1170439591862694</v>
+        <v>0.1170147808267777</v>
       </c>
       <c r="T48">
         <v>1.304323720440436</v>
       </c>
       <c r="U48">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.271738918130504</v>
+        <v>4.421669674591641</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08536818103366357</v>
+        <v>0.08411731329461013</v>
       </c>
       <c r="C49">
-        <v>9380.212356477668</v>
+        <v>9852.531442426125</v>
       </c>
       <c r="D49">
-        <v>14637.81035647767</v>
+        <v>15110.12944242613</v>
       </c>
       <c r="E49">
         <v>153.0980000000009</v>
@@ -5305,45 +5305,45 @@
         <v>1971.45</v>
       </c>
       <c r="M49">
-        <v>481.7176887271511</v>
+        <v>455.5536159271512</v>
       </c>
       <c r="N49">
-        <v>1489.732311272849</v>
+        <v>1515.896384072849</v>
       </c>
       <c r="O49">
-        <v>402.2277240436691</v>
+        <v>409.2920236996691</v>
       </c>
       <c r="P49">
-        <v>1087.504587229179</v>
+        <v>1106.60436037318</v>
       </c>
       <c r="Q49">
-        <v>1910.80458722918</v>
+        <v>1929.90436037318</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1181644030328868</v>
+        <v>0.1181347657893897</v>
       </c>
       <c r="T49">
         <v>1.324836638353148</v>
       </c>
       <c r="U49">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.04838520728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.092542263102665</v>
+        <v>4.327591596408841</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08527542875340667</v>
+        <v>0.0843487295894253</v>
       </c>
       <c r="C50">
-        <v>9259.971657105572</v>
+        <v>9607.188093324694</v>
       </c>
       <c r="D50">
-        <v>14672.20365710557</v>
+        <v>15019.42009332469</v>
       </c>
       <c r="E50">
         <v>307.7320000000009</v>
@@ -5387,37 +5387,37 @@
         <v>1971.45</v>
       </c>
       <c r="M50">
-        <v>491.9670012532607</v>
+        <v>472.6686780532607</v>
       </c>
       <c r="N50">
-        <v>1479.482998746739</v>
+        <v>1498.781321946739</v>
       </c>
       <c r="O50">
-        <v>399.4604096616196</v>
+        <v>404.6709569256196</v>
       </c>
       <c r="P50">
-        <v>1080.02258908512</v>
+        <v>1094.11036502112</v>
       </c>
       <c r="Q50">
-        <v>1903.32258908512</v>
+        <v>1917.41036502112</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1193279408736048</v>
+        <v>0.1192978270967176</v>
       </c>
       <c r="T50">
         <v>1.346138514647118</v>
       </c>
       <c r="U50">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.007280965954693</v>
+        <v>4.170891983195585</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08518267647314975</v>
+        <v>0.0842370458842405</v>
       </c>
       <c r="C51">
-        <v>9139.892960793941</v>
+        <v>9496.19492073899</v>
       </c>
       <c r="D51">
-        <v>14706.75896079394</v>
+        <v>15063.06092073899</v>
       </c>
       <c r="E51">
         <v>462.3660000000009</v>
@@ -5469,37 +5469,37 @@
         <v>1971.45</v>
       </c>
       <c r="M51">
-        <v>502.2163137793703</v>
+        <v>482.5159421793704</v>
       </c>
       <c r="N51">
-        <v>1469.23368622063</v>
+        <v>1488.93405782063</v>
       </c>
       <c r="O51">
-        <v>396.69309527957</v>
+        <v>402.01219561157</v>
       </c>
       <c r="P51">
-        <v>1072.54059094106</v>
+        <v>1086.92186220906</v>
       </c>
       <c r="Q51">
-        <v>1895.84059094106</v>
+        <v>1910.22186220906</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.120537107649253</v>
+        <v>0.1205064986513917</v>
       </c>
       <c r="T51">
         <v>1.368275758638891</v>
       </c>
       <c r="U51">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.925499721751535</v>
+        <v>4.085771738640572</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08508992419289285</v>
+        <v>0.08412536217905568</v>
       </c>
       <c r="C52">
-        <v>9019.977414871515</v>
+        <v>9385.456095093588</v>
       </c>
       <c r="D52">
-        <v>14741.47741487152</v>
+        <v>15106.95609509359</v>
       </c>
       <c r="E52">
         <v>617.0000000000009</v>
@@ -5551,37 +5551,37 @@
         <v>1971.45</v>
       </c>
       <c r="M52">
-        <v>512.4656263054799</v>
+        <v>492.3632063054799</v>
       </c>
       <c r="N52">
-        <v>1458.98437369452</v>
+        <v>1479.08679369452</v>
       </c>
       <c r="O52">
-        <v>393.9257808975204</v>
+        <v>399.3534342975204</v>
       </c>
       <c r="P52">
-        <v>1065.058592797</v>
+        <v>1079.733359397</v>
       </c>
       <c r="Q52">
-        <v>1888.358592797</v>
+        <v>1903.033359397</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.121794641095927</v>
+        <v>0.1217635170682527</v>
       </c>
       <c r="T52">
         <v>1.391298492390335</v>
       </c>
       <c r="U52">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.846989727316505</v>
+        <v>4.004056303867761</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08499717191263595</v>
+        <v>0.08401367847387087</v>
       </c>
       <c r="C53">
-        <v>8900.226177526749</v>
+        <v>9274.973846459734</v>
       </c>
       <c r="D53">
-        <v>14776.36017752675</v>
+        <v>15151.10784645974</v>
       </c>
       <c r="E53">
         <v>771.6340000000009</v>
@@ -5633,37 +5633,37 @@
         <v>1971.45</v>
       </c>
       <c r="M53">
-        <v>522.7149388315895</v>
+        <v>502.2104704315896</v>
       </c>
       <c r="N53">
-        <v>1448.73506116841</v>
+        <v>1469.23952956841</v>
       </c>
       <c r="O53">
-        <v>391.1584665154708</v>
+        <v>396.6946729834708</v>
       </c>
       <c r="P53">
-        <v>1057.57659465294</v>
+        <v>1072.544856584939</v>
       </c>
       <c r="Q53">
-        <v>1880.87659465294</v>
+        <v>1895.84485658494</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1231035024383837</v>
+        <v>0.1230718423592713</v>
       </c>
       <c r="T53">
         <v>1.415260929560205</v>
       </c>
       <c r="U53">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.771558556192651</v>
+        <v>3.925545395948785</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08490441963237905</v>
+        <v>0.08390199476868607</v>
       </c>
       <c r="C54">
-        <v>8780.640417936589</v>
+        <v>9164.750431055632</v>
       </c>
       <c r="D54">
-        <v>14811.40841793659</v>
+        <v>15195.51843105563</v>
       </c>
       <c r="E54">
         <v>926.2680000000009</v>
@@ -5715,37 +5715,37 @@
         <v>1971.45</v>
       </c>
       <c r="M54">
-        <v>532.964251357699</v>
+        <v>512.0577345576992</v>
       </c>
       <c r="N54">
-        <v>1438.485748642301</v>
+        <v>1459.392265442301</v>
       </c>
       <c r="O54">
-        <v>388.3911521334212</v>
+        <v>394.0359116694212</v>
       </c>
       <c r="P54">
-        <v>1050.094596508879</v>
+        <v>1065.356353772879</v>
       </c>
       <c r="Q54">
-        <v>1873.39459650888</v>
+        <v>1888.65635377288</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1244668996701095</v>
+        <v>0.1244346812040824</v>
       </c>
       <c r="T54">
         <v>1.440221801612154</v>
       </c>
       <c r="U54">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.699028583958178</v>
+        <v>3.850054138334385</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08481166735212213</v>
+        <v>0.08379031106350124</v>
       </c>
       <c r="C55">
-        <v>8661.221316397097</v>
+        <v>9054.788131630759</v>
       </c>
       <c r="D55">
-        <v>14846.6233163971</v>
+        <v>15240.19013163076</v>
       </c>
       <c r="E55">
         <v>1080.902000000001</v>
@@ -5797,37 +5797,37 @@
         <v>1971.45</v>
       </c>
       <c r="M55">
-        <v>543.2135638838087</v>
+        <v>521.9049986838087</v>
       </c>
       <c r="N55">
-        <v>1428.236436116191</v>
+        <v>1449.545001316191</v>
       </c>
       <c r="O55">
-        <v>385.6238377513717</v>
+        <v>391.3771503553717</v>
       </c>
       <c r="P55">
-        <v>1042.61259836482</v>
+        <v>1058.16785096082</v>
       </c>
       <c r="Q55">
-        <v>1865.91259836482</v>
+        <v>1881.46785096082</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1258883138053128</v>
+        <v>0.1258555131912258</v>
       </c>
       <c r="T55">
         <v>1.466244838432269</v>
       </c>
       <c r="U55">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.629235591808023</v>
+        <v>3.777411607422417</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08471891507186523</v>
+        <v>0.08367862735831644</v>
       </c>
       <c r="C56">
-        <v>8541.970064455934</v>
+        <v>8945.089257856966</v>
       </c>
       <c r="D56">
-        <v>14882.00606445594</v>
+        <v>15285.12525785697</v>
       </c>
       <c r="E56">
         <v>1235.536000000001</v>
@@ -5879,37 +5879,37 @@
         <v>1971.45</v>
       </c>
       <c r="M56">
-        <v>553.4628764099183</v>
+        <v>531.7522628099183</v>
       </c>
       <c r="N56">
-        <v>1417.987123590081</v>
+        <v>1439.697737190082</v>
       </c>
       <c r="O56">
-        <v>382.856523369322</v>
+        <v>388.718389041322</v>
       </c>
       <c r="P56">
-        <v>1035.130600220759</v>
+        <v>1050.97934814876</v>
       </c>
       <c r="Q56">
-        <v>1858.43060022076</v>
+        <v>1874.27934814876</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1273715285550903</v>
+        <v>0.1273381204821581</v>
       </c>
       <c r="T56">
         <v>1.493399311635869</v>
       </c>
       <c r="U56">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.562027525293059</v>
+        <v>3.707459540618297</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08462616279160833</v>
+        <v>0.08356694365313162</v>
       </c>
       <c r="C57">
-        <v>8422.88786504679</v>
+        <v>8835.656146726613</v>
       </c>
       <c r="D57">
-        <v>14917.55786504679</v>
+        <v>15330.32614672661</v>
       </c>
       <c r="E57">
         <v>1390.170000000001</v>
@@ -5961,37 +5961,37 @@
         <v>1971.45</v>
       </c>
       <c r="M57">
-        <v>563.7121889360278</v>
+        <v>541.5995269360279</v>
       </c>
       <c r="N57">
-        <v>1407.737811063972</v>
+        <v>1429.850473063972</v>
       </c>
       <c r="O57">
-        <v>380.0892089872725</v>
+        <v>386.0596277272725</v>
       </c>
       <c r="P57">
-        <v>1027.648602076699</v>
+        <v>1043.790845336699</v>
       </c>
       <c r="Q57">
-        <v>1850.9486020767</v>
+        <v>1867.0908453367</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1289206639604135</v>
+        <v>0.1288866214304652</v>
       </c>
       <c r="T57">
         <v>1.521760650315184</v>
       </c>
       <c r="U57">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.49726338846955</v>
+        <v>3.640051185334328</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08453341051135141</v>
+        <v>0.08345525994794679</v>
       </c>
       <c r="C58">
-        <v>8303.975932625686</v>
+        <v>8726.491162957682</v>
       </c>
       <c r="D58">
-        <v>14953.27993262569</v>
+        <v>15375.79516295768</v>
       </c>
       <c r="E58">
         <v>1544.804000000001</v>
@@ -6043,37 +6043,37 @@
         <v>1971.45</v>
       </c>
       <c r="M58">
-        <v>573.9615014621374</v>
+        <v>551.4467910621375</v>
       </c>
       <c r="N58">
-        <v>1397.488498537862</v>
+        <v>1420.003208937862</v>
       </c>
       <c r="O58">
-        <v>377.3218946052228</v>
+        <v>383.4008664132228</v>
       </c>
       <c r="P58">
-        <v>1020.16660393264</v>
+        <v>1036.602342524639</v>
       </c>
       <c r="Q58">
-        <v>1843.46660393264</v>
+        <v>1859.90234252464</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1305402146114331</v>
+        <v>0.1305055087855135</v>
       </c>
       <c r="T58">
         <v>1.551411140752649</v>
       </c>
       <c r="U58">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V58">
         <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.434812256532593</v>
+        <v>3.575050271310501</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08444065823109451</v>
+        <v>0.08334357624276199</v>
       </c>
       <c r="C59">
-        <v>8185.23549330925</v>
+        <v>8617.596699406145</v>
       </c>
       <c r="D59">
-        <v>14989.17349330925</v>
+        <v>15421.53469940615</v>
       </c>
       <c r="E59">
         <v>1699.438000000003</v>
@@ -6125,37 +6125,37 @@
         <v>1971.45</v>
       </c>
       <c r="M59">
-        <v>584.2108139882472</v>
+        <v>561.2940551882473</v>
       </c>
       <c r="N59">
-        <v>1387.239186011753</v>
+        <v>1410.155944811753</v>
       </c>
       <c r="O59">
-        <v>374.5545802231733</v>
+        <v>380.7421050991732</v>
       </c>
       <c r="P59">
-        <v>1012.684605788579</v>
+        <v>1029.413839712579</v>
       </c>
       <c r="Q59">
-        <v>1835.98460578858</v>
+        <v>1852.71383971258</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1322350931997095</v>
+        <v>0.1321996932268432</v>
       </c>
       <c r="T59">
         <v>1.582440723768602</v>
       </c>
       <c r="U59">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.374552392382898</v>
+        <v>3.51233009111207</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08434790595083759</v>
+        <v>0.08323189253757717</v>
       </c>
       <c r="C60">
-        <v>8066.667785015063</v>
+        <v>8508.975177485827</v>
       </c>
       <c r="D60">
-        <v>15025.23978501506</v>
+        <v>15467.54717748583</v>
       </c>
       <c r="E60">
         <v>1854.072000000001</v>
@@ -6207,37 +6207,37 @@
         <v>1971.45</v>
       </c>
       <c r="M60">
-        <v>594.4601265143566</v>
+        <v>571.1413193143568</v>
       </c>
       <c r="N60">
-        <v>1376.989873485643</v>
+        <v>1400.308680685643</v>
       </c>
       <c r="O60">
-        <v>371.7872658411237</v>
+        <v>378.0833437851236</v>
       </c>
       <c r="P60">
-        <v>1005.20260764452</v>
+        <v>1022.22533690052</v>
       </c>
       <c r="Q60">
-        <v>1828.50260764452</v>
+        <v>1845.52533690052</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1340106802921894</v>
+        <v>0.1339745531177599</v>
       </c>
       <c r="T60">
         <v>1.614947905975789</v>
       </c>
       <c r="U60">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.316370454583194</v>
+        <v>3.45177267574807</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0842551536705807</v>
+        <v>0.08312020883239236</v>
       </c>
       <c r="C61">
-        <v>7948.27405760388</v>
+        <v>8400.62904759557</v>
       </c>
       <c r="D61">
-        <v>15061.48005760388</v>
+        <v>15513.83504759557</v>
       </c>
       <c r="E61">
         <v>2008.706000000001</v>
@@ -6289,37 +6289,37 @@
         <v>1971.45</v>
       </c>
       <c r="M61">
-        <v>604.7094390404662</v>
+        <v>580.9885834404663</v>
       </c>
       <c r="N61">
-        <v>1366.740560959533</v>
+        <v>1390.461416559534</v>
       </c>
       <c r="O61">
-        <v>369.019951459074</v>
+        <v>375.4245824710741</v>
       </c>
       <c r="P61">
-        <v>997.7206095004594</v>
+        <v>1015.036834088459</v>
       </c>
       <c r="Q61">
-        <v>1821.02060950046</v>
+        <v>1838.33683408846</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1358728813891807</v>
+        <v>0.1358359915399408</v>
       </c>
       <c r="T61">
         <v>1.649040804388206</v>
       </c>
       <c r="U61">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V61">
         <v>0.27</v>
       </c>
       <c r="W61">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.260160785861445</v>
+        <v>3.393268054125221</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.0841624013903238</v>
+        <v>0.08300852512720755</v>
       </c>
       <c r="C62">
-        <v>7830.055573024118</v>
+        <v>8292.560789554384</v>
       </c>
       <c r="D62">
-        <v>15097.89557302412</v>
+        <v>15560.40078955438</v>
       </c>
       <c r="E62">
         <v>2163.340000000001</v>
@@ -6371,37 +6371,37 @@
         <v>1971.45</v>
       </c>
       <c r="M62">
-        <v>614.9587515665759</v>
+        <v>590.8358475665759</v>
       </c>
       <c r="N62">
-        <v>1356.491248433424</v>
+        <v>1380.614152433424</v>
       </c>
       <c r="O62">
-        <v>366.2526370770245</v>
+        <v>372.7658211570245</v>
       </c>
       <c r="P62">
-        <v>990.2386113563996</v>
+        <v>1007.848331276399</v>
       </c>
       <c r="Q62">
-        <v>1813.5386113564</v>
+        <v>1831.1483312764</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1378281925410215</v>
+        <v>0.1377905018832309</v>
       </c>
       <c r="T62">
         <v>1.684838347721244</v>
       </c>
       <c r="U62">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.205824772763754</v>
+        <v>3.336713586556467</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08406964911006688</v>
+        <v>0.08289684142202274</v>
       </c>
       <c r="C63">
-        <v>7712.013605458256</v>
+        <v>8184.772913044197</v>
       </c>
       <c r="D63">
-        <v>15134.48760545826</v>
+        <v>15607.2469130442</v>
       </c>
       <c r="E63">
         <v>2317.974000000001</v>
@@ -6453,37 +6453,37 @@
         <v>1971.45</v>
       </c>
       <c r="M63">
-        <v>625.2080640926855</v>
+        <v>600.6831116926855</v>
       </c>
       <c r="N63">
-        <v>1346.241935907314</v>
+        <v>1370.766888307314</v>
       </c>
       <c r="O63">
-        <v>363.4853226949749</v>
+        <v>370.1070598429749</v>
       </c>
       <c r="P63">
-        <v>982.7566132123393</v>
+        <v>1000.659828464339</v>
       </c>
       <c r="Q63">
-        <v>1806.056613212339</v>
+        <v>1823.95982846434</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1398837760596233</v>
+        <v>0.1398452435261768</v>
       </c>
       <c r="T63">
         <v>1.722471662507258</v>
       </c>
       <c r="U63">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.153270268292216</v>
+        <v>3.282013363826033</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08397689682980998</v>
+        <v>0.08278515771683792</v>
       </c>
       <c r="C64">
-        <v>7594.149441471483</v>
+        <v>8077.267958060802</v>
       </c>
       <c r="D64">
-        <v>15171.25744147149</v>
+        <v>15654.3759580608</v>
       </c>
       <c r="E64">
         <v>2472.608000000001</v>
@@ -6535,37 +6535,37 @@
         <v>1971.45</v>
       </c>
       <c r="M64">
-        <v>635.457376618795</v>
+        <v>610.5303758187952</v>
       </c>
       <c r="N64">
-        <v>1335.992623381205</v>
+        <v>1360.919624181205</v>
       </c>
       <c r="O64">
-        <v>360.7180083129253</v>
+        <v>367.4482985289253</v>
       </c>
       <c r="P64">
-        <v>975.2746150682794</v>
+        <v>993.4713256522793</v>
       </c>
       <c r="Q64">
-        <v>1798.57461506828</v>
+        <v>1816.77132565228</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1420475481844674</v>
+        <v>0.1420081294661198</v>
       </c>
       <c r="T64">
         <v>1.762085678071483</v>
       </c>
       <c r="U64">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.102411070416536</v>
+        <v>3.229077664409485</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08388414454955306</v>
+        <v>0.08267347401165311</v>
       </c>
       <c r="C65">
-        <v>7476.464380162501</v>
+        <v>7970.048495372901</v>
       </c>
       <c r="D65">
-        <v>15208.2063801625</v>
+        <v>15701.7904953729</v>
       </c>
       <c r="E65">
         <v>2627.242000000001</v>
@@ -6617,37 +6617,37 @@
         <v>1971.45</v>
       </c>
       <c r="M65">
-        <v>645.7066891449047</v>
+        <v>620.3776399449048</v>
       </c>
       <c r="N65">
-        <v>1325.743310855095</v>
+        <v>1351.072360055095</v>
       </c>
       <c r="O65">
-        <v>357.9506939308757</v>
+        <v>364.7895372148757</v>
       </c>
       <c r="P65">
-        <v>967.7926169242194</v>
+        <v>986.2828228402193</v>
       </c>
       <c r="Q65">
-        <v>1791.09261692422</v>
+        <v>1809.582822840219</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1443282809647084</v>
+        <v>0.1442879281595734</v>
       </c>
       <c r="T65">
         <v>1.803840991774315</v>
       </c>
       <c r="U65">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V65">
         <v>0.27</v>
       </c>
       <c r="W65">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.053166450251194</v>
+        <v>3.177822463387111</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08379139226929617</v>
+        <v>0.08256179030646829</v>
       </c>
       <c r="C66">
-        <v>7358.959733316464</v>
+        <v>7863.117126989575</v>
       </c>
       <c r="D66">
-        <v>15245.33573331646</v>
+        <v>15749.49312698958</v>
       </c>
       <c r="E66">
         <v>2781.876000000001</v>
@@ -6699,37 +6699,37 @@
         <v>1971.45</v>
       </c>
       <c r="M66">
-        <v>655.9560016710143</v>
+        <v>630.2249040710143</v>
       </c>
       <c r="N66">
-        <v>1315.493998328986</v>
+        <v>1341.225095928985</v>
       </c>
       <c r="O66">
-        <v>355.1833795488261</v>
+        <v>362.1307759008261</v>
       </c>
       <c r="P66">
-        <v>960.3106187801594</v>
+        <v>979.0943200281592</v>
       </c>
       <c r="Q66">
-        <v>1783.61061878016</v>
+        <v>1802.394320028159</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1467357211216295</v>
+        <v>0.1466943823359965</v>
       </c>
       <c r="T66">
         <v>1.847916045127305</v>
       </c>
       <c r="U66">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.005460724466019</v>
+        <v>3.128168987396688</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08493233998903923</v>
+        <v>0.08245010660128349</v>
       </c>
       <c r="C67">
-        <v>6759.830692986221</v>
+        <v>7756.476486636262</v>
       </c>
       <c r="D67">
-        <v>14800.84069298622</v>
+        <v>15797.48648663626</v>
       </c>
       <c r="E67">
         <v>2936.510000000001</v>
@@ -6781,45 +6781,45 @@
         <v>1971.45</v>
       </c>
       <c r="M67">
-        <v>692.3384601971237</v>
+        <v>640.0721681971239</v>
       </c>
       <c r="N67">
-        <v>1279.111539802876</v>
+        <v>1331.377831802876</v>
       </c>
       <c r="O67">
-        <v>345.3601157467766</v>
+        <v>359.4720145867765</v>
       </c>
       <c r="P67">
-        <v>933.7514240560995</v>
+        <v>971.9058172160993</v>
       </c>
       <c r="Q67">
-        <v>1757.0514240561</v>
+        <v>1795.2058172161</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1492807292875175</v>
+        <v>0.1492383481796438</v>
       </c>
       <c r="T67">
         <v>1.894509672957608</v>
       </c>
       <c r="U67">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V67">
         <v>0.27</v>
       </c>
       <c r="W67">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.847523448919312</v>
+        <v>3.080043310667508</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08485856770878233</v>
+        <v>0.08233842289609866</v>
       </c>
       <c r="C68">
-        <v>6633.15193639867</v>
+        <v>7650.129240239501</v>
       </c>
       <c r="D68">
-        <v>14828.79593639867</v>
+        <v>15845.7732402395</v>
       </c>
       <c r="E68">
         <v>3091.144000000001</v>
@@ -6863,45 +6863,45 @@
         <v>1971.45</v>
       </c>
       <c r="M68">
-        <v>702.9898211232334</v>
+        <v>649.9194323232335</v>
       </c>
       <c r="N68">
-        <v>1268.460178876766</v>
+        <v>1321.530567676766</v>
       </c>
       <c r="O68">
-        <v>342.4842482967269</v>
+        <v>356.8132532727269</v>
       </c>
       <c r="P68">
-        <v>925.9759305800394</v>
+        <v>964.7173144040393</v>
       </c>
       <c r="Q68">
-        <v>1749.27593058004</v>
+        <v>1788.01731440404</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1519754438161048</v>
+        <v>0.1519319590729175</v>
       </c>
       <c r="T68">
         <v>1.943844102424987</v>
       </c>
       <c r="U68">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.804379154238716</v>
+        <v>3.033375987778606</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08478479542852543</v>
+        <v>0.08344948919091386</v>
       </c>
       <c r="C69">
-        <v>6506.578981164139</v>
+        <v>7027.873900857196</v>
       </c>
       <c r="D69">
-        <v>14856.85698116414</v>
+        <v>15378.1519008572</v>
       </c>
       <c r="E69">
         <v>3245.778000000001</v>
@@ -6945,37 +6945,37 @@
         <v>1971.45</v>
       </c>
       <c r="M69">
-        <v>713.641182049343</v>
+        <v>685.667891449343</v>
       </c>
       <c r="N69">
-        <v>1257.808817950657</v>
+        <v>1285.782108550657</v>
       </c>
       <c r="O69">
-        <v>339.6083808466773</v>
+        <v>347.1611693086774</v>
       </c>
       <c r="P69">
-        <v>918.2004371039793</v>
+        <v>938.6209392419795</v>
       </c>
       <c r="Q69">
-        <v>1741.500437103979</v>
+        <v>1761.92093924198</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1548334743767277</v>
+        <v>0.154788819111238</v>
       </c>
       <c r="T69">
         <v>1.996168497314633</v>
       </c>
       <c r="U69">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.762522748951571</v>
+        <v>2.875225782897332</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08471102314826853</v>
+        <v>0.08335605548572902</v>
       </c>
       <c r="C70">
-        <v>6380.112429056084</v>
+        <v>6911.498383874357</v>
       </c>
       <c r="D70">
-        <v>14885.02442905608</v>
+        <v>15416.41038387436</v>
       </c>
       <c r="E70">
         <v>3400.412000000001</v>
@@ -7027,37 +7027,37 @@
         <v>1971.45</v>
       </c>
       <c r="M70">
-        <v>724.2925429754525</v>
+        <v>695.9017405754525</v>
       </c>
       <c r="N70">
-        <v>1247.157457024547</v>
+        <v>1275.548259424547</v>
       </c>
       <c r="O70">
-        <v>336.7325133966278</v>
+        <v>344.3980300446278</v>
       </c>
       <c r="P70">
-        <v>910.4249436279194</v>
+        <v>931.1502293799194</v>
       </c>
       <c r="Q70">
-        <v>1733.72494362792</v>
+        <v>1754.45022937992</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1578701318473895</v>
+        <v>0.1578242329019536</v>
       </c>
       <c r="T70">
         <v>2.05176316688488</v>
       </c>
       <c r="U70">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V70">
         <v>0.27</v>
       </c>
       <c r="W70">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.721897414408166</v>
+        <v>2.8329430507959</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08463725086801163</v>
+        <v>0.08326262178054422</v>
       </c>
       <c r="C71">
-        <v>6253.752886420303</v>
+        <v>6795.313704139573</v>
       </c>
       <c r="D71">
-        <v>14913.29888642031</v>
+        <v>15454.85970413958</v>
       </c>
       <c r="E71">
         <v>3555.046000000001</v>
@@ -7109,37 +7109,37 @@
         <v>1971.45</v>
       </c>
       <c r="M71">
-        <v>734.9439039015622</v>
+        <v>706.1355897015623</v>
       </c>
       <c r="N71">
-        <v>1236.506096098438</v>
+        <v>1265.314410298437</v>
       </c>
       <c r="O71">
-        <v>333.8566459465782</v>
+        <v>341.6348907805781</v>
       </c>
       <c r="P71">
-        <v>902.6494501518595</v>
+        <v>923.6795195178593</v>
       </c>
       <c r="Q71">
-        <v>1725.94945015186</v>
+        <v>1746.979519517859</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1611027027032553</v>
+        <v>0.1610554798404573</v>
       </c>
       <c r="T71">
         <v>2.110944589330628</v>
       </c>
       <c r="U71">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.682449625793555</v>
+        <v>2.791885905132191</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08456347858775473</v>
+        <v>0.08316918807535942</v>
       </c>
       <c r="C72">
-        <v>6127.500964218436</v>
+        <v>6679.321293096686</v>
       </c>
       <c r="D72">
-        <v>14941.68096421844</v>
+        <v>15493.50129309669</v>
       </c>
       <c r="E72">
         <v>3709.680000000003</v>
@@ -7191,37 +7191,37 @@
         <v>1971.45</v>
       </c>
       <c r="M72">
-        <v>745.5952648276718</v>
+        <v>716.369438827672</v>
       </c>
       <c r="N72">
-        <v>1225.854735172328</v>
+        <v>1255.080561172328</v>
       </c>
       <c r="O72">
-        <v>330.9807784965286</v>
+        <v>338.8717515165285</v>
       </c>
       <c r="P72">
-        <v>894.8739566757995</v>
+        <v>916.2088096557993</v>
       </c>
       <c r="Q72">
-        <v>1718.1739566758</v>
+        <v>1739.508809655799</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1645507782828456</v>
+        <v>0.1645021432415279</v>
       </c>
       <c r="T72">
         <v>2.174071439939426</v>
       </c>
       <c r="U72">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V72">
         <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.644128916853647</v>
+        <v>2.75200182077316</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08448970630749782</v>
+        <v>0.08307575437017461</v>
       </c>
       <c r="C73">
-        <v>6001.357278071971</v>
+        <v>6563.522596541485</v>
       </c>
       <c r="D73">
-        <v>14970.17127807197</v>
+        <v>15532.33659654149</v>
       </c>
       <c r="E73">
         <v>3864.314000000001</v>
@@ -7273,37 +7273,37 @@
         <v>1971.45</v>
       </c>
       <c r="M73">
-        <v>756.2466257537814</v>
+        <v>726.6032879537814</v>
       </c>
       <c r="N73">
-        <v>1215.203374246219</v>
+        <v>1244.846712046218</v>
       </c>
       <c r="O73">
-        <v>328.1049110464791</v>
+        <v>336.108612252479</v>
       </c>
       <c r="P73">
-        <v>887.0984631997395</v>
+        <v>908.7380997937394</v>
       </c>
       <c r="Q73">
-        <v>1710.39846319974</v>
+        <v>1732.03809979374</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1682366521782695</v>
+        <v>0.1681865075668102</v>
       </c>
       <c r="T73">
         <v>2.241551866452278</v>
       </c>
       <c r="U73">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V73">
         <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.606887664503596</v>
+        <v>2.713241231748186</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.0844159340272409</v>
+        <v>0.0829823206649898</v>
       </c>
       <c r="C74">
-        <v>5875.322448306746</v>
+        <v>6447.919074802063</v>
       </c>
       <c r="D74">
-        <v>14998.77044830675</v>
+        <v>15571.36707480206</v>
       </c>
       <c r="E74">
         <v>4018.948000000001</v>
@@ -7355,37 +7355,37 @@
         <v>1971.45</v>
       </c>
       <c r="M74">
-        <v>766.8979866798909</v>
+        <v>736.837137079891</v>
       </c>
       <c r="N74">
-        <v>1204.552013320109</v>
+        <v>1234.612862920109</v>
       </c>
       <c r="O74">
-        <v>325.2290435964294</v>
+        <v>333.3454729884294</v>
       </c>
       <c r="P74">
-        <v>879.3229697236795</v>
+        <v>901.2673899316794</v>
       </c>
       <c r="Q74">
-        <v>1702.62296972368</v>
+        <v>1724.56738993168</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1721858027805095</v>
+        <v>0.1721340407724698</v>
       </c>
       <c r="T74">
         <v>2.313852323430335</v>
       </c>
       <c r="U74">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V74">
         <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.57068089138549</v>
+        <v>2.675557325751684</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.084342161746984</v>
+        <v>0.08288888695980498</v>
       </c>
       <c r="C75">
-        <v>5749.397099997985</v>
+        <v>6332.512202921824</v>
       </c>
       <c r="D75">
-        <v>15027.47909999799</v>
+        <v>15610.59420292182</v>
       </c>
       <c r="E75">
         <v>4173.582000000001</v>
@@ -7437,37 +7437,37 @@
         <v>1971.45</v>
       </c>
       <c r="M75">
-        <v>777.5493476060005</v>
+        <v>747.0709862060006</v>
       </c>
       <c r="N75">
-        <v>1193.900652393999</v>
+        <v>1224.379013793999</v>
       </c>
       <c r="O75">
-        <v>322.3531761463798</v>
+        <v>330.5823337243798</v>
       </c>
       <c r="P75">
-        <v>871.5474762476194</v>
+        <v>893.7966800696192</v>
       </c>
       <c r="Q75">
-        <v>1694.84747624762</v>
+        <v>1717.096680069619</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1764274830569895</v>
+        <v>0.1763739838452154</v>
       </c>
       <c r="T75">
         <v>2.391508369814173</v>
       </c>
       <c r="U75">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.535466084654182</v>
+        <v>2.638905855535907</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.0842683894667271</v>
+        <v>0.08279545325462015</v>
       </c>
       <c r="C76">
-        <v>5623.581863015828</v>
+        <v>6217.303470845352</v>
       </c>
       <c r="D76">
-        <v>15056.29786301583</v>
+        <v>15650.01947084535</v>
       </c>
       <c r="E76">
         <v>4328.216000000001</v>
@@ -7519,37 +7519,37 @@
         <v>1971.45</v>
       </c>
       <c r="M76">
-        <v>788.2007085321101</v>
+        <v>757.3048353321102</v>
       </c>
       <c r="N76">
-        <v>1183.24929146789</v>
+        <v>1214.14516466789</v>
       </c>
       <c r="O76">
-        <v>319.4773086963302</v>
+        <v>327.8191944603303</v>
       </c>
       <c r="P76">
-        <v>863.7719827715594</v>
+        <v>886.3259702075595</v>
       </c>
       <c r="Q76">
-        <v>1687.07198277156</v>
+        <v>1709.62597020756</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1809954464316603</v>
+        <v>0.1809400763850952</v>
       </c>
       <c r="T76">
         <v>2.475137958227537</v>
       </c>
       <c r="U76">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V76">
         <v>0.27</v>
       </c>
       <c r="W76">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.501203029456152</v>
+        <v>2.603244965596233</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08567286718647019</v>
+        <v>0.08270201954943535</v>
       </c>
       <c r="C77">
-        <v>4938.606395683461</v>
+        <v>6102.29438360701</v>
       </c>
       <c r="D77">
-        <v>14525.95639568346</v>
+        <v>15689.64438360701</v>
       </c>
       <c r="E77">
         <v>4482.850000000001</v>
@@ -7601,45 +7601,45 @@
         <v>1971.45</v>
       </c>
       <c r="M77">
-        <v>830.1654544582199</v>
+        <v>767.5386844582198</v>
       </c>
       <c r="N77">
-        <v>1141.28454554178</v>
+        <v>1203.91131554178</v>
       </c>
       <c r="O77">
-        <v>308.1468272962807</v>
+        <v>325.0560551962806</v>
       </c>
       <c r="P77">
-        <v>833.1377182454994</v>
+        <v>878.8552603454993</v>
       </c>
       <c r="Q77">
-        <v>1656.4377182455</v>
+        <v>1702.1552603455</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1859288468763048</v>
+        <v>0.1858714563281654</v>
       </c>
       <c r="T77">
         <v>2.565457913713971</v>
       </c>
       <c r="U77">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V77">
         <v>0.27</v>
       </c>
       <c r="W77">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.374767571226632</v>
+        <v>2.568535032721616</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.08561880490621329</v>
+        <v>0.08260858584425054</v>
       </c>
       <c r="C78">
-        <v>4803.694392049561</v>
+        <v>5987.486461522509</v>
       </c>
       <c r="D78">
-        <v>14545.67839204956</v>
+        <v>15729.47046152251</v>
       </c>
       <c r="E78">
         <v>4637.484000000001</v>
@@ -7683,45 +7683,45 @@
         <v>1971.45</v>
       </c>
       <c r="M78">
-        <v>841.2343271843295</v>
+        <v>777.7725335843294</v>
       </c>
       <c r="N78">
-        <v>1130.21567281567</v>
+        <v>1193.677466415671</v>
       </c>
       <c r="O78">
-        <v>305.158231660231</v>
+        <v>322.2929159322311</v>
       </c>
       <c r="P78">
-        <v>825.0574411554394</v>
+        <v>871.3845504834394</v>
       </c>
       <c r="Q78">
-        <v>1648.35744115544</v>
+        <v>1694.68455048344</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1912733640246696</v>
+        <v>0.1912137845998248</v>
       </c>
       <c r="T78">
         <v>2.663304532157607</v>
       </c>
       <c r="U78">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V78">
         <v>0.27</v>
       </c>
       <c r="W78">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.343520629499966</v>
+        <v>2.534738519133174</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08556474262595637</v>
+        <v>0.08251515213906571</v>
       </c>
       <c r="C79">
-        <v>4668.836014619412</v>
+        <v>5872.881240383309</v>
       </c>
       <c r="D79">
-        <v>14565.45401461941</v>
+        <v>15769.49924038331</v>
       </c>
       <c r="E79">
         <v>4792.118000000001</v>
@@ -7765,45 +7765,45 @@
         <v>1971.45</v>
       </c>
       <c r="M79">
-        <v>852.303199910439</v>
+        <v>788.006382710439</v>
       </c>
       <c r="N79">
-        <v>1119.146800089561</v>
+        <v>1183.443617289561</v>
       </c>
       <c r="O79">
-        <v>302.1696360241814</v>
+        <v>319.5297766681814</v>
       </c>
       <c r="P79">
-        <v>816.9771640653793</v>
+        <v>863.9138406213793</v>
       </c>
       <c r="Q79">
-        <v>1640.27716406538</v>
+        <v>1687.213840621379</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1970826217946313</v>
+        <v>0.1970206631559763</v>
       </c>
       <c r="T79">
         <v>2.769659552205038</v>
       </c>
       <c r="U79">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V79">
         <v>0.27</v>
       </c>
       <c r="W79">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.313085296649317</v>
+        <v>2.501819837066509</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.08551068034569947</v>
+        <v>0.0844146184338809</v>
       </c>
       <c r="C80">
-        <v>4534.031482413775</v>
+        <v>4942.540176373062</v>
       </c>
       <c r="D80">
-        <v>14585.28348241378</v>
+        <v>14993.79217637306</v>
       </c>
       <c r="E80">
         <v>4946.752000000001</v>
@@ -7847,37 +7847,37 @@
         <v>1971.45</v>
       </c>
       <c r="M80">
-        <v>863.3720726365486</v>
+        <v>840.4553138365486</v>
       </c>
       <c r="N80">
-        <v>1108.077927363451</v>
+        <v>1130.994686163451</v>
       </c>
       <c r="O80">
-        <v>299.1810403881319</v>
+        <v>305.3685652641319</v>
       </c>
       <c r="P80">
-        <v>808.8968869753194</v>
+        <v>825.6261208993194</v>
       </c>
       <c r="Q80">
-        <v>1632.19688697532</v>
+        <v>1648.92612089932</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2034199939073169</v>
+        <v>0.203355439762687</v>
       </c>
       <c r="T80">
         <v>2.885683210438599</v>
       </c>
       <c r="U80">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.283430356948684</v>
+        <v>2.345692825714475</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08545661806544258</v>
+        <v>0.0843467347286961</v>
       </c>
       <c r="C81">
-        <v>4399.281015647777</v>
+        <v>4814.311374501178</v>
       </c>
       <c r="D81">
-        <v>14605.16701564778</v>
+        <v>15020.19737450118</v>
       </c>
       <c r="E81">
         <v>5101.386000000001</v>
@@ -7929,37 +7929,37 @@
         <v>1971.45</v>
       </c>
       <c r="M81">
-        <v>874.4409453626582</v>
+        <v>851.2303819626583</v>
       </c>
       <c r="N81">
-        <v>1097.009054637342</v>
+        <v>1120.219618037342</v>
       </c>
       <c r="O81">
-        <v>296.1924447520823</v>
+        <v>302.4592968700823</v>
       </c>
       <c r="P81">
-        <v>800.8166098852594</v>
+        <v>817.7603211672595</v>
       </c>
       <c r="Q81">
-        <v>1624.11660988526</v>
+        <v>1641.06032116726</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2103609252688297</v>
+        <v>0.2102935284271798</v>
       </c>
       <c r="T81">
         <v>3.01275674088488</v>
       </c>
       <c r="U81">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.254526175215157</v>
+        <v>2.316000511464925</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.08814735578518566</v>
+        <v>0.08427885102351128</v>
       </c>
       <c r="C82">
-        <v>3316.63927907267</v>
+        <v>4686.175739791903</v>
       </c>
       <c r="D82">
-        <v>13677.15927907267</v>
+        <v>15046.6957397919</v>
       </c>
       <c r="E82">
         <v>5256.020000000001</v>
@@ -8011,45 +8011,45 @@
         <v>1971.45</v>
       </c>
       <c r="M82">
-        <v>943.6522020887679</v>
+        <v>862.0054500887678</v>
       </c>
       <c r="N82">
-        <v>1027.797797911232</v>
+        <v>1109.444549911232</v>
       </c>
       <c r="O82">
-        <v>277.5054054360327</v>
+        <v>299.5500284760327</v>
       </c>
       <c r="P82">
-        <v>750.2923924751993</v>
+        <v>809.8945214351994</v>
       </c>
       <c r="Q82">
-        <v>1573.5923924752</v>
+        <v>1633.194521435199</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2179959497664936</v>
+        <v>0.2179254259581217</v>
       </c>
       <c r="T82">
         <v>3.152537624375789</v>
       </c>
       <c r="U82">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V82">
         <v>0.27</v>
       </c>
       <c r="W82">
-        <v>0.05568520728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.08917013666286</v>
+        <v>2.287050505071614</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08812760350492875</v>
+        <v>0.08421096731832646</v>
       </c>
       <c r="C83">
-        <v>3168.387759081663</v>
+        <v>4558.133766208231</v>
       </c>
       <c r="D83">
-        <v>13683.54175908166</v>
+        <v>15073.28776620823</v>
       </c>
       <c r="E83">
         <v>5410.654000000001</v>
@@ -8093,45 +8093,45 @@
         <v>1971.45</v>
       </c>
       <c r="M83">
-        <v>955.4478546148775</v>
+        <v>872.7805182148774</v>
       </c>
       <c r="N83">
-        <v>1016.002145385122</v>
+        <v>1098.669481785123</v>
       </c>
       <c r="O83">
-        <v>274.3205792539831</v>
+        <v>296.6407600819831</v>
       </c>
       <c r="P83">
-        <v>741.6815661311392</v>
+        <v>802.0287217031395</v>
       </c>
       <c r="Q83">
-        <v>1564.98156613114</v>
+        <v>1625.32872170314</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2264346610533854</v>
+        <v>0.2263606811238997</v>
       </c>
       <c r="T83">
         <v>3.307032285076267</v>
       </c>
       <c r="U83">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.05568520728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.063377912753442</v>
+        <v>2.258815313650977</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08810785122467185</v>
+        <v>0.08581916361314165</v>
       </c>
       <c r="C84">
-        <v>3020.142198671681</v>
+        <v>3797.769827156257</v>
       </c>
       <c r="D84">
-        <v>13689.93019867168</v>
+        <v>14467.55782715626</v>
       </c>
       <c r="E84">
         <v>5565.288000000003</v>
@@ -8175,37 +8175,37 @@
         <v>1971.45</v>
       </c>
       <c r="M84">
-        <v>967.2435071409873</v>
+        <v>919.0595527409871</v>
       </c>
       <c r="N84">
-        <v>1004.206492859013</v>
+        <v>1052.390447259013</v>
       </c>
       <c r="O84">
-        <v>271.1357530719334</v>
+        <v>284.1454207599335</v>
       </c>
       <c r="P84">
-        <v>733.0707397870792</v>
+        <v>768.2450264990792</v>
       </c>
       <c r="Q84">
-        <v>1556.370739787079</v>
+        <v>1591.54502649908</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2358110069277097</v>
+        <v>0.2357331868636531</v>
       </c>
       <c r="T84">
         <v>3.47869301918791</v>
       </c>
       <c r="U84">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V84">
         <v>0.27</v>
       </c>
       <c r="W84">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.03821476747596</v>
+        <v>2.145073182820832</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08808809894441494</v>
+        <v>0.08577171990795684</v>
       </c>
       <c r="C85">
-        <v>2871.902606193691</v>
+        <v>3660.307831510243</v>
       </c>
       <c r="D85">
-        <v>13696.32460619369</v>
+        <v>14484.72983151025</v>
       </c>
       <c r="E85">
         <v>5719.922000000003</v>
@@ -8257,37 +8257,37 @@
         <v>1971.45</v>
       </c>
       <c r="M85">
-        <v>979.0391596670969</v>
+        <v>930.2675960670967</v>
       </c>
       <c r="N85">
-        <v>992.4108403329029</v>
+        <v>1041.182403932903</v>
       </c>
       <c r="O85">
-        <v>267.9509268898838</v>
+        <v>281.1192490618839</v>
       </c>
       <c r="P85">
-        <v>724.4599134430191</v>
+        <v>760.0631548710192</v>
       </c>
       <c r="Q85">
-        <v>1547.759913443019</v>
+        <v>1583.363154871019</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2462904523166604</v>
+        <v>0.2462083403374951</v>
       </c>
       <c r="T85">
         <v>3.670549133783276</v>
       </c>
       <c r="U85">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V85">
         <v>0.27</v>
       </c>
       <c r="W85">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.013657963048539</v>
+        <v>2.119228927606123</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09377110666415803</v>
+        <v>0.08572427620277202</v>
       </c>
       <c r="C86">
-        <v>1094.701943013875</v>
+        <v>3522.886648301654</v>
       </c>
       <c r="D86">
-        <v>12073.75794301388</v>
+        <v>14501.94264830165</v>
       </c>
       <c r="E86">
         <v>5874.556000000001</v>
@@ -8339,45 +8339,45 @@
         <v>1971.45</v>
       </c>
       <c r="M86">
-        <v>1111.634892993206</v>
+        <v>941.4756393932062</v>
       </c>
       <c r="N86">
-        <v>859.8151070067936</v>
+        <v>1029.974360606794</v>
       </c>
       <c r="O86">
-        <v>232.1500788918343</v>
+        <v>278.0930773638343</v>
       </c>
       <c r="P86">
-        <v>627.6650281149593</v>
+        <v>751.8812832429594</v>
       </c>
       <c r="Q86">
-        <v>1450.96502811496</v>
+        <v>1575.18128324296</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2580798283792297</v>
+        <v>0.2579928879955671</v>
       </c>
       <c r="T86">
         <v>3.88638726270306</v>
       </c>
       <c r="U86">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V86">
         <v>0.27</v>
       </c>
       <c r="W86">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.773468980171755</v>
+        <v>2.094000011801289</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.09381924438390113</v>
+        <v>0.0856768324975872</v>
       </c>
       <c r="C87">
-        <v>927.9643961221282</v>
+        <v>3385.506423201025</v>
       </c>
       <c r="D87">
-        <v>12061.65439612213</v>
+        <v>14519.19642320103</v>
       </c>
       <c r="E87">
         <v>6029.190000000001</v>
@@ -8421,45 +8421,45 @@
         <v>1971.45</v>
       </c>
       <c r="M87">
-        <v>1124.868641719316</v>
+        <v>952.6836827193158</v>
       </c>
       <c r="N87">
-        <v>846.5813582806841</v>
+        <v>1018.766317280684</v>
       </c>
       <c r="O87">
-        <v>228.5769667357847</v>
+        <v>275.0669056657847</v>
       </c>
       <c r="P87">
-        <v>618.0043915448994</v>
+        <v>743.6994116148993</v>
       </c>
       <c r="Q87">
-        <v>1441.3043915449</v>
+        <v>1566.9994116149</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2714411212501417</v>
+        <v>0.2713487086747156</v>
       </c>
       <c r="T87">
         <v>4.13100380881215</v>
       </c>
       <c r="U87">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.752604639228558</v>
+        <v>2.069364717544803</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09681804210364421</v>
+        <v>0.08562938879240239</v>
       </c>
       <c r="C88">
-        <v>64.35646831166559</v>
+        <v>3248.167302572961</v>
       </c>
       <c r="D88">
-        <v>11352.68046831167</v>
+        <v>14536.49130257296</v>
       </c>
       <c r="E88">
         <v>6183.824000000001</v>
@@ -8503,45 +8503,45 @@
         <v>1971.45</v>
       </c>
       <c r="M88">
-        <v>1200.605453245425</v>
+        <v>963.8917260454253</v>
       </c>
       <c r="N88">
-        <v>770.8445467545746</v>
+        <v>1007.558273954574</v>
       </c>
       <c r="O88">
-        <v>208.1280276237352</v>
+        <v>272.0407339677352</v>
       </c>
       <c r="P88">
-        <v>562.7165191308394</v>
+        <v>735.5175399868393</v>
       </c>
       <c r="Q88">
-        <v>1386.01651913084</v>
+        <v>1558.81753998684</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2867111702454697</v>
+        <v>0.2866125037365996</v>
       </c>
       <c r="T88">
         <v>4.410565575793969</v>
       </c>
       <c r="U88">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V88">
         <v>0.27</v>
       </c>
       <c r="W88">
-        <v>0.06590520728985866</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.642046514673793</v>
+        <v>2.045302337108236</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09690048982338731</v>
+        <v>0.08558194508721759</v>
       </c>
       <c r="C89">
-        <v>-108.5944327751786</v>
+        <v>3110.869433480306</v>
       </c>
       <c r="D89">
-        <v>11334.36356722482</v>
+        <v>14553.82743348031</v>
       </c>
       <c r="E89">
         <v>6338.458000000001</v>
@@ -8585,45 +8585,45 @@
         <v>1971.45</v>
       </c>
       <c r="M89">
-        <v>1214.565981771535</v>
+        <v>975.099769371535</v>
       </c>
       <c r="N89">
-        <v>756.8840182284648</v>
+        <v>996.3502306284648</v>
       </c>
       <c r="O89">
-        <v>204.3586849216855</v>
+        <v>269.0145622696855</v>
       </c>
       <c r="P89">
-        <v>552.5253333067793</v>
+        <v>727.3356683587792</v>
       </c>
       <c r="Q89">
-        <v>1375.82533330678</v>
+        <v>1550.635668358779</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3043304575477713</v>
+        <v>0.3042245749618503</v>
       </c>
       <c r="T89">
         <v>4.733136845388374</v>
       </c>
       <c r="U89">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V89">
         <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.06590520728985866</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.623172416803979</v>
+        <v>2.021793114842624</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.09698293754313039</v>
+        <v>0.09054522138203278</v>
       </c>
       <c r="C90">
-        <v>-281.4863225273912</v>
+        <v>1341.880548906436</v>
       </c>
       <c r="D90">
-        <v>11316.10567747261</v>
+        <v>12939.47254890644</v>
       </c>
       <c r="E90">
         <v>6493.092000000001</v>
@@ -8667,45 +8667,45 @@
         <v>1971.45</v>
       </c>
       <c r="M90">
-        <v>1228.526510297645</v>
+        <v>1092.448590297645</v>
       </c>
       <c r="N90">
-        <v>742.9234897023553</v>
+        <v>879.001409702355</v>
       </c>
       <c r="O90">
-        <v>200.5893422196359</v>
+        <v>237.3303806196359</v>
       </c>
       <c r="P90">
-        <v>542.3341474827193</v>
+        <v>641.6710290827191</v>
       </c>
       <c r="Q90">
-        <v>1365.63414748272</v>
+        <v>1464.971029082719</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3248862927337899</v>
+        <v>0.3247719913913095</v>
       </c>
       <c r="T90">
         <v>5.109469993248514</v>
       </c>
       <c r="U90">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V90">
         <v>0.27</v>
       </c>
       <c r="W90">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.604727275703934</v>
+        <v>1.804615812138918</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.0970653852628735</v>
+        <v>0.09055471767684797</v>
       </c>
       <c r="C91">
-        <v>-454.3194856604787</v>
+        <v>1184.50098257386</v>
       </c>
       <c r="D91">
-        <v>11297.90651433952</v>
+        <v>12936.72698257386</v>
       </c>
       <c r="E91">
         <v>6647.726000000001</v>
@@ -8749,45 +8749,45 @@
         <v>1971.45</v>
       </c>
       <c r="M91">
-        <v>1242.487038823754</v>
+        <v>1104.862778823754</v>
       </c>
       <c r="N91">
-        <v>728.9629611762457</v>
+        <v>866.5872211762455</v>
       </c>
       <c r="O91">
-        <v>196.8199995175864</v>
+        <v>233.9785497175863</v>
       </c>
       <c r="P91">
-        <v>532.1429616586594</v>
+        <v>632.6086714586593</v>
       </c>
       <c r="Q91">
-        <v>1355.442961658659</v>
+        <v>1455.908671458659</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3491795524990845</v>
+        <v>0.349055301717034</v>
       </c>
       <c r="T91">
         <v>5.554227349810498</v>
       </c>
       <c r="U91">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V91">
         <v>0.27</v>
       </c>
       <c r="W91">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.586696632156698</v>
+        <v>1.784339229980053</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.09714783298261659</v>
+        <v>0.09056421397166314</v>
       </c>
       <c r="C92">
-        <v>-627.0942050612994</v>
+        <v>1027.122581131947</v>
       </c>
       <c r="D92">
-        <v>11279.7657949387</v>
+        <v>12933.98258113195</v>
       </c>
       <c r="E92">
         <v>6802.360000000001</v>
@@ -8831,45 +8831,45 @@
         <v>1971.45</v>
       </c>
       <c r="M92">
-        <v>1256.447567349864</v>
+        <v>1117.276967349864</v>
       </c>
       <c r="N92">
-        <v>715.0024326501361</v>
+        <v>854.1730326501358</v>
       </c>
       <c r="O92">
-        <v>193.0506568155368</v>
+        <v>230.6267188155367</v>
       </c>
       <c r="P92">
-        <v>521.9517758345994</v>
+        <v>623.5463138345991</v>
       </c>
       <c r="Q92">
-        <v>1345.2517758346</v>
+        <v>1446.846313834599</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.378331464217438</v>
+        <v>0.3781952741079035</v>
       </c>
       <c r="T92">
         <v>6.087936177684878</v>
       </c>
       <c r="U92">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V92">
         <v>0.27</v>
       </c>
       <c r="W92">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.56906666957718</v>
+        <v>1.76451323853583</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.09723028070235967</v>
+        <v>0.09316448026647833</v>
       </c>
       <c r="C93">
-        <v>-799.8107618027425</v>
+        <v>162.4248630413531</v>
       </c>
       <c r="D93">
-        <v>11261.68323819726</v>
+        <v>12223.91886304135</v>
       </c>
       <c r="E93">
         <v>6956.994000000002</v>
@@ -8913,37 +8913,37 @@
         <v>1971.45</v>
       </c>
       <c r="M93">
-        <v>1270.408095875973</v>
+        <v>1184.570762475973</v>
       </c>
       <c r="N93">
-        <v>701.0419041240266</v>
+        <v>786.8792375240264</v>
       </c>
       <c r="O93">
-        <v>189.2813141134872</v>
+        <v>212.4573941314871</v>
       </c>
       <c r="P93">
-        <v>511.7605900105394</v>
+        <v>574.4218433925392</v>
       </c>
       <c r="Q93">
-        <v>1335.06059001054</v>
+        <v>1397.72184339254</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4139615785398701</v>
+        <v>0.4138107959189661</v>
       </c>
       <c r="T93">
         <v>6.740246967309122</v>
       </c>
       <c r="U93">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V93">
         <v>0.27</v>
       </c>
       <c r="W93">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.551824178702705</v>
+        <v>1.664273728890035</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.09731272842210278</v>
+        <v>0.09320244656129351</v>
       </c>
       <c r="C94">
-        <v>-972.4694351582348</v>
+        <v>-1.99970561106602</v>
       </c>
       <c r="D94">
-        <v>11243.65856484177</v>
+        <v>12214.12829438893</v>
       </c>
       <c r="E94">
         <v>7111.628000000002</v>
@@ -8995,37 +8995,37 @@
         <v>1971.45</v>
       </c>
       <c r="M94">
-        <v>1284.368624402083</v>
+        <v>1197.588023602083</v>
       </c>
       <c r="N94">
-        <v>687.0813755979168</v>
+        <v>773.8619763979168</v>
       </c>
       <c r="O94">
-        <v>185.5119714114375</v>
+        <v>208.9427336274375</v>
       </c>
       <c r="P94">
-        <v>501.5694041864792</v>
+        <v>564.9192427704793</v>
       </c>
       <c r="Q94">
-        <v>1324.869404186479</v>
+        <v>1388.219242770479</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4584992214429103</v>
+        <v>0.4583301981827945</v>
       </c>
       <c r="T94">
         <v>7.555635454339425</v>
       </c>
       <c r="U94">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V94">
         <v>0.27</v>
       </c>
       <c r="W94">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.534956524586371</v>
+        <v>1.646183797054273</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.09739517614184587</v>
+        <v>0.09324041285610871</v>
       </c>
       <c r="C95">
-        <v>-1145.070502616099</v>
+        <v>-166.4086035897562</v>
       </c>
       <c r="D95">
-        <v>11225.6914973839</v>
+        <v>12204.35339641024</v>
       </c>
       <c r="E95">
         <v>7266.262000000002</v>
@@ -9077,37 +9077,37 @@
         <v>1971.45</v>
       </c>
       <c r="M95">
-        <v>1298.329152928193</v>
+        <v>1210.605284728193</v>
       </c>
       <c r="N95">
-        <v>673.1208470718072</v>
+        <v>760.8447152718072</v>
       </c>
       <c r="O95">
-        <v>181.742628709388</v>
+        <v>205.428073123388</v>
       </c>
       <c r="P95">
-        <v>491.3782183624193</v>
+        <v>555.4166421484192</v>
       </c>
       <c r="Q95">
-        <v>1314.67821836242</v>
+        <v>1378.716642148419</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5157619051753906</v>
+        <v>0.5155694296648594</v>
       </c>
       <c r="T95">
         <v>8.603992080521245</v>
       </c>
       <c r="U95">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V95">
         <v>0.27</v>
       </c>
       <c r="W95">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.518451615719851</v>
+        <v>1.628482896010679</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09747762386158897</v>
+        <v>0.09327837915092388</v>
       </c>
       <c r="C96">
-        <v>-1317.614239893837</v>
+        <v>-330.8018684880753</v>
       </c>
       <c r="D96">
-        <v>11207.78176010616</v>
+        <v>12194.59413151193</v>
       </c>
       <c r="E96">
         <v>7420.896000000002</v>
@@ -9159,37 +9159,37 @@
         <v>1971.45</v>
       </c>
       <c r="M96">
-        <v>1312.289681454302</v>
+        <v>1223.622545854302</v>
       </c>
       <c r="N96">
-        <v>659.1603185456977</v>
+        <v>747.8274541456976</v>
       </c>
       <c r="O96">
-        <v>177.9732860073384</v>
+        <v>201.9134126193384</v>
       </c>
       <c r="P96">
-        <v>481.1870325383593</v>
+        <v>545.9140415263593</v>
       </c>
       <c r="Q96">
-        <v>1304.487032538359</v>
+        <v>1369.214041526359</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5921121501520309</v>
+        <v>0.5918884049742795</v>
       </c>
       <c r="T96">
         <v>10.00180091543034</v>
       </c>
       <c r="U96">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V96">
         <v>0.27</v>
       </c>
       <c r="W96">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.502297875127087</v>
+        <v>1.611158609882906</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1088641215813321</v>
+        <v>0.09331634544573908</v>
       </c>
       <c r="C97">
-        <v>-3495.861322179342</v>
+        <v>-495.1795377792569</v>
       </c>
       <c r="D97">
-        <v>9184.16867782066</v>
+        <v>12184.85046222075</v>
       </c>
       <c r="E97">
         <v>7575.530000000003</v>
@@ -9241,45 +9241,45 @@
         <v>1971.45</v>
       </c>
       <c r="M97">
-        <v>1565.700958980412</v>
+        <v>1236.639806980412</v>
       </c>
       <c r="N97">
-        <v>405.7490410195878</v>
+        <v>734.8101930195878</v>
       </c>
       <c r="O97">
-        <v>109.5522410752887</v>
+        <v>198.3987521152887</v>
       </c>
       <c r="P97">
-        <v>296.1967999442991</v>
+        <v>536.4114409042991</v>
       </c>
       <c r="Q97">
-        <v>1119.496799944299</v>
+        <v>1359.711440904299</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6990024931193274</v>
+        <v>0.6987349704074677</v>
       </c>
       <c r="T97">
         <v>11.95873328430307</v>
       </c>
       <c r="U97">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V97">
         <v>0.27</v>
       </c>
       <c r="W97">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.259148491091053</v>
+        <v>1.594199045568349</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.134190246758262</v>
+        <v>0.09335431174055425</v>
       </c>
       <c r="C98">
-        <v>-6282.000653493327</v>
+        <v>-659.5416488168285</v>
       </c>
       <c r="D98">
-        <v>6552.663346506673</v>
+        <v>12175.12235118317</v>
       </c>
       <c r="E98">
         <v>7730.164000000002</v>
@@ -9323,45 +9323,45 @@
         <v>1971.45</v>
       </c>
       <c r="M98">
-        <v>2067.609074506522</v>
+        <v>1249.657068106521</v>
       </c>
       <c r="N98">
-        <v>-96.15907450652185</v>
+        <v>721.7929318934785</v>
       </c>
       <c r="O98">
-        <v>-25.9629501167609</v>
+        <v>194.8840916112392</v>
       </c>
       <c r="P98">
-        <v>-70.19612438976094</v>
+        <v>526.9088402822392</v>
       </c>
       <c r="Q98">
-        <v>753.1038756102392</v>
+        <v>1350.208840282239</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8725763532198402</v>
+        <v>0.8590048185572479</v>
       </c>
       <c r="T98">
-        <v>15.13649748443109</v>
+        <v>14.89413183761213</v>
       </c>
       <c r="U98">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V98">
-        <v>0.2574430082374457</v>
+        <v>0.27</v>
       </c>
       <c r="W98">
-        <v>0.1034241589890296</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.9534926231016507</v>
+        <v>1.577592805510345</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1351250578170272</v>
+        <v>0.09339227803536945</v>
       </c>
       <c r="C99">
-        <v>-6505.210060107976</v>
+        <v>-823.8882388351631</v>
       </c>
       <c r="D99">
-        <v>6484.087939892024</v>
+        <v>12165.40976116484</v>
       </c>
       <c r="E99">
         <v>7884.798000000002</v>
@@ -9405,45 +9405,45 @@
         <v>1971.45</v>
       </c>
       <c r="M99">
-        <v>2089.146669032631</v>
+        <v>1262.674329232631</v>
       </c>
       <c r="N99">
-        <v>-117.6966690326312</v>
+        <v>708.7756707673689</v>
       </c>
       <c r="O99">
-        <v>-31.77810063881044</v>
+        <v>191.3694311071896</v>
       </c>
       <c r="P99">
-        <v>-85.91856839382081</v>
+        <v>517.4062396601793</v>
       </c>
       <c r="Q99">
-        <v>737.3814316061794</v>
+        <v>1340.70623966018</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.148168470959787</v>
+        <v>1.126121232140217</v>
       </c>
       <c r="T99">
-        <v>20.18199664590811</v>
+        <v>19.78646275979394</v>
       </c>
       <c r="U99">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V99">
-        <v>0.2547889566061319</v>
+        <v>0.27</v>
       </c>
       <c r="W99">
-        <v>0.1037938182352923</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.9436628022449328</v>
+        <v>1.561328962154569</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1360598688757924</v>
+        <v>0.09343024433018464</v>
       </c>
       <c r="C100">
-        <v>-6726.999011557753</v>
+        <v>-988.2193449498845</v>
       </c>
       <c r="D100">
-        <v>6416.932988442248</v>
+        <v>12155.71265505012</v>
       </c>
       <c r="E100">
         <v>8039.432000000002</v>
@@ -9487,45 +9487,45 @@
         <v>1971.45</v>
       </c>
       <c r="M100">
-        <v>2110.684263558741</v>
+        <v>1275.691590358741</v>
       </c>
       <c r="N100">
-        <v>-139.2342635587411</v>
+        <v>695.7584096412593</v>
       </c>
       <c r="O100">
-        <v>-37.59325116086009</v>
+        <v>187.85477060314</v>
       </c>
       <c r="P100">
-        <v>-101.641012397881</v>
+        <v>507.9036390381193</v>
       </c>
       <c r="Q100">
-        <v>721.6589876021192</v>
+        <v>1331.203639038119</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.69935270643968</v>
+        <v>1.660354059306156</v>
       </c>
       <c r="T100">
-        <v>30.27299496886217</v>
+        <v>29.57112460415756</v>
       </c>
       <c r="U100">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V100">
-        <v>0.2521890692938244</v>
+        <v>0.27</v>
       </c>
       <c r="W100">
-        <v>0.1041559334153049</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.9340335899771273</v>
+        <v>1.545397033969318</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1369946799345576</v>
+        <v>0.09346821062499983</v>
       </c>
       <c r="C101">
-        <v>-6947.411189903854</v>
+        <v>-1152.535004158386</v>
       </c>
       <c r="D101">
-        <v>6351.154810096146</v>
+        <v>12146.03099584161</v>
       </c>
       <c r="E101">
         <v>8194.066000000003</v>
@@ -9569,45 +9569,45 @@
         <v>1971.45</v>
       </c>
       <c r="M101">
-        <v>2132.22185808485</v>
+        <v>1288.70885148485</v>
       </c>
       <c r="N101">
-        <v>-160.7718580848505</v>
+        <v>682.7411485151497</v>
       </c>
       <c r="O101">
-        <v>-43.40840168290963</v>
+        <v>184.3401100990904</v>
       </c>
       <c r="P101">
-        <v>-117.3634564019408</v>
+        <v>498.4010384160592</v>
       </c>
       <c r="Q101">
-        <v>705.9365435980593</v>
+        <v>1321.701038416059</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.35290541287936</v>
+        <v>3.263052540803971</v>
       </c>
       <c r="T101">
-        <v>60.54598993772434</v>
+        <v>58.92511013724842</v>
       </c>
       <c r="U101">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V101">
-        <v>0.2496417049575231</v>
+        <v>0.27</v>
       </c>
       <c r="W101">
-        <v>0.1045107331371353</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.9245989072500856</v>
+        <v>1.529786962919123</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08970954743829636</v>
+        <v>0.08956136373311155</v>
       </c>
       <c r="C2">
-        <v>15195.93288830094</v>
+        <v>15085.94810825857</v>
       </c>
       <c r="D2">
-        <v>13185.73288830094</v>
+        <v>13230.38210825857</v>
       </c>
       <c r="E2">
-        <v>-7114.7</v>
+        <v>-6960.066</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>154.634</v>
       </c>
       <c r="G2">
         <v>2010.2</v>
@@ -1451,28 +1451,28 @@
         <v>1971.45</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>9.074094126109598</v>
       </c>
       <c r="N2">
-        <v>1971.45</v>
+        <v>1962.37590587389</v>
       </c>
       <c r="O2">
-        <v>532.2915</v>
+        <v>529.8414945859504</v>
       </c>
       <c r="P2">
-        <v>1439.1585</v>
+        <v>1432.53441128794</v>
       </c>
       <c r="Q2">
-        <v>2262.4585</v>
+        <v>2255.83441128794</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08970954743829636</v>
+        <v>0.09003332490930602</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8101488798160107</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>217.2613566270371</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08956136373311155</v>
+        <v>0.08941318002792673</v>
       </c>
       <c r="C3">
-        <v>15085.94810825857</v>
+        <v>14976.26673589447</v>
       </c>
       <c r="D3">
-        <v>13230.38210825857</v>
+        <v>13275.33473589447</v>
       </c>
       <c r="E3">
-        <v>-6960.066</v>
+        <v>-6805.432</v>
       </c>
       <c r="F3">
-        <v>154.634</v>
+        <v>309.268</v>
       </c>
       <c r="G3">
         <v>2010.2</v>
@@ -1533,28 +1533,28 @@
         <v>1971.45</v>
       </c>
       <c r="M3">
-        <v>9.074094126109598</v>
+        <v>18.1481882522192</v>
       </c>
       <c r="N3">
-        <v>1962.37590587389</v>
+        <v>1953.301811747781</v>
       </c>
       <c r="O3">
-        <v>529.8414945859504</v>
+        <v>527.3914891719008</v>
       </c>
       <c r="P3">
-        <v>1432.53441128794</v>
+        <v>1425.91032257588</v>
       </c>
       <c r="Q3">
-        <v>2255.83441128794</v>
+        <v>2249.21032257588</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09003332490930602</v>
+        <v>0.09036371008380567</v>
       </c>
       <c r="T3">
-        <v>0.8101488798160107</v>
+        <v>0.8162000003134525</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>217.2613566270371</v>
+        <v>108.6306783135185</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08941318002792673</v>
+        <v>0.08926499632274192</v>
       </c>
       <c r="C4">
-        <v>14976.26673589447</v>
+        <v>14866.89187440046</v>
       </c>
       <c r="D4">
-        <v>13275.33473589447</v>
+        <v>13320.59387440046</v>
       </c>
       <c r="E4">
-        <v>-6805.432</v>
+        <v>-6650.798</v>
       </c>
       <c r="F4">
-        <v>309.268</v>
+        <v>463.902</v>
       </c>
       <c r="G4">
         <v>2010.2</v>
@@ -1615,28 +1615,28 @@
         <v>1971.45</v>
       </c>
       <c r="M4">
-        <v>18.1481882522192</v>
+        <v>27.2222823783288</v>
       </c>
       <c r="N4">
-        <v>1953.301811747781</v>
+        <v>1944.227717621671</v>
       </c>
       <c r="O4">
-        <v>527.3914891719008</v>
+        <v>524.9414837578512</v>
       </c>
       <c r="P4">
-        <v>1425.91032257588</v>
+        <v>1419.28623386382</v>
       </c>
       <c r="Q4">
-        <v>2249.21032257588</v>
+        <v>2242.58623386382</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09036371008380567</v>
+        <v>0.09070090732375893</v>
       </c>
       <c r="T4">
-        <v>0.8162000003134525</v>
+        <v>0.8223758861819758</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.6306783135185</v>
+        <v>72.42045220901235</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08926499632274192</v>
+        <v>0.08911681261755711</v>
       </c>
       <c r="C5">
-        <v>14866.89187440046</v>
+        <v>14757.82666943158</v>
       </c>
       <c r="D5">
-        <v>13320.59387440046</v>
+        <v>13366.16266943158</v>
       </c>
       <c r="E5">
-        <v>-6650.798</v>
+        <v>-6496.164</v>
       </c>
       <c r="F5">
-        <v>463.902</v>
+        <v>618.5360000000001</v>
       </c>
       <c r="G5">
         <v>2010.2</v>
@@ -1697,28 +1697,28 @@
         <v>1971.45</v>
       </c>
       <c r="M5">
-        <v>27.2222823783288</v>
+        <v>36.29637650443839</v>
       </c>
       <c r="N5">
-        <v>1944.227717621671</v>
+        <v>1935.153623495562</v>
       </c>
       <c r="O5">
-        <v>524.9414837578512</v>
+        <v>522.4914783438016</v>
       </c>
       <c r="P5">
-        <v>1419.28623386382</v>
+        <v>1412.66214515176</v>
       </c>
       <c r="Q5">
-        <v>2242.58623386382</v>
+        <v>2235.96214515176</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09070090732375893</v>
+        <v>0.09104512950621121</v>
       </c>
       <c r="T5">
-        <v>0.8223758861819758</v>
+        <v>0.8286804363394266</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.42045220901235</v>
+        <v>54.31533915675927</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08911681261755711</v>
+        <v>0.08896862891237228</v>
       </c>
       <c r="C6">
-        <v>14757.82666943158</v>
+        <v>14649.07430983484</v>
       </c>
       <c r="D6">
-        <v>13366.16266943158</v>
+        <v>13412.04430983484</v>
       </c>
       <c r="E6">
-        <v>-6496.164</v>
+        <v>-6341.53</v>
       </c>
       <c r="F6">
-        <v>618.5360000000001</v>
+        <v>773.1700000000001</v>
       </c>
       <c r="G6">
         <v>2010.2</v>
@@ -1779,28 +1779,28 @@
         <v>1971.45</v>
       </c>
       <c r="M6">
-        <v>36.29637650443839</v>
+        <v>45.37047063054799</v>
       </c>
       <c r="N6">
-        <v>1935.153623495562</v>
+        <v>1926.079529369452</v>
       </c>
       <c r="O6">
-        <v>522.4914783438016</v>
+        <v>520.041472929752</v>
       </c>
       <c r="P6">
-        <v>1412.66214515176</v>
+        <v>1406.0380564397</v>
       </c>
       <c r="Q6">
-        <v>2235.96214515176</v>
+        <v>2229.3380564397</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09104512950621121</v>
+        <v>0.09139659847145196</v>
       </c>
       <c r="T6">
-        <v>0.8286804363394266</v>
+        <v>0.8351177138686131</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.31533915675927</v>
+        <v>43.45227132540742</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08896862891237228</v>
+        <v>0.08882044520718747</v>
       </c>
       <c r="C7">
-        <v>14649.07430983484</v>
+        <v>14540.63802839314</v>
       </c>
       <c r="D7">
-        <v>13412.04430983484</v>
+        <v>13458.24202839314</v>
       </c>
       <c r="E7">
-        <v>-6341.53</v>
+        <v>-6186.896</v>
       </c>
       <c r="F7">
-        <v>773.1700000000001</v>
+        <v>927.8040000000002</v>
       </c>
       <c r="G7">
         <v>2010.2</v>
@@ -1861,28 +1861,28 @@
         <v>1971.45</v>
       </c>
       <c r="M7">
-        <v>45.37047063054799</v>
+        <v>54.4445647566576</v>
       </c>
       <c r="N7">
-        <v>1926.079529369452</v>
+        <v>1917.005435243342</v>
       </c>
       <c r="O7">
-        <v>520.041472929752</v>
+        <v>517.5914675157024</v>
       </c>
       <c r="P7">
-        <v>1406.0380564397</v>
+        <v>1399.41396772764</v>
       </c>
       <c r="Q7">
-        <v>2229.3380564397</v>
+        <v>2222.71396772764</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09139659847145196</v>
+        <v>0.09175554549978293</v>
       </c>
       <c r="T7">
-        <v>0.8351177138686131</v>
+        <v>0.8416919547494847</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.45227132540742</v>
+        <v>36.21022610450618</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08882044520718747</v>
+        <v>0.08867226150200266</v>
       </c>
       <c r="C8">
-        <v>14540.63802839314</v>
+        <v>14432.52110258452</v>
       </c>
       <c r="D8">
-        <v>13458.24202839314</v>
+        <v>13504.75910258452</v>
       </c>
       <c r="E8">
-        <v>-6186.896</v>
+        <v>-6032.262</v>
       </c>
       <c r="F8">
-        <v>927.8040000000001</v>
+        <v>1082.438</v>
       </c>
       <c r="G8">
         <v>2010.2</v>
@@ -1943,28 +1943,28 @@
         <v>1971.45</v>
       </c>
       <c r="M8">
-        <v>54.44456475665759</v>
+        <v>63.51865888276718</v>
       </c>
       <c r="N8">
-        <v>1917.005435243342</v>
+        <v>1907.931341117233</v>
       </c>
       <c r="O8">
-        <v>517.5914675157024</v>
+        <v>515.1414621016529</v>
       </c>
       <c r="P8">
-        <v>1399.41396772764</v>
+        <v>1392.78987901558</v>
       </c>
       <c r="Q8">
-        <v>2222.71396772764</v>
+        <v>2216.08987901558</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09175554549978293</v>
+        <v>0.09212221181904576</v>
       </c>
       <c r="T8">
-        <v>0.8416919547494847</v>
+        <v>0.8484075771546757</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.21022610450618</v>
+        <v>31.0373366610053</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08867226150200265</v>
+        <v>0.08852407779681785</v>
       </c>
       <c r="C9">
-        <v>14432.52110258453</v>
+        <v>14324.72685535733</v>
       </c>
       <c r="D9">
-        <v>13504.75910258453</v>
+        <v>13551.59885535733</v>
       </c>
       <c r="E9">
-        <v>-6032.262</v>
+        <v>-5877.628</v>
       </c>
       <c r="F9">
-        <v>1082.438</v>
+        <v>1237.072</v>
       </c>
       <c r="G9">
         <v>2010.2</v>
@@ -2025,28 +2025,28 @@
         <v>1971.45</v>
       </c>
       <c r="M9">
-        <v>63.51865888276718</v>
+        <v>72.59275300887678</v>
       </c>
       <c r="N9">
-        <v>1907.931341117233</v>
+        <v>1898.857246991123</v>
       </c>
       <c r="O9">
-        <v>515.1414621016529</v>
+        <v>512.6914566876032</v>
       </c>
       <c r="P9">
-        <v>1392.78987901558</v>
+        <v>1386.16579030352</v>
       </c>
       <c r="Q9">
-        <v>2216.08987901558</v>
+        <v>2209.46579030352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09212221181904576</v>
+        <v>0.09249684914524908</v>
       </c>
       <c r="T9">
-        <v>0.8484075771546757</v>
+        <v>0.8552691913512842</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.0373366610053</v>
+        <v>27.15766957837964</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08852407779681785</v>
+        <v>0.08837589409163303</v>
       </c>
       <c r="C10">
-        <v>14324.72685535733</v>
+        <v>14217.25865592146</v>
       </c>
       <c r="D10">
-        <v>13551.59885535733</v>
+        <v>13598.76465592146</v>
       </c>
       <c r="E10">
-        <v>-5877.628</v>
+        <v>-5722.994</v>
       </c>
       <c r="F10">
-        <v>1237.072</v>
+        <v>1391.706</v>
       </c>
       <c r="G10">
         <v>2010.2</v>
@@ -2107,28 +2107,28 @@
         <v>1971.45</v>
       </c>
       <c r="M10">
-        <v>72.59275300887678</v>
+        <v>81.66684713498638</v>
       </c>
       <c r="N10">
-        <v>1898.857246991123</v>
+        <v>1889.783152865013</v>
       </c>
       <c r="O10">
-        <v>512.6914566876032</v>
+        <v>510.2414512735537</v>
       </c>
       <c r="P10">
-        <v>1386.16579030352</v>
+        <v>1379.54170159146</v>
       </c>
       <c r="Q10">
-        <v>2209.46579030352</v>
+        <v>2202.84170159146</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09249684914524908</v>
+        <v>0.09287972025884149</v>
       </c>
       <c r="T10">
-        <v>0.8552691913512842</v>
+        <v>0.8622816102555104</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.15766957837964</v>
+        <v>24.14015073633745</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08837589409163303</v>
+        <v>0.08822771038644821</v>
       </c>
       <c r="C11">
-        <v>14217.25865592146</v>
+        <v>14110.11992055621</v>
       </c>
       <c r="D11">
-        <v>13598.76465592146</v>
+        <v>13646.25992055621</v>
       </c>
       <c r="E11">
-        <v>-5722.994</v>
+        <v>-5568.36</v>
       </c>
       <c r="F11">
-        <v>1391.706</v>
+        <v>1546.34</v>
       </c>
       <c r="G11">
         <v>2010.2</v>
@@ -2189,28 +2189,28 @@
         <v>1971.45</v>
       </c>
       <c r="M11">
-        <v>81.66684713498638</v>
+        <v>90.74094126109597</v>
       </c>
       <c r="N11">
-        <v>1889.783152865013</v>
+        <v>1880.709058738904</v>
       </c>
       <c r="O11">
-        <v>510.2414512735537</v>
+        <v>507.7914458595041</v>
       </c>
       <c r="P11">
-        <v>1379.54170159146</v>
+        <v>1372.9176128794</v>
       </c>
       <c r="Q11">
-        <v>2202.84170159146</v>
+        <v>2196.2176128794</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09287972025884149</v>
+        <v>0.09327109961940261</v>
       </c>
       <c r="T11">
-        <v>0.8622816102555104</v>
+        <v>0.8694498606909417</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.14015073633745</v>
+        <v>21.72613566270371</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08822771038644821</v>
+        <v>0.08807952668126341</v>
       </c>
       <c r="C12">
-        <v>14110.11992055621</v>
+        <v>14003.31411343517</v>
       </c>
       <c r="D12">
-        <v>13646.25992055621</v>
+        <v>13694.08811343517</v>
       </c>
       <c r="E12">
-        <v>-5568.36</v>
+        <v>-5413.726</v>
       </c>
       <c r="F12">
-        <v>1546.34</v>
+        <v>1700.974</v>
       </c>
       <c r="G12">
         <v>2010.2</v>
@@ -2271,28 +2271,28 @@
         <v>1971.45</v>
       </c>
       <c r="M12">
-        <v>90.74094126109598</v>
+        <v>99.81503538720558</v>
       </c>
       <c r="N12">
-        <v>1880.709058738904</v>
+        <v>1871.634964612794</v>
       </c>
       <c r="O12">
-        <v>507.7914458595041</v>
+        <v>505.3414404454545</v>
       </c>
       <c r="P12">
-        <v>1372.9176128794</v>
+        <v>1366.29352416734</v>
       </c>
       <c r="Q12">
-        <v>2196.2176128794</v>
+        <v>2189.59352416734</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09327109961940261</v>
+        <v>0.09367127402177411</v>
       </c>
       <c r="T12">
-        <v>0.8694498606909417</v>
+        <v>0.8767791954058208</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.72613566270371</v>
+        <v>19.75103242063973</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08807952668126341</v>
+        <v>0.0879313429760786</v>
       </c>
       <c r="C13">
-        <v>14003.31411343517</v>
+        <v>13896.84474746851</v>
       </c>
       <c r="D13">
-        <v>13694.08811343517</v>
+        <v>13742.25274746851</v>
       </c>
       <c r="E13">
-        <v>-5413.726</v>
+        <v>-5259.092</v>
       </c>
       <c r="F13">
-        <v>1700.974</v>
+        <v>1855.608</v>
       </c>
       <c r="G13">
         <v>2010.2</v>
@@ -2353,28 +2353,28 @@
         <v>1971.45</v>
       </c>
       <c r="M13">
-        <v>99.81503538720558</v>
+        <v>108.8891295133152</v>
       </c>
       <c r="N13">
-        <v>1871.634964612794</v>
+        <v>1862.560870486685</v>
       </c>
       <c r="O13">
-        <v>505.3414404454545</v>
+        <v>502.8914350314049</v>
       </c>
       <c r="P13">
-        <v>1366.29352416734</v>
+        <v>1359.66943545528</v>
       </c>
       <c r="Q13">
-        <v>2189.59352416734</v>
+        <v>2182.96943545528</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09367127402177411</v>
+        <v>0.09408054329692678</v>
       </c>
       <c r="T13">
-        <v>0.8767791954058208</v>
+        <v>0.8842751059096745</v>
       </c>
       <c r="U13">
         <v>0.05868110587651873</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.75103242063973</v>
+        <v>18.10511305225309</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0879313429760786</v>
+        <v>0.08778315927089378</v>
       </c>
       <c r="C14">
-        <v>13896.84474746851</v>
+        <v>13790.71538516304</v>
       </c>
       <c r="D14">
-        <v>13742.25274746851</v>
+        <v>13790.75738516304</v>
       </c>
       <c r="E14">
-        <v>-5259.092</v>
+        <v>-5104.458</v>
       </c>
       <c r="F14">
-        <v>1855.608</v>
+        <v>2010.242</v>
       </c>
       <c r="G14">
         <v>2010.2</v>
@@ -2435,28 +2435,28 @@
         <v>1971.45</v>
       </c>
       <c r="M14">
-        <v>108.8891295133152</v>
+        <v>117.9632236394248</v>
       </c>
       <c r="N14">
-        <v>1862.560870486685</v>
+        <v>1853.486776360575</v>
       </c>
       <c r="O14">
-        <v>502.8914350314049</v>
+        <v>500.4414296173553</v>
       </c>
       <c r="P14">
-        <v>1359.66943545528</v>
+        <v>1353.04534674322</v>
       </c>
       <c r="Q14">
-        <v>2182.96943545528</v>
+        <v>2176.34534674322</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09408054329692678</v>
+        <v>0.0944992210611634</v>
       </c>
       <c r="T14">
-        <v>0.8842751059096745</v>
+        <v>0.8919433361952258</v>
       </c>
       <c r="U14">
         <v>0.05868110587651873</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.10511305225309</v>
+        <v>16.71241204823362</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08778315927089378</v>
+        <v>0.08763497556570896</v>
       </c>
       <c r="C15">
-        <v>13790.71538516304</v>
+        <v>13684.92963950058</v>
       </c>
       <c r="D15">
-        <v>13790.75738516304</v>
+        <v>13839.60563950058</v>
       </c>
       <c r="E15">
-        <v>-5104.458</v>
+        <v>-4949.824</v>
       </c>
       <c r="F15">
-        <v>2010.242</v>
+        <v>2164.876</v>
       </c>
       <c r="G15">
         <v>2010.2</v>
@@ -2517,28 +2517,28 @@
         <v>1971.45</v>
       </c>
       <c r="M15">
-        <v>117.9632236394248</v>
+        <v>127.0373177655344</v>
       </c>
       <c r="N15">
-        <v>1853.486776360575</v>
+        <v>1844.412682234465</v>
       </c>
       <c r="O15">
-        <v>500.4414296173553</v>
+        <v>497.9914242033057</v>
       </c>
       <c r="P15">
-        <v>1353.04534674322</v>
+        <v>1346.42125803116</v>
       </c>
       <c r="Q15">
-        <v>2176.34534674322</v>
+        <v>2169.72125803116</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0944992210611634</v>
+        <v>0.09492763551759158</v>
       </c>
       <c r="T15">
-        <v>0.8919433361952258</v>
+        <v>0.8997898974176506</v>
       </c>
       <c r="U15">
         <v>0.05868110587651873</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.71241204823362</v>
+        <v>15.51866833050265</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08763497556570896</v>
+        <v>0.08748679186052417</v>
       </c>
       <c r="C16">
-        <v>13684.92963950058</v>
+        <v>13579.4911748351</v>
       </c>
       <c r="D16">
-        <v>13839.60563950058</v>
+        <v>13888.8011748351</v>
       </c>
       <c r="E16">
-        <v>-4949.824</v>
+        <v>-4795.189999999999</v>
       </c>
       <c r="F16">
-        <v>2164.876</v>
+        <v>2319.510000000001</v>
       </c>
       <c r="G16">
         <v>2010.2</v>
@@ -2599,28 +2599,28 @@
         <v>1971.45</v>
       </c>
       <c r="M16">
-        <v>127.0373177655344</v>
+        <v>136.111411891644</v>
       </c>
       <c r="N16">
-        <v>1844.412682234465</v>
+        <v>1835.338588108356</v>
       </c>
       <c r="O16">
-        <v>497.9914242033057</v>
+        <v>495.5414187892561</v>
       </c>
       <c r="P16">
-        <v>1346.42125803116</v>
+        <v>1339.7971693191</v>
       </c>
       <c r="Q16">
-        <v>2169.72125803116</v>
+        <v>2163.0971693191</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09492763551759158</v>
+        <v>0.09536613031417102</v>
       </c>
       <c r="T16">
-        <v>0.8997898974176506</v>
+        <v>0.9078210836100148</v>
       </c>
       <c r="U16">
         <v>0.05868110587651873</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.51866833050265</v>
+        <v>14.48409044180247</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08748679186052416</v>
+        <v>0.08733860815533935</v>
       </c>
       <c r="C17">
-        <v>13579.49117483511</v>
+        <v>13474.4037078091</v>
       </c>
       <c r="D17">
-        <v>13888.80117483511</v>
+        <v>13938.34770780909</v>
       </c>
       <c r="E17">
-        <v>-4795.19</v>
+        <v>-4640.556</v>
       </c>
       <c r="F17">
-        <v>2319.51</v>
+        <v>2474.144</v>
       </c>
       <c r="G17">
         <v>2010.2</v>
@@ -2681,28 +2681,28 @@
         <v>1971.45</v>
       </c>
       <c r="M17">
-        <v>136.111411891644</v>
+        <v>145.1855060177536</v>
       </c>
       <c r="N17">
-        <v>1835.338588108356</v>
+        <v>1826.264493982246</v>
       </c>
       <c r="O17">
-        <v>495.5414187892561</v>
+        <v>493.0914133752065</v>
       </c>
       <c r="P17">
-        <v>1339.7971693191</v>
+        <v>1333.17308060704</v>
       </c>
       <c r="Q17">
-        <v>2163.0971693191</v>
+        <v>2156.47308060704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09536613031417102</v>
+        <v>0.09581506546304995</v>
       </c>
       <c r="T17">
-        <v>0.9078210836100148</v>
+        <v>0.9160434885212447</v>
       </c>
       <c r="U17">
         <v>0.05868110587651873</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.48409044180247</v>
+        <v>13.57883478918982</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08733860815533935</v>
+        <v>0.08719042445015453</v>
       </c>
       <c r="C18">
-        <v>13474.4037078091</v>
+        <v>13369.67100828948</v>
       </c>
       <c r="D18">
-        <v>13938.34770780909</v>
+        <v>13988.24900828947</v>
       </c>
       <c r="E18">
-        <v>-4640.556</v>
+        <v>-4485.922</v>
       </c>
       <c r="F18">
-        <v>2474.144</v>
+        <v>2628.778</v>
       </c>
       <c r="G18">
         <v>2010.2</v>
@@ -2763,28 +2763,28 @@
         <v>1971.45</v>
       </c>
       <c r="M18">
-        <v>145.1855060177536</v>
+        <v>154.2596001438632</v>
       </c>
       <c r="N18">
-        <v>1826.264493982246</v>
+        <v>1817.190399856137</v>
       </c>
       <c r="O18">
-        <v>493.0914133752065</v>
+        <v>490.6414079611569</v>
       </c>
       <c r="P18">
-        <v>1333.17308060704</v>
+        <v>1326.54899189498</v>
       </c>
       <c r="Q18">
-        <v>2156.47308060704</v>
+        <v>2149.84899189498</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09581506546304995</v>
+        <v>0.0962748183263597</v>
       </c>
       <c r="T18">
-        <v>0.9160434885212447</v>
+        <v>0.9244640236712994</v>
       </c>
       <c r="U18">
         <v>0.05868110587651873</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.57883478918982</v>
+        <v>12.78007980159042</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08719042445015453</v>
+        <v>0.0870422407449697</v>
       </c>
       <c r="C19">
-        <v>13369.67100828948</v>
+        <v>13265.29690032381</v>
       </c>
       <c r="D19">
-        <v>13988.24900828947</v>
+        <v>14038.50890032381</v>
       </c>
       <c r="E19">
-        <v>-4485.922</v>
+        <v>-4331.287999999999</v>
       </c>
       <c r="F19">
-        <v>2628.778</v>
+        <v>2783.412000000001</v>
       </c>
       <c r="G19">
         <v>2010.2</v>
@@ -2845,28 +2845,28 @@
         <v>1971.45</v>
       </c>
       <c r="M19">
-        <v>154.2596001438632</v>
+        <v>163.3336942699728</v>
       </c>
       <c r="N19">
-        <v>1817.190399856137</v>
+        <v>1808.116305730027</v>
       </c>
       <c r="O19">
-        <v>490.6414079611569</v>
+        <v>488.1914025471073</v>
       </c>
       <c r="P19">
-        <v>1326.54899189498</v>
+        <v>1319.92490318292</v>
       </c>
       <c r="Q19">
-        <v>2149.84899189498</v>
+        <v>2143.22490318292</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0962748183263597</v>
+        <v>0.09674578467414043</v>
       </c>
       <c r="T19">
-        <v>0.9244640236712994</v>
+        <v>0.933089937727453</v>
       </c>
       <c r="U19">
         <v>0.05868110587651873</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.78007980159042</v>
+        <v>12.07007536816872</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08704224074496972</v>
+        <v>0.08689405703978491</v>
       </c>
       <c r="C20">
-        <v>13265.29690032381</v>
+        <v>13161.28526311719</v>
       </c>
       <c r="D20">
-        <v>14038.50890032381</v>
+        <v>14089.13126311719</v>
       </c>
       <c r="E20">
-        <v>-4331.288</v>
+        <v>-4176.654</v>
       </c>
       <c r="F20">
-        <v>2783.412</v>
+        <v>2938.046</v>
       </c>
       <c r="G20">
         <v>2010.2</v>
@@ -2927,28 +2927,28 @@
         <v>1971.45</v>
       </c>
       <c r="M20">
-        <v>163.3336942699728</v>
+        <v>172.4077883960824</v>
       </c>
       <c r="N20">
-        <v>1808.116305730027</v>
+        <v>1799.042211603917</v>
       </c>
       <c r="O20">
-        <v>488.1914025471073</v>
+        <v>485.7413971330577</v>
       </c>
       <c r="P20">
-        <v>1319.92490318292</v>
+        <v>1313.30081447086</v>
       </c>
       <c r="Q20">
-        <v>2143.22490318292</v>
+        <v>2136.60081447086</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09674578467414043</v>
+        <v>0.09722837982063179</v>
       </c>
       <c r="T20">
-        <v>0.933089937727453</v>
+        <v>0.9419288373158574</v>
       </c>
       <c r="U20">
         <v>0.05868110587651873</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.07007536816873</v>
+        <v>11.43480824352827</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08689405703978491</v>
+        <v>0.08674587333460011</v>
       </c>
       <c r="C21">
-        <v>13161.28526311719</v>
+        <v>13057.6400320303</v>
       </c>
       <c r="D21">
-        <v>14089.13126311719</v>
+        <v>14140.1200320303</v>
       </c>
       <c r="E21">
-        <v>-4176.654</v>
+        <v>-4022.02</v>
       </c>
       <c r="F21">
-        <v>2938.046</v>
+        <v>3092.68</v>
       </c>
       <c r="G21">
         <v>2010.2</v>
@@ -3009,28 +3009,28 @@
         <v>1971.45</v>
       </c>
       <c r="M21">
-        <v>172.4077883960824</v>
+        <v>181.481882522192</v>
       </c>
       <c r="N21">
-        <v>1799.042211603917</v>
+        <v>1789.968117477808</v>
       </c>
       <c r="O21">
-        <v>485.7413971330577</v>
+        <v>483.2913917190082</v>
       </c>
       <c r="P21">
-        <v>1313.30081447086</v>
+        <v>1306.6767257588</v>
       </c>
       <c r="Q21">
-        <v>2136.60081447086</v>
+        <v>2129.9767257588</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09722837982063179</v>
+        <v>0.09772303984578545</v>
       </c>
       <c r="T21">
-        <v>0.9419288373158574</v>
+        <v>0.950988709393972</v>
       </c>
       <c r="U21">
         <v>0.05868110587651873</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.43480824352827</v>
+        <v>10.86306783135185</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08674587333460011</v>
+        <v>0.08659768962941529</v>
       </c>
       <c r="C22">
-        <v>13057.6400320303</v>
+        <v>12954.36519959929</v>
       </c>
       <c r="D22">
-        <v>14140.1200320303</v>
+        <v>14191.47919959929</v>
       </c>
       <c r="E22">
-        <v>-4022.02</v>
+        <v>-3867.385999999999</v>
       </c>
       <c r="F22">
-        <v>3092.68</v>
+        <v>3247.314000000001</v>
       </c>
       <c r="G22">
         <v>2010.2</v>
@@ -3091,28 +3091,28 @@
         <v>1971.45</v>
       </c>
       <c r="M22">
-        <v>181.481882522192</v>
+        <v>190.5559766483016</v>
       </c>
       <c r="N22">
-        <v>1789.968117477808</v>
+        <v>1780.894023351698</v>
       </c>
       <c r="O22">
-        <v>483.2913917190082</v>
+        <v>480.8413863049586</v>
       </c>
       <c r="P22">
-        <v>1306.6767257588</v>
+        <v>1300.05263704674</v>
       </c>
       <c r="Q22">
-        <v>2129.9767257588</v>
+        <v>2123.35263704674</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09772303984578545</v>
+        <v>0.09823022290955058</v>
       </c>
       <c r="T22">
-        <v>0.950988709393972</v>
+        <v>0.9602779453221653</v>
       </c>
       <c r="U22">
         <v>0.05868110587651873</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.86306783135185</v>
+        <v>10.34577888700176</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08659768962941529</v>
+        <v>0.08644950592423047</v>
       </c>
       <c r="C23">
-        <v>12954.36519959929</v>
+        <v>12851.4648165778</v>
       </c>
       <c r="D23">
-        <v>14191.47919959929</v>
+        <v>14243.2128165778</v>
       </c>
       <c r="E23">
-        <v>-3867.386</v>
+        <v>-3712.751999999999</v>
       </c>
       <c r="F23">
-        <v>3247.314</v>
+        <v>3401.948</v>
       </c>
       <c r="G23">
         <v>2010.2</v>
@@ -3173,28 +3173,28 @@
         <v>1971.45</v>
       </c>
       <c r="M23">
-        <v>190.5559766483016</v>
+        <v>199.6300707744112</v>
       </c>
       <c r="N23">
-        <v>1780.894023351698</v>
+        <v>1771.819929225589</v>
       </c>
       <c r="O23">
-        <v>480.8413863049586</v>
+        <v>478.3913808909089</v>
       </c>
       <c r="P23">
-        <v>1300.05263704674</v>
+        <v>1293.42854833468</v>
       </c>
       <c r="Q23">
-        <v>2123.35263704674</v>
+        <v>2116.72854833468</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09823022290955058</v>
+        <v>0.0987504106672584</v>
       </c>
       <c r="T23">
-        <v>0.9602779453221653</v>
+        <v>0.9698053667869789</v>
       </c>
       <c r="U23">
         <v>0.05868110587651873</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.34577888700177</v>
+        <v>9.875516210319867</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08644950592423047</v>
+        <v>0.08630132221904566</v>
       </c>
       <c r="C24">
-        <v>12851.4648165778</v>
+        <v>12748.9429930021</v>
       </c>
       <c r="D24">
-        <v>14243.2128165778</v>
+        <v>14295.3249930021</v>
       </c>
       <c r="E24">
-        <v>-3712.751999999999</v>
+        <v>-3558.117999999999</v>
       </c>
       <c r="F24">
-        <v>3401.948</v>
+        <v>3556.582</v>
       </c>
       <c r="G24">
         <v>2010.2</v>
@@ -3255,28 +3255,28 @@
         <v>1971.45</v>
       </c>
       <c r="M24">
-        <v>199.6300707744112</v>
+        <v>208.7041649005208</v>
       </c>
       <c r="N24">
-        <v>1771.819929225589</v>
+        <v>1762.745835099479</v>
       </c>
       <c r="O24">
-        <v>478.3913808909089</v>
+        <v>475.9413754768594</v>
       </c>
       <c r="P24">
-        <v>1293.42854833468</v>
+        <v>1286.80445962262</v>
       </c>
       <c r="Q24">
-        <v>2116.72854833468</v>
+        <v>2110.10445962262</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0987504106672584</v>
+        <v>0.09928410979529631</v>
       </c>
       <c r="T24">
-        <v>0.9698053667869789</v>
+        <v>0.9795802537443851</v>
       </c>
       <c r="U24">
         <v>0.05868110587651873</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.875516210319867</v>
+        <v>9.446145940305961</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08630132221904566</v>
+        <v>0.08615313851386083</v>
       </c>
       <c r="C25">
-        <v>12748.9429930021</v>
+        <v>12646.8038992795</v>
       </c>
       <c r="D25">
-        <v>14295.3249930021</v>
+        <v>14347.8198992795</v>
       </c>
       <c r="E25">
-        <v>-3558.117999999999</v>
+        <v>-3403.483999999999</v>
       </c>
       <c r="F25">
-        <v>3556.582</v>
+        <v>3711.216000000001</v>
       </c>
       <c r="G25">
         <v>2010.2</v>
@@ -3337,28 +3337,28 @@
         <v>1971.45</v>
       </c>
       <c r="M25">
-        <v>208.7041649005208</v>
+        <v>217.7782590266304</v>
       </c>
       <c r="N25">
-        <v>1762.745835099479</v>
+        <v>1753.671740973369</v>
       </c>
       <c r="O25">
-        <v>475.9413754768594</v>
+        <v>473.4913700628098</v>
       </c>
       <c r="P25">
-        <v>1286.80445962262</v>
+        <v>1280.18037091056</v>
       </c>
       <c r="Q25">
-        <v>2110.10445962262</v>
+        <v>2103.48037091056</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09928410979529631</v>
+        <v>0.09983185363722993</v>
       </c>
       <c r="T25">
-        <v>0.9795802537443851</v>
+        <v>0.9896123745690915</v>
       </c>
       <c r="U25">
         <v>0.05868110587651873</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.446145940305961</v>
+        <v>9.052556526126544</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08615313851386083</v>
+        <v>0.08627870480867603</v>
       </c>
       <c r="C26">
-        <v>12646.8038992795</v>
+        <v>12447.662482554</v>
       </c>
       <c r="D26">
-        <v>14347.8198992795</v>
+        <v>14303.312482554</v>
       </c>
       <c r="E26">
-        <v>-3403.483999999999</v>
+        <v>-3248.849999999999</v>
       </c>
       <c r="F26">
-        <v>3711.216</v>
+        <v>3865.85</v>
       </c>
       <c r="G26">
         <v>2010.2</v>
@@ -3419,45 +3419,45 @@
         <v>1971.45</v>
       </c>
       <c r="M26">
-        <v>217.7782590266304</v>
+        <v>232.6511281527399</v>
       </c>
       <c r="N26">
-        <v>1753.671740973369</v>
+        <v>1738.79887184726</v>
       </c>
       <c r="O26">
-        <v>473.4913700628098</v>
+        <v>469.4756953987602</v>
       </c>
       <c r="P26">
-        <v>1280.18037091056</v>
+        <v>1269.323176448499</v>
       </c>
       <c r="Q26">
-        <v>2103.48037091056</v>
+        <v>2092.6231764485</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09983185363722993</v>
+        <v>0.1003942039816151</v>
       </c>
       <c r="T26">
-        <v>0.9896123745690915</v>
+        <v>0.9999120186157902</v>
       </c>
       <c r="U26">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.04283720728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>9.052556526126544</v>
+        <v>8.473846723432628</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08627870480867603</v>
+        <v>0.08614147110349121</v>
       </c>
       <c r="C27">
-        <v>12447.662482554</v>
+        <v>12341.6855224364</v>
       </c>
       <c r="D27">
-        <v>14303.312482554</v>
+        <v>14351.96952243639</v>
       </c>
       <c r="E27">
-        <v>-3248.849999999999</v>
+        <v>-3094.215999999999</v>
       </c>
       <c r="F27">
-        <v>3865.85</v>
+        <v>4020.484</v>
       </c>
       <c r="G27">
         <v>2010.2</v>
@@ -3501,28 +3501,28 @@
         <v>1971.45</v>
       </c>
       <c r="M27">
-        <v>232.6511281527399</v>
+        <v>241.9571732788495</v>
       </c>
       <c r="N27">
-        <v>1738.79887184726</v>
+        <v>1729.49282672115</v>
       </c>
       <c r="O27">
-        <v>469.4756953987602</v>
+        <v>466.9630632147106</v>
       </c>
       <c r="P27">
-        <v>1269.323176448499</v>
+        <v>1262.52976350644</v>
       </c>
       <c r="Q27">
-        <v>2092.6231764485</v>
+        <v>2085.82976350644</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1003942039816151</v>
+        <v>0.1009717529839567</v>
       </c>
       <c r="T27">
-        <v>0.9999120186157902</v>
+        <v>1.010490031420507</v>
       </c>
       <c r="U27">
         <v>0.06018110587651872</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.473846723432628</v>
+        <v>8.147929541762142</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08614147110349121</v>
+        <v>0.08600423739830639</v>
       </c>
       <c r="C28">
-        <v>12341.6855224364</v>
+        <v>12236.04073555717</v>
       </c>
       <c r="D28">
-        <v>14351.96952243639</v>
+        <v>14400.95873555717</v>
       </c>
       <c r="E28">
-        <v>-3094.215999999999</v>
+        <v>-2939.581999999999</v>
       </c>
       <c r="F28">
-        <v>4020.484</v>
+        <v>4175.118</v>
       </c>
       <c r="G28">
         <v>2010.2</v>
@@ -3583,28 +3583,28 @@
         <v>1971.45</v>
       </c>
       <c r="M28">
-        <v>241.9571732788495</v>
+        <v>251.2632184049591</v>
       </c>
       <c r="N28">
-        <v>1729.49282672115</v>
+        <v>1720.186781595041</v>
       </c>
       <c r="O28">
-        <v>466.9630632147106</v>
+        <v>464.450431030661</v>
       </c>
       <c r="P28">
-        <v>1262.52976350644</v>
+        <v>1255.73635056438</v>
       </c>
       <c r="Q28">
-        <v>2085.82976350644</v>
+        <v>2079.03635056438</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1009717529839567</v>
+        <v>0.1015651252466364</v>
       </c>
       <c r="T28">
-        <v>1.010490031420507</v>
+        <v>1.021357852795217</v>
       </c>
       <c r="U28">
         <v>0.06018110587651872</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.147929541762142</v>
+        <v>7.84615437354873</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08600423739830639</v>
+        <v>0.08586700369312159</v>
       </c>
       <c r="C29">
-        <v>12236.04073555717</v>
+        <v>12130.73153510121</v>
       </c>
       <c r="D29">
-        <v>14400.95873555717</v>
+        <v>14450.28353510122</v>
       </c>
       <c r="E29">
-        <v>-2939.581999999999</v>
+        <v>-2784.947999999999</v>
       </c>
       <c r="F29">
-        <v>4175.118</v>
+        <v>4329.752</v>
       </c>
       <c r="G29">
         <v>2010.2</v>
@@ -3665,28 +3665,28 @@
         <v>1971.45</v>
       </c>
       <c r="M29">
-        <v>251.2632184049591</v>
+        <v>260.5692635310687</v>
       </c>
       <c r="N29">
-        <v>1720.186781595041</v>
+        <v>1710.880736468931</v>
       </c>
       <c r="O29">
-        <v>464.450431030661</v>
+        <v>461.9377988466114</v>
       </c>
       <c r="P29">
-        <v>1255.73635056438</v>
+        <v>1248.94293762232</v>
       </c>
       <c r="Q29">
-        <v>2079.03635056438</v>
+        <v>2072.24293762232</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1015651252466364</v>
+        <v>0.1021749800721683</v>
       </c>
       <c r="T29">
-        <v>1.021357852795217</v>
+        <v>1.032527558097002</v>
       </c>
       <c r="U29">
         <v>0.06018110587651872</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.84615437354873</v>
+        <v>7.565934574493419</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08586700369312159</v>
+        <v>0.08572976998793677</v>
       </c>
       <c r="C30">
-        <v>12130.73153510121</v>
+        <v>12025.76138117626</v>
       </c>
       <c r="D30">
-        <v>14450.28353510122</v>
+        <v>14499.94738117627</v>
       </c>
       <c r="E30">
-        <v>-2784.947999999999</v>
+        <v>-2630.313999999998</v>
       </c>
       <c r="F30">
-        <v>4329.752</v>
+        <v>4484.386000000001</v>
       </c>
       <c r="G30">
         <v>2010.2</v>
@@ -3747,28 +3747,28 @@
         <v>1971.45</v>
       </c>
       <c r="M30">
-        <v>260.5692635310687</v>
+        <v>269.8753086571784</v>
       </c>
       <c r="N30">
-        <v>1710.880736468931</v>
+        <v>1701.574691342822</v>
       </c>
       <c r="O30">
-        <v>461.9377988466114</v>
+        <v>459.4251666625618</v>
       </c>
       <c r="P30">
-        <v>1248.94293762232</v>
+        <v>1242.14952468026</v>
       </c>
       <c r="Q30">
-        <v>2072.24293762232</v>
+        <v>2065.44952468026</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1021749800721683</v>
+        <v>0.1028020139068701</v>
       </c>
       <c r="T30">
-        <v>1.032527558097002</v>
+        <v>1.044011902984753</v>
       </c>
       <c r="U30">
         <v>0.06018110587651872</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.565934574493419</v>
+        <v>7.30504027882123</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08572976998793677</v>
+        <v>0.08559253628275193</v>
       </c>
       <c r="C31">
-        <v>12025.76138117627</v>
+        <v>11921.13378162193</v>
       </c>
       <c r="D31">
-        <v>14499.94738117627</v>
+        <v>14549.95378162193</v>
       </c>
       <c r="E31">
-        <v>-2630.313999999999</v>
+        <v>-2475.679999999999</v>
       </c>
       <c r="F31">
-        <v>4484.386</v>
+        <v>4639.02</v>
       </c>
       <c r="G31">
         <v>2010.2</v>
@@ -3829,28 +3829,28 @@
         <v>1971.45</v>
       </c>
       <c r="M31">
-        <v>269.8753086571783</v>
+        <v>279.1813537832879</v>
       </c>
       <c r="N31">
-        <v>1701.574691342822</v>
+        <v>1692.268646216712</v>
       </c>
       <c r="O31">
-        <v>459.4251666625618</v>
+        <v>456.9125344785122</v>
       </c>
       <c r="P31">
-        <v>1242.14952468026</v>
+        <v>1235.3561117382</v>
       </c>
       <c r="Q31">
-        <v>2065.44952468026</v>
+        <v>2058.6561117382</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1028020139068701</v>
+        <v>0.1034469629939919</v>
       </c>
       <c r="T31">
-        <v>1.044011902984753</v>
+        <v>1.055824372012154</v>
       </c>
       <c r="U31">
         <v>0.06018110587651872</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.305040278821232</v>
+        <v>7.061538936193856</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08559253628275193</v>
+        <v>0.08545530257756714</v>
       </c>
       <c r="C32">
-        <v>11921.13378162193</v>
+        <v>11816.85229283563</v>
       </c>
       <c r="D32">
-        <v>14549.95378162193</v>
+        <v>14600.30629283563</v>
       </c>
       <c r="E32">
-        <v>-2475.679999999999</v>
+        <v>-2321.045999999999</v>
       </c>
       <c r="F32">
-        <v>4639.02</v>
+        <v>4793.654</v>
       </c>
       <c r="G32">
         <v>2010.2</v>
@@ -3911,28 +3911,28 @@
         <v>1971.45</v>
       </c>
       <c r="M32">
-        <v>279.1813537832879</v>
+        <v>288.4873989093975</v>
       </c>
       <c r="N32">
-        <v>1692.268646216712</v>
+        <v>1682.962601090602</v>
       </c>
       <c r="O32">
-        <v>456.9125344785122</v>
+        <v>454.3999022944626</v>
       </c>
       <c r="P32">
-        <v>1235.3561117382</v>
+        <v>1228.56269879614</v>
       </c>
       <c r="Q32">
-        <v>2058.6561117382</v>
+        <v>2051.86269879614</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1034469629939919</v>
+        <v>0.1041106062575521</v>
       </c>
       <c r="T32">
-        <v>1.055824372012154</v>
+        <v>1.067979231446146</v>
       </c>
       <c r="U32">
         <v>0.06018110587651872</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.061538936193856</v>
+        <v>6.833747357606958</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08545530257756714</v>
+        <v>0.08571518887238232</v>
       </c>
       <c r="C33">
-        <v>11816.85229283563</v>
+        <v>11567.15624721326</v>
       </c>
       <c r="D33">
-        <v>14600.30629283563</v>
+        <v>14505.24424721326</v>
       </c>
       <c r="E33">
-        <v>-2321.045999999999</v>
+        <v>-2166.411999999999</v>
       </c>
       <c r="F33">
-        <v>4793.654</v>
+        <v>4948.288</v>
       </c>
       <c r="G33">
         <v>2010.2</v>
@@ -3993,45 +3993,45 @@
         <v>1971.45</v>
       </c>
       <c r="M33">
-        <v>288.4873989093975</v>
+        <v>306.2055336355071</v>
       </c>
       <c r="N33">
-        <v>1682.962601090602</v>
+        <v>1665.244466364493</v>
       </c>
       <c r="O33">
-        <v>454.3999022944626</v>
+        <v>449.6160059184131</v>
       </c>
       <c r="P33">
-        <v>1228.56269879614</v>
+        <v>1215.62846044608</v>
       </c>
       <c r="Q33">
-        <v>2051.86269879614</v>
+        <v>2038.92846044608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1041106062575521</v>
+        <v>0.1047937684406287</v>
       </c>
       <c r="T33">
-        <v>1.067979231446146</v>
+        <v>1.080491586745843</v>
       </c>
       <c r="U33">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.04393220728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.833747357606958</v>
+        <v>6.438322575668155</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08571518887238232</v>
+        <v>0.08559036516719751</v>
       </c>
       <c r="C34">
-        <v>11567.15624721326</v>
+        <v>11458.02568313147</v>
       </c>
       <c r="D34">
-        <v>14505.24424721326</v>
+        <v>14550.74768313148</v>
       </c>
       <c r="E34">
-        <v>-2166.411999999999</v>
+        <v>-2011.777999999999</v>
       </c>
       <c r="F34">
-        <v>4948.288</v>
+        <v>5102.922</v>
       </c>
       <c r="G34">
         <v>2010.2</v>
@@ -4075,28 +4075,28 @@
         <v>1971.45</v>
       </c>
       <c r="M34">
-        <v>306.2055336355071</v>
+        <v>315.7744565616167</v>
       </c>
       <c r="N34">
-        <v>1665.244466364493</v>
+        <v>1655.675543438383</v>
       </c>
       <c r="O34">
-        <v>449.6160059184131</v>
+        <v>447.0323967283635</v>
       </c>
       <c r="P34">
-        <v>1215.62846044608</v>
+        <v>1208.64314671002</v>
       </c>
       <c r="Q34">
-        <v>2038.92846044608</v>
+        <v>2031.94314671002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1047937684406287</v>
+        <v>0.1054973235246928</v>
       </c>
       <c r="T34">
-        <v>1.080491586745843</v>
+        <v>1.093377445188816</v>
       </c>
       <c r="U34">
         <v>0.06188110587651872</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.438322575668155</v>
+        <v>6.243221891556998</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08559036516719751</v>
+        <v>0.08546554146201268</v>
       </c>
       <c r="C35">
-        <v>11458.02568313147</v>
+        <v>11349.18150906282</v>
       </c>
       <c r="D35">
-        <v>14550.74768313148</v>
+        <v>14596.53750906282</v>
       </c>
       <c r="E35">
-        <v>-2011.777999999999</v>
+        <v>-1857.143999999999</v>
       </c>
       <c r="F35">
-        <v>5102.922</v>
+        <v>5257.556</v>
       </c>
       <c r="G35">
         <v>2010.2</v>
@@ -4157,28 +4157,28 @@
         <v>1971.45</v>
       </c>
       <c r="M35">
-        <v>315.7744565616167</v>
+        <v>325.3433794877263</v>
       </c>
       <c r="N35">
-        <v>1655.675543438383</v>
+        <v>1646.106620512274</v>
       </c>
       <c r="O35">
-        <v>447.0323967283635</v>
+        <v>444.4487875383139</v>
       </c>
       <c r="P35">
-        <v>1208.64314671002</v>
+        <v>1201.65783297396</v>
       </c>
       <c r="Q35">
-        <v>2031.94314671002</v>
+        <v>2024.95783297396</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1054973235246928</v>
+        <v>0.106222198459789</v>
       </c>
       <c r="T35">
-        <v>1.093377445188816</v>
+        <v>1.106653784190666</v>
       </c>
       <c r="U35">
         <v>0.06188110587651872</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.243221891556998</v>
+        <v>6.059597718275911</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08546554146201268</v>
+        <v>0.08534071775682787</v>
       </c>
       <c r="C36">
-        <v>11349.18150906282</v>
+        <v>11240.62643726931</v>
       </c>
       <c r="D36">
-        <v>14596.53750906282</v>
+        <v>14642.61643726931</v>
       </c>
       <c r="E36">
-        <v>-1857.143999999999</v>
+        <v>-1702.509999999998</v>
       </c>
       <c r="F36">
-        <v>5257.556</v>
+        <v>5412.190000000001</v>
       </c>
       <c r="G36">
         <v>2010.2</v>
@@ -4239,28 +4239,28 @@
         <v>1971.45</v>
       </c>
       <c r="M36">
-        <v>325.3433794877263</v>
+        <v>334.912302413836</v>
       </c>
       <c r="N36">
-        <v>1646.106620512274</v>
+        <v>1636.537697586164</v>
       </c>
       <c r="O36">
-        <v>444.4487875383139</v>
+        <v>441.8651783482643</v>
       </c>
       <c r="P36">
-        <v>1201.65783297396</v>
+        <v>1194.672519237899</v>
       </c>
       <c r="Q36">
-        <v>2024.95783297396</v>
+        <v>2017.9725192379</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.106222198459789</v>
+        <v>0.1069693772390421</v>
       </c>
       <c r="T36">
-        <v>1.106653784190666</v>
+        <v>1.120338625931035</v>
       </c>
       <c r="U36">
         <v>0.06188110587651872</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.059597718275911</v>
+        <v>5.886466354896597</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08534071775682787</v>
+        <v>0.08521589405164307</v>
       </c>
       <c r="C37">
-        <v>11240.62643726931</v>
+        <v>11132.36321437018</v>
       </c>
       <c r="D37">
-        <v>14642.61643726931</v>
+        <v>14688.98721437018</v>
       </c>
       <c r="E37">
-        <v>-1702.509999999998</v>
+        <v>-1547.875999999998</v>
       </c>
       <c r="F37">
-        <v>5412.190000000001</v>
+        <v>5566.824000000001</v>
       </c>
       <c r="G37">
         <v>2010.2</v>
@@ -4321,28 +4321,28 @@
         <v>1971.45</v>
       </c>
       <c r="M37">
-        <v>334.912302413836</v>
+        <v>344.4812253399456</v>
       </c>
       <c r="N37">
-        <v>1636.537697586164</v>
+        <v>1626.968774660054</v>
       </c>
       <c r="O37">
-        <v>441.8651783482643</v>
+        <v>439.2815691582147</v>
       </c>
       <c r="P37">
-        <v>1194.672519237899</v>
+        <v>1187.68720550184</v>
       </c>
       <c r="Q37">
-        <v>2017.9725192379</v>
+        <v>2010.98720550184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1069693772390421</v>
+        <v>0.1077399053551468</v>
       </c>
       <c r="T37">
-        <v>1.120338625931035</v>
+        <v>1.13445111897579</v>
       </c>
       <c r="U37">
         <v>0.06188110587651872</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.886466354896597</v>
+        <v>5.722953400593914</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08521589405164308</v>
+        <v>0.08530715034645825</v>
       </c>
       <c r="C38">
-        <v>11132.36321437017</v>
+        <v>10943.79959565519</v>
       </c>
       <c r="D38">
-        <v>14688.98721437017</v>
+        <v>14655.05759565519</v>
       </c>
       <c r="E38">
-        <v>-1547.875999999999</v>
+        <v>-1393.241999999999</v>
       </c>
       <c r="F38">
-        <v>5566.824000000001</v>
+        <v>5721.458000000001</v>
       </c>
       <c r="G38">
         <v>2010.2</v>
@@ -4403,45 +4403,45 @@
         <v>1971.45</v>
       </c>
       <c r="M38">
-        <v>344.4812253399455</v>
+        <v>358.6273146660552</v>
       </c>
       <c r="N38">
-        <v>1626.968774660054</v>
+        <v>1612.822685333945</v>
       </c>
       <c r="O38">
-        <v>439.2815691582147</v>
+        <v>435.4621250401651</v>
       </c>
       <c r="P38">
-        <v>1187.68720550184</v>
+        <v>1177.36056029378</v>
       </c>
       <c r="Q38">
-        <v>2010.98720550184</v>
+        <v>2000.66056029378</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1077399053551468</v>
+        <v>0.1085348946812866</v>
       </c>
       <c r="T38">
-        <v>1.13445111897579</v>
+        <v>1.14901162767276</v>
       </c>
       <c r="U38">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.04517320728985866</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>5.722953400593915</v>
+        <v>5.497210946789608</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08530715034645825</v>
+        <v>0.08518816664127343</v>
       </c>
       <c r="C39">
-        <v>10943.79959565519</v>
+        <v>10833.4355681144</v>
       </c>
       <c r="D39">
-        <v>14655.05759565519</v>
+        <v>14699.3275681144</v>
       </c>
       <c r="E39">
-        <v>-1393.241999999999</v>
+        <v>-1238.607999999999</v>
       </c>
       <c r="F39">
-        <v>5721.458000000001</v>
+        <v>5876.092000000001</v>
       </c>
       <c r="G39">
         <v>2010.2</v>
@@ -4485,28 +4485,28 @@
         <v>1971.45</v>
       </c>
       <c r="M39">
-        <v>358.6273146660552</v>
+        <v>368.3199447921647</v>
       </c>
       <c r="N39">
-        <v>1612.822685333945</v>
+        <v>1603.130055207835</v>
       </c>
       <c r="O39">
-        <v>435.4621250401651</v>
+        <v>432.8451149061155</v>
       </c>
       <c r="P39">
-        <v>1177.36056029378</v>
+        <v>1170.28494030172</v>
       </c>
       <c r="Q39">
-        <v>2000.66056029378</v>
+        <v>1993.58494030172</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1085348946812866</v>
+        <v>0.1093555288243986</v>
       </c>
       <c r="T39">
-        <v>1.14901162767276</v>
+        <v>1.164041830198664</v>
       </c>
       <c r="U39">
         <v>0.06268110587651873</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.497210946789608</v>
+        <v>5.352547500821461</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08518816664127343</v>
+        <v>0.08506918293608863</v>
       </c>
       <c r="C40">
-        <v>10833.4355681144</v>
+        <v>10723.3398122797</v>
       </c>
       <c r="D40">
-        <v>14699.3275681144</v>
+        <v>14743.8658122797</v>
       </c>
       <c r="E40">
-        <v>-1238.607999999999</v>
+        <v>-1083.973999999999</v>
       </c>
       <c r="F40">
-        <v>5876.092000000001</v>
+        <v>6030.726000000001</v>
       </c>
       <c r="G40">
         <v>2010.2</v>
@@ -4567,28 +4567,28 @@
         <v>1971.45</v>
       </c>
       <c r="M40">
-        <v>368.3199447921647</v>
+        <v>378.0125749182744</v>
       </c>
       <c r="N40">
-        <v>1603.130055207835</v>
+        <v>1593.437425081725</v>
       </c>
       <c r="O40">
-        <v>432.8451149061155</v>
+        <v>430.2281047720659</v>
       </c>
       <c r="P40">
-        <v>1170.28494030172</v>
+        <v>1163.20932030966</v>
       </c>
       <c r="Q40">
-        <v>1993.58494030172</v>
+        <v>1986.50932030966</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1093555288243986</v>
+        <v>0.1102030690049897</v>
       </c>
       <c r="T40">
-        <v>1.164041830198664</v>
+        <v>1.179564826250008</v>
       </c>
       <c r="U40">
         <v>0.06268110587651873</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.352547500821461</v>
+        <v>5.215302693108089</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08506918293608863</v>
+        <v>0.08495019923090383</v>
       </c>
       <c r="C41">
-        <v>10723.3398122797</v>
+        <v>10613.51477411271</v>
       </c>
       <c r="D41">
-        <v>14743.8658122797</v>
+        <v>14788.67477411271</v>
       </c>
       <c r="E41">
-        <v>-1083.973999999999</v>
+        <v>-929.3399999999992</v>
       </c>
       <c r="F41">
-        <v>6030.726000000001</v>
+        <v>6185.360000000001</v>
       </c>
       <c r="G41">
         <v>2010.2</v>
@@ -4649,28 +4649,28 @@
         <v>1971.45</v>
       </c>
       <c r="M41">
-        <v>378.0125749182744</v>
+        <v>387.7052050443839</v>
       </c>
       <c r="N41">
-        <v>1593.437425081725</v>
+        <v>1583.744794955616</v>
       </c>
       <c r="O41">
-        <v>430.2281047720659</v>
+        <v>427.6110946380163</v>
       </c>
       <c r="P41">
-        <v>1163.20932030966</v>
+        <v>1156.1337003176</v>
       </c>
       <c r="Q41">
-        <v>1986.50932030966</v>
+        <v>1979.4337003176</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1102030690049897</v>
+        <v>0.1110788605249339</v>
       </c>
       <c r="T41">
-        <v>1.179564826250008</v>
+        <v>1.195605255503063</v>
       </c>
       <c r="U41">
         <v>0.06268110587651873</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.215302693108089</v>
+        <v>5.084920125780387</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08495019923090383</v>
+        <v>0.08483121552571901</v>
       </c>
       <c r="C42">
-        <v>10613.51477411271</v>
+        <v>10503.96292940039</v>
       </c>
       <c r="D42">
-        <v>14788.67477411271</v>
+        <v>14833.75692940039</v>
       </c>
       <c r="E42">
-        <v>-929.3399999999992</v>
+        <v>-774.7059999999983</v>
       </c>
       <c r="F42">
-        <v>6185.360000000001</v>
+        <v>6339.994000000002</v>
       </c>
       <c r="G42">
         <v>2010.2</v>
@@ -4731,28 +4731,28 @@
         <v>1971.45</v>
       </c>
       <c r="M42">
-        <v>387.7052050443839</v>
+        <v>397.3978351704936</v>
       </c>
       <c r="N42">
-        <v>1583.744794955616</v>
+        <v>1574.052164829506</v>
       </c>
       <c r="O42">
-        <v>427.6110946380163</v>
+        <v>424.9940845039667</v>
       </c>
       <c r="P42">
-        <v>1156.1337003176</v>
+        <v>1149.05808032554</v>
       </c>
       <c r="Q42">
-        <v>1979.4337003176</v>
+        <v>1972.35808032554</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1110788605249339</v>
+        <v>0.1119843398930118</v>
       </c>
       <c r="T42">
-        <v>1.195605255503063</v>
+        <v>1.212189428120628</v>
       </c>
       <c r="U42">
         <v>0.06268110587651873</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.084920125780387</v>
+        <v>4.960897683688183</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08483121552571901</v>
+        <v>0.0847122318205342</v>
       </c>
       <c r="C43">
-        <v>10503.96292940039</v>
+        <v>10394.68678421096</v>
       </c>
       <c r="D43">
-        <v>14833.75692940039</v>
+        <v>14879.11478421096</v>
       </c>
       <c r="E43">
-        <v>-774.7059999999983</v>
+        <v>-620.0719999999983</v>
       </c>
       <c r="F43">
-        <v>6339.994000000002</v>
+        <v>6494.628000000002</v>
       </c>
       <c r="G43">
         <v>2010.2</v>
@@ -4813,28 +4813,28 @@
         <v>1971.45</v>
       </c>
       <c r="M43">
-        <v>397.3978351704936</v>
+        <v>407.0904652966032</v>
       </c>
       <c r="N43">
-        <v>1574.052164829506</v>
+        <v>1564.359534703397</v>
       </c>
       <c r="O43">
-        <v>424.9940845039667</v>
+        <v>422.3770743699171</v>
       </c>
       <c r="P43">
-        <v>1149.05808032554</v>
+        <v>1141.98246033348</v>
       </c>
       <c r="Q43">
-        <v>1972.35808032554</v>
+        <v>1965.28246033348</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1119843398930118</v>
+        <v>0.1129210426875751</v>
       </c>
       <c r="T43">
-        <v>1.212189428120628</v>
+        <v>1.229345468759489</v>
       </c>
       <c r="U43">
         <v>0.06268110587651873</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.960897683688183</v>
+        <v>4.842781072171797</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0847122318205342</v>
+        <v>0.08459324811534938</v>
       </c>
       <c r="C44">
-        <v>10394.68678421096</v>
+        <v>10285.68887535835</v>
       </c>
       <c r="D44">
-        <v>14879.11478421096</v>
+        <v>14924.75087535836</v>
       </c>
       <c r="E44">
-        <v>-620.0719999999992</v>
+        <v>-465.4379999999992</v>
       </c>
       <c r="F44">
-        <v>6494.628000000001</v>
+        <v>6649.262000000001</v>
       </c>
       <c r="G44">
         <v>2010.2</v>
@@ -4895,28 +4895,28 @@
         <v>1971.45</v>
       </c>
       <c r="M44">
-        <v>407.0904652966032</v>
+        <v>416.7830954227127</v>
       </c>
       <c r="N44">
-        <v>1564.359534703397</v>
+        <v>1554.666904577287</v>
       </c>
       <c r="O44">
-        <v>422.3770743699171</v>
+        <v>419.7600642358676</v>
       </c>
       <c r="P44">
-        <v>1141.98246033348</v>
+        <v>1134.90684034142</v>
       </c>
       <c r="Q44">
-        <v>1965.28246033348</v>
+        <v>1958.20684034142</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1129210426875751</v>
+        <v>0.1138906122468599</v>
       </c>
       <c r="T44">
-        <v>1.229345468759489</v>
+        <v>1.247103475736555</v>
       </c>
       <c r="U44">
         <v>0.06268110587651873</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.842781072171798</v>
+        <v>4.730158256539896</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08459324811534938</v>
+        <v>0.08447426441016456</v>
       </c>
       <c r="C45">
-        <v>10285.68887535835</v>
+        <v>10176.97177087515</v>
       </c>
       <c r="D45">
-        <v>14924.75087535836</v>
+        <v>14970.66777087515</v>
       </c>
       <c r="E45">
-        <v>-465.4379999999992</v>
+        <v>-310.8039999999992</v>
       </c>
       <c r="F45">
-        <v>6649.262000000001</v>
+        <v>6803.896000000001</v>
       </c>
       <c r="G45">
         <v>2010.2</v>
@@ -4977,28 +4977,28 @@
         <v>1971.45</v>
       </c>
       <c r="M45">
-        <v>416.7830954227127</v>
+        <v>426.4757255488224</v>
       </c>
       <c r="N45">
-        <v>1554.666904577287</v>
+        <v>1544.974274451178</v>
       </c>
       <c r="O45">
-        <v>419.7600642358676</v>
+        <v>417.1430541018179</v>
       </c>
       <c r="P45">
-        <v>1134.90684034142</v>
+        <v>1127.83122034936</v>
       </c>
       <c r="Q45">
-        <v>1958.20684034142</v>
+        <v>1951.13122034936</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1138906122468599</v>
+        <v>0.1148948092904049</v>
       </c>
       <c r="T45">
-        <v>1.247103475736555</v>
+        <v>1.265495697248517</v>
       </c>
       <c r="U45">
         <v>0.06268110587651873</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.730158256539896</v>
+        <v>4.622654659800352</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08447426441016456</v>
+        <v>0.08435528070497975</v>
       </c>
       <c r="C46">
-        <v>10176.97177087515</v>
+        <v>10068.53807049427</v>
       </c>
       <c r="D46">
-        <v>14970.66777087515</v>
+        <v>15016.86807049428</v>
       </c>
       <c r="E46">
-        <v>-310.8039999999992</v>
+        <v>-156.1699999999992</v>
       </c>
       <c r="F46">
-        <v>6803.896000000001</v>
+        <v>6958.530000000001</v>
       </c>
       <c r="G46">
         <v>2010.2</v>
@@ -5059,28 +5059,28 @@
         <v>1971.45</v>
       </c>
       <c r="M46">
-        <v>426.4757255488224</v>
+        <v>436.1683556749319</v>
       </c>
       <c r="N46">
-        <v>1544.974274451178</v>
+        <v>1535.281644325068</v>
       </c>
       <c r="O46">
-        <v>417.1430541018179</v>
+        <v>414.5260439677684</v>
       </c>
       <c r="P46">
-        <v>1127.83122034936</v>
+        <v>1120.755600357299</v>
       </c>
       <c r="Q46">
-        <v>1951.13122034936</v>
+        <v>1944.0556003573</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1148948092904049</v>
+        <v>0.1159355225900788</v>
       </c>
       <c r="T46">
-        <v>1.265495697248517</v>
+        <v>1.284556726815459</v>
       </c>
       <c r="U46">
         <v>0.06268110587651873</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.622654659800352</v>
+        <v>4.519929000693677</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08435528070497975</v>
+        <v>0.08423629699979496</v>
       </c>
       <c r="C47">
-        <v>10068.53807049427</v>
+        <v>9960.390406139675</v>
       </c>
       <c r="D47">
-        <v>15016.86807049428</v>
+        <v>15063.35440613968</v>
       </c>
       <c r="E47">
-        <v>-156.1699999999992</v>
+        <v>-1.535999999999149</v>
       </c>
       <c r="F47">
-        <v>6958.530000000001</v>
+        <v>7113.164000000001</v>
       </c>
       <c r="G47">
         <v>2010.2</v>
@@ -5141,28 +5141,28 @@
         <v>1971.45</v>
       </c>
       <c r="M47">
-        <v>436.1683556749319</v>
+        <v>445.8609858010415</v>
       </c>
       <c r="N47">
-        <v>1535.281644325068</v>
+        <v>1525.589014198958</v>
       </c>
       <c r="O47">
-        <v>414.5260439677684</v>
+        <v>411.9090338337188</v>
       </c>
       <c r="P47">
-        <v>1120.755600357299</v>
+        <v>1113.67998036524</v>
       </c>
       <c r="Q47">
-        <v>1944.0556003573</v>
+        <v>1936.97998036524</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1159355225900788</v>
+        <v>0.1170147808267777</v>
       </c>
       <c r="T47">
-        <v>1.284556726815459</v>
+        <v>1.304323720440436</v>
       </c>
       <c r="U47">
         <v>0.06268110587651873</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.519929000693677</v>
+        <v>4.421669674591641</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08423629699979496</v>
+        <v>0.08411731329461013</v>
       </c>
       <c r="C48">
-        <v>9960.390406139675</v>
+        <v>9852.531442426125</v>
       </c>
       <c r="D48">
-        <v>15063.35440613968</v>
+        <v>15110.12944242613</v>
       </c>
       <c r="E48">
-        <v>-1.535999999999149</v>
+        <v>153.0980000000009</v>
       </c>
       <c r="F48">
-        <v>7113.164000000001</v>
+        <v>7267.798000000001</v>
       </c>
       <c r="G48">
         <v>2010.2</v>
@@ -5223,28 +5223,28 @@
         <v>1971.45</v>
       </c>
       <c r="M48">
-        <v>445.8609858010415</v>
+        <v>455.5536159271512</v>
       </c>
       <c r="N48">
-        <v>1525.589014198958</v>
+        <v>1515.896384072849</v>
       </c>
       <c r="O48">
-        <v>411.9090338337188</v>
+        <v>409.2920236996691</v>
       </c>
       <c r="P48">
-        <v>1113.67998036524</v>
+        <v>1106.60436037318</v>
       </c>
       <c r="Q48">
-        <v>1936.97998036524</v>
+        <v>1929.90436037318</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1170147808267777</v>
+        <v>0.1181347657893897</v>
       </c>
       <c r="T48">
-        <v>1.304323720440436</v>
+        <v>1.324836638353148</v>
       </c>
       <c r="U48">
         <v>0.06268110587651873</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.421669674591641</v>
+        <v>4.327591596408841</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08411731329461013</v>
+        <v>0.0843487295894253</v>
       </c>
       <c r="C49">
-        <v>9852.531442426125</v>
+        <v>9607.188093324694</v>
       </c>
       <c r="D49">
-        <v>15110.12944242613</v>
+        <v>15019.42009332469</v>
       </c>
       <c r="E49">
-        <v>153.0980000000009</v>
+        <v>307.7320000000018</v>
       </c>
       <c r="F49">
-        <v>7267.798000000001</v>
+        <v>7422.432000000002</v>
       </c>
       <c r="G49">
         <v>2010.2</v>
@@ -5305,45 +5305,45 @@
         <v>1971.45</v>
       </c>
       <c r="M49">
-        <v>455.5536159271512</v>
+        <v>472.6686780532608</v>
       </c>
       <c r="N49">
-        <v>1515.896384072849</v>
+        <v>1498.781321946739</v>
       </c>
       <c r="O49">
-        <v>409.2920236996691</v>
+        <v>404.6709569256195</v>
       </c>
       <c r="P49">
-        <v>1106.60436037318</v>
+        <v>1094.110365021119</v>
       </c>
       <c r="Q49">
-        <v>1929.90436037318</v>
+        <v>1917.41036502112</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1181347657893897</v>
+        <v>0.1192978270967176</v>
       </c>
       <c r="T49">
-        <v>1.324836638353148</v>
+        <v>1.346138514647118</v>
       </c>
       <c r="U49">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.04575720728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.327591596408841</v>
+        <v>4.170891983195583</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0843487295894253</v>
+        <v>0.0842370458842405</v>
       </c>
       <c r="C50">
-        <v>9607.188093324694</v>
+        <v>9496.19492073899</v>
       </c>
       <c r="D50">
-        <v>15019.42009332469</v>
+        <v>15063.06092073899</v>
       </c>
       <c r="E50">
-        <v>307.7320000000009</v>
+        <v>462.3660000000009</v>
       </c>
       <c r="F50">
-        <v>7422.432000000001</v>
+        <v>7577.066000000001</v>
       </c>
       <c r="G50">
         <v>2010.2</v>
@@ -5387,28 +5387,28 @@
         <v>1971.45</v>
       </c>
       <c r="M50">
-        <v>472.6686780532607</v>
+        <v>482.5159421793704</v>
       </c>
       <c r="N50">
-        <v>1498.781321946739</v>
+        <v>1488.93405782063</v>
       </c>
       <c r="O50">
-        <v>404.6709569256196</v>
+        <v>402.01219561157</v>
       </c>
       <c r="P50">
-        <v>1094.11036502112</v>
+        <v>1086.92186220906</v>
       </c>
       <c r="Q50">
-        <v>1917.41036502112</v>
+        <v>1910.22186220906</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1192978270967176</v>
+        <v>0.1205064986513917</v>
       </c>
       <c r="T50">
-        <v>1.346138514647118</v>
+        <v>1.368275758638891</v>
       </c>
       <c r="U50">
         <v>0.06368110587651873</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.170891983195585</v>
+        <v>4.085771738640572</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0842370458842405</v>
+        <v>0.08412536217905568</v>
       </c>
       <c r="C51">
-        <v>9496.19492073899</v>
+        <v>9385.456095093588</v>
       </c>
       <c r="D51">
-        <v>15063.06092073899</v>
+        <v>15106.95609509359</v>
       </c>
       <c r="E51">
-        <v>462.3660000000009</v>
+        <v>617.0000000000009</v>
       </c>
       <c r="F51">
-        <v>7577.066000000001</v>
+        <v>7731.700000000001</v>
       </c>
       <c r="G51">
         <v>2010.2</v>
@@ -5469,28 +5469,28 @@
         <v>1971.45</v>
       </c>
       <c r="M51">
-        <v>482.5159421793704</v>
+        <v>492.3632063054799</v>
       </c>
       <c r="N51">
-        <v>1488.93405782063</v>
+        <v>1479.08679369452</v>
       </c>
       <c r="O51">
-        <v>402.01219561157</v>
+        <v>399.3534342975204</v>
       </c>
       <c r="P51">
-        <v>1086.92186220906</v>
+        <v>1079.733359397</v>
       </c>
       <c r="Q51">
-        <v>1910.22186220906</v>
+        <v>1903.033359397</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1205064986513917</v>
+        <v>0.1217635170682527</v>
       </c>
       <c r="T51">
-        <v>1.368275758638891</v>
+        <v>1.391298492390335</v>
       </c>
       <c r="U51">
         <v>0.06368110587651873</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.085771738640572</v>
+        <v>4.004056303867761</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08412536217905568</v>
+        <v>0.08401367847387087</v>
       </c>
       <c r="C52">
-        <v>9385.456095093588</v>
+        <v>9274.973846459734</v>
       </c>
       <c r="D52">
-        <v>15106.95609509359</v>
+        <v>15151.10784645974</v>
       </c>
       <c r="E52">
-        <v>617.0000000000009</v>
+        <v>771.6340000000009</v>
       </c>
       <c r="F52">
-        <v>7731.700000000001</v>
+        <v>7886.334000000001</v>
       </c>
       <c r="G52">
         <v>2010.2</v>
@@ -5551,28 +5551,28 @@
         <v>1971.45</v>
       </c>
       <c r="M52">
-        <v>492.3632063054799</v>
+        <v>502.2104704315896</v>
       </c>
       <c r="N52">
-        <v>1479.08679369452</v>
+        <v>1469.23952956841</v>
       </c>
       <c r="O52">
-        <v>399.3534342975204</v>
+        <v>396.6946729834708</v>
       </c>
       <c r="P52">
-        <v>1079.733359397</v>
+        <v>1072.544856584939</v>
       </c>
       <c r="Q52">
-        <v>1903.033359397</v>
+        <v>1895.84485658494</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1217635170682527</v>
+        <v>0.1230718423592713</v>
       </c>
       <c r="T52">
-        <v>1.391298492390335</v>
+        <v>1.415260929560205</v>
       </c>
       <c r="U52">
         <v>0.06368110587651873</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.004056303867761</v>
+        <v>3.925545395948785</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08401367847387087</v>
+        <v>0.08390199476868607</v>
       </c>
       <c r="C53">
-        <v>9274.973846459734</v>
+        <v>9164.750431055632</v>
       </c>
       <c r="D53">
-        <v>15151.10784645974</v>
+        <v>15195.51843105563</v>
       </c>
       <c r="E53">
-        <v>771.6340000000009</v>
+        <v>926.2680000000009</v>
       </c>
       <c r="F53">
-        <v>7886.334000000001</v>
+        <v>8040.968000000001</v>
       </c>
       <c r="G53">
         <v>2010.2</v>
@@ -5633,28 +5633,28 @@
         <v>1971.45</v>
       </c>
       <c r="M53">
-        <v>502.2104704315896</v>
+        <v>512.0577345576992</v>
       </c>
       <c r="N53">
-        <v>1469.23952956841</v>
+        <v>1459.392265442301</v>
       </c>
       <c r="O53">
-        <v>396.6946729834708</v>
+        <v>394.0359116694212</v>
       </c>
       <c r="P53">
-        <v>1072.544856584939</v>
+        <v>1065.356353772879</v>
       </c>
       <c r="Q53">
-        <v>1895.84485658494</v>
+        <v>1888.65635377288</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1230718423592713</v>
+        <v>0.1244346812040824</v>
       </c>
       <c r="T53">
-        <v>1.415260929560205</v>
+        <v>1.440221801612154</v>
       </c>
       <c r="U53">
         <v>0.06368110587651873</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.925545395948785</v>
+        <v>3.850054138334385</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08390199476868607</v>
+        <v>0.08379031106350124</v>
       </c>
       <c r="C54">
-        <v>9164.750431055632</v>
+        <v>9054.788131630759</v>
       </c>
       <c r="D54">
-        <v>15195.51843105563</v>
+        <v>15240.19013163076</v>
       </c>
       <c r="E54">
-        <v>926.2680000000009</v>
+        <v>1080.902000000001</v>
       </c>
       <c r="F54">
-        <v>8040.968000000001</v>
+        <v>8195.602000000001</v>
       </c>
       <c r="G54">
         <v>2010.2</v>
@@ -5715,28 +5715,28 @@
         <v>1971.45</v>
       </c>
       <c r="M54">
-        <v>512.0577345576992</v>
+        <v>521.9049986838087</v>
       </c>
       <c r="N54">
-        <v>1459.392265442301</v>
+        <v>1449.545001316191</v>
       </c>
       <c r="O54">
-        <v>394.0359116694212</v>
+        <v>391.3771503553717</v>
       </c>
       <c r="P54">
-        <v>1065.356353772879</v>
+        <v>1058.16785096082</v>
       </c>
       <c r="Q54">
-        <v>1888.65635377288</v>
+        <v>1881.46785096082</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1244346812040824</v>
+        <v>0.1258555131912258</v>
       </c>
       <c r="T54">
-        <v>1.440221801612154</v>
+        <v>1.466244838432269</v>
       </c>
       <c r="U54">
         <v>0.06368110587651873</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.850054138334385</v>
+        <v>3.777411607422417</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08379031106350124</v>
+        <v>0.08367862735831644</v>
       </c>
       <c r="C55">
-        <v>9054.788131630759</v>
+        <v>8945.089257856966</v>
       </c>
       <c r="D55">
-        <v>15240.19013163076</v>
+        <v>15285.12525785697</v>
       </c>
       <c r="E55">
-        <v>1080.902000000001</v>
+        <v>1235.536000000001</v>
       </c>
       <c r="F55">
-        <v>8195.602000000001</v>
+        <v>8350.236000000001</v>
       </c>
       <c r="G55">
         <v>2010.2</v>
@@ -5797,28 +5797,28 @@
         <v>1971.45</v>
       </c>
       <c r="M55">
-        <v>521.9049986838087</v>
+        <v>531.7522628099183</v>
       </c>
       <c r="N55">
-        <v>1449.545001316191</v>
+        <v>1439.697737190082</v>
       </c>
       <c r="O55">
-        <v>391.3771503553717</v>
+        <v>388.718389041322</v>
       </c>
       <c r="P55">
-        <v>1058.16785096082</v>
+        <v>1050.97934814876</v>
       </c>
       <c r="Q55">
-        <v>1881.46785096082</v>
+        <v>1874.27934814876</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1258555131912258</v>
+        <v>0.1273381204821581</v>
       </c>
       <c r="T55">
-        <v>1.466244838432269</v>
+        <v>1.493399311635869</v>
       </c>
       <c r="U55">
         <v>0.06368110587651873</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.777411607422417</v>
+        <v>3.707459540618297</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08367862735831644</v>
+        <v>0.08356694365313162</v>
       </c>
       <c r="C56">
-        <v>8945.089257856966</v>
+        <v>8835.656146726613</v>
       </c>
       <c r="D56">
-        <v>15285.12525785697</v>
+        <v>15330.32614672661</v>
       </c>
       <c r="E56">
-        <v>1235.536000000001</v>
+        <v>1390.170000000001</v>
       </c>
       <c r="F56">
-        <v>8350.236000000001</v>
+        <v>8504.870000000001</v>
       </c>
       <c r="G56">
         <v>2010.2</v>
@@ -5879,28 +5879,28 @@
         <v>1971.45</v>
       </c>
       <c r="M56">
-        <v>531.7522628099183</v>
+        <v>541.5995269360279</v>
       </c>
       <c r="N56">
-        <v>1439.697737190082</v>
+        <v>1429.850473063972</v>
       </c>
       <c r="O56">
-        <v>388.718389041322</v>
+        <v>386.0596277272725</v>
       </c>
       <c r="P56">
-        <v>1050.97934814876</v>
+        <v>1043.790845336699</v>
       </c>
       <c r="Q56">
-        <v>1874.27934814876</v>
+        <v>1867.0908453367</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1273381204821581</v>
+        <v>0.1288866214304652</v>
       </c>
       <c r="T56">
-        <v>1.493399311635869</v>
+        <v>1.521760650315184</v>
       </c>
       <c r="U56">
         <v>0.06368110587651873</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.707459540618297</v>
+        <v>3.640051185334328</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08356694365313162</v>
+        <v>0.08345525994794679</v>
       </c>
       <c r="C57">
-        <v>8835.656146726613</v>
+        <v>8726.491162957682</v>
       </c>
       <c r="D57">
-        <v>15330.32614672661</v>
+        <v>15375.79516295768</v>
       </c>
       <c r="E57">
-        <v>1390.170000000001</v>
+        <v>1544.804000000001</v>
       </c>
       <c r="F57">
-        <v>8504.870000000001</v>
+        <v>8659.504000000001</v>
       </c>
       <c r="G57">
         <v>2010.2</v>
@@ -5961,28 +5961,28 @@
         <v>1971.45</v>
       </c>
       <c r="M57">
-        <v>541.5995269360279</v>
+        <v>551.4467910621375</v>
       </c>
       <c r="N57">
-        <v>1429.850473063972</v>
+        <v>1420.003208937862</v>
       </c>
       <c r="O57">
-        <v>386.0596277272725</v>
+        <v>383.4008664132228</v>
       </c>
       <c r="P57">
-        <v>1043.790845336699</v>
+        <v>1036.602342524639</v>
       </c>
       <c r="Q57">
-        <v>1867.0908453367</v>
+        <v>1859.90234252464</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1288866214304652</v>
+        <v>0.1305055087855135</v>
       </c>
       <c r="T57">
-        <v>1.521760650315184</v>
+        <v>1.551411140752649</v>
       </c>
       <c r="U57">
         <v>0.06368110587651873</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.640051185334328</v>
+        <v>3.575050271310501</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08345525994794679</v>
+        <v>0.08334357624276199</v>
       </c>
       <c r="C58">
-        <v>8726.491162957682</v>
+        <v>8617.596699406145</v>
       </c>
       <c r="D58">
-        <v>15375.79516295768</v>
+        <v>15421.53469940615</v>
       </c>
       <c r="E58">
-        <v>1544.804000000001</v>
+        <v>1699.438000000003</v>
       </c>
       <c r="F58">
-        <v>8659.504000000001</v>
+        <v>8814.138000000003</v>
       </c>
       <c r="G58">
         <v>2010.2</v>
@@ -6043,28 +6043,28 @@
         <v>1971.45</v>
       </c>
       <c r="M58">
-        <v>551.4467910621375</v>
+        <v>561.2940551882473</v>
       </c>
       <c r="N58">
-        <v>1420.003208937862</v>
+        <v>1410.155944811753</v>
       </c>
       <c r="O58">
-        <v>383.4008664132228</v>
+        <v>380.7421050991732</v>
       </c>
       <c r="P58">
-        <v>1036.602342524639</v>
+        <v>1029.413839712579</v>
       </c>
       <c r="Q58">
-        <v>1859.90234252464</v>
+        <v>1852.71383971258</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1305055087855135</v>
+        <v>0.1321996932268432</v>
       </c>
       <c r="T58">
-        <v>1.551411140752649</v>
+        <v>1.582440723768602</v>
       </c>
       <c r="U58">
         <v>0.06368110587651873</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.575050271310501</v>
+        <v>3.51233009111207</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08334357624276199</v>
+        <v>0.08323189253757719</v>
       </c>
       <c r="C59">
-        <v>8617.596699406145</v>
+        <v>8508.975177485814</v>
       </c>
       <c r="D59">
-        <v>15421.53469940615</v>
+        <v>15467.54717748582</v>
       </c>
       <c r="E59">
-        <v>1699.438000000003</v>
+        <v>1854.072000000003</v>
       </c>
       <c r="F59">
-        <v>8814.138000000003</v>
+        <v>8968.772000000003</v>
       </c>
       <c r="G59">
         <v>2010.2</v>
@@ -6125,28 +6125,28 @@
         <v>1971.45</v>
       </c>
       <c r="M59">
-        <v>561.2940551882473</v>
+        <v>571.1413193143569</v>
       </c>
       <c r="N59">
-        <v>1410.155944811753</v>
+        <v>1400.308680685643</v>
       </c>
       <c r="O59">
-        <v>380.7421050991732</v>
+        <v>378.0833437851236</v>
       </c>
       <c r="P59">
-        <v>1029.413839712579</v>
+        <v>1022.225336900519</v>
       </c>
       <c r="Q59">
-        <v>1852.71383971258</v>
+        <v>1845.52533690052</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1321996932268432</v>
+        <v>0.1339745531177599</v>
       </c>
       <c r="T59">
-        <v>1.582440723768602</v>
+        <v>1.61494790597579</v>
       </c>
       <c r="U59">
         <v>0.06368110587651873</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.51233009111207</v>
+        <v>3.451772675748069</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08323189253757717</v>
+        <v>0.08312020883239236</v>
       </c>
       <c r="C60">
-        <v>8508.975177485827</v>
+        <v>8400.62904759557</v>
       </c>
       <c r="D60">
-        <v>15467.54717748583</v>
+        <v>15513.83504759557</v>
       </c>
       <c r="E60">
-        <v>1854.072000000001</v>
+        <v>2008.706000000001</v>
       </c>
       <c r="F60">
-        <v>8968.772000000001</v>
+        <v>9123.406000000001</v>
       </c>
       <c r="G60">
         <v>2010.2</v>
@@ -6207,28 +6207,28 @@
         <v>1971.45</v>
       </c>
       <c r="M60">
-        <v>571.1413193143568</v>
+        <v>580.9885834404663</v>
       </c>
       <c r="N60">
-        <v>1400.308680685643</v>
+        <v>1390.461416559534</v>
       </c>
       <c r="O60">
-        <v>378.0833437851236</v>
+        <v>375.4245824710741</v>
       </c>
       <c r="P60">
-        <v>1022.22533690052</v>
+        <v>1015.036834088459</v>
       </c>
       <c r="Q60">
-        <v>1845.52533690052</v>
+        <v>1838.33683408846</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1339745531177599</v>
+        <v>0.1358359915399408</v>
       </c>
       <c r="T60">
-        <v>1.614947905975789</v>
+        <v>1.649040804388206</v>
       </c>
       <c r="U60">
         <v>0.06368110587651873</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.45177267574807</v>
+        <v>3.393268054125221</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08312020883239236</v>
+        <v>0.08300852512720755</v>
       </c>
       <c r="C61">
-        <v>8400.62904759557</v>
+        <v>8292.560789554384</v>
       </c>
       <c r="D61">
-        <v>15513.83504759557</v>
+        <v>15560.40078955438</v>
       </c>
       <c r="E61">
-        <v>2008.706000000001</v>
+        <v>2163.340000000001</v>
       </c>
       <c r="F61">
-        <v>9123.406000000001</v>
+        <v>9278.040000000001</v>
       </c>
       <c r="G61">
         <v>2010.2</v>
@@ -6289,28 +6289,28 @@
         <v>1971.45</v>
       </c>
       <c r="M61">
-        <v>580.9885834404663</v>
+        <v>590.8358475665759</v>
       </c>
       <c r="N61">
-        <v>1390.461416559534</v>
+        <v>1380.614152433424</v>
       </c>
       <c r="O61">
-        <v>375.4245824710741</v>
+        <v>372.7658211570245</v>
       </c>
       <c r="P61">
-        <v>1015.036834088459</v>
+        <v>1007.848331276399</v>
       </c>
       <c r="Q61">
-        <v>1838.33683408846</v>
+        <v>1831.1483312764</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1358359915399408</v>
+        <v>0.1377905018832309</v>
       </c>
       <c r="T61">
-        <v>1.649040804388206</v>
+        <v>1.684838347721244</v>
       </c>
       <c r="U61">
         <v>0.06368110587651873</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.393268054125221</v>
+        <v>3.336713586556467</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08300852512720755</v>
+        <v>0.08289684142202274</v>
       </c>
       <c r="C62">
-        <v>8292.560789554384</v>
+        <v>8184.772913044197</v>
       </c>
       <c r="D62">
-        <v>15560.40078955438</v>
+        <v>15607.2469130442</v>
       </c>
       <c r="E62">
-        <v>2163.340000000001</v>
+        <v>2317.974000000001</v>
       </c>
       <c r="F62">
-        <v>9278.040000000001</v>
+        <v>9432.674000000001</v>
       </c>
       <c r="G62">
         <v>2010.2</v>
@@ -6371,28 +6371,28 @@
         <v>1971.45</v>
       </c>
       <c r="M62">
-        <v>590.8358475665759</v>
+        <v>600.6831116926855</v>
       </c>
       <c r="N62">
-        <v>1380.614152433424</v>
+        <v>1370.766888307314</v>
       </c>
       <c r="O62">
-        <v>372.7658211570245</v>
+        <v>370.1070598429749</v>
       </c>
       <c r="P62">
-        <v>1007.848331276399</v>
+        <v>1000.659828464339</v>
       </c>
       <c r="Q62">
-        <v>1831.1483312764</v>
+        <v>1823.95982846434</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1377905018832309</v>
+        <v>0.1398452435261768</v>
       </c>
       <c r="T62">
-        <v>1.684838347721244</v>
+        <v>1.722471662507258</v>
       </c>
       <c r="U62">
         <v>0.06368110587651873</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.336713586556467</v>
+        <v>3.282013363826033</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08289684142202274</v>
+        <v>0.08278515771683792</v>
       </c>
       <c r="C63">
-        <v>8184.772913044197</v>
+        <v>8077.267958060802</v>
       </c>
       <c r="D63">
-        <v>15607.2469130442</v>
+        <v>15654.3759580608</v>
       </c>
       <c r="E63">
-        <v>2317.974000000001</v>
+        <v>2472.608000000001</v>
       </c>
       <c r="F63">
-        <v>9432.674000000001</v>
+        <v>9587.308000000001</v>
       </c>
       <c r="G63">
         <v>2010.2</v>
@@ -6453,28 +6453,28 @@
         <v>1971.45</v>
       </c>
       <c r="M63">
-        <v>600.6831116926855</v>
+        <v>610.5303758187952</v>
       </c>
       <c r="N63">
-        <v>1370.766888307314</v>
+        <v>1360.919624181205</v>
       </c>
       <c r="O63">
-        <v>370.1070598429749</v>
+        <v>367.4482985289253</v>
       </c>
       <c r="P63">
-        <v>1000.659828464339</v>
+        <v>993.4713256522793</v>
       </c>
       <c r="Q63">
-        <v>1823.95982846434</v>
+        <v>1816.77132565228</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1398452435261768</v>
+        <v>0.1420081294661198</v>
       </c>
       <c r="T63">
-        <v>1.722471662507258</v>
+        <v>1.762085678071483</v>
       </c>
       <c r="U63">
         <v>0.06368110587651873</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.282013363826033</v>
+        <v>3.229077664409485</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08278515771683792</v>
+        <v>0.08267347401165311</v>
       </c>
       <c r="C64">
-        <v>8077.267958060802</v>
+        <v>7970.048495372901</v>
       </c>
       <c r="D64">
-        <v>15654.3759580608</v>
+        <v>15701.7904953729</v>
       </c>
       <c r="E64">
-        <v>2472.608000000001</v>
+        <v>2627.242000000001</v>
       </c>
       <c r="F64">
-        <v>9587.308000000001</v>
+        <v>9741.942000000001</v>
       </c>
       <c r="G64">
         <v>2010.2</v>
@@ -6535,28 +6535,28 @@
         <v>1971.45</v>
       </c>
       <c r="M64">
-        <v>610.5303758187952</v>
+        <v>620.3776399449048</v>
       </c>
       <c r="N64">
-        <v>1360.919624181205</v>
+        <v>1351.072360055095</v>
       </c>
       <c r="O64">
-        <v>367.4482985289253</v>
+        <v>364.7895372148757</v>
       </c>
       <c r="P64">
-        <v>993.4713256522793</v>
+        <v>986.2828228402193</v>
       </c>
       <c r="Q64">
-        <v>1816.77132565228</v>
+        <v>1809.582822840219</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1420081294661198</v>
+        <v>0.1442879281595734</v>
       </c>
       <c r="T64">
-        <v>1.762085678071483</v>
+        <v>1.803840991774315</v>
       </c>
       <c r="U64">
         <v>0.06368110587651873</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.229077664409485</v>
+        <v>3.177822463387111</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08267347401165311</v>
+        <v>0.08256179030646829</v>
       </c>
       <c r="C65">
-        <v>7970.048495372901</v>
+        <v>7863.117126989575</v>
       </c>
       <c r="D65">
-        <v>15701.7904953729</v>
+        <v>15749.49312698958</v>
       </c>
       <c r="E65">
-        <v>2627.242000000001</v>
+        <v>2781.876000000001</v>
       </c>
       <c r="F65">
-        <v>9741.942000000001</v>
+        <v>9896.576000000001</v>
       </c>
       <c r="G65">
         <v>2010.2</v>
@@ -6617,28 +6617,28 @@
         <v>1971.45</v>
       </c>
       <c r="M65">
-        <v>620.3776399449048</v>
+        <v>630.2249040710143</v>
       </c>
       <c r="N65">
-        <v>1351.072360055095</v>
+        <v>1341.225095928985</v>
       </c>
       <c r="O65">
-        <v>364.7895372148757</v>
+        <v>362.1307759008261</v>
       </c>
       <c r="P65">
-        <v>986.2828228402193</v>
+        <v>979.0943200281592</v>
       </c>
       <c r="Q65">
-        <v>1809.582822840219</v>
+        <v>1802.394320028159</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1442879281595734</v>
+        <v>0.1466943823359965</v>
       </c>
       <c r="T65">
-        <v>1.803840991774315</v>
+        <v>1.847916045127305</v>
       </c>
       <c r="U65">
         <v>0.06368110587651873</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.177822463387111</v>
+        <v>3.128168987396688</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08256179030646829</v>
+        <v>0.08245010660128349</v>
       </c>
       <c r="C66">
-        <v>7863.117126989575</v>
+        <v>7756.476486636262</v>
       </c>
       <c r="D66">
-        <v>15749.49312698958</v>
+        <v>15797.48648663626</v>
       </c>
       <c r="E66">
-        <v>2781.876000000001</v>
+        <v>2936.510000000001</v>
       </c>
       <c r="F66">
-        <v>9896.576000000001</v>
+        <v>10051.21</v>
       </c>
       <c r="G66">
         <v>2010.2</v>
@@ -6699,28 +6699,28 @@
         <v>1971.45</v>
       </c>
       <c r="M66">
-        <v>630.2249040710143</v>
+        <v>640.0721681971239</v>
       </c>
       <c r="N66">
-        <v>1341.225095928985</v>
+        <v>1331.377831802876</v>
       </c>
       <c r="O66">
-        <v>362.1307759008261</v>
+        <v>359.4720145867765</v>
       </c>
       <c r="P66">
-        <v>979.0943200281592</v>
+        <v>971.9058172160993</v>
       </c>
       <c r="Q66">
-        <v>1802.394320028159</v>
+        <v>1795.2058172161</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1466943823359965</v>
+        <v>0.1492383481796438</v>
       </c>
       <c r="T66">
-        <v>1.847916045127305</v>
+        <v>1.894509672957608</v>
       </c>
       <c r="U66">
         <v>0.06368110587651873</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.128168987396688</v>
+        <v>3.080043310667508</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08245010660128349</v>
+        <v>0.08233842289609866</v>
       </c>
       <c r="C67">
-        <v>7756.476486636262</v>
+        <v>7650.129240239501</v>
       </c>
       <c r="D67">
-        <v>15797.48648663626</v>
+        <v>15845.7732402395</v>
       </c>
       <c r="E67">
-        <v>2936.510000000001</v>
+        <v>3091.144000000001</v>
       </c>
       <c r="F67">
-        <v>10051.21</v>
+        <v>10205.844</v>
       </c>
       <c r="G67">
         <v>2010.2</v>
@@ -6781,28 +6781,28 @@
         <v>1971.45</v>
       </c>
       <c r="M67">
-        <v>640.0721681971239</v>
+        <v>649.9194323232335</v>
       </c>
       <c r="N67">
-        <v>1331.377831802876</v>
+        <v>1321.530567676766</v>
       </c>
       <c r="O67">
-        <v>359.4720145867765</v>
+        <v>356.8132532727269</v>
       </c>
       <c r="P67">
-        <v>971.9058172160993</v>
+        <v>964.7173144040393</v>
       </c>
       <c r="Q67">
-        <v>1795.2058172161</v>
+        <v>1788.01731440404</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1492383481796438</v>
+        <v>0.1519319590729175</v>
       </c>
       <c r="T67">
-        <v>1.894509672957608</v>
+        <v>1.943844102424987</v>
       </c>
       <c r="U67">
         <v>0.06368110587651873</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.080043310667508</v>
+        <v>3.033375987778606</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08233842289609866</v>
+        <v>0.08344948919091386</v>
       </c>
       <c r="C68">
-        <v>7650.129240239501</v>
+        <v>7027.873900857196</v>
       </c>
       <c r="D68">
-        <v>15845.7732402395</v>
+        <v>15378.1519008572</v>
       </c>
       <c r="E68">
-        <v>3091.144000000001</v>
+        <v>3245.778000000001</v>
       </c>
       <c r="F68">
-        <v>10205.844</v>
+        <v>10360.478</v>
       </c>
       <c r="G68">
         <v>2010.2</v>
@@ -6863,45 +6863,45 @@
         <v>1971.45</v>
       </c>
       <c r="M68">
-        <v>649.9194323232335</v>
+        <v>685.667891449343</v>
       </c>
       <c r="N68">
-        <v>1321.530567676766</v>
+        <v>1285.782108550657</v>
       </c>
       <c r="O68">
-        <v>356.8132532727269</v>
+        <v>347.1611693086774</v>
       </c>
       <c r="P68">
-        <v>964.7173144040393</v>
+        <v>938.6209392419795</v>
       </c>
       <c r="Q68">
-        <v>1788.01731440404</v>
+        <v>1761.92093924198</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1519319590729175</v>
+        <v>0.154788819111238</v>
       </c>
       <c r="T68">
-        <v>1.943844102424987</v>
+        <v>1.996168497314633</v>
       </c>
       <c r="U68">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.04648720728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.033375987778606</v>
+        <v>2.875225782897332</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08344948919091386</v>
+        <v>0.08335605548572902</v>
       </c>
       <c r="C69">
-        <v>7027.873900857196</v>
+        <v>6911.498383874357</v>
       </c>
       <c r="D69">
-        <v>15378.1519008572</v>
+        <v>15416.41038387436</v>
       </c>
       <c r="E69">
-        <v>3245.778000000001</v>
+        <v>3400.412000000001</v>
       </c>
       <c r="F69">
-        <v>10360.478</v>
+        <v>10515.112</v>
       </c>
       <c r="G69">
         <v>2010.2</v>
@@ -6945,28 +6945,28 @@
         <v>1971.45</v>
       </c>
       <c r="M69">
-        <v>685.667891449343</v>
+        <v>695.9017405754525</v>
       </c>
       <c r="N69">
-        <v>1285.782108550657</v>
+        <v>1275.548259424547</v>
       </c>
       <c r="O69">
-        <v>347.1611693086774</v>
+        <v>344.3980300446278</v>
       </c>
       <c r="P69">
-        <v>938.6209392419795</v>
+        <v>931.1502293799194</v>
       </c>
       <c r="Q69">
-        <v>1761.92093924198</v>
+        <v>1754.45022937992</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.154788819111238</v>
+        <v>0.1578242329019536</v>
       </c>
       <c r="T69">
-        <v>1.996168497314633</v>
+        <v>2.05176316688488</v>
       </c>
       <c r="U69">
         <v>0.06618110587651872</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.875225782897332</v>
+        <v>2.8329430507959</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08335605548572902</v>
+        <v>0.08326262178054422</v>
       </c>
       <c r="C70">
-        <v>6911.498383874357</v>
+        <v>6795.313704139573</v>
       </c>
       <c r="D70">
-        <v>15416.41038387436</v>
+        <v>15454.85970413958</v>
       </c>
       <c r="E70">
-        <v>3400.412000000001</v>
+        <v>3555.046000000001</v>
       </c>
       <c r="F70">
-        <v>10515.112</v>
+        <v>10669.746</v>
       </c>
       <c r="G70">
         <v>2010.2</v>
@@ -7027,28 +7027,28 @@
         <v>1971.45</v>
       </c>
       <c r="M70">
-        <v>695.9017405754525</v>
+        <v>706.1355897015623</v>
       </c>
       <c r="N70">
-        <v>1275.548259424547</v>
+        <v>1265.314410298437</v>
       </c>
       <c r="O70">
-        <v>344.3980300446278</v>
+        <v>341.6348907805781</v>
       </c>
       <c r="P70">
-        <v>931.1502293799194</v>
+        <v>923.6795195178593</v>
       </c>
       <c r="Q70">
-        <v>1754.45022937992</v>
+        <v>1746.979519517859</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1578242329019536</v>
+        <v>0.1610554798404573</v>
       </c>
       <c r="T70">
-        <v>2.05176316688488</v>
+        <v>2.110944589330628</v>
       </c>
       <c r="U70">
         <v>0.06618110587651872</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.8329430507959</v>
+        <v>2.791885905132191</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08326262178054422</v>
+        <v>0.08316918807535942</v>
       </c>
       <c r="C71">
-        <v>6795.313704139573</v>
+        <v>6679.321293096686</v>
       </c>
       <c r="D71">
-        <v>15454.85970413958</v>
+        <v>15493.50129309669</v>
       </c>
       <c r="E71">
-        <v>3555.046000000001</v>
+        <v>3709.680000000003</v>
       </c>
       <c r="F71">
-        <v>10669.746</v>
+        <v>10824.38</v>
       </c>
       <c r="G71">
         <v>2010.2</v>
@@ -7109,28 +7109,28 @@
         <v>1971.45</v>
       </c>
       <c r="M71">
-        <v>706.1355897015623</v>
+        <v>716.369438827672</v>
       </c>
       <c r="N71">
-        <v>1265.314410298437</v>
+        <v>1255.080561172328</v>
       </c>
       <c r="O71">
-        <v>341.6348907805781</v>
+        <v>338.8717515165285</v>
       </c>
       <c r="P71">
-        <v>923.6795195178593</v>
+        <v>916.2088096557993</v>
       </c>
       <c r="Q71">
-        <v>1746.979519517859</v>
+        <v>1739.508809655799</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1610554798404573</v>
+        <v>0.1645021432415279</v>
       </c>
       <c r="T71">
-        <v>2.110944589330628</v>
+        <v>2.174071439939426</v>
       </c>
       <c r="U71">
         <v>0.06618110587651872</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.791885905132191</v>
+        <v>2.75200182077316</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08316918807535942</v>
+        <v>0.0830757543701746</v>
       </c>
       <c r="C72">
-        <v>6679.321293096686</v>
+        <v>6563.52259654149</v>
       </c>
       <c r="D72">
-        <v>15493.50129309669</v>
+        <v>15532.33659654149</v>
       </c>
       <c r="E72">
-        <v>3709.680000000003</v>
+        <v>3864.314000000003</v>
       </c>
       <c r="F72">
-        <v>10824.38</v>
+        <v>10979.014</v>
       </c>
       <c r="G72">
         <v>2010.2</v>
@@ -7191,28 +7191,28 @@
         <v>1971.45</v>
       </c>
       <c r="M72">
-        <v>716.369438827672</v>
+        <v>726.6032879537815</v>
       </c>
       <c r="N72">
-        <v>1255.080561172328</v>
+        <v>1244.846712046218</v>
       </c>
       <c r="O72">
-        <v>338.8717515165285</v>
+        <v>336.108612252479</v>
       </c>
       <c r="P72">
-        <v>916.2088096557993</v>
+        <v>908.7380997937394</v>
       </c>
       <c r="Q72">
-        <v>1739.508809655799</v>
+        <v>1732.03809979374</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1645021432415279</v>
+        <v>0.1681865075668102</v>
       </c>
       <c r="T72">
-        <v>2.174071439939426</v>
+        <v>2.241551866452279</v>
       </c>
       <c r="U72">
         <v>0.06618110587651872</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.75200182077316</v>
+        <v>2.713241231748186</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08307575437017461</v>
+        <v>0.0829823206649898</v>
       </c>
       <c r="C73">
-        <v>6563.522596541485</v>
+        <v>6447.919074802063</v>
       </c>
       <c r="D73">
-        <v>15532.33659654149</v>
+        <v>15571.36707480206</v>
       </c>
       <c r="E73">
-        <v>3864.314000000001</v>
+        <v>4018.948000000001</v>
       </c>
       <c r="F73">
-        <v>10979.014</v>
+        <v>11133.648</v>
       </c>
       <c r="G73">
         <v>2010.2</v>
@@ -7273,28 +7273,28 @@
         <v>1971.45</v>
       </c>
       <c r="M73">
-        <v>726.6032879537814</v>
+        <v>736.837137079891</v>
       </c>
       <c r="N73">
-        <v>1244.846712046218</v>
+        <v>1234.612862920109</v>
       </c>
       <c r="O73">
-        <v>336.108612252479</v>
+        <v>333.3454729884294</v>
       </c>
       <c r="P73">
-        <v>908.7380997937394</v>
+        <v>901.2673899316794</v>
       </c>
       <c r="Q73">
-        <v>1732.03809979374</v>
+        <v>1724.56738993168</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1681865075668102</v>
+        <v>0.1721340407724698</v>
       </c>
       <c r="T73">
-        <v>2.241551866452278</v>
+        <v>2.313852323430335</v>
       </c>
       <c r="U73">
         <v>0.06618110587651872</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.713241231748186</v>
+        <v>2.675557325751684</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0829823206649898</v>
+        <v>0.08288888695980498</v>
       </c>
       <c r="C74">
-        <v>6447.919074802063</v>
+        <v>6332.512202921824</v>
       </c>
       <c r="D74">
-        <v>15571.36707480206</v>
+        <v>15610.59420292182</v>
       </c>
       <c r="E74">
-        <v>4018.948000000001</v>
+        <v>4173.582000000001</v>
       </c>
       <c r="F74">
-        <v>11133.648</v>
+        <v>11288.282</v>
       </c>
       <c r="G74">
         <v>2010.2</v>
@@ -7355,28 +7355,28 @@
         <v>1971.45</v>
       </c>
       <c r="M74">
-        <v>736.837137079891</v>
+        <v>747.0709862060006</v>
       </c>
       <c r="N74">
-        <v>1234.612862920109</v>
+        <v>1224.379013793999</v>
       </c>
       <c r="O74">
-        <v>333.3454729884294</v>
+        <v>330.5823337243798</v>
       </c>
       <c r="P74">
-        <v>901.2673899316794</v>
+        <v>893.7966800696192</v>
       </c>
       <c r="Q74">
-        <v>1724.56738993168</v>
+        <v>1717.096680069619</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1721340407724698</v>
+        <v>0.1763739838452154</v>
       </c>
       <c r="T74">
-        <v>2.313852323430335</v>
+        <v>2.391508369814173</v>
       </c>
       <c r="U74">
         <v>0.06618110587651872</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.675557325751684</v>
+        <v>2.638905855535907</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08288888695980498</v>
+        <v>0.08279545325462015</v>
       </c>
       <c r="C75">
-        <v>6332.512202921824</v>
+        <v>6217.303470845352</v>
       </c>
       <c r="D75">
-        <v>15610.59420292182</v>
+        <v>15650.01947084535</v>
       </c>
       <c r="E75">
-        <v>4173.582000000001</v>
+        <v>4328.216000000001</v>
       </c>
       <c r="F75">
-        <v>11288.282</v>
+        <v>11442.916</v>
       </c>
       <c r="G75">
         <v>2010.2</v>
@@ -7437,28 +7437,28 @@
         <v>1971.45</v>
       </c>
       <c r="M75">
-        <v>747.0709862060006</v>
+        <v>757.3048353321102</v>
       </c>
       <c r="N75">
-        <v>1224.379013793999</v>
+        <v>1214.14516466789</v>
       </c>
       <c r="O75">
-        <v>330.5823337243798</v>
+        <v>327.8191944603303</v>
       </c>
       <c r="P75">
-        <v>893.7966800696192</v>
+        <v>886.3259702075595</v>
       </c>
       <c r="Q75">
-        <v>1717.096680069619</v>
+        <v>1709.62597020756</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1763739838452154</v>
+        <v>0.1809400763850952</v>
       </c>
       <c r="T75">
-        <v>2.391508369814173</v>
+        <v>2.475137958227537</v>
       </c>
       <c r="U75">
         <v>0.06618110587651872</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.638905855535907</v>
+        <v>2.603244965596233</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08279545325462015</v>
+        <v>0.08270201954943535</v>
       </c>
       <c r="C76">
-        <v>6217.303470845352</v>
+        <v>6102.29438360701</v>
       </c>
       <c r="D76">
-        <v>15650.01947084535</v>
+        <v>15689.64438360701</v>
       </c>
       <c r="E76">
-        <v>4328.216000000001</v>
+        <v>4482.850000000001</v>
       </c>
       <c r="F76">
-        <v>11442.916</v>
+        <v>11597.55</v>
       </c>
       <c r="G76">
         <v>2010.2</v>
@@ -7519,28 +7519,28 @@
         <v>1971.45</v>
       </c>
       <c r="M76">
-        <v>757.3048353321102</v>
+        <v>767.5386844582198</v>
       </c>
       <c r="N76">
-        <v>1214.14516466789</v>
+        <v>1203.91131554178</v>
       </c>
       <c r="O76">
-        <v>327.8191944603303</v>
+        <v>325.0560551962806</v>
       </c>
       <c r="P76">
-        <v>886.3259702075595</v>
+        <v>878.8552603454993</v>
       </c>
       <c r="Q76">
-        <v>1709.62597020756</v>
+        <v>1702.1552603455</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1809400763850952</v>
+        <v>0.1858714563281654</v>
       </c>
       <c r="T76">
-        <v>2.475137958227537</v>
+        <v>2.565457913713971</v>
       </c>
       <c r="U76">
         <v>0.06618110587651872</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.603244965596233</v>
+        <v>2.568535032721616</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08270201954943535</v>
+        <v>0.08260858584425054</v>
       </c>
       <c r="C77">
-        <v>6102.29438360701</v>
+        <v>5987.486461522509</v>
       </c>
       <c r="D77">
-        <v>15689.64438360701</v>
+        <v>15729.47046152251</v>
       </c>
       <c r="E77">
-        <v>4482.850000000001</v>
+        <v>4637.484000000001</v>
       </c>
       <c r="F77">
-        <v>11597.55</v>
+        <v>11752.184</v>
       </c>
       <c r="G77">
         <v>2010.2</v>
@@ -7601,28 +7601,28 @@
         <v>1971.45</v>
       </c>
       <c r="M77">
-        <v>767.5386844582198</v>
+        <v>777.7725335843294</v>
       </c>
       <c r="N77">
-        <v>1203.91131554178</v>
+        <v>1193.677466415671</v>
       </c>
       <c r="O77">
-        <v>325.0560551962806</v>
+        <v>322.2929159322311</v>
       </c>
       <c r="P77">
-        <v>878.8552603454993</v>
+        <v>871.3845504834394</v>
       </c>
       <c r="Q77">
-        <v>1702.1552603455</v>
+        <v>1694.68455048344</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1858714563281654</v>
+        <v>0.1912137845998248</v>
       </c>
       <c r="T77">
-        <v>2.565457913713971</v>
+        <v>2.663304532157607</v>
       </c>
       <c r="U77">
         <v>0.06618110587651872</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.568535032721616</v>
+        <v>2.534738519133174</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08260858584425054</v>
+        <v>0.08251515213906571</v>
       </c>
       <c r="C78">
-        <v>5987.486461522509</v>
+        <v>5872.881240383309</v>
       </c>
       <c r="D78">
-        <v>15729.47046152251</v>
+        <v>15769.49924038331</v>
       </c>
       <c r="E78">
-        <v>4637.484000000001</v>
+        <v>4792.118000000001</v>
       </c>
       <c r="F78">
-        <v>11752.184</v>
+        <v>11906.818</v>
       </c>
       <c r="G78">
         <v>2010.2</v>
@@ -7683,28 +7683,28 @@
         <v>1971.45</v>
       </c>
       <c r="M78">
-        <v>777.7725335843294</v>
+        <v>788.006382710439</v>
       </c>
       <c r="N78">
-        <v>1193.677466415671</v>
+        <v>1183.443617289561</v>
       </c>
       <c r="O78">
-        <v>322.2929159322311</v>
+        <v>319.5297766681814</v>
       </c>
       <c r="P78">
-        <v>871.3845504834394</v>
+        <v>863.9138406213793</v>
       </c>
       <c r="Q78">
-        <v>1694.68455048344</v>
+        <v>1687.213840621379</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1912137845998248</v>
+        <v>0.1970206631559763</v>
       </c>
       <c r="T78">
-        <v>2.663304532157607</v>
+        <v>2.769659552205038</v>
       </c>
       <c r="U78">
         <v>0.06618110587651872</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.534738519133174</v>
+        <v>2.501819837066509</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08251515213906571</v>
+        <v>0.0844146184338809</v>
       </c>
       <c r="C79">
-        <v>5872.881240383309</v>
+        <v>4942.540176373062</v>
       </c>
       <c r="D79">
-        <v>15769.49924038331</v>
+        <v>14993.79217637306</v>
       </c>
       <c r="E79">
-        <v>4792.118000000001</v>
+        <v>4946.752000000001</v>
       </c>
       <c r="F79">
-        <v>11906.818</v>
+        <v>12061.452</v>
       </c>
       <c r="G79">
         <v>2010.2</v>
@@ -7765,45 +7765,45 @@
         <v>1971.45</v>
       </c>
       <c r="M79">
-        <v>788.006382710439</v>
+        <v>840.4553138365486</v>
       </c>
       <c r="N79">
-        <v>1183.443617289561</v>
+        <v>1130.994686163451</v>
       </c>
       <c r="O79">
-        <v>319.5297766681814</v>
+        <v>305.3685652641319</v>
       </c>
       <c r="P79">
-        <v>863.9138406213793</v>
+        <v>825.6261208993194</v>
       </c>
       <c r="Q79">
-        <v>1687.213840621379</v>
+        <v>1648.92612089932</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1970206631559763</v>
+        <v>0.203355439762687</v>
       </c>
       <c r="T79">
-        <v>2.769659552205038</v>
+        <v>2.885683210438599</v>
       </c>
       <c r="U79">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V79">
         <v>0.27</v>
       </c>
       <c r="W79">
-        <v>0.04831220728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.501819837066509</v>
+        <v>2.345692825714475</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0844146184338809</v>
+        <v>0.0843467347286961</v>
       </c>
       <c r="C80">
-        <v>4942.540176373062</v>
+        <v>4814.311374501178</v>
       </c>
       <c r="D80">
-        <v>14993.79217637306</v>
+        <v>15020.19737450118</v>
       </c>
       <c r="E80">
-        <v>4946.752000000001</v>
+        <v>5101.386000000001</v>
       </c>
       <c r="F80">
-        <v>12061.452</v>
+        <v>12216.086</v>
       </c>
       <c r="G80">
         <v>2010.2</v>
@@ -7847,28 +7847,28 @@
         <v>1971.45</v>
       </c>
       <c r="M80">
-        <v>840.4553138365486</v>
+        <v>851.2303819626583</v>
       </c>
       <c r="N80">
-        <v>1130.994686163451</v>
+        <v>1120.219618037342</v>
       </c>
       <c r="O80">
-        <v>305.3685652641319</v>
+        <v>302.4592968700823</v>
       </c>
       <c r="P80">
-        <v>825.6261208993194</v>
+        <v>817.7603211672595</v>
       </c>
       <c r="Q80">
-        <v>1648.92612089932</v>
+        <v>1641.06032116726</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.203355439762687</v>
+        <v>0.2102935284271798</v>
       </c>
       <c r="T80">
-        <v>2.885683210438599</v>
+        <v>3.01275674088488</v>
       </c>
       <c r="U80">
         <v>0.06968110587651873</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.345692825714475</v>
+        <v>2.316000511464925</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0843467347286961</v>
+        <v>0.08427885102351128</v>
       </c>
       <c r="C81">
-        <v>4814.311374501178</v>
+        <v>4686.175739791903</v>
       </c>
       <c r="D81">
-        <v>15020.19737450118</v>
+        <v>15046.6957397919</v>
       </c>
       <c r="E81">
-        <v>5101.386000000001</v>
+        <v>5256.020000000001</v>
       </c>
       <c r="F81">
-        <v>12216.086</v>
+        <v>12370.72</v>
       </c>
       <c r="G81">
         <v>2010.2</v>
@@ -7929,28 +7929,28 @@
         <v>1971.45</v>
       </c>
       <c r="M81">
-        <v>851.2303819626583</v>
+        <v>862.0054500887678</v>
       </c>
       <c r="N81">
-        <v>1120.219618037342</v>
+        <v>1109.444549911232</v>
       </c>
       <c r="O81">
-        <v>302.4592968700823</v>
+        <v>299.5500284760327</v>
       </c>
       <c r="P81">
-        <v>817.7603211672595</v>
+        <v>809.8945214351994</v>
       </c>
       <c r="Q81">
-        <v>1641.06032116726</v>
+        <v>1633.194521435199</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2102935284271798</v>
+        <v>0.2179254259581217</v>
       </c>
       <c r="T81">
-        <v>3.01275674088488</v>
+        <v>3.152537624375789</v>
       </c>
       <c r="U81">
         <v>0.06968110587651873</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.316000511464925</v>
+        <v>2.287050505071614</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08427885102351128</v>
+        <v>0.08421096731832646</v>
       </c>
       <c r="C82">
-        <v>4686.175739791903</v>
+        <v>4558.133766208231</v>
       </c>
       <c r="D82">
-        <v>15046.6957397919</v>
+        <v>15073.28776620823</v>
       </c>
       <c r="E82">
-        <v>5256.020000000001</v>
+        <v>5410.654000000001</v>
       </c>
       <c r="F82">
-        <v>12370.72</v>
+        <v>12525.354</v>
       </c>
       <c r="G82">
         <v>2010.2</v>
@@ -8011,28 +8011,28 @@
         <v>1971.45</v>
       </c>
       <c r="M82">
-        <v>862.0054500887678</v>
+        <v>872.7805182148774</v>
       </c>
       <c r="N82">
-        <v>1109.444549911232</v>
+        <v>1098.669481785123</v>
       </c>
       <c r="O82">
-        <v>299.5500284760327</v>
+        <v>296.6407600819831</v>
       </c>
       <c r="P82">
-        <v>809.8945214351994</v>
+        <v>802.0287217031395</v>
       </c>
       <c r="Q82">
-        <v>1633.194521435199</v>
+        <v>1625.32872170314</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2179254259581217</v>
+        <v>0.2263606811238997</v>
       </c>
       <c r="T82">
-        <v>3.152537624375789</v>
+        <v>3.307032285076267</v>
       </c>
       <c r="U82">
         <v>0.06968110587651873</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.287050505071614</v>
+        <v>2.258815313650977</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08421096731832646</v>
+        <v>0.08581916361314165</v>
       </c>
       <c r="C83">
-        <v>4558.133766208231</v>
+        <v>3797.769827156257</v>
       </c>
       <c r="D83">
-        <v>15073.28776620823</v>
+        <v>14467.55782715626</v>
       </c>
       <c r="E83">
-        <v>5410.654000000001</v>
+        <v>5565.288000000003</v>
       </c>
       <c r="F83">
-        <v>12525.354</v>
+        <v>12679.988</v>
       </c>
       <c r="G83">
         <v>2010.2</v>
@@ -8093,45 +8093,45 @@
         <v>1971.45</v>
       </c>
       <c r="M83">
-        <v>872.7805182148774</v>
+        <v>919.0595527409871</v>
       </c>
       <c r="N83">
-        <v>1098.669481785123</v>
+        <v>1052.390447259013</v>
       </c>
       <c r="O83">
-        <v>296.6407600819831</v>
+        <v>284.1454207599335</v>
       </c>
       <c r="P83">
-        <v>802.0287217031395</v>
+        <v>768.2450264990792</v>
       </c>
       <c r="Q83">
-        <v>1625.32872170314</v>
+        <v>1591.54502649908</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2263606811238997</v>
+        <v>0.2357331868636531</v>
       </c>
       <c r="T83">
-        <v>3.307032285076267</v>
+        <v>3.47869301918791</v>
       </c>
       <c r="U83">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.05086720728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.258815313650977</v>
+        <v>2.145073182820832</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08581916361314165</v>
+        <v>0.08577171990795684</v>
       </c>
       <c r="C84">
-        <v>3797.769827156257</v>
+        <v>3660.307831510243</v>
       </c>
       <c r="D84">
-        <v>14467.55782715626</v>
+        <v>14484.72983151025</v>
       </c>
       <c r="E84">
-        <v>5565.288000000003</v>
+        <v>5719.922000000003</v>
       </c>
       <c r="F84">
-        <v>12679.988</v>
+        <v>12834.622</v>
       </c>
       <c r="G84">
         <v>2010.2</v>
@@ -8175,28 +8175,28 @@
         <v>1971.45</v>
       </c>
       <c r="M84">
-        <v>919.0595527409871</v>
+        <v>930.2675960670967</v>
       </c>
       <c r="N84">
-        <v>1052.390447259013</v>
+        <v>1041.182403932903</v>
       </c>
       <c r="O84">
-        <v>284.1454207599335</v>
+        <v>281.1192490618839</v>
       </c>
       <c r="P84">
-        <v>768.2450264990792</v>
+        <v>760.0631548710192</v>
       </c>
       <c r="Q84">
-        <v>1591.54502649908</v>
+        <v>1583.363154871019</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2357331868636531</v>
+        <v>0.2462083403374951</v>
       </c>
       <c r="T84">
-        <v>3.47869301918791</v>
+        <v>3.670549133783276</v>
       </c>
       <c r="U84">
         <v>0.07248110587651872</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.145073182820832</v>
+        <v>2.119228927606123</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08577171990795684</v>
+        <v>0.08572427620277204</v>
       </c>
       <c r="C85">
-        <v>3660.307831510243</v>
+        <v>3522.886648301648</v>
       </c>
       <c r="D85">
-        <v>14484.72983151025</v>
+        <v>14501.94264830165</v>
       </c>
       <c r="E85">
-        <v>5719.922000000003</v>
+        <v>5874.556000000003</v>
       </c>
       <c r="F85">
-        <v>12834.622</v>
+        <v>12989.256</v>
       </c>
       <c r="G85">
         <v>2010.2</v>
@@ -8257,28 +8257,28 @@
         <v>1971.45</v>
       </c>
       <c r="M85">
-        <v>930.2675960670967</v>
+        <v>941.4756393932063</v>
       </c>
       <c r="N85">
-        <v>1041.182403932903</v>
+        <v>1029.974360606794</v>
       </c>
       <c r="O85">
-        <v>281.1192490618839</v>
+        <v>278.0930773638343</v>
       </c>
       <c r="P85">
-        <v>760.0631548710192</v>
+        <v>751.8812832429594</v>
       </c>
       <c r="Q85">
-        <v>1583.363154871019</v>
+        <v>1575.18128324296</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2462083403374951</v>
+        <v>0.2579928879955673</v>
       </c>
       <c r="T85">
-        <v>3.670549133783276</v>
+        <v>3.886387262703063</v>
       </c>
       <c r="U85">
         <v>0.07248110587651872</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.119228927606123</v>
+        <v>2.094000011801289</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08572427620277202</v>
+        <v>0.0856768324975872</v>
       </c>
       <c r="C86">
-        <v>3522.886648301654</v>
+        <v>3385.506423201025</v>
       </c>
       <c r="D86">
-        <v>14501.94264830165</v>
+        <v>14519.19642320103</v>
       </c>
       <c r="E86">
-        <v>5874.556000000001</v>
+        <v>6029.190000000001</v>
       </c>
       <c r="F86">
-        <v>12989.256</v>
+        <v>13143.89</v>
       </c>
       <c r="G86">
         <v>2010.2</v>
@@ -8339,28 +8339,28 @@
         <v>1971.45</v>
       </c>
       <c r="M86">
-        <v>941.4756393932062</v>
+        <v>952.6836827193158</v>
       </c>
       <c r="N86">
-        <v>1029.974360606794</v>
+        <v>1018.766317280684</v>
       </c>
       <c r="O86">
-        <v>278.0930773638343</v>
+        <v>275.0669056657847</v>
       </c>
       <c r="P86">
-        <v>751.8812832429594</v>
+        <v>743.6994116148993</v>
       </c>
       <c r="Q86">
-        <v>1575.18128324296</v>
+        <v>1566.9994116149</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2579928879955671</v>
+        <v>0.2713487086747156</v>
       </c>
       <c r="T86">
-        <v>3.88638726270306</v>
+        <v>4.13100380881215</v>
       </c>
       <c r="U86">
         <v>0.07248110587651872</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.094000011801289</v>
+        <v>2.069364717544803</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0856768324975872</v>
+        <v>0.08562938879240239</v>
       </c>
       <c r="C87">
-        <v>3385.506423201025</v>
+        <v>3248.167302572961</v>
       </c>
       <c r="D87">
-        <v>14519.19642320103</v>
+        <v>14536.49130257296</v>
       </c>
       <c r="E87">
-        <v>6029.190000000001</v>
+        <v>6183.824000000001</v>
       </c>
       <c r="F87">
-        <v>13143.89</v>
+        <v>13298.524</v>
       </c>
       <c r="G87">
         <v>2010.2</v>
@@ -8421,28 +8421,28 @@
         <v>1971.45</v>
       </c>
       <c r="M87">
-        <v>952.6836827193158</v>
+        <v>963.8917260454253</v>
       </c>
       <c r="N87">
-        <v>1018.766317280684</v>
+        <v>1007.558273954574</v>
       </c>
       <c r="O87">
-        <v>275.0669056657847</v>
+        <v>272.0407339677352</v>
       </c>
       <c r="P87">
-        <v>743.6994116148993</v>
+        <v>735.5175399868393</v>
       </c>
       <c r="Q87">
-        <v>1566.9994116149</v>
+        <v>1558.81753998684</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2713487086747156</v>
+        <v>0.2866125037365996</v>
       </c>
       <c r="T87">
-        <v>4.13100380881215</v>
+        <v>4.410565575793969</v>
       </c>
       <c r="U87">
         <v>0.07248110587651872</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.069364717544803</v>
+        <v>2.045302337108236</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08562938879240239</v>
+        <v>0.08558194508721759</v>
       </c>
       <c r="C88">
-        <v>3248.167302572961</v>
+        <v>3110.869433480306</v>
       </c>
       <c r="D88">
-        <v>14536.49130257296</v>
+        <v>14553.82743348031</v>
       </c>
       <c r="E88">
-        <v>6183.824000000001</v>
+        <v>6338.458000000001</v>
       </c>
       <c r="F88">
-        <v>13298.524</v>
+        <v>13453.158</v>
       </c>
       <c r="G88">
         <v>2010.2</v>
@@ -8503,28 +8503,28 @@
         <v>1971.45</v>
       </c>
       <c r="M88">
-        <v>963.8917260454253</v>
+        <v>975.099769371535</v>
       </c>
       <c r="N88">
-        <v>1007.558273954574</v>
+        <v>996.3502306284648</v>
       </c>
       <c r="O88">
-        <v>272.0407339677352</v>
+        <v>269.0145622696855</v>
       </c>
       <c r="P88">
-        <v>735.5175399868393</v>
+        <v>727.3356683587792</v>
       </c>
       <c r="Q88">
-        <v>1558.81753998684</v>
+        <v>1550.635668358779</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2866125037365996</v>
+        <v>0.3042245749618503</v>
       </c>
       <c r="T88">
-        <v>4.410565575793969</v>
+        <v>4.733136845388374</v>
       </c>
       <c r="U88">
         <v>0.07248110587651872</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.045302337108236</v>
+        <v>2.021793114842624</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08558194508721759</v>
+        <v>0.09054522138203278</v>
       </c>
       <c r="C89">
-        <v>3110.869433480306</v>
+        <v>1341.880548906436</v>
       </c>
       <c r="D89">
-        <v>14553.82743348031</v>
+        <v>12939.47254890644</v>
       </c>
       <c r="E89">
-        <v>6338.458000000001</v>
+        <v>6493.092000000001</v>
       </c>
       <c r="F89">
-        <v>13453.158</v>
+        <v>13607.792</v>
       </c>
       <c r="G89">
         <v>2010.2</v>
@@ -8585,45 +8585,45 @@
         <v>1971.45</v>
       </c>
       <c r="M89">
-        <v>975.099769371535</v>
+        <v>1092.448590297645</v>
       </c>
       <c r="N89">
-        <v>996.3502306284648</v>
+        <v>879.001409702355</v>
       </c>
       <c r="O89">
-        <v>269.0145622696855</v>
+        <v>237.3303806196359</v>
       </c>
       <c r="P89">
-        <v>727.3356683587792</v>
+        <v>641.6710290827191</v>
       </c>
       <c r="Q89">
-        <v>1550.635668358779</v>
+        <v>1464.971029082719</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3042245749618503</v>
+        <v>0.3247719913913095</v>
       </c>
       <c r="T89">
-        <v>4.733136845388374</v>
+        <v>5.109469993248514</v>
       </c>
       <c r="U89">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V89">
         <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.05291120728985867</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.021793114842624</v>
+        <v>1.804615812138918</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09054522138203278</v>
+        <v>0.09055471767684797</v>
       </c>
       <c r="C90">
-        <v>1341.880548906436</v>
+        <v>1184.50098257386</v>
       </c>
       <c r="D90">
-        <v>12939.47254890644</v>
+        <v>12936.72698257386</v>
       </c>
       <c r="E90">
-        <v>6493.092000000001</v>
+        <v>6647.726000000001</v>
       </c>
       <c r="F90">
-        <v>13607.792</v>
+        <v>13762.426</v>
       </c>
       <c r="G90">
         <v>2010.2</v>
@@ -8667,28 +8667,28 @@
         <v>1971.45</v>
       </c>
       <c r="M90">
-        <v>1092.448590297645</v>
+        <v>1104.862778823754</v>
       </c>
       <c r="N90">
-        <v>879.001409702355</v>
+        <v>866.5872211762455</v>
       </c>
       <c r="O90">
-        <v>237.3303806196359</v>
+        <v>233.9785497175863</v>
       </c>
       <c r="P90">
-        <v>641.6710290827191</v>
+        <v>632.6086714586593</v>
       </c>
       <c r="Q90">
-        <v>1464.971029082719</v>
+        <v>1455.908671458659</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3247719913913095</v>
+        <v>0.349055301717034</v>
       </c>
       <c r="T90">
-        <v>5.109469993248514</v>
+        <v>5.554227349810498</v>
       </c>
       <c r="U90">
         <v>0.08028110587651874</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.804615812138918</v>
+        <v>1.784339229980053</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09055471767684797</v>
+        <v>0.09056421397166314</v>
       </c>
       <c r="C91">
-        <v>1184.50098257386</v>
+        <v>1027.122581131947</v>
       </c>
       <c r="D91">
-        <v>12936.72698257386</v>
+        <v>12933.98258113195</v>
       </c>
       <c r="E91">
-        <v>6647.726000000001</v>
+        <v>6802.360000000001</v>
       </c>
       <c r="F91">
-        <v>13762.426</v>
+        <v>13917.06</v>
       </c>
       <c r="G91">
         <v>2010.2</v>
@@ -8749,28 +8749,28 @@
         <v>1971.45</v>
       </c>
       <c r="M91">
-        <v>1104.862778823754</v>
+        <v>1117.276967349864</v>
       </c>
       <c r="N91">
-        <v>866.5872211762455</v>
+        <v>854.1730326501358</v>
       </c>
       <c r="O91">
-        <v>233.9785497175863</v>
+        <v>230.6267188155367</v>
       </c>
       <c r="P91">
-        <v>632.6086714586593</v>
+        <v>623.5463138345991</v>
       </c>
       <c r="Q91">
-        <v>1455.908671458659</v>
+        <v>1446.846313834599</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.349055301717034</v>
+        <v>0.3781952741079035</v>
       </c>
       <c r="T91">
-        <v>5.554227349810498</v>
+        <v>6.087936177684878</v>
       </c>
       <c r="U91">
         <v>0.08028110587651874</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.784339229980053</v>
+        <v>1.76451323853583</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09056421397166314</v>
+        <v>0.09316448026647833</v>
       </c>
       <c r="C92">
-        <v>1027.122581131947</v>
+        <v>162.4248630413531</v>
       </c>
       <c r="D92">
-        <v>12933.98258113195</v>
+        <v>12223.91886304135</v>
       </c>
       <c r="E92">
-        <v>6802.360000000001</v>
+        <v>6956.994000000002</v>
       </c>
       <c r="F92">
-        <v>13917.06</v>
+        <v>14071.694</v>
       </c>
       <c r="G92">
         <v>2010.2</v>
@@ -8831,45 +8831,45 @@
         <v>1971.45</v>
       </c>
       <c r="M92">
-        <v>1117.276967349864</v>
+        <v>1184.570762475973</v>
       </c>
       <c r="N92">
-        <v>854.1730326501358</v>
+        <v>786.8792375240264</v>
       </c>
       <c r="O92">
-        <v>230.6267188155367</v>
+        <v>212.4573941314871</v>
       </c>
       <c r="P92">
-        <v>623.5463138345991</v>
+        <v>574.4218433925392</v>
       </c>
       <c r="Q92">
-        <v>1446.846313834599</v>
+        <v>1397.72184339254</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3781952741079035</v>
+        <v>0.4138107959189661</v>
       </c>
       <c r="T92">
-        <v>6.087936177684878</v>
+        <v>6.740246967309122</v>
       </c>
       <c r="U92">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V92">
         <v>0.27</v>
       </c>
       <c r="W92">
-        <v>0.05860520728985868</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.76451323853583</v>
+        <v>1.664273728890035</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09316448026647833</v>
+        <v>0.09320244656129351</v>
       </c>
       <c r="C93">
-        <v>162.4248630413531</v>
+        <v>-1.99970561106602</v>
       </c>
       <c r="D93">
-        <v>12223.91886304135</v>
+        <v>12214.12829438893</v>
       </c>
       <c r="E93">
-        <v>6956.994000000002</v>
+        <v>7111.628000000002</v>
       </c>
       <c r="F93">
-        <v>14071.694</v>
+        <v>14226.328</v>
       </c>
       <c r="G93">
         <v>2010.2</v>
@@ -8913,28 +8913,28 @@
         <v>1971.45</v>
       </c>
       <c r="M93">
-        <v>1184.570762475973</v>
+        <v>1197.588023602083</v>
       </c>
       <c r="N93">
-        <v>786.8792375240264</v>
+        <v>773.8619763979168</v>
       </c>
       <c r="O93">
-        <v>212.4573941314871</v>
+        <v>208.9427336274375</v>
       </c>
       <c r="P93">
-        <v>574.4218433925392</v>
+        <v>564.9192427704793</v>
       </c>
       <c r="Q93">
-        <v>1397.72184339254</v>
+        <v>1388.219242770479</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4138107959189661</v>
+        <v>0.4583301981827945</v>
       </c>
       <c r="T93">
-        <v>6.740246967309122</v>
+        <v>7.555635454339425</v>
       </c>
       <c r="U93">
         <v>0.08418110587651872</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.664273728890035</v>
+        <v>1.646183797054273</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09320244656129351</v>
+        <v>0.09324041285610871</v>
       </c>
       <c r="C94">
-        <v>-1.99970561106602</v>
+        <v>-166.4086035897562</v>
       </c>
       <c r="D94">
-        <v>12214.12829438893</v>
+        <v>12204.35339641024</v>
       </c>
       <c r="E94">
-        <v>7111.628000000002</v>
+        <v>7266.262000000002</v>
       </c>
       <c r="F94">
-        <v>14226.328</v>
+        <v>14380.962</v>
       </c>
       <c r="G94">
         <v>2010.2</v>
@@ -8995,28 +8995,28 @@
         <v>1971.45</v>
       </c>
       <c r="M94">
-        <v>1197.588023602083</v>
+        <v>1210.605284728193</v>
       </c>
       <c r="N94">
-        <v>773.8619763979168</v>
+        <v>760.8447152718072</v>
       </c>
       <c r="O94">
-        <v>208.9427336274375</v>
+        <v>205.428073123388</v>
       </c>
       <c r="P94">
-        <v>564.9192427704793</v>
+        <v>555.4166421484192</v>
       </c>
       <c r="Q94">
-        <v>1388.219242770479</v>
+        <v>1378.716642148419</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4583301981827945</v>
+        <v>0.5155694296648594</v>
       </c>
       <c r="T94">
-        <v>7.555635454339425</v>
+        <v>8.603992080521245</v>
       </c>
       <c r="U94">
         <v>0.08418110587651872</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.646183797054273</v>
+        <v>1.628482896010679</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09324041285610871</v>
+        <v>0.09327837915092388</v>
       </c>
       <c r="C95">
-        <v>-166.4086035897562</v>
+        <v>-330.8018684880753</v>
       </c>
       <c r="D95">
-        <v>12204.35339641024</v>
+        <v>12194.59413151193</v>
       </c>
       <c r="E95">
-        <v>7266.262000000002</v>
+        <v>7420.896000000002</v>
       </c>
       <c r="F95">
-        <v>14380.962</v>
+        <v>14535.596</v>
       </c>
       <c r="G95">
         <v>2010.2</v>
@@ -9077,28 +9077,28 @@
         <v>1971.45</v>
       </c>
       <c r="M95">
-        <v>1210.605284728193</v>
+        <v>1223.622545854302</v>
       </c>
       <c r="N95">
-        <v>760.8447152718072</v>
+        <v>747.8274541456976</v>
       </c>
       <c r="O95">
-        <v>205.428073123388</v>
+        <v>201.9134126193384</v>
       </c>
       <c r="P95">
-        <v>555.4166421484192</v>
+        <v>545.9140415263593</v>
       </c>
       <c r="Q95">
-        <v>1378.716642148419</v>
+        <v>1369.214041526359</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5155694296648594</v>
+        <v>0.5918884049742795</v>
       </c>
       <c r="T95">
-        <v>8.603992080521245</v>
+        <v>10.00180091543034</v>
       </c>
       <c r="U95">
         <v>0.08418110587651872</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.628482896010679</v>
+        <v>1.611158609882906</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09327837915092388</v>
+        <v>0.09331634544573908</v>
       </c>
       <c r="C96">
-        <v>-330.8018684880753</v>
+        <v>-495.1795377792569</v>
       </c>
       <c r="D96">
-        <v>12194.59413151193</v>
+        <v>12184.85046222075</v>
       </c>
       <c r="E96">
-        <v>7420.896000000002</v>
+        <v>7575.530000000003</v>
       </c>
       <c r="F96">
-        <v>14535.596</v>
+        <v>14690.23</v>
       </c>
       <c r="G96">
         <v>2010.2</v>
@@ -9159,28 +9159,28 @@
         <v>1971.45</v>
       </c>
       <c r="M96">
-        <v>1223.622545854302</v>
+        <v>1236.639806980412</v>
       </c>
       <c r="N96">
-        <v>747.8274541456976</v>
+        <v>734.8101930195878</v>
       </c>
       <c r="O96">
-        <v>201.9134126193384</v>
+        <v>198.3987521152887</v>
       </c>
       <c r="P96">
-        <v>545.9140415263593</v>
+        <v>536.4114409042991</v>
       </c>
       <c r="Q96">
-        <v>1369.214041526359</v>
+        <v>1359.711440904299</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5918884049742795</v>
+        <v>0.6987349704074677</v>
       </c>
       <c r="T96">
-        <v>10.00180091543034</v>
+        <v>11.95873328430307</v>
       </c>
       <c r="U96">
         <v>0.08418110587651872</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.611158609882906</v>
+        <v>1.594199045568349</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09331634544573908</v>
+        <v>0.09335431174055425</v>
       </c>
       <c r="C97">
-        <v>-495.1795377792569</v>
+        <v>-659.5416488168303</v>
       </c>
       <c r="D97">
-        <v>12184.85046222075</v>
+        <v>12175.12235118317</v>
       </c>
       <c r="E97">
-        <v>7575.530000000003</v>
+        <v>7730.164000000003</v>
       </c>
       <c r="F97">
-        <v>14690.23</v>
+        <v>14844.864</v>
       </c>
       <c r="G97">
         <v>2010.2</v>
@@ -9241,28 +9241,28 @@
         <v>1971.45</v>
       </c>
       <c r="M97">
-        <v>1236.639806980412</v>
+        <v>1249.657068106522</v>
       </c>
       <c r="N97">
-        <v>734.8101930195878</v>
+        <v>721.7929318934782</v>
       </c>
       <c r="O97">
-        <v>198.3987521152887</v>
+        <v>194.8840916112391</v>
       </c>
       <c r="P97">
-        <v>536.4114409042991</v>
+        <v>526.9088402822391</v>
       </c>
       <c r="Q97">
-        <v>1359.711440904299</v>
+        <v>1350.208840282239</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6987349704074677</v>
+        <v>0.8590048185572499</v>
       </c>
       <c r="T97">
-        <v>11.95873328430307</v>
+        <v>14.89413183761217</v>
       </c>
       <c r="U97">
         <v>0.08418110587651872</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.594199045568349</v>
+        <v>1.577592805510345</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09335431174055425</v>
+        <v>0.09339227803536945</v>
       </c>
       <c r="C98">
-        <v>-659.5416488168285</v>
+        <v>-823.8882388351631</v>
       </c>
       <c r="D98">
-        <v>12175.12235118317</v>
+        <v>12165.40976116484</v>
       </c>
       <c r="E98">
-        <v>7730.164000000002</v>
+        <v>7884.798000000002</v>
       </c>
       <c r="F98">
-        <v>14844.864</v>
+        <v>14999.498</v>
       </c>
       <c r="G98">
         <v>2010.2</v>
@@ -9323,28 +9323,28 @@
         <v>1971.45</v>
       </c>
       <c r="M98">
-        <v>1249.657068106521</v>
+        <v>1262.674329232631</v>
       </c>
       <c r="N98">
-        <v>721.7929318934785</v>
+        <v>708.7756707673689</v>
       </c>
       <c r="O98">
-        <v>194.8840916112392</v>
+        <v>191.3694311071896</v>
       </c>
       <c r="P98">
-        <v>526.9088402822392</v>
+        <v>517.4062396601793</v>
       </c>
       <c r="Q98">
-        <v>1350.208840282239</v>
+        <v>1340.70623966018</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8590048185572479</v>
+        <v>1.126121232140217</v>
       </c>
       <c r="T98">
-        <v>14.89413183761213</v>
+        <v>19.78646275979394</v>
       </c>
       <c r="U98">
         <v>0.08418110587651872</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.577592805510345</v>
+        <v>1.561328962154569</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09339227803536945</v>
+        <v>0.09343024433018464</v>
       </c>
       <c r="C99">
-        <v>-823.8882388351631</v>
+        <v>-988.2193449498845</v>
       </c>
       <c r="D99">
-        <v>12165.40976116484</v>
+        <v>12155.71265505012</v>
       </c>
       <c r="E99">
-        <v>7884.798000000002</v>
+        <v>8039.432000000002</v>
       </c>
       <c r="F99">
-        <v>14999.498</v>
+        <v>15154.132</v>
       </c>
       <c r="G99">
         <v>2010.2</v>
@@ -9405,28 +9405,28 @@
         <v>1971.45</v>
       </c>
       <c r="M99">
-        <v>1262.674329232631</v>
+        <v>1275.691590358741</v>
       </c>
       <c r="N99">
-        <v>708.7756707673689</v>
+        <v>695.7584096412593</v>
       </c>
       <c r="O99">
-        <v>191.3694311071896</v>
+        <v>187.85477060314</v>
       </c>
       <c r="P99">
-        <v>517.4062396601793</v>
+        <v>507.9036390381193</v>
       </c>
       <c r="Q99">
-        <v>1340.70623966018</v>
+        <v>1331.203639038119</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.126121232140217</v>
+        <v>1.660354059306156</v>
       </c>
       <c r="T99">
-        <v>19.78646275979394</v>
+        <v>29.57112460415756</v>
       </c>
       <c r="U99">
         <v>0.08418110587651872</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.561328962154569</v>
+        <v>1.545397033969318</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09343024433018464</v>
+        <v>0.09346821062499983</v>
       </c>
       <c r="C100">
-        <v>-988.2193449498845</v>
+        <v>-1152.535004158386</v>
       </c>
       <c r="D100">
-        <v>12155.71265505012</v>
+        <v>12146.03099584161</v>
       </c>
       <c r="E100">
-        <v>8039.432000000002</v>
+        <v>8194.066000000003</v>
       </c>
       <c r="F100">
-        <v>15154.132</v>
+        <v>15308.766</v>
       </c>
       <c r="G100">
         <v>2010.2</v>
@@ -9487,28 +9487,28 @@
         <v>1971.45</v>
       </c>
       <c r="M100">
-        <v>1275.691590358741</v>
+        <v>1288.70885148485</v>
       </c>
       <c r="N100">
-        <v>695.7584096412593</v>
+        <v>682.7411485151497</v>
       </c>
       <c r="O100">
-        <v>187.85477060314</v>
+        <v>184.3401100990904</v>
       </c>
       <c r="P100">
-        <v>507.9036390381193</v>
+        <v>498.4010384160592</v>
       </c>
       <c r="Q100">
-        <v>1331.203639038119</v>
+        <v>1321.701038416059</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.660354059306156</v>
+        <v>3.263052540803971</v>
       </c>
       <c r="T100">
-        <v>29.57112460415756</v>
+        <v>58.92511013724842</v>
       </c>
       <c r="U100">
         <v>0.08418110587651872</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.545397033969318</v>
+        <v>1.529786962919123</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09346821062499983</v>
-      </c>
-      <c r="C101">
-        <v>-1152.535004158386</v>
-      </c>
-      <c r="D101">
-        <v>12146.03099584161</v>
-      </c>
-      <c r="E101">
-        <v>8194.066000000003</v>
-      </c>
-      <c r="F101">
-        <v>15308.766</v>
-      </c>
-      <c r="G101">
-        <v>2010.2</v>
-      </c>
-      <c r="H101">
-        <v>8348.700000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2794.75</v>
-      </c>
-      <c r="K101">
-        <v>823.3000000000002</v>
-      </c>
-      <c r="L101">
-        <v>1971.45</v>
-      </c>
-      <c r="M101">
-        <v>1288.70885148485</v>
-      </c>
-      <c r="N101">
-        <v>682.7411485151497</v>
-      </c>
-      <c r="O101">
-        <v>184.3401100990904</v>
-      </c>
-      <c r="P101">
-        <v>498.4010384160592</v>
-      </c>
-      <c r="Q101">
-        <v>1321.701038416059</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.263052540803971</v>
-      </c>
-      <c r="T101">
-        <v>58.92511013724842</v>
-      </c>
-      <c r="U101">
-        <v>0.08418110587651872</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.06145220728985867</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.529786962919123</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
